--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -1749,19 +1749,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>47.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="49">
@@ -1777,19 +1777,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>46.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="50">
@@ -7097,19 +7097,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E239" t="n">
         <v>4.4</v>
       </c>
       <c r="F239" t="n">
-        <v>48.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="240">
@@ -7125,19 +7125,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E240" t="n">
         <v>4.4</v>
       </c>
       <c r="F240" t="n">
-        <v>51.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="241">
@@ -7209,19 +7209,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E243" t="n">
         <v>4.2</v>
       </c>
       <c r="F243" t="n">
-        <v>47.7</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="244">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E244" t="n">
         <v>4.2</v>
       </c>
       <c r="F244" t="n">
-        <v>53.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="245">
@@ -8413,19 +8413,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E286" t="n">
         <v>4.7</v>
       </c>
       <c r="F286" t="n">
-        <v>51.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="287">
@@ -8441,19 +8441,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E287" t="n">
         <v>4.7</v>
       </c>
       <c r="F287" t="n">
-        <v>48.2</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="288">
@@ -8497,19 +8497,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E289" t="n">
         <v>4.5</v>
       </c>
       <c r="F289" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="290">
@@ -8525,19 +8525,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E290" t="n">
         <v>4.5</v>
       </c>
       <c r="F290" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="291">
@@ -10541,19 +10541,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E362" t="n">
         <v>13.7</v>
       </c>
       <c r="F362" t="n">
-        <v>52.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="363">
@@ -10569,19 +10569,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E363" t="n">
         <v>13.7</v>
       </c>
       <c r="F363" t="n">
-        <v>46.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="364">
@@ -10597,19 +10597,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E364" t="n">
         <v>13.6</v>
       </c>
       <c r="F364" t="n">
-        <v>46.2</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="365">
@@ -10625,19 +10625,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E365" t="n">
         <v>13.6</v>
       </c>
       <c r="F365" t="n">
-        <v>54.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="366">
@@ -11605,19 +11605,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E400" t="n">
         <v>0.7</v>
       </c>
       <c r="F400" t="n">
-        <v>41</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="401">
@@ -11633,19 +11633,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E401" t="n">
         <v>0.7</v>
       </c>
       <c r="F401" t="n">
-        <v>46.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="402">
@@ -13537,19 +13537,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E469" t="n">
         <v>11.1</v>
       </c>
       <c r="F469" t="n">
-        <v>46.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="470">
@@ -13565,19 +13565,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E470" t="n">
         <v>11.1</v>
       </c>
       <c r="F470" t="n">
-        <v>49.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="471">
@@ -13593,19 +13593,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E471" t="n">
         <v>11.1</v>
       </c>
       <c r="F471" t="n">
-        <v>53</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="472">
@@ -15637,19 +15637,19 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E544" t="n">
         <v>3.7</v>
       </c>
       <c r="F544" t="n">
-        <v>52.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="545">
@@ -15665,19 +15665,19 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E545" t="n">
         <v>3.7</v>
       </c>
       <c r="F545" t="n">
-        <v>49.1</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="546">
@@ -16617,19 +16617,19 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E579" t="n">
         <v>7.6</v>
       </c>
       <c r="F579" t="n">
-        <v>51.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="580">
@@ -16645,19 +16645,19 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E580" t="n">
         <v>7.6</v>
       </c>
       <c r="F580" t="n">
-        <v>47.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="581">
@@ -16981,19 +16981,19 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E592" t="n">
         <v>4.1</v>
       </c>
       <c r="F592" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="593">
@@ -17009,19 +17009,19 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E593" t="n">
         <v>4.1</v>
       </c>
       <c r="F593" t="n">
-        <v>50.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="594">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -18085,7 +18085,7 @@
         <v>6.8</v>
       </c>
       <c r="F631" t="n">
-        <v>50.7</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="632">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -18113,7 +18113,7 @@
         <v>6.8</v>
       </c>
       <c r="F632" t="n">
-        <v>53.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="633">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -18477,7 +18477,7 @@
         <v>3.6</v>
       </c>
       <c r="F645" t="n">
-        <v>52.7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="646">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -18505,7 +18505,7 @@
         <v>3.6</v>
       </c>
       <c r="F646" t="n">
-        <v>46</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="647">
@@ -19277,19 +19277,19 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E674" t="n">
         <v>9</v>
       </c>
       <c r="F674" t="n">
-        <v>51.4</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="675">
@@ -19305,19 +19305,19 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E675" t="n">
         <v>9</v>
       </c>
       <c r="F675" t="n">
-        <v>52.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="676">
@@ -19585,19 +19585,19 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E685" t="n">
         <v>5.3</v>
       </c>
       <c r="F685" t="n">
-        <v>48.9</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="686">
@@ -19613,19 +19613,19 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E686" t="n">
         <v>5.3</v>
       </c>
       <c r="F686" t="n">
-        <v>44.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="687">
@@ -19641,19 +19641,19 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E687" t="n">
         <v>5.3</v>
       </c>
       <c r="F687" t="n">
-        <v>52.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="688">
@@ -19669,19 +19669,19 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E688" t="n">
         <v>5.1</v>
       </c>
       <c r="F688" t="n">
-        <v>50.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="689">
@@ -19697,19 +19697,19 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E689" t="n">
         <v>5.1</v>
       </c>
       <c r="F689" t="n">
-        <v>48.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="690">
@@ -19921,19 +19921,19 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E697" t="n">
         <v>3.1</v>
       </c>
       <c r="F697" t="n">
-        <v>50.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="698">
@@ -19949,19 +19949,19 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E698" t="n">
         <v>3.1</v>
       </c>
       <c r="F698" t="n">
-        <v>53.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="699">
@@ -20677,19 +20677,19 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E724" t="n">
         <v>8.4</v>
       </c>
       <c r="F724" t="n">
-        <v>51.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="725">
@@ -20705,19 +20705,19 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E725" t="n">
         <v>8.4</v>
       </c>
       <c r="F725" t="n">
-        <v>47.1</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="726">
@@ -20733,19 +20733,19 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E726" t="n">
         <v>8</v>
       </c>
       <c r="F726" t="n">
-        <v>50.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="727">
@@ -20761,19 +20761,19 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E727" t="n">
         <v>8</v>
       </c>
       <c r="F727" t="n">
-        <v>49.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="728">
@@ -21237,19 +21237,19 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E744" t="n">
         <v>3.6</v>
       </c>
       <c r="F744" t="n">
-        <v>45.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="745">
@@ -21265,19 +21265,19 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E745" t="n">
         <v>3.6</v>
       </c>
       <c r="F745" t="n">
-        <v>48</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="746">
@@ -22077,19 +22077,19 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E774" t="n">
         <v>7.6</v>
       </c>
       <c r="F774" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="775">
@@ -22105,19 +22105,19 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E775" t="n">
         <v>7.6</v>
       </c>
       <c r="F775" t="n">
-        <v>49.6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="776">
@@ -22133,19 +22133,19 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E776" t="n">
         <v>7.6</v>
       </c>
       <c r="F776" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="777">
@@ -22385,19 +22385,19 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E785" t="n">
         <v>5</v>
       </c>
       <c r="F785" t="n">
-        <v>51.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="786">
@@ -22413,19 +22413,19 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E786" t="n">
         <v>5</v>
       </c>
       <c r="F786" t="n">
-        <v>47.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="787">
@@ -25493,19 +25493,19 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E896" t="n">
         <v>3</v>
       </c>
       <c r="F896" t="n">
-        <v>51.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="897">
@@ -25521,19 +25521,19 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E897" t="n">
         <v>3</v>
       </c>
       <c r="F897" t="n">
-        <v>51</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="898">
@@ -26837,19 +26837,19 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E944" t="n">
         <v>3.5</v>
       </c>
       <c r="F944" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="945">
@@ -26865,19 +26865,19 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E945" t="n">
         <v>3.5</v>
       </c>
       <c r="F945" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="946">
@@ -28293,7 +28293,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -29189,19 +29189,19 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1028" t="n">
         <v>7</v>
       </c>
       <c r="F1028" t="n">
-        <v>45.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1029">
@@ -29217,19 +29217,19 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1029" t="n">
         <v>7</v>
       </c>
       <c r="F1029" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1030">
@@ -32409,19 +32409,19 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1143" t="n">
         <v>3.7</v>
       </c>
       <c r="F1143" t="n">
-        <v>45.5</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1144">
@@ -32437,19 +32437,19 @@
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1144" t="n">
         <v>3.7</v>
       </c>
       <c r="F1144" t="n">
-        <v>44.9</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1145">
@@ -34789,19 +34789,19 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1228" t="n">
         <v>1.1</v>
       </c>
       <c r="F1228" t="n">
-        <v>43.7</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1229">
@@ -34817,19 +34817,19 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1229" t="n">
         <v>1.1</v>
       </c>
       <c r="F1229" t="n">
-        <v>46.1</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1230">
@@ -36189,19 +36189,19 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1278" t="n">
         <v>1</v>
       </c>
       <c r="F1278" t="n">
-        <v>52.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1279">
@@ -36217,19 +36217,19 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1279" t="n">
         <v>1</v>
       </c>
       <c r="F1279" t="n">
-        <v>50.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1280">
@@ -38569,19 +38569,19 @@
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1363" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1363" t="n">
         <v>1.1</v>
       </c>
       <c r="F1363" t="n">
-        <v>47.3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1364">
@@ -38597,19 +38597,19 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1364" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1364" t="n">
         <v>1.1</v>
       </c>
       <c r="F1364" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1365">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="F2" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="F3" t="n">
         <v>47</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="F4" t="n">
         <v>53</v>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="F6" t="n">
         <v>48.5</v>
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="8">
@@ -685,19 +685,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="F10" t="n">
-        <v>50.5</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="11">
@@ -713,19 +713,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>53.1</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="12">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F12" t="n">
         <v>51.6</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="F13" t="n">
         <v>51.3</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="F14" t="n">
         <v>54.2</v>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="F15" t="n">
         <v>52.1</v>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F16" t="n">
         <v>54.4</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F20" t="n">
         <v>52.3</v>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F21" t="n">
         <v>45.1</v>
@@ -1117,7 +1117,7 @@
         <v>8.5</v>
       </c>
       <c r="F25" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="26">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>49.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="27">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="28">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F32" t="n">
         <v>52.1</v>
@@ -1385,19 +1385,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>5.6</v>
       </c>
       <c r="F35" t="n">
-        <v>52.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="36">
@@ -1413,19 +1413,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>5.5</v>
       </c>
       <c r="F36" t="n">
-        <v>47.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="37">
@@ -1481,7 +1481,7 @@
         <v>4.7</v>
       </c>
       <c r="F38" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="39">
@@ -1497,19 +1497,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F39" t="n">
-        <v>47.2</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="40">
@@ -1525,19 +1525,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F40" t="n">
-        <v>49.8</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="41">
@@ -1553,19 +1553,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>4.2</v>
       </c>
       <c r="F41" t="n">
-        <v>51.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="42">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F42" t="n">
-        <v>40.7</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="43">
@@ -1705,7 +1705,7 @@
         <v>3.4</v>
       </c>
       <c r="F46" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="47">
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F48" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="49">
@@ -5753,19 +5753,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E191" t="n">
         <v>4.2</v>
       </c>
       <c r="F191" t="n">
-        <v>44.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="192">
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>4.2</v>
       </c>
       <c r="F192" t="n">
-        <v>53.9</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="193">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="F202" t="n">
         <v>50</v>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="F203" t="n">
         <v>46.7</v>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="F204" t="n">
         <v>46.3</v>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="F205" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="206">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>16.3</v>
+        <v>16.8</v>
       </c>
       <c r="F206" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="207">
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="F208" t="n">
         <v>49.1</v>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="F209" t="n">
-        <v>51.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="210">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6297,7 +6297,7 @@
         <v>14.3</v>
       </c>
       <c r="F210" t="n">
-        <v>47</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="211">
@@ -6313,19 +6313,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>13.4</v>
       </c>
       <c r="F211" t="n">
-        <v>50.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="212">
@@ -6341,19 +6341,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="F212" t="n">
-        <v>52.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="213">
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="F214" t="n">
         <v>54.3</v>
@@ -6425,19 +6425,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E215" t="n">
         <v>12.2</v>
       </c>
       <c r="F215" t="n">
-        <v>52.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="216">
@@ -6453,19 +6453,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F216" t="n">
-        <v>55</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="217">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F217" t="n">
         <v>52.3</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F220" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="221">
@@ -6633,7 +6633,7 @@
         <v>8.4</v>
       </c>
       <c r="F222" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="223">
@@ -6745,7 +6745,7 @@
         <v>7.9</v>
       </c>
       <c r="F226" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="227">
@@ -6773,7 +6773,7 @@
         <v>7.6</v>
       </c>
       <c r="F227" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="228">
@@ -6801,7 +6801,7 @@
         <v>7.4</v>
       </c>
       <c r="F228" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="229">
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F230" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="231">
@@ -6882,7 +6882,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F231" t="n">
         <v>51.6</v>
@@ -6913,7 +6913,7 @@
         <v>5.7</v>
       </c>
       <c r="F232" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="233">
@@ -6969,7 +6969,7 @@
         <v>5.1</v>
       </c>
       <c r="F234" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="235">
@@ -7025,7 +7025,7 @@
         <v>4.5</v>
       </c>
       <c r="F236" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="237">
@@ -7053,7 +7053,7 @@
         <v>4.5</v>
       </c>
       <c r="F237" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="238">
@@ -7125,19 +7125,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E240" t="n">
         <v>4.4</v>
       </c>
       <c r="F240" t="n">
-        <v>51.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="241">
@@ -7153,19 +7153,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E241" t="n">
         <v>4.4</v>
       </c>
       <c r="F241" t="n">
-        <v>47.5</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="242">
@@ -7181,19 +7181,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F242" t="n">
-        <v>39.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="243">
@@ -7361,7 +7361,7 @@
         <v>3.1</v>
       </c>
       <c r="F248" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="249">
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F249" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="250">
@@ -7417,7 +7417,7 @@
         <v>2.5</v>
       </c>
       <c r="F250" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="251">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="F252" t="n">
         <v>50.5</v>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="F253" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="254">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="F254" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="255">
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="F255" t="n">
         <v>50.9</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F256" t="n">
         <v>52.5</v>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="F257" t="n">
         <v>50.7</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="F258" t="n">
         <v>48.2</v>
@@ -7669,7 +7669,7 @@
         <v>15.9</v>
       </c>
       <c r="F259" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="260">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="F260" t="n">
         <v>53.3</v>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="F261" t="n">
         <v>55.7</v>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="F262" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="263">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F263" t="n">
         <v>51.4</v>
@@ -7809,7 +7809,7 @@
         <v>12.7</v>
       </c>
       <c r="F264" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="265">
@@ -7825,19 +7825,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="F265" t="n">
-        <v>54.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="266">
@@ -7853,19 +7853,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F266" t="n">
-        <v>49.8</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="267">
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F267" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="268">
@@ -7921,7 +7921,7 @@
         <v>10.9</v>
       </c>
       <c r="F268" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="269">
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F269" t="n">
         <v>49.1</v>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F270" t="n">
         <v>46.3</v>
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F271" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="272">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F272" t="n">
         <v>48.8</v>
@@ -8061,7 +8061,7 @@
         <v>8.5</v>
       </c>
       <c r="F273" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="274">
@@ -8089,7 +8089,7 @@
         <v>8.4</v>
       </c>
       <c r="F274" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="275">
@@ -8145,7 +8145,7 @@
         <v>7.1</v>
       </c>
       <c r="F276" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="277">
@@ -8173,7 +8173,7 @@
         <v>6.5</v>
       </c>
       <c r="F277" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="278">
@@ -8229,7 +8229,7 @@
         <v>5.9</v>
       </c>
       <c r="F279" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="280">
@@ -8257,7 +8257,7 @@
         <v>5.3</v>
       </c>
       <c r="F280" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="281">
@@ -8285,7 +8285,7 @@
         <v>5.3</v>
       </c>
       <c r="F281" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="282">
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F282" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="283">
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F284" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="285">
@@ -8397,7 +8397,7 @@
         <v>4.7</v>
       </c>
       <c r="F285" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="286">
@@ -8453,7 +8453,7 @@
         <v>4.6</v>
       </c>
       <c r="F287" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="288">
@@ -8537,7 +8537,7 @@
         <v>4.4</v>
       </c>
       <c r="F290" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="291">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F292" t="n">
         <v>53.6</v>
@@ -8621,7 +8621,7 @@
         <v>3.9</v>
       </c>
       <c r="F293" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="294">
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F294" t="n">
         <v>52.3</v>
@@ -8677,7 +8677,7 @@
         <v>3.5</v>
       </c>
       <c r="F295" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="296">
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F297" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="298">
@@ -8761,7 +8761,7 @@
         <v>2.7</v>
       </c>
       <c r="F298" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="299">
@@ -8789,7 +8789,7 @@
         <v>2.5</v>
       </c>
       <c r="F299" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="300">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F300" t="n">
         <v>46.8</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F301" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="302">
@@ -9673,19 +9673,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E331" t="n">
         <v>5.2</v>
       </c>
       <c r="F331" t="n">
-        <v>54.3</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="332">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E332" t="n">
         <v>5.2</v>
       </c>
       <c r="F332" t="n">
-        <v>44.8</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="333">
@@ -12725,19 +12725,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E440" t="n">
         <v>4.4</v>
       </c>
       <c r="F440" t="n">
-        <v>52.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="441">
@@ -12753,19 +12753,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E441" t="n">
         <v>4.4</v>
       </c>
       <c r="F441" t="n">
-        <v>48</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="442">
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="F452" t="n">
         <v>49.4</v>
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="F453" t="n">
         <v>55</v>
@@ -13129,7 +13129,7 @@
         <v>25</v>
       </c>
       <c r="F454" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="455">
@@ -13157,7 +13157,7 @@
         <v>22.6</v>
       </c>
       <c r="F455" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="456">
@@ -13182,7 +13182,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F456" t="n">
         <v>49.2</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="F457" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="458">
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="F459" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="460">
@@ -13294,10 +13294,10 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="F460" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="461">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E463" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="F463" t="n">
         <v>44.6</v>
@@ -13409,7 +13409,7 @@
         <v>12.6</v>
       </c>
       <c r="F464" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="465">
@@ -13425,19 +13425,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E465" t="n">
         <v>12.2</v>
       </c>
       <c r="F465" t="n">
-        <v>54.1</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="466">
@@ -13453,19 +13453,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E466" t="n">
         <v>12.2</v>
       </c>
       <c r="F466" t="n">
-        <v>46.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="467">
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="F467" t="n">
         <v>54.7</v>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -13518,10 +13518,10 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F468" t="n">
-        <v>50.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="469">
@@ -13537,19 +13537,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E469" t="n">
         <v>11.2</v>
       </c>
       <c r="F469" t="n">
-        <v>49.4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="470">
@@ -13565,19 +13565,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E470" t="n">
         <v>11.2</v>
       </c>
       <c r="F470" t="n">
-        <v>46.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="471">
@@ -13605,7 +13605,7 @@
         <v>10.9</v>
       </c>
       <c r="F471" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="472">
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="F473" t="n">
         <v>52.9</v>
@@ -13689,7 +13689,7 @@
         <v>10.2</v>
       </c>
       <c r="F474" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="475">
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F475" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="476">
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="F476" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="477">
@@ -13798,7 +13798,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F478" t="n">
         <v>52.3</v>
@@ -13826,10 +13826,10 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F479" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="480">
@@ -13857,7 +13857,7 @@
         <v>6.5</v>
       </c>
       <c r="F480" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="481">
@@ -13885,7 +13885,7 @@
         <v>6.4</v>
       </c>
       <c r="F481" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="482">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -13969,7 +13969,7 @@
         <v>5.4</v>
       </c>
       <c r="F484" t="n">
-        <v>50.4</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="485">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -13997,7 +13997,7 @@
         <v>5.4</v>
       </c>
       <c r="F485" t="n">
-        <v>45.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="486">
@@ -14053,7 +14053,7 @@
         <v>4.8</v>
       </c>
       <c r="F487" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="488">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F488" t="n">
         <v>51.6</v>
@@ -14106,7 +14106,7 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F489" t="n">
         <v>57.3</v>
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F490" t="n">
         <v>46.2</v>
@@ -14165,7 +14165,7 @@
         <v>4</v>
       </c>
       <c r="F491" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="492">
@@ -14193,7 +14193,7 @@
         <v>3.9</v>
       </c>
       <c r="F492" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="493">
@@ -14209,19 +14209,19 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E493" t="n">
         <v>3.5</v>
       </c>
       <c r="F493" t="n">
-        <v>50.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="494">
@@ -14249,7 +14249,7 @@
         <v>3.5</v>
       </c>
       <c r="F494" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="495">
@@ -14293,19 +14293,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E496" t="n">
         <v>3.4</v>
       </c>
       <c r="F496" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="497">
@@ -14361,7 +14361,7 @@
         <v>3.1</v>
       </c>
       <c r="F498" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="499">
@@ -14414,10 +14414,10 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F500" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="501">
@@ -14445,7 +14445,7 @@
         <v>1.8</v>
       </c>
       <c r="F501" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="502">
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="F502" t="n">
         <v>47.9</v>
@@ -14498,7 +14498,7 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="F503" t="n">
         <v>55.1</v>
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="F504" t="n">
         <v>45.8</v>
@@ -14557,7 +14557,7 @@
         <v>20.6</v>
       </c>
       <c r="F505" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="506">
@@ -14585,7 +14585,7 @@
         <v>20.5</v>
       </c>
       <c r="F506" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="507">
@@ -14638,7 +14638,7 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="F508" t="n">
         <v>48.6</v>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="F509" t="n">
         <v>48</v>
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="F510" t="n">
         <v>50.5</v>
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="F513" t="n">
         <v>49</v>
@@ -14809,7 +14809,7 @@
         <v>12.9</v>
       </c>
       <c r="F514" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="515">
@@ -14825,19 +14825,19 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F515" t="n">
-        <v>48.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="516">
@@ -14853,19 +14853,19 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E516" t="n">
         <v>12.7</v>
       </c>
       <c r="F516" t="n">
-        <v>52.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="517">
@@ -14890,7 +14890,7 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F517" t="n">
         <v>44.7</v>
@@ -14937,19 +14937,19 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="F519" t="n">
-        <v>53.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="520">
@@ -14965,19 +14965,19 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E520" t="n">
         <v>10.8</v>
       </c>
       <c r="F520" t="n">
-        <v>50.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="521">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F521" t="n">
         <v>48.8</v>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F523" t="n">
         <v>53.4</v>
@@ -15089,7 +15089,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F524" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="525">
@@ -15114,10 +15114,10 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F525" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="526">
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F526" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="527">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F535" t="n">
         <v>56</v>
@@ -15478,10 +15478,10 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F538" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="539">
@@ -15506,7 +15506,7 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F539" t="n">
         <v>51.3</v>
@@ -15537,7 +15537,7 @@
         <v>4.5</v>
       </c>
       <c r="F540" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="541">
@@ -15565,7 +15565,7 @@
         <v>4.4</v>
       </c>
       <c r="F541" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="542">
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F543" t="n">
         <v>50.2</v>
@@ -15665,12 +15665,12 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E545" t="n">
@@ -15693,19 +15693,19 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F546" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="547">
@@ -15721,19 +15721,19 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E547" t="n">
         <v>3.6</v>
       </c>
       <c r="F547" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="548">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F548" t="n">
         <v>51.7</v>
@@ -15817,7 +15817,7 @@
         <v>1.8</v>
       </c>
       <c r="F550" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="551">
@@ -15845,7 +15845,7 @@
         <v>1.7</v>
       </c>
       <c r="F551" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="552">
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="F602" t="n">
         <v>53.5</v>
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="F603" t="n">
         <v>47.1</v>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F604" t="n">
         <v>44.7</v>
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="F606" t="n">
         <v>46.9</v>
@@ -17410,10 +17410,10 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="F607" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="608">
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="F608" t="n">
         <v>48.6</v>
@@ -17469,7 +17469,7 @@
         <v>18.6</v>
       </c>
       <c r="F609" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="610">
@@ -17522,7 +17522,7 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="F611" t="n">
         <v>50.7</v>
@@ -17550,7 +17550,7 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F612" t="n">
         <v>47.7</v>
@@ -17581,7 +17581,7 @@
         <v>13.4</v>
       </c>
       <c r="F613" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="614">
@@ -17665,7 +17665,7 @@
         <v>12.2</v>
       </c>
       <c r="F616" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="617">
@@ -17693,7 +17693,7 @@
         <v>12</v>
       </c>
       <c r="F617" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="618">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="F618" t="n">
         <v>54.4</v>
@@ -17774,7 +17774,7 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F620" t="n">
         <v>53.6</v>
@@ -17802,10 +17802,10 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F621" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="622">
@@ -17886,10 +17886,10 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F624" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="625">
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F628" t="n">
         <v>48.9</v>
@@ -18082,7 +18082,7 @@
         </is>
       </c>
       <c r="E631" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F631" t="n">
         <v>53.1</v>
@@ -18110,7 +18110,7 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F632" t="n">
         <v>50.7</v>
@@ -18138,10 +18138,10 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F633" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="634">
@@ -18169,7 +18169,7 @@
         <v>6.6</v>
       </c>
       <c r="F634" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="635">
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F636" t="n">
         <v>51.1</v>
@@ -18250,10 +18250,10 @@
         </is>
       </c>
       <c r="E637" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F637" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="638">
@@ -18309,7 +18309,7 @@
         <v>4.5</v>
       </c>
       <c r="F639" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="640">
@@ -18362,7 +18362,7 @@
         </is>
       </c>
       <c r="E641" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F641" t="n">
         <v>54.8</v>
@@ -18381,19 +18381,19 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E642" t="n">
         <v>3.8</v>
       </c>
       <c r="F642" t="n">
-        <v>48.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="643">
@@ -18409,19 +18409,19 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E643" t="n">
         <v>3.8</v>
       </c>
       <c r="F643" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="644">
@@ -18449,7 +18449,7 @@
         <v>3.7</v>
       </c>
       <c r="F644" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="645">
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F648" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="649">
@@ -18586,7 +18586,7 @@
         </is>
       </c>
       <c r="E649" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F649" t="n">
         <v>51.1</v>
@@ -18969,19 +18969,19 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E663" t="n">
         <v>13.3</v>
       </c>
       <c r="F663" t="n">
-        <v>51.5</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="664">
@@ -18997,19 +18997,19 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E664" t="n">
         <v>13.3</v>
       </c>
       <c r="F664" t="n">
-        <v>50.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="665">
@@ -20070,10 +20070,10 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="F702" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="703">
@@ -20098,10 +20098,10 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="F703" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="704">
@@ -20154,10 +20154,10 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="F705" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="706">
@@ -20213,7 +20213,7 @@
         <v>18.2</v>
       </c>
       <c r="F707" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="708">
@@ -20266,10 +20266,10 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="F709" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="710">
@@ -20297,7 +20297,7 @@
         <v>15</v>
       </c>
       <c r="F710" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="711">
@@ -20322,10 +20322,10 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="F711" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="712">
@@ -20353,7 +20353,7 @@
         <v>14.5</v>
       </c>
       <c r="F712" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="713">
@@ -20369,19 +20369,19 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="F713" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="714">
@@ -20397,19 +20397,19 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E714" t="n">
         <v>12.7</v>
       </c>
       <c r="F714" t="n">
-        <v>51.9</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="715">
@@ -20434,10 +20434,10 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F715" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="716">
@@ -20465,7 +20465,7 @@
         <v>11.3</v>
       </c>
       <c r="F716" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="717">
@@ -20490,7 +20490,7 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F717" t="n">
         <v>53.3</v>
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F719" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="720">
@@ -20593,19 +20593,19 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E721" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="F721" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="722">
@@ -20621,19 +20621,19 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F722" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="723">
@@ -20658,10 +20658,10 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F723" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="724">
@@ -20686,7 +20686,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="F724" t="n">
         <v>47.1</v>
@@ -20714,10 +20714,10 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F725" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="726">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F726" t="n">
         <v>50.7</v>
@@ -20761,19 +20761,19 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F727" t="n">
-        <v>49.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="728">
@@ -20789,19 +20789,19 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E728" t="n">
         <v>8</v>
       </c>
       <c r="F728" t="n">
-        <v>51.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="729">
@@ -20829,7 +20829,7 @@
         <v>7.8</v>
       </c>
       <c r="F729" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="730">
@@ -20885,7 +20885,7 @@
         <v>7.1</v>
       </c>
       <c r="F731" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="732">
@@ -20913,7 +20913,7 @@
         <v>7</v>
       </c>
       <c r="F732" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="733">
@@ -20941,7 +20941,7 @@
         <v>6.4</v>
       </c>
       <c r="F733" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="734">
@@ -20969,7 +20969,7 @@
         <v>6.3</v>
       </c>
       <c r="F734" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="735">
@@ -20997,7 +20997,7 @@
         <v>6</v>
       </c>
       <c r="F735" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="736">
@@ -21050,10 +21050,10 @@
         </is>
       </c>
       <c r="E737" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F737" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="738">
@@ -21081,7 +21081,7 @@
         <v>4.6</v>
       </c>
       <c r="F738" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="739">
@@ -21109,7 +21109,7 @@
         <v>4.5</v>
       </c>
       <c r="F739" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="740">
@@ -21137,7 +21137,7 @@
         <v>4.3</v>
       </c>
       <c r="F740" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="741">
@@ -21153,19 +21153,19 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F741" t="n">
-        <v>54</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="742">
@@ -21181,19 +21181,19 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E742" t="n">
         <v>3.9</v>
       </c>
       <c r="F742" t="n">
-        <v>51.3</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="743">
@@ -21221,7 +21221,7 @@
         <v>3.8</v>
       </c>
       <c r="F743" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="744">
@@ -21249,7 +21249,7 @@
         <v>3.6</v>
       </c>
       <c r="F744" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="745">
@@ -21305,7 +21305,7 @@
         <v>3.4</v>
       </c>
       <c r="F746" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="747">
@@ -21333,7 +21333,7 @@
         <v>3.4</v>
       </c>
       <c r="F747" t="n">
-        <v>54.9</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="748">
@@ -21361,7 +21361,7 @@
         <v>3.4</v>
       </c>
       <c r="F748" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="749">
@@ -21389,7 +21389,7 @@
         <v>3.2</v>
       </c>
       <c r="F749" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="750">
@@ -21417,7 +21417,7 @@
         <v>2.9</v>
       </c>
       <c r="F750" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="751">
@@ -21445,7 +21445,7 @@
         <v>2.7</v>
       </c>
       <c r="F751" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="752">
@@ -22049,19 +22049,19 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E773" t="n">
         <v>7.8</v>
       </c>
       <c r="F773" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="774">
@@ -22077,19 +22077,19 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E774" t="n">
         <v>7.8</v>
       </c>
       <c r="F774" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="775">
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>28.5</v>
+        <v>28.1</v>
       </c>
       <c r="F802" t="n">
         <v>53.4</v>
@@ -22898,7 +22898,7 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="F803" t="n">
         <v>47.8</v>
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="F804" t="n">
         <v>47.1</v>
@@ -22954,10 +22954,10 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="F805" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="806">
@@ -23010,7 +23010,7 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F807" t="n">
         <v>48.9</v>
@@ -23038,10 +23038,10 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="F808" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="809">
@@ -23066,10 +23066,10 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="F809" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="810">
@@ -23094,7 +23094,7 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="F810" t="n">
         <v>50.9</v>
@@ -23125,7 +23125,7 @@
         <v>15.3</v>
       </c>
       <c r="F811" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="812">
@@ -23150,7 +23150,7 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="F812" t="n">
         <v>50.3</v>
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="E813" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F813" t="n">
         <v>51</v>
@@ -23234,7 +23234,7 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F815" t="n">
         <v>45.8</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F817" t="n">
         <v>51.8</v>
@@ -23309,19 +23309,19 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E818" t="n">
         <v>11</v>
       </c>
       <c r="F818" t="n">
-        <v>53.4</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="819">
@@ -23337,19 +23337,19 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E819" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="F819" t="n">
-        <v>44.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="820">
@@ -23374,7 +23374,7 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="F820" t="n">
         <v>53</v>
@@ -23430,7 +23430,7 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F822" t="n">
         <v>53.3</v>
@@ -23514,7 +23514,7 @@
         </is>
       </c>
       <c r="E825" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F825" t="n">
         <v>48.1</v>
@@ -23561,19 +23561,19 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E827" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F827" t="n">
-        <v>53.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="828">
@@ -23589,19 +23589,19 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E828" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F828" t="n">
-        <v>47.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="829">
@@ -23654,10 +23654,10 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F830" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="831">
@@ -23713,7 +23713,7 @@
         <v>6.1</v>
       </c>
       <c r="F832" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="833">
@@ -23741,7 +23741,7 @@
         <v>6</v>
       </c>
       <c r="F833" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="834">
@@ -23878,10 +23878,10 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F838" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="839">
@@ -23906,7 +23906,7 @@
         </is>
       </c>
       <c r="E839" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F839" t="n">
         <v>49.7</v>
@@ -23953,7 +23953,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -23962,10 +23962,10 @@
         </is>
       </c>
       <c r="E841" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F841" t="n">
-        <v>50.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="842">
@@ -23981,19 +23981,19 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E842" t="n">
         <v>4.4</v>
       </c>
       <c r="F842" t="n">
-        <v>45.3</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="843">
@@ -24009,19 +24009,19 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E843" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F843" t="n">
-        <v>48.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="844">
@@ -24046,7 +24046,7 @@
         </is>
       </c>
       <c r="E844" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F844" t="n">
         <v>51.9</v>
@@ -24105,7 +24105,7 @@
         <v>3.5</v>
       </c>
       <c r="F846" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="847">
@@ -24217,7 +24217,7 @@
         <v>2.7</v>
       </c>
       <c r="F850" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="851">
@@ -24270,7 +24270,7 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="F852" t="n">
         <v>49.5</v>
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="E853" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="F853" t="n">
         <v>54.6</v>
@@ -24329,7 +24329,7 @@
         <v>24.5</v>
       </c>
       <c r="F854" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="855">
@@ -24385,7 +24385,7 @@
         <v>21.5</v>
       </c>
       <c r="F856" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="857">
@@ -24466,7 +24466,7 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F859" t="n">
         <v>48</v>
@@ -24494,10 +24494,10 @@
         </is>
       </c>
       <c r="E860" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="F860" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="861">
@@ -24522,7 +24522,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F861" t="n">
         <v>45</v>
@@ -24606,7 +24606,7 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="F864" t="n">
         <v>46</v>
@@ -24625,19 +24625,19 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E865" t="n">
         <v>12.4</v>
       </c>
       <c r="F865" t="n">
-        <v>53</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="866">
@@ -24681,19 +24681,19 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E867" t="n">
         <v>12.3</v>
       </c>
       <c r="F867" t="n">
-        <v>47</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="868">
@@ -24749,7 +24749,7 @@
         <v>11.5</v>
       </c>
       <c r="F869" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="870">
@@ -24777,7 +24777,7 @@
         <v>11.4</v>
       </c>
       <c r="F870" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="871">
@@ -24858,10 +24858,10 @@
         </is>
       </c>
       <c r="E873" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F873" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="874">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -24886,10 +24886,10 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F874" t="n">
-        <v>53.4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="875">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -24914,10 +24914,10 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F875" t="n">
-        <v>51</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="876">
@@ -24945,7 +24945,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F876" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="877">
@@ -24973,7 +24973,7 @@
         <v>8</v>
       </c>
       <c r="F877" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="878">
@@ -24998,7 +24998,7 @@
         </is>
       </c>
       <c r="E878" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="F878" t="n">
         <v>53.4</v>
@@ -25029,7 +25029,7 @@
         <v>6.4</v>
       </c>
       <c r="F879" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="880">
@@ -25045,19 +25045,19 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E880" t="n">
         <v>6</v>
       </c>
       <c r="F880" t="n">
-        <v>50.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="881">
@@ -25085,7 +25085,7 @@
         <v>6</v>
       </c>
       <c r="F881" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="882">
@@ -25101,19 +25101,19 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E882" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F882" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="883">
@@ -25129,19 +25129,19 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E883" t="n">
         <v>5.9</v>
       </c>
       <c r="F883" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="884">
@@ -25169,7 +25169,7 @@
         <v>5.7</v>
       </c>
       <c r="F884" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="885">
@@ -25197,7 +25197,7 @@
         <v>5.6</v>
       </c>
       <c r="F885" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="886">
@@ -25225,7 +25225,7 @@
         <v>5.3</v>
       </c>
       <c r="F886" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="887">
@@ -25253,7 +25253,7 @@
         <v>5.3</v>
       </c>
       <c r="F887" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="888">
@@ -25281,7 +25281,7 @@
         <v>4.8</v>
       </c>
       <c r="F888" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="889">
@@ -25306,7 +25306,7 @@
         </is>
       </c>
       <c r="E889" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F889" t="n">
         <v>56.4</v>
@@ -25365,7 +25365,7 @@
         <v>4.1</v>
       </c>
       <c r="F891" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="892">
@@ -25393,7 +25393,7 @@
         <v>3.9</v>
       </c>
       <c r="F892" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="893">
@@ -25409,19 +25409,19 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E893" t="n">
         <v>3.6</v>
       </c>
       <c r="F893" t="n">
-        <v>48.3</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="894">
@@ -25437,19 +25437,19 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E894" t="n">
         <v>3.6</v>
       </c>
       <c r="F894" t="n">
-        <v>52.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="895">
@@ -25477,7 +25477,7 @@
         <v>3.3</v>
       </c>
       <c r="F895" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="896">
@@ -25502,10 +25502,10 @@
         </is>
       </c>
       <c r="E896" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F896" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="897">
@@ -25533,7 +25533,7 @@
         <v>3</v>
       </c>
       <c r="F897" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="898">
@@ -25561,7 +25561,7 @@
         <v>2.6</v>
       </c>
       <c r="F898" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="899">
@@ -25589,7 +25589,7 @@
         <v>2.3</v>
       </c>
       <c r="F899" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="900">
@@ -25645,7 +25645,7 @@
         <v>1.6</v>
       </c>
       <c r="F901" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="902">
@@ -25670,7 +25670,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="F902" t="n">
         <v>48.5</v>
@@ -25698,7 +25698,7 @@
         </is>
       </c>
       <c r="E903" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="F903" t="n">
         <v>54.4</v>
@@ -25782,7 +25782,7 @@
         </is>
       </c>
       <c r="E906" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F906" t="n">
         <v>49</v>
@@ -25813,7 +25813,7 @@
         <v>18.3</v>
       </c>
       <c r="F907" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="908">
@@ -25838,7 +25838,7 @@
         </is>
       </c>
       <c r="E908" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F908" t="n">
         <v>50.6</v>
@@ -25866,10 +25866,10 @@
         </is>
       </c>
       <c r="E909" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="F909" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="910">
@@ -25894,10 +25894,10 @@
         </is>
       </c>
       <c r="E910" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="F910" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="911">
@@ -25922,10 +25922,10 @@
         </is>
       </c>
       <c r="E911" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="F911" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="912">
@@ -25981,7 +25981,7 @@
         <v>13.3</v>
       </c>
       <c r="F913" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="914">
@@ -26009,7 +26009,7 @@
         <v>13.1</v>
       </c>
       <c r="F914" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="915">
@@ -26037,7 +26037,7 @@
         <v>13.1</v>
       </c>
       <c r="F915" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="916">
@@ -26146,7 +26146,7 @@
         </is>
       </c>
       <c r="E919" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F919" t="n">
         <v>44.8</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="E920" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F920" t="n">
         <v>52.2</v>
@@ -26193,19 +26193,19 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E921" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F921" t="n">
-        <v>53.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="922">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -26230,10 +26230,10 @@
         </is>
       </c>
       <c r="E922" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F922" t="n">
-        <v>51.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="923">
@@ -26249,19 +26249,19 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E923" t="n">
         <v>10.2</v>
       </c>
       <c r="F923" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="924">
@@ -26289,7 +26289,7 @@
         <v>9.9</v>
       </c>
       <c r="F924" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="925">
@@ -26345,7 +26345,7 @@
         <v>9.4</v>
       </c>
       <c r="F926" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="927">
@@ -26398,7 +26398,7 @@
         </is>
       </c>
       <c r="E928" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F928" t="n">
         <v>53.4</v>
@@ -26454,7 +26454,7 @@
         </is>
       </c>
       <c r="E930" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F930" t="n">
         <v>45.1</v>
@@ -26485,7 +26485,7 @@
         <v>6.1</v>
       </c>
       <c r="F931" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="932">
@@ -26594,7 +26594,7 @@
         </is>
       </c>
       <c r="E935" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F935" t="n">
         <v>51.4</v>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="E936" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F936" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="937">
@@ -26737,7 +26737,7 @@
         <v>4.3</v>
       </c>
       <c r="F940" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="941">
@@ -26818,10 +26818,10 @@
         </is>
       </c>
       <c r="E943" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F943" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="944">
@@ -26846,7 +26846,7 @@
         </is>
       </c>
       <c r="E944" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F944" t="n">
         <v>48.9</v>
@@ -26877,7 +26877,7 @@
         <v>3.5</v>
       </c>
       <c r="F945" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="946">
@@ -26902,7 +26902,7 @@
         </is>
       </c>
       <c r="E946" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F946" t="n">
         <v>51.7</v>
@@ -26933,7 +26933,7 @@
         <v>3.2</v>
       </c>
       <c r="F947" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="948">
@@ -26961,7 +26961,7 @@
         <v>3.1</v>
       </c>
       <c r="F948" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="949">
@@ -27045,7 +27045,7 @@
         <v>1.5</v>
       </c>
       <c r="F951" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="952">
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="F952" t="n">
         <v>53.6</v>
@@ -27098,7 +27098,7 @@
         </is>
       </c>
       <c r="E953" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="F953" t="n">
         <v>47.6</v>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="E954" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="F954" t="n">
         <v>47</v>
@@ -27154,10 +27154,10 @@
         </is>
       </c>
       <c r="E955" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="F955" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="956">
@@ -27238,7 +27238,7 @@
         </is>
       </c>
       <c r="E958" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="F958" t="n">
         <v>47.9</v>
@@ -27350,7 +27350,7 @@
         </is>
       </c>
       <c r="E962" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="F962" t="n">
         <v>50.4</v>
@@ -27425,19 +27425,19 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E965" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F965" t="n">
-        <v>51.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="966">
@@ -27453,19 +27453,19 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E966" t="n">
         <v>12.7</v>
       </c>
       <c r="F966" t="n">
-        <v>52.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="967">
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="E967" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F967" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="968">
@@ -27546,10 +27546,10 @@
         </is>
       </c>
       <c r="E969" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="F969" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="970">
@@ -27574,10 +27574,10 @@
         </is>
       </c>
       <c r="E970" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F970" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="971">
@@ -27605,7 +27605,7 @@
         <v>10.1</v>
       </c>
       <c r="F971" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="972">
@@ -27630,7 +27630,7 @@
         </is>
       </c>
       <c r="E972" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F972" t="n">
         <v>50.9</v>
@@ -27733,19 +27733,19 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E976" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="F976" t="n">
-        <v>53.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="977">
@@ -27789,19 +27789,19 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E978" t="n">
         <v>8.1</v>
       </c>
       <c r="F978" t="n">
-        <v>47.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="979">
@@ -27857,7 +27857,7 @@
         <v>7</v>
       </c>
       <c r="F980" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="981">
@@ -27985,19 +27985,19 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E985" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F985" t="n">
-        <v>54.5</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="986">
@@ -28013,19 +28013,19 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E986" t="n">
         <v>5.2</v>
       </c>
       <c r="F986" t="n">
-        <v>53.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="987">
@@ -28078,7 +28078,7 @@
         </is>
       </c>
       <c r="E988" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F988" t="n">
         <v>51.4</v>
@@ -28106,7 +28106,7 @@
         </is>
       </c>
       <c r="E989" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F989" t="n">
         <v>52.1</v>
@@ -28165,7 +28165,7 @@
         <v>4.3</v>
       </c>
       <c r="F991" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="992">
@@ -28193,7 +28193,7 @@
         <v>4.1</v>
       </c>
       <c r="F992" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="993">
@@ -28237,19 +28237,19 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E994" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F994" t="n">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="995">
@@ -28265,19 +28265,19 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E995" t="n">
         <v>3.6</v>
       </c>
       <c r="F995" t="n">
-        <v>50.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="996">
@@ -28293,19 +28293,19 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E996" t="n">
         <v>3.6</v>
       </c>
       <c r="F996" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="997">
@@ -28389,7 +28389,7 @@
         <v>2.7</v>
       </c>
       <c r="F999" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1000">
@@ -28470,10 +28470,10 @@
         </is>
       </c>
       <c r="E1002" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="F1002" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1003">
@@ -28498,7 +28498,7 @@
         </is>
       </c>
       <c r="E1003" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="F1003" t="n">
         <v>52.7</v>
@@ -28526,10 +28526,10 @@
         </is>
       </c>
       <c r="E1004" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="F1004" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1005">
@@ -28554,7 +28554,7 @@
         </is>
       </c>
       <c r="E1005" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F1005" t="n">
         <v>47.1</v>
@@ -28585,7 +28585,7 @@
         <v>20.7</v>
       </c>
       <c r="F1006" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1007">
@@ -28666,10 +28666,10 @@
         </is>
       </c>
       <c r="E1009" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="F1009" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1010">
@@ -28722,7 +28722,7 @@
         </is>
       </c>
       <c r="E1011" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="F1011" t="n">
         <v>51.1</v>
@@ -28750,7 +28750,7 @@
         </is>
       </c>
       <c r="E1012" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="F1012" t="n">
         <v>50.5</v>
@@ -28781,7 +28781,7 @@
         <v>13.2</v>
       </c>
       <c r="F1013" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1014">
@@ -28893,7 +28893,7 @@
         <v>11.7</v>
       </c>
       <c r="F1017" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1018">
@@ -28918,7 +28918,7 @@
         </is>
       </c>
       <c r="E1018" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="F1018" t="n">
         <v>53.8</v>
@@ -28946,7 +28946,7 @@
         </is>
       </c>
       <c r="E1019" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F1019" t="n">
         <v>50.5</v>
@@ -28974,7 +28974,7 @@
         </is>
       </c>
       <c r="E1020" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F1020" t="n">
         <v>53.5</v>
@@ -28993,19 +28993,19 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F1021" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1022">
@@ -29021,19 +29021,19 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1022" t="n">
         <v>9.4</v>
       </c>
       <c r="F1022" t="n">
-        <v>43.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1023">
@@ -29049,19 +29049,19 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1023" t="n">
         <v>9.4</v>
       </c>
       <c r="F1023" t="n">
-        <v>53.6</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1024">
@@ -29086,10 +29086,10 @@
         </is>
       </c>
       <c r="E1024" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="F1024" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="1025">
@@ -29145,7 +29145,7 @@
         <v>7.7</v>
       </c>
       <c r="F1026" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1027">
@@ -29173,7 +29173,7 @@
         <v>7.3</v>
       </c>
       <c r="F1027" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1028">
@@ -29201,7 +29201,7 @@
         <v>7</v>
       </c>
       <c r="F1028" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1029">
@@ -29341,7 +29341,7 @@
         <v>6.5</v>
       </c>
       <c r="F1033" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1034">
@@ -29369,7 +29369,7 @@
         <v>6.4</v>
       </c>
       <c r="F1034" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1035">
@@ -29394,10 +29394,10 @@
         </is>
       </c>
       <c r="E1035" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F1035" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1036">
@@ -29453,7 +29453,7 @@
         <v>5.6</v>
       </c>
       <c r="F1037" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1038">
@@ -29478,7 +29478,7 @@
         </is>
       </c>
       <c r="E1038" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F1038" t="n">
         <v>49.8</v>
@@ -29506,10 +29506,10 @@
         </is>
       </c>
       <c r="E1039" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F1039" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1040">
@@ -29537,7 +29537,7 @@
         <v>4.5</v>
       </c>
       <c r="F1040" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1041">
@@ -29649,7 +29649,7 @@
         <v>3.8</v>
       </c>
       <c r="F1044" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1045">
@@ -29705,7 +29705,7 @@
         <v>3.3</v>
       </c>
       <c r="F1046" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1047">
@@ -29789,7 +29789,7 @@
         <v>3.2</v>
       </c>
       <c r="F1049" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1050">
@@ -29817,7 +29817,7 @@
         <v>2.7</v>
       </c>
       <c r="F1050" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1051">
@@ -29845,7 +29845,7 @@
         <v>1.9</v>
       </c>
       <c r="F1051" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1052">
@@ -29870,7 +29870,7 @@
         </is>
       </c>
       <c r="E1052" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="F1052" t="n">
         <v>47.5</v>
@@ -29898,10 +29898,10 @@
         </is>
       </c>
       <c r="E1053" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="F1053" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1054">
@@ -29926,7 +29926,7 @@
         </is>
       </c>
       <c r="E1054" t="n">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="F1054" t="n">
         <v>51.9</v>
@@ -29954,10 +29954,10 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="F1055" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1056">
@@ -30013,7 +30013,7 @@
         <v>17.9</v>
       </c>
       <c r="F1057" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1058">
@@ -30038,7 +30038,7 @@
         </is>
       </c>
       <c r="E1058" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="F1058" t="n">
         <v>49.6</v>
@@ -30066,10 +30066,10 @@
         </is>
       </c>
       <c r="E1059" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="F1059" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1060">
@@ -30097,7 +30097,7 @@
         <v>15.6</v>
       </c>
       <c r="F1060" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1061">
@@ -30150,10 +30150,10 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="F1062" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1063">
@@ -30178,7 +30178,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="F1063" t="n">
         <v>46.9</v>
@@ -30206,7 +30206,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F1064" t="n">
         <v>50.1</v>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -30234,10 +30234,10 @@
         </is>
       </c>
       <c r="E1065" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F1065" t="n">
-        <v>53.9</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1066">
@@ -30253,7 +30253,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -30265,7 +30265,7 @@
         <v>11.4</v>
       </c>
       <c r="F1066" t="n">
-        <v>52.2</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1067">
@@ -30293,7 +30293,7 @@
         <v>10.9</v>
       </c>
       <c r="F1067" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1068">
@@ -30321,7 +30321,7 @@
         <v>10.3</v>
       </c>
       <c r="F1068" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1069">
@@ -30349,7 +30349,7 @@
         <v>10</v>
       </c>
       <c r="F1069" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1070">
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F1070" t="n">
         <v>53</v>
@@ -30393,19 +30393,19 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1071" t="n">
         <v>9.5</v>
       </c>
       <c r="F1071" t="n">
-        <v>53</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="1072">
@@ -30421,19 +30421,19 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1072" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F1072" t="n">
-        <v>54.4</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1073">
@@ -30514,7 +30514,7 @@
         </is>
       </c>
       <c r="E1075" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F1075" t="n">
         <v>51.8</v>
@@ -30598,10 +30598,10 @@
         </is>
       </c>
       <c r="E1078" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F1078" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1079">
@@ -30626,10 +30626,10 @@
         </is>
       </c>
       <c r="E1079" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F1079" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1080">
@@ -30657,7 +30657,7 @@
         <v>7</v>
       </c>
       <c r="F1080" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1081">
@@ -30685,7 +30685,7 @@
         <v>6.8</v>
       </c>
       <c r="F1081" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1082">
@@ -30710,10 +30710,10 @@
         </is>
       </c>
       <c r="E1082" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="F1082" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1083">
@@ -30729,19 +30729,19 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1083" t="n">
         <v>6.3</v>
       </c>
       <c r="F1083" t="n">
-        <v>43.5</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1084">
@@ -30757,19 +30757,19 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1084" t="n">
         <v>6.3</v>
       </c>
       <c r="F1084" t="n">
-        <v>51.8</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1085">
@@ -30797,7 +30797,7 @@
         <v>5.5</v>
       </c>
       <c r="F1085" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1086">
@@ -30825,7 +30825,7 @@
         <v>5.3</v>
       </c>
       <c r="F1086" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1087">
@@ -30853,7 +30853,7 @@
         <v>4.9</v>
       </c>
       <c r="F1087" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1088">
@@ -30909,7 +30909,7 @@
         <v>4.9</v>
       </c>
       <c r="F1089" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1090">
@@ -30925,19 +30925,19 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1090" t="n">
         <v>4.7</v>
       </c>
       <c r="F1090" t="n">
-        <v>50.4</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1091">
@@ -30953,19 +30953,19 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1091" t="n">
         <v>4.7</v>
       </c>
       <c r="F1091" t="n">
-        <v>44.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1092">
@@ -31049,7 +31049,7 @@
         <v>4.1</v>
       </c>
       <c r="F1094" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1095">
@@ -31077,7 +31077,7 @@
         <v>4</v>
       </c>
       <c r="F1095" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1096">
@@ -31105,7 +31105,7 @@
         <v>3.8</v>
       </c>
       <c r="F1096" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="1097">
@@ -31133,7 +31133,7 @@
         <v>3.2</v>
       </c>
       <c r="F1097" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1098">
@@ -31161,7 +31161,7 @@
         <v>3</v>
       </c>
       <c r="F1098" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1099">
@@ -31245,7 +31245,7 @@
         <v>2.6</v>
       </c>
       <c r="F1101" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1102">
@@ -31270,10 +31270,10 @@
         </is>
       </c>
       <c r="E1102" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="F1102" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1103">
@@ -31298,10 +31298,10 @@
         </is>
       </c>
       <c r="E1103" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="F1103" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1104">
@@ -31326,10 +31326,10 @@
         </is>
       </c>
       <c r="E1104" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="F1104" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1105">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="E1106" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="F1106" t="n">
         <v>50.2</v>
@@ -31410,10 +31410,10 @@
         </is>
       </c>
       <c r="E1107" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="F1107" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1108">
@@ -31441,7 +31441,7 @@
         <v>16.5</v>
       </c>
       <c r="F1108" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1109">
@@ -31494,10 +31494,10 @@
         </is>
       </c>
       <c r="E1110" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="F1110" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1111">
@@ -31525,7 +31525,7 @@
         <v>15.4</v>
       </c>
       <c r="F1111" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1112">
@@ -31550,10 +31550,10 @@
         </is>
       </c>
       <c r="E1112" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="F1112" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1113">
@@ -31581,7 +31581,7 @@
         <v>13</v>
       </c>
       <c r="F1113" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1114">
@@ -31606,7 +31606,7 @@
         </is>
       </c>
       <c r="E1114" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="F1114" t="n">
         <v>53</v>
@@ -31634,10 +31634,10 @@
         </is>
       </c>
       <c r="E1115" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F1115" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="1116">
@@ -31662,10 +31662,10 @@
         </is>
       </c>
       <c r="E1116" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F1116" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1117">
@@ -31681,19 +31681,19 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F1117" t="n">
-        <v>50.9</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1118">
@@ -31709,19 +31709,19 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1118" t="n">
         <v>11.1</v>
       </c>
       <c r="F1118" t="n">
-        <v>47.4</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1119">
@@ -31774,10 +31774,10 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F1120" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1121">
@@ -31793,19 +31793,19 @@
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F1121" t="n">
-        <v>52.1</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1122">
@@ -31821,19 +31821,19 @@
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1122" t="n">
         <v>9.5</v>
       </c>
       <c r="F1122" t="n">
-        <v>48.4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1123">
@@ -31849,19 +31849,19 @@
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F1123" t="n">
-        <v>49.1</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1124">
@@ -31877,19 +31877,19 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1124" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F1124" t="n">
-        <v>51.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1125">
@@ -31942,7 +31942,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F1126" t="n">
         <v>48.7</v>
@@ -31961,19 +31961,19 @@
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F1127" t="n">
-        <v>52.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1128">
@@ -31989,19 +31989,19 @@
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1128" t="n">
         <v>7.8</v>
       </c>
       <c r="F1128" t="n">
-        <v>49.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1129">
@@ -32026,10 +32026,10 @@
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F1129" t="n">
-        <v>51.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1130">
@@ -32057,7 +32057,7 @@
         <v>7.4</v>
       </c>
       <c r="F1130" t="n">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1131">
@@ -32073,19 +32073,19 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1131" t="n">
         <v>6.9</v>
       </c>
       <c r="F1131" t="n">
-        <v>51.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1132">
@@ -32101,19 +32101,19 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F1132" t="n">
-        <v>49.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1133">
@@ -32141,7 +32141,7 @@
         <v>6.8</v>
       </c>
       <c r="F1133" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1134">
@@ -32169,7 +32169,7 @@
         <v>6.5</v>
       </c>
       <c r="F1134" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1135">
@@ -32197,7 +32197,7 @@
         <v>6.3</v>
       </c>
       <c r="F1135" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1136">
@@ -32225,7 +32225,7 @@
         <v>5.8</v>
       </c>
       <c r="F1136" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1137">
@@ -32250,10 +32250,10 @@
         </is>
       </c>
       <c r="E1137" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F1137" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1138">
@@ -32278,10 +32278,10 @@
         </is>
       </c>
       <c r="E1138" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F1138" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1139">
@@ -32306,10 +32306,10 @@
         </is>
       </c>
       <c r="E1139" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F1139" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1140">
@@ -32325,19 +32325,19 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1140" t="n">
         <v>4.5</v>
       </c>
       <c r="F1140" t="n">
-        <v>51.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1141">
@@ -32353,19 +32353,19 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1141" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F1141" t="n">
-        <v>54</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1142">
@@ -32393,7 +32393,7 @@
         <v>4.1</v>
       </c>
       <c r="F1142" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1143">
@@ -32421,7 +32421,7 @@
         <v>3.7</v>
       </c>
       <c r="F1143" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1144">
@@ -32437,19 +32437,19 @@
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1144" t="n">
         <v>3.6</v>
       </c>
       <c r="F1144" t="n">
-        <v>45.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1145">
@@ -32465,19 +32465,19 @@
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1145" t="n">
         <v>3.6</v>
       </c>
       <c r="F1145" t="n">
-        <v>46.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1146">
@@ -32493,19 +32493,19 @@
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1146" t="n">
         <v>3.6</v>
       </c>
       <c r="F1146" t="n">
-        <v>48.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1147">
@@ -32521,19 +32521,19 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1147" t="n">
         <v>3.4</v>
       </c>
       <c r="F1147" t="n">
-        <v>52</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1148">
@@ -32549,19 +32549,19 @@
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1148" t="n">
-        <v>47.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1149">
@@ -32586,10 +32586,10 @@
         </is>
       </c>
       <c r="E1149" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F1149" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1150">
@@ -32642,10 +32642,10 @@
         </is>
       </c>
       <c r="E1151" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1151" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1152">
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="F1152" t="n">
         <v>47.5</v>
@@ -32698,10 +32698,10 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="F1153" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1154">
@@ -32729,7 +32729,7 @@
         <v>27.1</v>
       </c>
       <c r="F1154" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1155">
@@ -32782,10 +32782,10 @@
         </is>
       </c>
       <c r="E1156" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="F1156" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1157">
@@ -32813,7 +32813,7 @@
         <v>17.8</v>
       </c>
       <c r="F1157" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1158">
@@ -32838,10 +32838,10 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="F1158" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1159">
@@ -32866,10 +32866,10 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="F1159" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1160">
@@ -32894,10 +32894,10 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="F1160" t="n">
-        <v>55.7</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="1161">
@@ -32922,10 +32922,10 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="F1161" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1162">
@@ -32941,19 +32941,19 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1162" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="F1162" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1163">
@@ -32969,19 +32969,19 @@
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1163" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1163" t="n">
         <v>13.3</v>
       </c>
       <c r="F1163" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1164">
@@ -33009,7 +33009,7 @@
         <v>12</v>
       </c>
       <c r="F1164" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1165">
@@ -33034,10 +33034,10 @@
         </is>
       </c>
       <c r="E1165" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F1165" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1166">
@@ -33065,7 +33065,7 @@
         <v>11.5</v>
       </c>
       <c r="F1166" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1167">
@@ -33081,19 +33081,19 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1167" t="n">
         <v>11.3</v>
       </c>
       <c r="F1167" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1168">
@@ -33109,19 +33109,19 @@
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1168" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1168" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F1168" t="n">
-        <v>50.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1169">
@@ -33137,19 +33137,19 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1169" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F1169" t="n">
-        <v>45.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1170">
@@ -33174,7 +33174,7 @@
         </is>
       </c>
       <c r="E1170" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="F1170" t="n">
         <v>51.6</v>
@@ -33205,7 +33205,7 @@
         <v>10.5</v>
       </c>
       <c r="F1171" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1172">
@@ -33230,10 +33230,10 @@
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="F1172" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="1173">
@@ -33258,10 +33258,10 @@
         </is>
       </c>
       <c r="E1173" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F1173" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1174">
@@ -33286,7 +33286,7 @@
         </is>
       </c>
       <c r="E1174" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F1174" t="n">
         <v>52.1</v>
@@ -33317,7 +33317,7 @@
         <v>7.7</v>
       </c>
       <c r="F1175" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1176">
@@ -33342,10 +33342,10 @@
         </is>
       </c>
       <c r="E1176" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F1176" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1177">
@@ -33389,19 +33389,19 @@
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1178" t="n">
         <v>6.9</v>
       </c>
       <c r="F1178" t="n">
-        <v>48.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1179">
@@ -33417,19 +33417,19 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1179" t="n">
         <v>6.8</v>
       </c>
       <c r="F1179" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1180">
@@ -33457,7 +33457,7 @@
         <v>6.1</v>
       </c>
       <c r="F1180" t="n">
-        <v>54.6</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="1181">
@@ -33473,19 +33473,19 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F1181" t="n">
-        <v>44.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1182">
@@ -33510,10 +33510,10 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F1182" t="n">
-        <v>44</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1183">
@@ -33529,19 +33529,19 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1183" t="n">
         <v>5.9</v>
       </c>
       <c r="F1183" t="n">
-        <v>53.4</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1184">
@@ -33566,7 +33566,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F1184" t="n">
         <v>48</v>
@@ -33594,10 +33594,10 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F1185" t="n">
-        <v>54.3</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="1186">
@@ -33625,7 +33625,7 @@
         <v>5.5</v>
       </c>
       <c r="F1186" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1187">
@@ -33650,7 +33650,7 @@
         </is>
       </c>
       <c r="E1187" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F1187" t="n">
         <v>49.1</v>
@@ -33678,10 +33678,10 @@
         </is>
       </c>
       <c r="E1188" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F1188" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1189">
@@ -33706,10 +33706,10 @@
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F1189" t="n">
-        <v>53.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1190">
@@ -33737,7 +33737,7 @@
         <v>4.1</v>
       </c>
       <c r="F1190" t="n">
-        <v>44.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1191">
@@ -33762,10 +33762,10 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1191" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1192">
@@ -33793,7 +33793,7 @@
         <v>3.8</v>
       </c>
       <c r="F1192" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1193">
@@ -33821,7 +33821,7 @@
         <v>3.8</v>
       </c>
       <c r="F1193" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1194">
@@ -33846,10 +33846,10 @@
         </is>
       </c>
       <c r="E1194" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="F1194" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1195">
@@ -33933,7 +33933,7 @@
         <v>3.3</v>
       </c>
       <c r="F1197" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1198">
@@ -33961,7 +33961,7 @@
         <v>2.4</v>
       </c>
       <c r="F1198" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1199">
@@ -33989,7 +33989,7 @@
         <v>2.2</v>
       </c>
       <c r="F1199" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1200">
@@ -34014,10 +34014,10 @@
         </is>
       </c>
       <c r="E1200" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1200" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1201">
@@ -34045,7 +34045,7 @@
         <v>1.9</v>
       </c>
       <c r="F1201" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="1202">
@@ -34185,7 +34185,7 @@
         <v>3.2</v>
       </c>
       <c r="F1206" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1207">
@@ -34241,7 +34241,7 @@
         <v>3</v>
       </c>
       <c r="F1208" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1209">
@@ -34257,19 +34257,19 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1209" t="n">
         <v>2.9</v>
       </c>
       <c r="F1209" t="n">
-        <v>46.1</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1210">
@@ -34285,19 +34285,19 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1210" t="n">
         <v>2.9</v>
       </c>
       <c r="F1210" t="n">
-        <v>50.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1211">
@@ -34353,7 +34353,7 @@
         <v>2.5</v>
       </c>
       <c r="F1212" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1213">
@@ -34378,10 +34378,10 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1213" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1214">
@@ -34537,19 +34537,19 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1219" t="n">
         <v>1.8</v>
       </c>
       <c r="F1219" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1220">
@@ -34565,19 +34565,19 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1220" t="n">
         <v>1.8</v>
       </c>
       <c r="F1220" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1221">
@@ -34605,7 +34605,7 @@
         <v>1.7</v>
       </c>
       <c r="F1221" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1222">
@@ -34633,7 +34633,7 @@
         <v>1.6</v>
       </c>
       <c r="F1222" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1223">
@@ -34705,19 +34705,19 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1225" t="n">
         <v>1.5</v>
       </c>
       <c r="F1225" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1226">
@@ -34733,19 +34733,19 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1226" t="n">
         <v>1.5</v>
       </c>
       <c r="F1226" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1227">
@@ -34770,7 +34770,7 @@
         </is>
       </c>
       <c r="E1227" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F1227" t="n">
         <v>52.6</v>
@@ -34801,7 +34801,7 @@
         <v>1.2</v>
       </c>
       <c r="F1228" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1229">
@@ -34857,7 +34857,7 @@
         <v>1.1</v>
       </c>
       <c r="F1230" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1231">
@@ -34885,7 +34885,7 @@
         <v>1.1</v>
       </c>
       <c r="F1231" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1232">
@@ -34913,7 +34913,7 @@
         <v>1.1</v>
       </c>
       <c r="F1232" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1233">
@@ -34941,7 +34941,7 @@
         <v>1.1</v>
       </c>
       <c r="F1233" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1234">
@@ -34997,7 +34997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1235" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1236">
@@ -35053,7 +35053,7 @@
         <v>1</v>
       </c>
       <c r="F1237" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1238">
@@ -35109,7 +35109,7 @@
         <v>0.9</v>
       </c>
       <c r="F1239" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="1240">
@@ -35165,7 +35165,7 @@
         <v>0.8</v>
       </c>
       <c r="F1241" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1242">
@@ -35193,7 +35193,7 @@
         <v>0.7</v>
       </c>
       <c r="F1242" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1243">
@@ -35249,7 +35249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1244" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1245">
@@ -35277,7 +35277,7 @@
         <v>0.5</v>
       </c>
       <c r="F1245" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1246">
@@ -35305,7 +35305,7 @@
         <v>5.9</v>
       </c>
       <c r="F1246" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1247">
@@ -35330,10 +35330,10 @@
         </is>
       </c>
       <c r="E1247" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F1247" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1248">
@@ -35417,7 +35417,7 @@
         <v>3.8</v>
       </c>
       <c r="F1250" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1251">
@@ -35442,7 +35442,7 @@
         </is>
       </c>
       <c r="E1251" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1251" t="n">
         <v>48.5</v>
@@ -35473,7 +35473,7 @@
         <v>3</v>
       </c>
       <c r="F1252" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1253">
@@ -35501,7 +35501,7 @@
         <v>2.9</v>
       </c>
       <c r="F1253" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1254">
@@ -35526,10 +35526,10 @@
         </is>
       </c>
       <c r="E1254" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F1254" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1255">
@@ -35557,7 +35557,7 @@
         <v>2.8</v>
       </c>
       <c r="F1255" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1256">
@@ -35613,7 +35613,7 @@
         <v>2.8</v>
       </c>
       <c r="F1257" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1258">
@@ -35641,7 +35641,7 @@
         <v>2.4</v>
       </c>
       <c r="F1258" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1259">
@@ -35669,7 +35669,7 @@
         <v>2.4</v>
       </c>
       <c r="F1259" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1260">
@@ -35694,10 +35694,10 @@
         </is>
       </c>
       <c r="E1260" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F1260" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1261">
@@ -35753,7 +35753,7 @@
         <v>1.9</v>
       </c>
       <c r="F1262" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1263">
@@ -35781,7 +35781,7 @@
         <v>1.9</v>
       </c>
       <c r="F1263" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1264">
@@ -35809,7 +35809,7 @@
         <v>1.8</v>
       </c>
       <c r="F1264" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1265">
@@ -35837,7 +35837,7 @@
         <v>1.8</v>
       </c>
       <c r="F1265" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1266">
@@ -35893,7 +35893,7 @@
         <v>1.7</v>
       </c>
       <c r="F1267" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1268">
@@ -35921,7 +35921,7 @@
         <v>1.6</v>
       </c>
       <c r="F1268" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1269">
@@ -35937,19 +35937,19 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1269" t="n">
         <v>1.4</v>
       </c>
       <c r="F1269" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1270">
@@ -35965,19 +35965,19 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1270" t="n">
         <v>1.4</v>
       </c>
       <c r="F1270" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1271">
@@ -36002,10 +36002,10 @@
         </is>
       </c>
       <c r="E1271" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1271" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1272">
@@ -36033,7 +36033,7 @@
         <v>1.2</v>
       </c>
       <c r="F1272" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1273">
@@ -36061,7 +36061,7 @@
         <v>1.2</v>
       </c>
       <c r="F1273" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1274">
@@ -36117,7 +36117,7 @@
         <v>1.1</v>
       </c>
       <c r="F1275" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1276">
@@ -36133,19 +36133,19 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1276" t="n">
         <v>1</v>
       </c>
       <c r="F1276" t="n">
-        <v>49.6</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1277">
@@ -36161,19 +36161,19 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1277" t="n">
         <v>1</v>
       </c>
       <c r="F1277" t="n">
-        <v>52.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1278">
@@ -36201,7 +36201,7 @@
         <v>1</v>
       </c>
       <c r="F1278" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1279">
@@ -36229,7 +36229,7 @@
         <v>1</v>
       </c>
       <c r="F1279" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1280">
@@ -36257,7 +36257,7 @@
         <v>0.9</v>
       </c>
       <c r="F1280" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1281">
@@ -36369,7 +36369,7 @@
         <v>0.7</v>
       </c>
       <c r="F1284" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1285">
@@ -36397,7 +36397,7 @@
         <v>0.6</v>
       </c>
       <c r="F1285" t="n">
-        <v>51.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1286">
@@ -36425,7 +36425,7 @@
         <v>0.5</v>
       </c>
       <c r="F1286" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1287">
@@ -36441,19 +36441,19 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1287" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1287" t="n">
         <v>0.5</v>
       </c>
       <c r="F1287" t="n">
-        <v>47.2</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="1288">
@@ -36469,19 +36469,19 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1288" t="n">
         <v>0.5</v>
       </c>
       <c r="F1288" t="n">
-        <v>55.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1289">
@@ -36509,7 +36509,7 @@
         <v>0.3</v>
       </c>
       <c r="F1289" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1290">
@@ -36649,7 +36649,7 @@
         <v>3.6</v>
       </c>
       <c r="F1294" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1295">
@@ -36733,7 +36733,7 @@
         <v>3.1</v>
       </c>
       <c r="F1297" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1298">
@@ -36845,7 +36845,7 @@
         <v>2.3</v>
       </c>
       <c r="F1301" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1302">
@@ -36901,7 +36901,7 @@
         <v>2.3</v>
       </c>
       <c r="F1303" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1304">
@@ -36929,7 +36929,7 @@
         <v>2.1</v>
       </c>
       <c r="F1304" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1305">
@@ -36957,7 +36957,7 @@
         <v>2</v>
       </c>
       <c r="F1305" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1306">
@@ -36985,7 +36985,7 @@
         <v>1.8</v>
       </c>
       <c r="F1306" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1307">
@@ -37013,7 +37013,7 @@
         <v>1.8</v>
       </c>
       <c r="F1307" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1308">
@@ -37038,10 +37038,10 @@
         </is>
       </c>
       <c r="E1308" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1308" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1309">
@@ -37069,7 +37069,7 @@
         <v>1.7</v>
       </c>
       <c r="F1309" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1310">
@@ -37094,7 +37094,7 @@
         </is>
       </c>
       <c r="E1310" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1310" t="n">
         <v>47</v>
@@ -37125,7 +37125,7 @@
         <v>1.6</v>
       </c>
       <c r="F1311" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1312">
@@ -37150,10 +37150,10 @@
         </is>
       </c>
       <c r="E1312" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1312" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1313">
@@ -37181,7 +37181,7 @@
         <v>1.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1314">
@@ -37237,7 +37237,7 @@
         <v>1.4</v>
       </c>
       <c r="F1315" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1316">
@@ -37293,7 +37293,7 @@
         <v>1.2</v>
       </c>
       <c r="F1317" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1318">
@@ -37405,7 +37405,7 @@
         <v>1.1</v>
       </c>
       <c r="F1321" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1322">
@@ -37430,7 +37430,7 @@
         </is>
       </c>
       <c r="E1322" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1322" t="n">
         <v>44.5</v>
@@ -37461,7 +37461,7 @@
         <v>1</v>
       </c>
       <c r="F1323" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1324">
@@ -37489,7 +37489,7 @@
         <v>1</v>
       </c>
       <c r="F1324" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1325">
@@ -37533,19 +37533,19 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1326" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1326" t="n">
         <v>0.8</v>
       </c>
       <c r="F1326" t="n">
-        <v>47</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1327">
@@ -37561,19 +37561,19 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1327" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1327" t="n">
         <v>0.8</v>
       </c>
       <c r="F1327" t="n">
-        <v>40.6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1328">
@@ -37601,7 +37601,7 @@
         <v>0.7</v>
       </c>
       <c r="F1328" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1329">
@@ -37685,7 +37685,7 @@
         <v>0.6</v>
       </c>
       <c r="F1331" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1332">
@@ -37713,7 +37713,7 @@
         <v>0.5</v>
       </c>
       <c r="F1332" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1333">
@@ -37741,7 +37741,7 @@
         <v>0.4</v>
       </c>
       <c r="F1333" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1334">
@@ -37881,7 +37881,7 @@
         <v>3.4</v>
       </c>
       <c r="F1338" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1339">
@@ -37909,7 +37909,7 @@
         <v>3.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1340">
@@ -38161,7 +38161,7 @@
         <v>2.1</v>
       </c>
       <c r="F1348" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1349">
@@ -38217,7 +38217,7 @@
         <v>1.8</v>
       </c>
       <c r="F1350" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1351">
@@ -38273,7 +38273,7 @@
         <v>1.6</v>
       </c>
       <c r="F1352" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1353">
@@ -38329,7 +38329,7 @@
         <v>1.6</v>
       </c>
       <c r="F1354" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1355">
@@ -38413,7 +38413,7 @@
         <v>1.5</v>
       </c>
       <c r="F1357" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="1358">
@@ -38441,7 +38441,7 @@
         <v>1.5</v>
       </c>
       <c r="F1358" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1359">
@@ -38525,7 +38525,7 @@
         <v>1.1</v>
       </c>
       <c r="F1361" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1362">
@@ -38553,7 +38553,7 @@
         <v>1.1</v>
       </c>
       <c r="F1362" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1363">
@@ -38581,7 +38581,7 @@
         <v>1.1</v>
       </c>
       <c r="F1363" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1364">
@@ -38665,7 +38665,7 @@
         <v>1.1</v>
       </c>
       <c r="F1366" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1367">
@@ -38681,19 +38681,19 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1367" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1367" t="n">
         <v>1.1</v>
       </c>
       <c r="F1367" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1368">
@@ -38709,19 +38709,19 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1368" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1368" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F1368" t="n">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1369">
@@ -38749,7 +38749,7 @@
         <v>1</v>
       </c>
       <c r="F1369" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="1370">
@@ -38777,7 +38777,7 @@
         <v>0.9</v>
       </c>
       <c r="F1370" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1371">
@@ -38861,7 +38861,7 @@
         <v>0.8</v>
       </c>
       <c r="F1373" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1374">
@@ -38889,7 +38889,7 @@
         <v>0.7</v>
       </c>
       <c r="F1374" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1375">
@@ -38917,7 +38917,7 @@
         <v>0.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1376">
@@ -38973,7 +38973,7 @@
         <v>0.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1378">
@@ -39029,7 +39029,7 @@
         <v>6.2</v>
       </c>
       <c r="F1379" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1380">
@@ -39085,7 +39085,7 @@
         <v>3.8</v>
       </c>
       <c r="F1381" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1382">
@@ -39113,7 +39113,7 @@
         <v>3.4</v>
       </c>
       <c r="F1382" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1383">
@@ -39141,7 +39141,7 @@
         <v>3</v>
       </c>
       <c r="F1383" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1384">
@@ -39169,7 +39169,7 @@
         <v>2.9</v>
       </c>
       <c r="F1384" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1385">
@@ -39197,7 +39197,7 @@
         <v>2.8</v>
       </c>
       <c r="F1385" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1386">
@@ -39250,7 +39250,7 @@
         </is>
       </c>
       <c r="E1387" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1387" t="n">
         <v>50.8</v>
@@ -39337,7 +39337,7 @@
         <v>2.3</v>
       </c>
       <c r="F1390" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1391">
@@ -39365,7 +39365,7 @@
         <v>2.2</v>
       </c>
       <c r="F1391" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1392">
@@ -39393,7 +39393,7 @@
         <v>2.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1393">
@@ -39421,7 +39421,7 @@
         <v>2</v>
       </c>
       <c r="F1393" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1394">
@@ -39449,7 +39449,7 @@
         <v>2</v>
       </c>
       <c r="F1394" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1395">
@@ -39505,7 +39505,7 @@
         <v>1.8</v>
       </c>
       <c r="F1396" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1397">
@@ -39533,7 +39533,7 @@
         <v>1.7</v>
       </c>
       <c r="F1397" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1398">
@@ -39558,10 +39558,10 @@
         </is>
       </c>
       <c r="E1398" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1398" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1399">
@@ -39614,10 +39614,10 @@
         </is>
       </c>
       <c r="E1400" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1400" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1401">
@@ -39673,7 +39673,7 @@
         <v>1.4</v>
       </c>
       <c r="F1402" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1403">
@@ -39701,7 +39701,7 @@
         <v>1.3</v>
       </c>
       <c r="F1403" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1404">
@@ -39757,7 +39757,7 @@
         <v>1.3</v>
       </c>
       <c r="F1405" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1406">
@@ -39785,7 +39785,7 @@
         <v>1.2</v>
       </c>
       <c r="F1406" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1407">
@@ -39813,7 +39813,7 @@
         <v>1.2</v>
       </c>
       <c r="F1407" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1408">
@@ -39925,7 +39925,7 @@
         <v>0.9</v>
       </c>
       <c r="F1411" t="n">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>0.9</v>
       </c>
       <c r="F1412" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>0.9</v>
       </c>
       <c r="F1413" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1414">
@@ -40009,7 +40009,7 @@
         <v>0.8</v>
       </c>
       <c r="F1414" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1415">
@@ -40065,7 +40065,7 @@
         <v>0.8</v>
       </c>
       <c r="F1416" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1417">
@@ -40121,7 +40121,7 @@
         <v>0.7</v>
       </c>
       <c r="F1418" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1419">
@@ -40205,7 +40205,7 @@
         <v>0.6</v>
       </c>
       <c r="F1421" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1422">
@@ -40289,7 +40289,7 @@
         <v>6.3</v>
       </c>
       <c r="F1424" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1425">
@@ -40317,7 +40317,7 @@
         <v>4</v>
       </c>
       <c r="F1425" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1426">
@@ -40373,7 +40373,7 @@
         <v>3.3</v>
       </c>
       <c r="F1427" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1428">
@@ -40398,10 +40398,10 @@
         </is>
       </c>
       <c r="E1428" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1428" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1429">
@@ -40426,10 +40426,10 @@
         </is>
       </c>
       <c r="E1429" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F1429" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1430">
@@ -40457,7 +40457,7 @@
         <v>2.9</v>
       </c>
       <c r="F1430" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1431">
@@ -40485,7 +40485,7 @@
         <v>2.7</v>
       </c>
       <c r="F1431" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1432">
@@ -40569,7 +40569,7 @@
         <v>2.4</v>
       </c>
       <c r="F1434" t="n">
-        <v>52.3</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1435">
@@ -40594,10 +40594,10 @@
         </is>
       </c>
       <c r="E1435" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1436">
@@ -40613,19 +40613,19 @@
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1436" t="n">
         <v>2.1</v>
       </c>
       <c r="F1436" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1437">
@@ -40641,19 +40641,19 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1437" t="n">
         <v>2.1</v>
       </c>
       <c r="F1437" t="n">
-        <v>50.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1438">
@@ -40709,7 +40709,7 @@
         <v>2</v>
       </c>
       <c r="F1439" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1440">
@@ -40781,19 +40781,19 @@
       </c>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1442" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1442" t="n">
         <v>1.9</v>
       </c>
       <c r="F1442" t="n">
-        <v>50.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1443">
@@ -40809,19 +40809,19 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1443" t="n">
         <v>1.9</v>
       </c>
       <c r="F1443" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1444">
@@ -40877,7 +40877,7 @@
         <v>1.6</v>
       </c>
       <c r="F1445" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1446">
@@ -40905,7 +40905,7 @@
         <v>1.5</v>
       </c>
       <c r="F1446" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1447">
@@ -40933,7 +40933,7 @@
         <v>1.4</v>
       </c>
       <c r="F1447" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1448">
@@ -40986,10 +40986,10 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F1449" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1450">
@@ -41005,19 +41005,19 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1450" t="n">
         <v>1.1</v>
       </c>
       <c r="F1450" t="n">
-        <v>47.3</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="1451">
@@ -41033,19 +41033,19 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1451" t="n">
         <v>1.1</v>
       </c>
       <c r="F1451" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1452">
@@ -41061,19 +41061,19 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1452" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F1452" t="n">
-        <v>41.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1453">
@@ -41101,7 +41101,7 @@
         <v>1</v>
       </c>
       <c r="F1453" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1454">
@@ -41129,7 +41129,7 @@
         <v>1</v>
       </c>
       <c r="F1454" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1455">
@@ -41157,7 +41157,7 @@
         <v>0.8</v>
       </c>
       <c r="F1455" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1456">
@@ -41185,7 +41185,7 @@
         <v>0.8</v>
       </c>
       <c r="F1456" t="n">
-        <v>44.9</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1457">
@@ -41213,7 +41213,7 @@
         <v>0.8</v>
       </c>
       <c r="F1457" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="1458">
@@ -41238,7 +41238,7 @@
         </is>
       </c>
       <c r="E1458" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F1458" t="n">
         <v>45.5</v>
@@ -41269,7 +41269,7 @@
         <v>0.6</v>
       </c>
       <c r="F1459" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1460">
@@ -41297,7 +41297,7 @@
         <v>0.6</v>
       </c>
       <c r="F1460" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1461">
@@ -41325,7 +41325,7 @@
         <v>0.6</v>
       </c>
       <c r="F1461" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1462">
@@ -41353,7 +41353,7 @@
         <v>0.5</v>
       </c>
       <c r="F1462" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1463">
@@ -41381,7 +41381,7 @@
         <v>0.5</v>
       </c>
       <c r="F1463" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1464">
@@ -41406,10 +41406,10 @@
         </is>
       </c>
       <c r="E1464" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F1464" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1465">
@@ -41437,7 +41437,7 @@
         <v>0.4</v>
       </c>
       <c r="F1465" t="n">
-        <v>42.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1466">
@@ -41462,10 +41462,10 @@
         </is>
       </c>
       <c r="E1466" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="F1466" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1467">
@@ -41490,7 +41490,7 @@
         </is>
       </c>
       <c r="E1467" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F1467" t="n">
         <v>41.7</v>
@@ -41521,7 +41521,7 @@
         <v>5.8</v>
       </c>
       <c r="F1468" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1469">
@@ -41546,10 +41546,10 @@
         </is>
       </c>
       <c r="E1469" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F1469" t="n">
-        <v>48</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1470">
@@ -41577,7 +41577,7 @@
         <v>4.3</v>
       </c>
       <c r="F1470" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1471">
@@ -41593,19 +41593,19 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1471" t="n">
         <v>4</v>
       </c>
       <c r="F1471" t="n">
-        <v>47.1</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1472">
@@ -41621,19 +41621,19 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1472" t="n">
         <v>3.9</v>
       </c>
       <c r="F1472" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1473">
@@ -41661,7 +41661,7 @@
         <v>3.9</v>
       </c>
       <c r="F1473" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1474">
@@ -41677,19 +41677,19 @@
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1474" t="n">
         <v>3.4</v>
       </c>
       <c r="F1474" t="n">
-        <v>41.5</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="1475">
@@ -41705,19 +41705,19 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1475" t="n">
         <v>3.4</v>
       </c>
       <c r="F1475" t="n">
-        <v>28.1</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1476">
@@ -41742,10 +41742,10 @@
         </is>
       </c>
       <c r="E1476" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F1476" t="n">
-        <v>48.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1477">
@@ -41770,10 +41770,10 @@
         </is>
       </c>
       <c r="E1477" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1477" t="n">
-        <v>52.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1478">
@@ -41789,19 +41789,19 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1478" t="n">
         <v>2.3</v>
       </c>
       <c r="F1478" t="n">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1479">
@@ -41817,19 +41817,19 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1479" t="n">
         <v>2.3</v>
       </c>
       <c r="F1479" t="n">
-        <v>45.3</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1480">
@@ -41857,7 +41857,7 @@
         <v>2.3</v>
       </c>
       <c r="F1480" t="n">
-        <v>41.9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1481">
@@ -41885,7 +41885,7 @@
         <v>1.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>53.3</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="1482">
@@ -41913,7 +41913,7 @@
         <v>1.9</v>
       </c>
       <c r="F1482" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="1483">
@@ -41938,10 +41938,10 @@
         </is>
       </c>
       <c r="E1483" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1483" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1484">
@@ -41969,7 +41969,7 @@
         <v>1.8</v>
       </c>
       <c r="F1484" t="n">
-        <v>47.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1485">
@@ -42025,7 +42025,7 @@
         <v>1.6</v>
       </c>
       <c r="F1486" t="n">
-        <v>42</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1487">
@@ -42041,19 +42041,19 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1487" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1487" t="n">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1488">
@@ -42069,19 +42069,19 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1488" t="n">
         <v>1.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>47.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1489">
@@ -42097,19 +42097,19 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1489" t="n">
         <v>1.5</v>
       </c>
       <c r="F1489" t="n">
-        <v>35.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1490">
@@ -42125,19 +42125,19 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1490" t="n">
         <v>1.4</v>
       </c>
       <c r="F1490" t="n">
-        <v>39.1</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="1491">
@@ -42153,19 +42153,19 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1491" t="n">
         <v>1.4</v>
       </c>
       <c r="F1491" t="n">
-        <v>50.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="1492">
@@ -42193,7 +42193,7 @@
         <v>1.4</v>
       </c>
       <c r="F1492" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="1493">
@@ -42209,19 +42209,19 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1493" t="n">
         <v>1.3</v>
       </c>
       <c r="F1493" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1494">
@@ -42237,19 +42237,19 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1494" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1494" t="n">
-        <v>49.1</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="1495">
@@ -42265,19 +42265,19 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1495" t="n">
         <v>1.2</v>
       </c>
       <c r="F1495" t="n">
-        <v>37.8</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="1496">
@@ -42305,7 +42305,7 @@
         <v>1</v>
       </c>
       <c r="F1496" t="n">
-        <v>53.6</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1497">
@@ -42321,19 +42321,19 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1497" t="n">
         <v>0.8</v>
       </c>
       <c r="F1497" t="n">
-        <v>47.2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1498">
@@ -42349,19 +42349,19 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1498" t="n">
         <v>0.8</v>
       </c>
       <c r="F1498" t="n">
-        <v>56.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>0.8</v>
       </c>
       <c r="F1499" t="n">
-        <v>38.8</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>0.7</v>
       </c>
       <c r="F1500" t="n">
-        <v>46.1</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1501">
@@ -42445,7 +42445,7 @@
         <v>0.6</v>
       </c>
       <c r="F1501" t="n">
-        <v>62.1</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>0.5</v>
       </c>
       <c r="F1502" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="1503">
@@ -42498,7 +42498,7 @@
         </is>
       </c>
       <c r="E1503" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F1503" t="n">
         <v>44.3</v>
@@ -42529,7 +42529,7 @@
         <v>0.4</v>
       </c>
       <c r="F1504" t="n">
-        <v>30.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="1505">
@@ -42545,19 +42545,19 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1505" t="n">
         <v>0.4</v>
       </c>
       <c r="F1505" t="n">
-        <v>40.4</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="1506">
@@ -42573,19 +42573,19 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1506" t="n">
         <v>0.4</v>
       </c>
       <c r="F1506" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1507">
@@ -42601,19 +42601,19 @@
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1507" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F1507" t="n">
-        <v>71.3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1508">
@@ -42797,12 +42797,12 @@
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1514" t="n">
@@ -42825,19 +42825,19 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1515" t="n">
         <v>3.5</v>
       </c>
       <c r="F1515" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1516">
@@ -42853,19 +42853,19 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1516" t="n">
         <v>3.5</v>
       </c>
       <c r="F1516" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1517" t="n">
         <v>3.5</v>
       </c>
       <c r="F1517" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1518">
@@ -42909,19 +42909,19 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1518" t="n">
         <v>3.5</v>
       </c>
       <c r="F1518" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>3.5</v>
       </c>
       <c r="F1519" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1520">
@@ -42965,19 +42965,19 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1520" t="n">
         <v>3.5</v>
       </c>
       <c r="F1520" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1521">
@@ -42993,19 +42993,19 @@
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1521" t="n">
         <v>3.5</v>
       </c>
       <c r="F1521" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1522">
@@ -43021,19 +43021,19 @@
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1522" t="n">
         <v>3.5</v>
       </c>
       <c r="F1522" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1523">
@@ -43049,12 +43049,12 @@
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1523" t="n">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -725,7 +725,7 @@
         <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -753,7 +753,7 @@
         <v>13.8</v>
       </c>
       <c r="F12" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="13">
@@ -5753,19 +5753,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E191" t="n">
         <v>4.2</v>
       </c>
       <c r="F191" t="n">
-        <v>53.9</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="192">
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>4.2</v>
       </c>
       <c r="F192" t="n">
-        <v>44.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="193">
@@ -9253,19 +9253,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>11</v>
       </c>
       <c r="F316" t="n">
-        <v>46.4</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="317">
@@ -9281,19 +9281,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E317" t="n">
         <v>11</v>
       </c>
       <c r="F317" t="n">
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="318">
@@ -9673,19 +9673,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E331" t="n">
         <v>5.2</v>
       </c>
       <c r="F331" t="n">
-        <v>44.8</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="332">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E332" t="n">
         <v>5.2</v>
       </c>
       <c r="F332" t="n">
-        <v>54.3</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="333">
@@ -9841,19 +9841,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E337" t="n">
         <v>4.3</v>
       </c>
       <c r="F337" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="338">
@@ -9869,19 +9869,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E338" t="n">
         <v>4.3</v>
       </c>
       <c r="F338" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="339">
@@ -12725,19 +12725,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E440" t="n">
         <v>4.4</v>
       </c>
       <c r="F440" t="n">
-        <v>48</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="441">
@@ -12753,19 +12753,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E441" t="n">
         <v>4.4</v>
       </c>
       <c r="F441" t="n">
-        <v>52.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="442">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -12793,7 +12793,7 @@
         <v>4.2</v>
       </c>
       <c r="F442" t="n">
-        <v>51.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="443">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -12821,7 +12821,7 @@
         <v>4.2</v>
       </c>
       <c r="F443" t="n">
-        <v>45.6</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="444">
@@ -13425,19 +13425,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E465" t="n">
         <v>12.2</v>
       </c>
       <c r="F465" t="n">
-        <v>46.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="466">
@@ -13453,19 +13453,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E466" t="n">
         <v>12.2</v>
       </c>
       <c r="F466" t="n">
-        <v>54</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="467">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -13969,7 +13969,7 @@
         <v>5.4</v>
       </c>
       <c r="F484" t="n">
-        <v>45.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="485">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -13997,7 +13997,7 @@
         <v>5.4</v>
       </c>
       <c r="F485" t="n">
-        <v>50.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="486">
@@ -14349,12 +14349,12 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -14937,19 +14937,19 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E519" t="n">
         <v>10.8</v>
       </c>
       <c r="F519" t="n">
-        <v>50.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="520">
@@ -14965,19 +14965,19 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E520" t="n">
         <v>10.8</v>
       </c>
       <c r="F520" t="n">
-        <v>53.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="521">
@@ -15637,19 +15637,19 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E544" t="n">
         <v>3.7</v>
       </c>
       <c r="F544" t="n">
-        <v>52.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="545">
@@ -15665,19 +15665,19 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E545" t="n">
         <v>3.7</v>
       </c>
       <c r="F545" t="n">
-        <v>49.1</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="546">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E546" t="n">
@@ -18381,19 +18381,19 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E642" t="n">
         <v>3.8</v>
       </c>
       <c r="F642" t="n">
-        <v>49.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="643">
@@ -18409,19 +18409,19 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E643" t="n">
         <v>3.8</v>
       </c>
       <c r="F643" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="644">
@@ -19921,12 +19921,12 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E697" t="n">
@@ -19949,19 +19949,19 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E698" t="n">
         <v>3.1</v>
       </c>
       <c r="F698" t="n">
-        <v>53.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="699">
@@ -19977,19 +19977,19 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E699" t="n">
         <v>3.1</v>
       </c>
       <c r="F699" t="n">
-        <v>50.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="700">
@@ -20369,19 +20369,19 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E713" t="n">
         <v>12.7</v>
       </c>
       <c r="F713" t="n">
-        <v>52.2</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="714">
@@ -20397,19 +20397,19 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E714" t="n">
         <v>12.7</v>
       </c>
       <c r="F714" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="715">
@@ -22049,19 +22049,19 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E773" t="n">
         <v>7.8</v>
       </c>
       <c r="F773" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="774">
@@ -22077,19 +22077,19 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E774" t="n">
         <v>7.8</v>
       </c>
       <c r="F774" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="775">
@@ -25073,19 +25073,19 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E881" t="n">
         <v>6</v>
       </c>
       <c r="F881" t="n">
-        <v>46.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="882">
@@ -25101,19 +25101,19 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E882" t="n">
         <v>6</v>
       </c>
       <c r="F882" t="n">
-        <v>50.4</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="883">
@@ -25409,19 +25409,19 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E893" t="n">
         <v>3.6</v>
       </c>
       <c r="F893" t="n">
-        <v>52.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="894">
@@ -25437,19 +25437,19 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E894" t="n">
         <v>3.6</v>
       </c>
       <c r="F894" t="n">
-        <v>48.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="895">
@@ -30729,19 +30729,19 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1083" t="n">
         <v>6.3</v>
       </c>
       <c r="F1083" t="n">
-        <v>51.7</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1084">
@@ -30757,19 +30757,19 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1084" t="n">
         <v>6.3</v>
       </c>
       <c r="F1084" t="n">
-        <v>43.7</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1085">
@@ -30925,19 +30925,19 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1090" t="n">
         <v>4.7</v>
       </c>
       <c r="F1090" t="n">
-        <v>44.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1091">
@@ -30953,19 +30953,19 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1091" t="n">
         <v>4.7</v>
       </c>
       <c r="F1091" t="n">
-        <v>50.5</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1092">
@@ -32101,19 +32101,19 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1132" t="n">
         <v>6.8</v>
       </c>
       <c r="F1132" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1133">
@@ -32129,19 +32129,19 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1133" t="n">
         <v>6.8</v>
       </c>
       <c r="F1133" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1134">
@@ -32437,19 +32437,19 @@
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1144" t="n">
         <v>3.6</v>
       </c>
       <c r="F1144" t="n">
-        <v>48.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1145">
@@ -32465,19 +32465,19 @@
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1145" t="n">
         <v>3.6</v>
       </c>
       <c r="F1145" t="n">
-        <v>45.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1146">
@@ -32493,19 +32493,19 @@
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1146" t="n">
         <v>3.6</v>
       </c>
       <c r="F1146" t="n">
-        <v>46.7</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1147">
@@ -33473,19 +33473,19 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1181" t="n">
         <v>6</v>
       </c>
       <c r="F1181" t="n">
-        <v>54</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1182">
@@ -33501,19 +33501,19 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1182" t="n">
         <v>6</v>
       </c>
       <c r="F1182" t="n">
-        <v>44.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1183">
@@ -33585,19 +33585,19 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1185" t="n">
         <v>5.5</v>
       </c>
       <c r="F1185" t="n">
-        <v>54.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1186">
@@ -33613,19 +33613,19 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1186" t="n">
         <v>5.5</v>
       </c>
       <c r="F1186" t="n">
-        <v>45.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1187">
@@ -33641,19 +33641,19 @@
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1187" t="n">
         <v>5.5</v>
       </c>
       <c r="F1187" t="n">
-        <v>49.1</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="1188">
@@ -34073,7 +34073,7 @@
         <v>5.7</v>
       </c>
       <c r="F1202" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1203">
@@ -34434,7 +34434,7 @@
         </is>
       </c>
       <c r="E1215" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F1215" t="n">
         <v>50.5</v>
@@ -34549,7 +34549,7 @@
         <v>1.8</v>
       </c>
       <c r="F1219" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1220">
@@ -34633,7 +34633,7 @@
         <v>1.6</v>
       </c>
       <c r="F1222" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1223">
@@ -34789,19 +34789,19 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1228" t="n">
         <v>1.2</v>
       </c>
       <c r="F1228" t="n">
-        <v>46.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1229">
@@ -34817,19 +34817,19 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1229" t="n">
         <v>1.2</v>
       </c>
       <c r="F1229" t="n">
-        <v>43.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1230">
@@ -34885,7 +34885,7 @@
         <v>1.1</v>
       </c>
       <c r="F1231" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1232">
@@ -34941,7 +34941,7 @@
         <v>1.1</v>
       </c>
       <c r="F1233" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1234">
@@ -35025,7 +35025,7 @@
         <v>1.1</v>
       </c>
       <c r="F1236" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1237">
@@ -35109,7 +35109,7 @@
         <v>0.9</v>
       </c>
       <c r="F1239" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1240">
@@ -35165,7 +35165,7 @@
         <v>0.8</v>
       </c>
       <c r="F1241" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1242">
@@ -35221,7 +35221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1243" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1244">
@@ -35249,7 +35249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1244" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1245">
@@ -35305,7 +35305,7 @@
         <v>5.9</v>
       </c>
       <c r="F1246" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1247">
@@ -35333,7 +35333,7 @@
         <v>4.3</v>
       </c>
       <c r="F1247" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1248">
@@ -35389,7 +35389,7 @@
         <v>4</v>
       </c>
       <c r="F1249" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1250">
@@ -35414,10 +35414,10 @@
         </is>
       </c>
       <c r="E1250" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F1250" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1251">
@@ -35442,10 +35442,10 @@
         </is>
       </c>
       <c r="E1251" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1251" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1252">
@@ -35473,7 +35473,7 @@
         <v>3</v>
       </c>
       <c r="F1252" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1253">
@@ -35489,19 +35489,19 @@
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1253" t="n">
         <v>2.9</v>
       </c>
       <c r="F1253" t="n">
-        <v>47.4</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1254">
@@ -35517,19 +35517,19 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1254" t="n">
         <v>2.9</v>
       </c>
       <c r="F1254" t="n">
-        <v>49.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1255">
@@ -35557,7 +35557,7 @@
         <v>2.8</v>
       </c>
       <c r="F1255" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1256">
@@ -35573,19 +35573,19 @@
       </c>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1256" t="n">
         <v>2.8</v>
       </c>
       <c r="F1256" t="n">
-        <v>48.7</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1257">
@@ -35601,19 +35601,19 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1257" t="n">
         <v>2.8</v>
       </c>
       <c r="F1257" t="n">
-        <v>43.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1258">
@@ -35641,7 +35641,7 @@
         <v>2.4</v>
       </c>
       <c r="F1258" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1259">
@@ -35753,7 +35753,7 @@
         <v>1.9</v>
       </c>
       <c r="F1262" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1263">
@@ -35781,7 +35781,7 @@
         <v>1.9</v>
       </c>
       <c r="F1263" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1264">
@@ -35837,7 +35837,7 @@
         <v>1.8</v>
       </c>
       <c r="F1265" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1266">
@@ -35865,7 +35865,7 @@
         <v>1.7</v>
       </c>
       <c r="F1266" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1267">
@@ -35893,7 +35893,7 @@
         <v>1.7</v>
       </c>
       <c r="F1267" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1268">
@@ -35937,19 +35937,19 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1269" t="n">
         <v>1.4</v>
       </c>
       <c r="F1269" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1270">
@@ -35965,19 +35965,19 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1270" t="n">
         <v>1.4</v>
       </c>
       <c r="F1270" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1271">
@@ -36049,19 +36049,19 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1273" t="n">
         <v>1.2</v>
       </c>
       <c r="F1273" t="n">
-        <v>44.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1274">
@@ -36077,19 +36077,19 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1274" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1274" t="n">
         <v>1.2</v>
       </c>
       <c r="F1274" t="n">
-        <v>47.9</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1275">
@@ -36117,7 +36117,7 @@
         <v>1.1</v>
       </c>
       <c r="F1275" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1276">
@@ -36142,10 +36142,10 @@
         </is>
       </c>
       <c r="E1276" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1276" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1277">
@@ -36173,7 +36173,7 @@
         <v>1</v>
       </c>
       <c r="F1277" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1278">
@@ -36229,7 +36229,7 @@
         <v>1</v>
       </c>
       <c r="F1279" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1280">
@@ -36257,7 +36257,7 @@
         <v>0.9</v>
       </c>
       <c r="F1280" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1281">
@@ -36313,7 +36313,7 @@
         <v>0.8</v>
       </c>
       <c r="F1282" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1283">
@@ -36341,7 +36341,7 @@
         <v>0.7</v>
       </c>
       <c r="F1283" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1284">
@@ -36369,7 +36369,7 @@
         <v>0.7</v>
       </c>
       <c r="F1284" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1285">
@@ -36397,7 +36397,7 @@
         <v>0.6</v>
       </c>
       <c r="F1285" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1286">
@@ -36453,7 +36453,7 @@
         <v>0.5</v>
       </c>
       <c r="F1287" t="n">
-        <v>55.4</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="1288">
@@ -36481,7 +36481,7 @@
         <v>0.5</v>
       </c>
       <c r="F1288" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1289">
@@ -36509,7 +36509,7 @@
         <v>0.3</v>
       </c>
       <c r="F1289" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1290">
@@ -36565,7 +36565,7 @@
         <v>4.9</v>
       </c>
       <c r="F1291" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1292">
@@ -36621,7 +36621,7 @@
         <v>4.1</v>
       </c>
       <c r="F1293" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1294">
@@ -36761,7 +36761,7 @@
         <v>2.8</v>
       </c>
       <c r="F1298" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1299">
@@ -36817,7 +36817,7 @@
         <v>2.4</v>
       </c>
       <c r="F1300" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1301">
@@ -36926,7 +36926,7 @@
         </is>
       </c>
       <c r="E1304" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F1304" t="n">
         <v>48.8</v>
@@ -36985,7 +36985,7 @@
         <v>1.8</v>
       </c>
       <c r="F1306" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1307">
@@ -37001,19 +37001,19 @@
       </c>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1307" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1307" t="n">
         <v>1.8</v>
       </c>
       <c r="F1307" t="n">
-        <v>45.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1308">
@@ -37029,19 +37029,19 @@
       </c>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1308" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1308" t="n">
         <v>1.8</v>
       </c>
       <c r="F1308" t="n">
-        <v>53.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1309">
@@ -37069,7 +37069,7 @@
         <v>1.7</v>
       </c>
       <c r="F1309" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1310">
@@ -37097,7 +37097,7 @@
         <v>1.7</v>
       </c>
       <c r="F1310" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1311">
@@ -37153,7 +37153,7 @@
         <v>1.6</v>
       </c>
       <c r="F1312" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1313">
@@ -37181,7 +37181,7 @@
         <v>1.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1314">
@@ -37237,7 +37237,7 @@
         <v>1.4</v>
       </c>
       <c r="F1315" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1316">
@@ -37265,7 +37265,7 @@
         <v>1.3</v>
       </c>
       <c r="F1316" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1317">
@@ -37349,7 +37349,7 @@
         <v>1.2</v>
       </c>
       <c r="F1319" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1320">
@@ -37405,7 +37405,7 @@
         <v>1.1</v>
       </c>
       <c r="F1321" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1322">
@@ -37461,7 +37461,7 @@
         <v>1</v>
       </c>
       <c r="F1323" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1324">
@@ -37489,7 +37489,7 @@
         <v>1</v>
       </c>
       <c r="F1324" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="1325">
@@ -37517,7 +37517,7 @@
         <v>1</v>
       </c>
       <c r="F1325" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1326">
@@ -37533,19 +37533,19 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1326" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1326" t="n">
         <v>0.8</v>
       </c>
       <c r="F1326" t="n">
-        <v>40.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1327">
@@ -37561,19 +37561,19 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1327" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1327" t="n">
         <v>0.8</v>
       </c>
       <c r="F1327" t="n">
-        <v>47</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1328">
@@ -37601,7 +37601,7 @@
         <v>0.7</v>
       </c>
       <c r="F1328" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1329">
@@ -37657,7 +37657,7 @@
         <v>0.6</v>
       </c>
       <c r="F1330" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1331">
@@ -37685,7 +37685,7 @@
         <v>0.6</v>
       </c>
       <c r="F1331" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1332">
@@ -37713,7 +37713,7 @@
         <v>0.5</v>
       </c>
       <c r="F1332" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1333">
@@ -37766,7 +37766,7 @@
         </is>
       </c>
       <c r="E1334" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F1334" t="n">
         <v>48.6</v>
@@ -37881,7 +37881,7 @@
         <v>3.4</v>
       </c>
       <c r="F1338" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1339">
@@ -37937,7 +37937,7 @@
         <v>2.9</v>
       </c>
       <c r="F1340" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1341">
@@ -38021,7 +38021,7 @@
         <v>2.6</v>
       </c>
       <c r="F1343" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1344">
@@ -38245,7 +38245,7 @@
         <v>1.8</v>
       </c>
       <c r="F1351" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1352">
@@ -38289,7 +38289,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1353" t="inlineStr">
@@ -38301,7 +38301,7 @@
         <v>1.6</v>
       </c>
       <c r="F1353" t="n">
-        <v>49.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1354">
@@ -38317,7 +38317,7 @@
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1354" t="inlineStr">
@@ -38329,7 +38329,7 @@
         <v>1.6</v>
       </c>
       <c r="F1354" t="n">
-        <v>53.9</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1355">
@@ -38385,7 +38385,7 @@
         <v>1.6</v>
       </c>
       <c r="F1356" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1357">
@@ -38413,7 +38413,7 @@
         <v>1.5</v>
       </c>
       <c r="F1357" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1358">
@@ -38469,7 +38469,7 @@
         <v>1.3</v>
       </c>
       <c r="F1359" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1360">
@@ -38497,7 +38497,7 @@
         <v>1.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1361">
@@ -38553,7 +38553,7 @@
         <v>1.1</v>
       </c>
       <c r="F1362" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1363">
@@ -38721,7 +38721,7 @@
         <v>1</v>
       </c>
       <c r="F1368" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1369">
@@ -38737,19 +38737,19 @@
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1369" t="n">
         <v>1</v>
       </c>
       <c r="F1369" t="n">
-        <v>39.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1370">
@@ -38765,19 +38765,19 @@
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1370" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1370" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F1370" t="n">
-        <v>48.5</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1371">
@@ -38805,7 +38805,7 @@
         <v>0.9</v>
       </c>
       <c r="F1371" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1372">
@@ -38830,7 +38830,7 @@
         </is>
       </c>
       <c r="E1372" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1372" t="n">
         <v>47.5</v>
@@ -38861,7 +38861,7 @@
         <v>0.8</v>
       </c>
       <c r="F1373" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1374">
@@ -38889,7 +38889,7 @@
         <v>0.7</v>
       </c>
       <c r="F1374" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1375">
@@ -38917,7 +38917,7 @@
         <v>0.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1376">
@@ -38973,7 +38973,7 @@
         <v>0.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1378">
@@ -39085,7 +39085,7 @@
         <v>3.8</v>
       </c>
       <c r="F1381" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1382">
@@ -39141,7 +39141,7 @@
         <v>3</v>
       </c>
       <c r="F1383" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1384">
@@ -39169,7 +39169,7 @@
         <v>2.9</v>
       </c>
       <c r="F1384" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1385">
@@ -39197,7 +39197,7 @@
         <v>2.8</v>
       </c>
       <c r="F1385" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1386">
@@ -39253,7 +39253,7 @@
         <v>2.6</v>
       </c>
       <c r="F1387" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1388">
@@ -39309,7 +39309,7 @@
         <v>2.3</v>
       </c>
       <c r="F1389" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1390">
@@ -39325,19 +39325,19 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1390" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1390" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1390" t="n">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1391">
@@ -39353,19 +39353,19 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1391" t="n">
         <v>2.2</v>
       </c>
       <c r="F1391" t="n">
-        <v>47.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1392">
@@ -39393,7 +39393,7 @@
         <v>2.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1393">
@@ -39449,7 +39449,7 @@
         <v>2</v>
       </c>
       <c r="F1394" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1395">
@@ -39533,7 +39533,7 @@
         <v>1.7</v>
       </c>
       <c r="F1397" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1398">
@@ -39617,7 +39617,7 @@
         <v>1.6</v>
       </c>
       <c r="F1400" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1401">
@@ -39645,7 +39645,7 @@
         <v>1.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1402">
@@ -39673,7 +39673,7 @@
         <v>1.4</v>
       </c>
       <c r="F1402" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1403">
@@ -39701,7 +39701,7 @@
         <v>1.3</v>
       </c>
       <c r="F1403" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1404">
@@ -39773,19 +39773,19 @@
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1406" t="n">
         <v>1.2</v>
       </c>
       <c r="F1406" t="n">
-        <v>44.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1407">
@@ -39801,19 +39801,19 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1407" t="n">
         <v>1.2</v>
       </c>
       <c r="F1407" t="n">
-        <v>51.7</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1408">
@@ -39841,7 +39841,7 @@
         <v>1.2</v>
       </c>
       <c r="F1408" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1409">
@@ -39869,7 +39869,7 @@
         <v>1</v>
       </c>
       <c r="F1409" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1410">
@@ -39897,7 +39897,7 @@
         <v>1</v>
       </c>
       <c r="F1410" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1411">
@@ -39953,7 +39953,7 @@
         <v>0.9</v>
       </c>
       <c r="F1412" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>0.9</v>
       </c>
       <c r="F1413" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1414">
@@ -40009,7 +40009,7 @@
         <v>0.8</v>
       </c>
       <c r="F1414" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1415">
@@ -40037,7 +40037,7 @@
         <v>0.8</v>
       </c>
       <c r="F1415" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1416">
@@ -40065,7 +40065,7 @@
         <v>0.8</v>
       </c>
       <c r="F1416" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1417">
@@ -40093,7 +40093,7 @@
         <v>0.8</v>
       </c>
       <c r="F1417" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1418">
@@ -40121,7 +40121,7 @@
         <v>0.7</v>
       </c>
       <c r="F1418" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1419">
@@ -40149,7 +40149,7 @@
         <v>0.7</v>
       </c>
       <c r="F1419" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1420">
@@ -40205,7 +40205,7 @@
         <v>0.6</v>
       </c>
       <c r="F1421" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1422">
@@ -40261,7 +40261,7 @@
         <v>6.6</v>
       </c>
       <c r="F1423" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1424">
@@ -40286,7 +40286,7 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F1424" t="n">
         <v>46.2</v>
@@ -40317,7 +40317,7 @@
         <v>4</v>
       </c>
       <c r="F1425" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1426">
@@ -40345,7 +40345,7 @@
         <v>3.5</v>
       </c>
       <c r="F1426" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1427">
@@ -40401,7 +40401,7 @@
         <v>3.1</v>
       </c>
       <c r="F1428" t="n">
-        <v>48.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1429">
@@ -40429,7 +40429,7 @@
         <v>3</v>
       </c>
       <c r="F1429" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1430">
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="E1430" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F1430" t="n">
         <v>50.7</v>
@@ -40485,7 +40485,7 @@
         <v>2.7</v>
       </c>
       <c r="F1431" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1432">
@@ -40513,7 +40513,7 @@
         <v>2.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1433">
@@ -40538,10 +40538,10 @@
         </is>
       </c>
       <c r="E1433" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F1433" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1434">
@@ -40597,7 +40597,7 @@
         <v>2.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1436">
@@ -40625,7 +40625,7 @@
         <v>2.1</v>
       </c>
       <c r="F1436" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1437">
@@ -40681,7 +40681,7 @@
         <v>2.1</v>
       </c>
       <c r="F1438" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1439">
@@ -40709,7 +40709,7 @@
         <v>2</v>
       </c>
       <c r="F1439" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1440">
@@ -40737,7 +40737,7 @@
         <v>2</v>
       </c>
       <c r="F1440" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1441">
@@ -40753,19 +40753,19 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1441" t="n">
         <v>1.9</v>
       </c>
       <c r="F1441" t="n">
-        <v>51.7</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1442">
@@ -40809,19 +40809,19 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1443" t="n">
         <v>1.9</v>
       </c>
       <c r="F1443" t="n">
-        <v>50.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1444">
@@ -40849,7 +40849,7 @@
         <v>1.6</v>
       </c>
       <c r="F1444" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1445">
@@ -40905,7 +40905,7 @@
         <v>1.5</v>
       </c>
       <c r="F1446" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1447">
@@ -40933,7 +40933,7 @@
         <v>1.4</v>
       </c>
       <c r="F1447" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1448">
@@ -40961,7 +40961,7 @@
         <v>1.3</v>
       </c>
       <c r="F1448" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1449">
@@ -40986,10 +40986,10 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1449" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1450">
@@ -41017,7 +41017,7 @@
         <v>1.1</v>
       </c>
       <c r="F1450" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1451">
@@ -41045,7 +41045,7 @@
         <v>1.1</v>
       </c>
       <c r="F1451" t="n">
-        <v>46.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1452">
@@ -41070,7 +41070,7 @@
         </is>
       </c>
       <c r="E1452" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1452" t="n">
         <v>46.9</v>
@@ -41101,7 +41101,7 @@
         <v>1</v>
       </c>
       <c r="F1453" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1454">
@@ -41129,7 +41129,7 @@
         <v>1</v>
       </c>
       <c r="F1454" t="n">
-        <v>45.4</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1455">
@@ -41157,7 +41157,7 @@
         <v>0.8</v>
       </c>
       <c r="F1455" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1456">
@@ -41173,19 +41173,19 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1456" t="n">
         <v>0.8</v>
       </c>
       <c r="F1456" t="n">
-        <v>44.4</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1457">
@@ -41201,19 +41201,19 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1457" t="n">
         <v>0.8</v>
       </c>
       <c r="F1457" t="n">
-        <v>37.5</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1458">
@@ -41241,7 +41241,7 @@
         <v>0.6</v>
       </c>
       <c r="F1458" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1459">
@@ -41269,7 +41269,7 @@
         <v>0.6</v>
       </c>
       <c r="F1459" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1460">
@@ -41297,7 +41297,7 @@
         <v>0.6</v>
       </c>
       <c r="F1460" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1461">
@@ -41325,7 +41325,7 @@
         <v>0.6</v>
       </c>
       <c r="F1461" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1462">
@@ -41353,7 +41353,7 @@
         <v>0.5</v>
       </c>
       <c r="F1462" t="n">
-        <v>44.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1463">
@@ -41381,7 +41381,7 @@
         <v>0.5</v>
       </c>
       <c r="F1463" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="1464">
@@ -41409,7 +41409,7 @@
         <v>0.4</v>
       </c>
       <c r="F1464" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1465">
@@ -41437,7 +41437,7 @@
         <v>0.4</v>
       </c>
       <c r="F1465" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1466">
@@ -41462,10 +41462,10 @@
         </is>
       </c>
       <c r="E1466" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1467">
@@ -41493,7 +41493,7 @@
         <v>5.9</v>
       </c>
       <c r="F1467" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="1468">
@@ -41518,10 +41518,10 @@
         </is>
       </c>
       <c r="E1468" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F1468" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="1469">
@@ -41549,7 +41549,7 @@
         <v>5.5</v>
       </c>
       <c r="F1469" t="n">
-        <v>47.6</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1470">
@@ -41577,7 +41577,7 @@
         <v>4.3</v>
       </c>
       <c r="F1470" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1471">
@@ -41605,7 +41605,7 @@
         <v>4</v>
       </c>
       <c r="F1471" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1472">
@@ -41633,7 +41633,7 @@
         <v>3.9</v>
       </c>
       <c r="F1472" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1473">
@@ -41658,10 +41658,10 @@
         </is>
       </c>
       <c r="E1473" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F1473" t="n">
-        <v>44.8</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1474">
@@ -41677,19 +41677,19 @@
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1474" t="n">
         <v>3.4</v>
       </c>
       <c r="F1474" t="n">
-        <v>27.6</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="1475">
@@ -41705,19 +41705,19 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1475" t="n">
         <v>3.4</v>
       </c>
       <c r="F1475" t="n">
-        <v>41.9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1476">
@@ -41745,7 +41745,7 @@
         <v>2.9</v>
       </c>
       <c r="F1476" t="n">
-        <v>47.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1477">
@@ -41770,10 +41770,10 @@
         </is>
       </c>
       <c r="E1477" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>49.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1478">
@@ -41801,7 +41801,7 @@
         <v>2.3</v>
       </c>
       <c r="F1478" t="n">
-        <v>47.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1479">
@@ -41817,19 +41817,19 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1479" t="n">
         <v>2.3</v>
       </c>
       <c r="F1479" t="n">
-        <v>46.6</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="1480">
@@ -41845,19 +41845,19 @@
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1480" t="n">
         <v>2.3</v>
       </c>
       <c r="F1480" t="n">
-        <v>43</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1481">
@@ -41882,10 +41882,10 @@
         </is>
       </c>
       <c r="E1481" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1481" t="n">
-        <v>54.2</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="1482">
@@ -41910,10 +41910,10 @@
         </is>
       </c>
       <c r="E1482" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1482" t="n">
-        <v>39.1</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1483">
@@ -41929,19 +41929,19 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1483" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F1483" t="n">
-        <v>46.6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1484">
@@ -41957,19 +41957,19 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1484" t="n">
         <v>1.8</v>
       </c>
       <c r="F1484" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1485">
@@ -41985,19 +41985,19 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1485" t="n">
         <v>1.8</v>
       </c>
       <c r="F1485" t="n">
-        <v>45</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1486">
@@ -42022,7 +42022,7 @@
         </is>
       </c>
       <c r="E1486" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1486" t="n">
         <v>40.6</v>
@@ -42050,10 +42050,10 @@
         </is>
       </c>
       <c r="E1487" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1487" t="n">
-        <v>45.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1488">
@@ -42069,19 +42069,19 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1488" t="n">
         <v>1.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>49.3</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1489">
@@ -42097,19 +42097,19 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1489" t="n">
         <v>1.5</v>
       </c>
       <c r="F1489" t="n">
-        <v>50.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1490">
@@ -42125,19 +42125,19 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1490" t="n">
         <v>1.4</v>
       </c>
       <c r="F1490" t="n">
-        <v>35.9</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="1491">
@@ -42153,19 +42153,19 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1491" t="n">
         <v>1.4</v>
       </c>
       <c r="F1491" t="n">
-        <v>38.1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="1492">
@@ -42181,19 +42181,19 @@
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1492" t="n">
         <v>1.4</v>
       </c>
       <c r="F1492" t="n">
-        <v>25.9</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="1493">
@@ -42221,7 +42221,7 @@
         <v>1.3</v>
       </c>
       <c r="F1493" t="n">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1494">
@@ -42249,7 +42249,7 @@
         <v>1.3</v>
       </c>
       <c r="F1494" t="n">
-        <v>39.1</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="1495">
@@ -42305,7 +42305,7 @@
         <v>1</v>
       </c>
       <c r="F1496" t="n">
-        <v>50.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>0.8</v>
       </c>
       <c r="F1497" t="n">
-        <v>57</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>0.8</v>
       </c>
       <c r="F1498" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>0.8</v>
       </c>
       <c r="F1499" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>0.7</v>
       </c>
       <c r="F1500" t="n">
-        <v>44.9</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1501">
@@ -42442,10 +42442,10 @@
         </is>
       </c>
       <c r="E1501" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F1501" t="n">
-        <v>59.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>0.5</v>
       </c>
       <c r="F1502" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="1503">
@@ -42489,19 +42489,19 @@
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1503" t="n">
         <v>0.4</v>
       </c>
       <c r="F1503" t="n">
-        <v>44.3</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="1504">
@@ -42517,19 +42517,19 @@
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1504" t="n">
         <v>0.4</v>
       </c>
       <c r="F1504" t="n">
-        <v>34.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1505">
@@ -42545,19 +42545,19 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1505" t="n">
         <v>0.4</v>
       </c>
       <c r="F1505" t="n">
-        <v>58.9</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1506">
@@ -42573,19 +42573,19 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1506" t="n">
         <v>0.4</v>
       </c>
       <c r="F1506" t="n">
-        <v>38.6</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="1507">
@@ -42610,7 +42610,7 @@
         </is>
       </c>
       <c r="E1507" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1507" t="n">
         <v>39</v>
@@ -42669,7 +42669,7 @@
         <v>0.2</v>
       </c>
       <c r="F1509" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="1510">
@@ -42797,12 +42797,12 @@
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1514" t="n">
@@ -42825,19 +42825,19 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1515" t="n">
         <v>3.5</v>
       </c>
       <c r="F1515" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1516">
@@ -42853,19 +42853,19 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1516" t="n">
         <v>3.5</v>
       </c>
       <c r="F1516" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1517" t="n">
         <v>3.5</v>
       </c>
       <c r="F1517" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1518">
@@ -42909,19 +42909,19 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1518" t="n">
         <v>3.5</v>
       </c>
       <c r="F1518" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>3.5</v>
       </c>
       <c r="F1519" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1520">
@@ -42965,19 +42965,19 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1520" t="n">
         <v>3.5</v>
       </c>
       <c r="F1520" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1521">
@@ -42993,19 +42993,19 @@
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1521" t="n">
         <v>3.5</v>
       </c>
       <c r="F1521" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1522">
@@ -43021,7 +43021,7 @@
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
@@ -43049,19 +43049,19 @@
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1523" t="n">
         <v>3.5</v>
       </c>
       <c r="F1523" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="F3" t="n">
         <v>47.1</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
         <v>52.8</v>
@@ -557,7 +557,7 @@
         <v>21.8</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="F6" t="n">
         <v>48.4</v>
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="F7" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="8">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="F8" t="n">
         <v>47.6</v>
@@ -697,7 +697,7 @@
         <v>13.9</v>
       </c>
       <c r="F10" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +753,7 @@
         <v>13.4</v>
       </c>
       <c r="F12" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="13">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>50.7</v>
@@ -825,19 +825,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="16">
@@ -853,19 +853,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>12.2</v>
       </c>
       <c r="F16" t="n">
-        <v>54.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -1005,7 +1005,7 @@
         <v>9.9</v>
       </c>
       <c r="F21" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="22">
@@ -1077,19 +1077,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>48.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="25">
@@ -1105,19 +1105,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>49.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="26">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F26" t="n">
         <v>50.2</v>
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="28">
@@ -1257,7 +1257,7 @@
         <v>6.8</v>
       </c>
       <c r="F30" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="31">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F31" t="n">
         <v>48.2</v>
@@ -1301,19 +1301,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>5.9</v>
       </c>
       <c r="F32" t="n">
-        <v>52</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="33">
@@ -1329,19 +1329,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>5.9</v>
       </c>
       <c r="F33" t="n">
-        <v>46.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -1357,19 +1357,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="35">
@@ -1397,7 +1397,7 @@
         <v>5.6</v>
       </c>
       <c r="F35" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="36">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F36" t="n">
         <v>52.4</v>
@@ -1453,7 +1453,7 @@
         <v>5.2</v>
       </c>
       <c r="F37" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="38">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F38" t="n">
         <v>53.8</v>
@@ -1733,7 +1733,7 @@
         <v>3.4</v>
       </c>
       <c r="F47" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="48">
@@ -1761,7 +1761,7 @@
         <v>3.2</v>
       </c>
       <c r="F48" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="49">
@@ -1845,7 +1845,7 @@
         <v>1.8</v>
       </c>
       <c r="F51" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="52">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="F172" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="173">
@@ -5249,19 +5249,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E173" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="F173" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="174">
@@ -5753,19 +5753,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E191" t="n">
         <v>4.2</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="192">
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>4.2</v>
       </c>
       <c r="F192" t="n">
-        <v>44.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="193">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="F202" t="n">
         <v>50.1</v>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="F203" t="n">
         <v>46.7</v>
@@ -6129,7 +6129,7 @@
         <v>25.9</v>
       </c>
       <c r="F204" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="205">
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="F205" t="n">
         <v>52.1</v>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="207">
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="F208" t="n">
         <v>49</v>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6269,7 +6269,7 @@
         <v>14.2</v>
       </c>
       <c r="F209" t="n">
-        <v>46.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="210">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6297,7 +6297,7 @@
         <v>14.2</v>
       </c>
       <c r="F210" t="n">
-        <v>51.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="211">
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="F212" t="n">
         <v>53.3</v>
@@ -6369,19 +6369,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E213" t="n">
         <v>12.6</v>
       </c>
       <c r="F213" t="n">
-        <v>50.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="214">
@@ -6397,19 +6397,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E214" t="n">
         <v>12.5</v>
       </c>
       <c r="F214" t="n">
-        <v>52.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="215">
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="F216" t="n">
         <v>54.1</v>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F217" t="n">
         <v>52.3</v>
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F218" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="219">
@@ -6549,7 +6549,7 @@
         <v>10.1</v>
       </c>
       <c r="F219" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="220">
@@ -6605,7 +6605,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F221" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="222">
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F222" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="223">
@@ -6649,19 +6649,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E223" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="F223" t="n">
-        <v>52.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="224">
@@ -6677,19 +6677,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E224" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="F224" t="n">
-        <v>45.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="225">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F225" t="n">
         <v>44.9</v>
@@ -6941,7 +6941,7 @@
         <v>5.5</v>
       </c>
       <c r="F233" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="234">
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F235" t="n">
         <v>45.4</v>
@@ -7013,19 +7013,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E236" t="n">
         <v>4.5</v>
       </c>
       <c r="F236" t="n">
-        <v>50.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="237">
@@ -7041,19 +7041,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F237" t="n">
-        <v>49.1</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="238">
@@ -7069,19 +7069,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E238" t="n">
         <v>4.4</v>
       </c>
       <c r="F238" t="n">
-        <v>48.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="239">
@@ -7097,19 +7097,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E239" t="n">
         <v>4.4</v>
       </c>
       <c r="F239" t="n">
-        <v>47.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="240">
@@ -7125,19 +7125,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E240" t="n">
         <v>4.4</v>
       </c>
       <c r="F240" t="n">
-        <v>39.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="241">
@@ -7193,7 +7193,7 @@
         <v>4.3</v>
       </c>
       <c r="F242" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="243">
@@ -7209,19 +7209,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E243" t="n">
         <v>4.2</v>
       </c>
       <c r="F243" t="n">
-        <v>47.9</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="244">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E244" t="n">
         <v>4.2</v>
       </c>
       <c r="F244" t="n">
-        <v>53.3</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="245">
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F249" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="250">
@@ -7685,19 +7685,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E260" t="n">
         <v>16.2</v>
       </c>
       <c r="F260" t="n">
-        <v>53.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="261">
@@ -7713,19 +7713,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E261" t="n">
         <v>16.2</v>
       </c>
       <c r="F261" t="n">
-        <v>51.5</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="262">
@@ -8021,19 +8021,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E272" t="n">
         <v>8.6</v>
       </c>
       <c r="F272" t="n">
-        <v>48.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="273">
@@ -8049,19 +8049,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E273" t="n">
         <v>8.6</v>
       </c>
       <c r="F273" t="n">
-        <v>51.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="274">
@@ -8441,19 +8441,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E287" t="n">
         <v>4.6</v>
       </c>
       <c r="F287" t="n">
-        <v>50.2</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="288">
@@ -8469,19 +8469,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E288" t="n">
         <v>4.6</v>
       </c>
       <c r="F288" t="n">
-        <v>51.8</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="289">
@@ -8497,19 +8497,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E289" t="n">
         <v>4.4</v>
       </c>
       <c r="F289" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="290">
@@ -8525,19 +8525,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E290" t="n">
         <v>4.4</v>
       </c>
       <c r="F290" t="n">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="291">
@@ -8581,19 +8581,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E292" t="n">
         <v>4</v>
       </c>
       <c r="F292" t="n">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="293">
@@ -8609,19 +8609,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E293" t="n">
         <v>4</v>
       </c>
       <c r="F293" t="n">
-        <v>52.9</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="294">
@@ -9533,19 +9533,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E326" t="n">
         <v>5.7</v>
       </c>
       <c r="F326" t="n">
-        <v>47.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="327">
@@ -9561,19 +9561,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E327" t="n">
         <v>5.7</v>
       </c>
       <c r="F327" t="n">
-        <v>46.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="328">
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="F352" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="353">
@@ -10298,10 +10298,10 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="F353" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="354">
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="F354" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="355">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="F355" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="356">
@@ -10385,7 +10385,7 @@
         <v>23</v>
       </c>
       <c r="F356" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="357">
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="F357" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="358">
@@ -10429,19 +10429,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="F358" t="n">
-        <v>54.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="359">
@@ -10457,19 +10457,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E359" t="n">
         <v>19.7</v>
       </c>
       <c r="F359" t="n">
-        <v>55.1</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="360">
@@ -10485,19 +10485,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="F360" t="n">
-        <v>49.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="361">
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="F361" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="362">
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="F362" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="363">
@@ -10581,7 +10581,7 @@
         <v>14.2</v>
       </c>
       <c r="F363" t="n">
-        <v>52.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="364">
@@ -10609,7 +10609,7 @@
         <v>13.3</v>
       </c>
       <c r="F364" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="365">
@@ -10637,7 +10637,7 @@
         <v>12.9</v>
       </c>
       <c r="F365" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="366">
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F366" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="367">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F367" t="n">
         <v>47.6</v>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F368" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="369">
@@ -10737,19 +10737,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E369" t="n">
         <v>9.6</v>
       </c>
       <c r="F369" t="n">
-        <v>46.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="370">
@@ -10765,19 +10765,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F370" t="n">
-        <v>49.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="371">
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F371" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="372">
@@ -10833,7 +10833,7 @@
         <v>8.5</v>
       </c>
       <c r="F372" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="373">
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="F373" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="374">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F374" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="375">
@@ -10914,10 +10914,10 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F375" t="n">
-        <v>49.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="376">
@@ -10945,7 +10945,7 @@
         <v>6.4</v>
       </c>
       <c r="F376" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="377">
@@ -10973,7 +10973,7 @@
         <v>5.7</v>
       </c>
       <c r="F377" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="378">
@@ -10989,19 +10989,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F378" t="n">
-        <v>53.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="379">
@@ -11017,19 +11017,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E379" t="n">
         <v>5.5</v>
       </c>
       <c r="F379" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="380">
@@ -11057,7 +11057,7 @@
         <v>5.3</v>
       </c>
       <c r="F380" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="381">
@@ -11085,7 +11085,7 @@
         <v>5.1</v>
       </c>
       <c r="F381" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="382">
@@ -11113,7 +11113,7 @@
         <v>4.3</v>
       </c>
       <c r="F382" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="383">
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F383" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="384">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F384" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="385">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F385" t="n">
-        <v>38.8</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="386">
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F386" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="387">
@@ -11250,10 +11250,10 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F387" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="388">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F388" t="n">
-        <v>43.7</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="389">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -11309,7 +11309,7 @@
         <v>2.9</v>
       </c>
       <c r="F389" t="n">
-        <v>40.9</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="390">
@@ -11337,7 +11337,7 @@
         <v>2.7</v>
       </c>
       <c r="F390" t="n">
-        <v>45.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="391">
@@ -11365,7 +11365,7 @@
         <v>2.6</v>
       </c>
       <c r="F391" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="392">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F392" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="393">
@@ -11409,19 +11409,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F393" t="n">
-        <v>47.1</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="394">
@@ -11437,19 +11437,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E394" t="n">
         <v>2.1</v>
       </c>
       <c r="F394" t="n">
-        <v>32.1</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="395">
@@ -11474,10 +11474,10 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F395" t="n">
-        <v>42.8</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="396">
@@ -11505,7 +11505,7 @@
         <v>1.8</v>
       </c>
       <c r="F396" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="397">
@@ -11530,10 +11530,10 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F397" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="398">
@@ -11561,7 +11561,7 @@
         <v>1.4</v>
       </c>
       <c r="F398" t="n">
-        <v>41.8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="399">
@@ -11589,7 +11589,7 @@
         <v>1.3</v>
       </c>
       <c r="F399" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="400">
@@ -11605,19 +11605,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E400" t="n">
         <v>0.7</v>
       </c>
       <c r="F400" t="n">
-        <v>45.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="401">
@@ -11633,19 +11633,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E401" t="n">
         <v>0.7</v>
       </c>
       <c r="F401" t="n">
-        <v>40.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="402">
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="F453" t="n">
         <v>55.1</v>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="F454" t="n">
         <v>50.3</v>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="F457" t="n">
         <v>46.6</v>
@@ -13266,7 +13266,7 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="F459" t="n">
         <v>51.1</v>
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F460" t="n">
         <v>47.9</v>
@@ -13325,7 +13325,7 @@
         <v>14.4</v>
       </c>
       <c r="F461" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="462">
@@ -13341,19 +13341,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F462" t="n">
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="463">
@@ -13369,19 +13369,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E463" t="n">
         <v>13.4</v>
       </c>
       <c r="F463" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="464">
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F464" t="n">
         <v>52.1</v>
@@ -13425,19 +13425,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F465" t="n">
-        <v>53.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="466">
@@ -13453,19 +13453,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E466" t="n">
         <v>12.2</v>
       </c>
       <c r="F466" t="n">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="467">
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F468" t="n">
         <v>46.6</v>
@@ -13549,7 +13549,7 @@
         <v>11.3</v>
       </c>
       <c r="F469" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="470">
@@ -13577,7 +13577,7 @@
         <v>11.2</v>
       </c>
       <c r="F470" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="471">
@@ -13661,7 +13661,7 @@
         <v>10.3</v>
       </c>
       <c r="F473" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="474">
@@ -13686,7 +13686,7 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="F474" t="n">
         <v>52.9</v>
@@ -13717,7 +13717,7 @@
         <v>9.6</v>
       </c>
       <c r="F475" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="476">
@@ -13773,7 +13773,7 @@
         <v>7.7</v>
       </c>
       <c r="F477" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="478">
@@ -13826,7 +13826,7 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="F479" t="n">
         <v>53.1</v>
@@ -13845,19 +13845,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F480" t="n">
-        <v>45.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="481">
@@ -13873,19 +13873,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E481" t="n">
         <v>6.5</v>
       </c>
       <c r="F481" t="n">
-        <v>48.6</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="482">
@@ -13913,7 +13913,7 @@
         <v>5.9</v>
       </c>
       <c r="F482" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="483">
@@ -13941,7 +13941,7 @@
         <v>5.8</v>
       </c>
       <c r="F483" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="484">
@@ -14053,7 +14053,7 @@
         <v>5</v>
       </c>
       <c r="F487" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="488">
@@ -14081,7 +14081,7 @@
         <v>4.8</v>
       </c>
       <c r="F488" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="489">
@@ -14137,7 +14137,7 @@
         <v>4.2</v>
       </c>
       <c r="F490" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="491">
@@ -14162,10 +14162,10 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F491" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="492">
@@ -14193,7 +14193,7 @@
         <v>4</v>
       </c>
       <c r="F492" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="493">
@@ -14305,7 +14305,7 @@
         <v>3.5</v>
       </c>
       <c r="F496" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="497">
@@ -14333,7 +14333,7 @@
         <v>3.2</v>
       </c>
       <c r="F497" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="498">
@@ -14361,7 +14361,7 @@
         <v>3.2</v>
       </c>
       <c r="F498" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="499">
@@ -14389,7 +14389,7 @@
         <v>3.2</v>
       </c>
       <c r="F499" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="500">
@@ -14405,19 +14405,19 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E500" t="n">
         <v>1.8</v>
       </c>
       <c r="F500" t="n">
-        <v>47.7</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="501">
@@ -14433,19 +14433,19 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E501" t="n">
         <v>1.8</v>
       </c>
       <c r="F501" t="n">
-        <v>51.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="502">
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="F502" t="n">
         <v>48</v>
@@ -14498,10 +14498,10 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="F503" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="504">
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F504" t="n">
         <v>45.9</v>
@@ -14610,10 +14610,10 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F507" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="508">
@@ -14638,7 +14638,7 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F508" t="n">
         <v>48.6</v>
@@ -14666,10 +14666,10 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="F509" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="510">
@@ -14694,10 +14694,10 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="F510" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="511">
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="F511" t="n">
         <v>50.6</v>
@@ -14750,10 +14750,10 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="F512" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="513">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="F513" t="n">
         <v>48.9</v>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -14806,10 +14806,10 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="F514" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="515">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -14837,7 +14837,7 @@
         <v>13</v>
       </c>
       <c r="F515" t="n">
-        <v>52.2</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="516">
@@ -14862,7 +14862,7 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F516" t="n">
         <v>48.5</v>
@@ -14977,7 +14977,7 @@
         <v>10.6</v>
       </c>
       <c r="F520" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="521">
@@ -15005,7 +15005,7 @@
         <v>10.4</v>
       </c>
       <c r="F521" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="522">
@@ -15021,19 +15021,19 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E522" t="n">
         <v>10.1</v>
       </c>
       <c r="F522" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="523">
@@ -15049,16 +15049,16 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F523" t="n">
         <v>53.5</v>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F524" t="n">
         <v>52</v>
@@ -15117,7 +15117,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F525" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="526">
@@ -15133,19 +15133,19 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E526" t="n">
         <v>8.1</v>
       </c>
       <c r="F526" t="n">
-        <v>53.4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="527">
@@ -15161,19 +15161,19 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="F527" t="n">
-        <v>51.1</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="528">
@@ -15245,19 +15245,19 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E530" t="n">
         <v>6.8</v>
       </c>
       <c r="F530" t="n">
-        <v>46.3</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="531">
@@ -15273,19 +15273,19 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F531" t="n">
-        <v>44.3</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="532">
@@ -15313,7 +15313,7 @@
         <v>5.7</v>
       </c>
       <c r="F532" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="533">
@@ -15413,19 +15413,19 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E536" t="n">
         <v>4.8</v>
       </c>
       <c r="F536" t="n">
-        <v>48.1</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="537">
@@ -15441,19 +15441,19 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E537" t="n">
         <v>4.8</v>
       </c>
       <c r="F537" t="n">
-        <v>55.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="538">
@@ -15469,19 +15469,19 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F538" t="n">
-        <v>45</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="539">
@@ -15497,19 +15497,19 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E539" t="n">
         <v>4.7</v>
       </c>
       <c r="F539" t="n">
-        <v>51.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="540">
@@ -15525,19 +15525,19 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E540" t="n">
         <v>4.7</v>
       </c>
       <c r="F540" t="n">
-        <v>51.4</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="541">
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F542" t="n">
         <v>53.7</v>
@@ -15693,19 +15693,19 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E546" t="n">
         <v>3.7</v>
       </c>
       <c r="F546" t="n">
-        <v>52.3</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="547">
@@ -15721,19 +15721,19 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E547" t="n">
         <v>3.7</v>
       </c>
       <c r="F547" t="n">
-        <v>49.3</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="548">
@@ -15817,7 +15817,7 @@
         <v>1.8</v>
       </c>
       <c r="F550" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="551">
@@ -16925,19 +16925,19 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E590" t="n">
         <v>4.3</v>
       </c>
       <c r="F590" t="n">
-        <v>49.7</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="591">
@@ -16953,19 +16953,19 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E591" t="n">
         <v>4.3</v>
       </c>
       <c r="F591" t="n">
-        <v>52.4</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="592">
@@ -16981,19 +16981,19 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E592" t="n">
         <v>4.2</v>
       </c>
       <c r="F592" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="593">
@@ -17009,19 +17009,19 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E593" t="n">
         <v>4.2</v>
       </c>
       <c r="F593" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="594">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="F603" t="n">
         <v>53.4</v>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="F604" t="n">
         <v>44.8</v>
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="F607" t="n">
         <v>48.6</v>
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="F608" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="609">
@@ -17522,7 +17522,7 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F611" t="n">
         <v>50.8</v>
@@ -17606,10 +17606,10 @@
         </is>
       </c>
       <c r="E614" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F614" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="615">
@@ -17662,7 +17662,7 @@
         </is>
       </c>
       <c r="E616" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F616" t="n">
         <v>52.4</v>
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F618" t="n">
         <v>52</v>
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="F619" t="n">
         <v>54.2</v>
@@ -17805,7 +17805,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F621" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="622">
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="F622" t="n">
         <v>53.6</v>
@@ -17858,7 +17858,7 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="F623" t="n">
         <v>43.2</v>
@@ -17886,10 +17886,10 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="F624" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="625">
@@ -17933,19 +17933,19 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E626" t="n">
         <v>7.7</v>
       </c>
       <c r="F626" t="n">
-        <v>46</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="627">
@@ -17961,19 +17961,19 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="F627" t="n">
-        <v>49.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="628">
@@ -18054,7 +18054,7 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="F630" t="n">
         <v>51.6</v>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -18085,7 +18085,7 @@
         <v>7</v>
       </c>
       <c r="F631" t="n">
-        <v>50.7</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="632">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -18110,10 +18110,10 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F632" t="n">
-        <v>53.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="633">
@@ -18197,7 +18197,7 @@
         <v>6.2</v>
       </c>
       <c r="F635" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="636">
@@ -18225,7 +18225,7 @@
         <v>6.2</v>
       </c>
       <c r="F636" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="637">
@@ -18337,7 +18337,7 @@
         <v>4.5</v>
       </c>
       <c r="F640" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="641">
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F648" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="649">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F652" t="n">
         <v>47.5</v>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="F653" t="n">
         <v>45</v>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="F654" t="n">
         <v>52</v>
@@ -18782,10 +18782,10 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="F656" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="657">
@@ -18866,10 +18866,10 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="F659" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="660">
@@ -18897,7 +18897,7 @@
         <v>16</v>
       </c>
       <c r="F660" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="661">
@@ -19006,7 +19006,7 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="F664" t="n">
         <v>50.3</v>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F665" t="n">
         <v>52.3</v>
@@ -19053,7 +19053,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -19062,10 +19062,10 @@
         </is>
       </c>
       <c r="E666" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F666" t="n">
-        <v>54.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="667">
@@ -19081,16 +19081,16 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="F667" t="n">
         <v>51</v>
@@ -19109,19 +19109,19 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E668" t="n">
         <v>10.5</v>
       </c>
       <c r="F668" t="n">
-        <v>51</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="669">
@@ -19202,7 +19202,7 @@
         </is>
       </c>
       <c r="E671" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F671" t="n">
         <v>50.5</v>
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F675" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="676">
@@ -19342,7 +19342,7 @@
         </is>
       </c>
       <c r="E676" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F676" t="n">
         <v>54.5</v>
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F679" t="n">
         <v>51.5</v>
@@ -19513,7 +19513,7 @@
         <v>6.8</v>
       </c>
       <c r="F682" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="683">
@@ -19541,7 +19541,7 @@
         <v>5.8</v>
       </c>
       <c r="F683" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="684">
@@ -19585,19 +19585,19 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E685" t="n">
         <v>5.4</v>
       </c>
       <c r="F685" t="n">
-        <v>52.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="686">
@@ -19613,19 +19613,19 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E686" t="n">
         <v>5.4</v>
       </c>
       <c r="F686" t="n">
-        <v>48.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="687">
@@ -19641,19 +19641,19 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F687" t="n">
-        <v>44.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="688">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F688" t="n">
         <v>50.7</v>
@@ -19765,7 +19765,7 @@
         <v>4.9</v>
       </c>
       <c r="F691" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="692">
@@ -19837,19 +19837,19 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E694" t="n">
         <v>3.7</v>
       </c>
       <c r="F694" t="n">
-        <v>54</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="695">
@@ -19865,19 +19865,19 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F695" t="n">
-        <v>46.8</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="696">
@@ -19949,19 +19949,19 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F698" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="699">
@@ -19977,19 +19977,19 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E699" t="n">
         <v>3.1</v>
       </c>
       <c r="F699" t="n">
-        <v>53.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="700">
@@ -20017,7 +20017,7 @@
         <v>3.1</v>
       </c>
       <c r="F700" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="701">
@@ -20045,7 +20045,7 @@
         <v>2.5</v>
       </c>
       <c r="F701" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="702">
@@ -20073,7 +20073,7 @@
         <v>36.5</v>
       </c>
       <c r="F702" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="703">
@@ -20101,7 +20101,7 @@
         <v>30.9</v>
       </c>
       <c r="F703" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="704">
@@ -20154,10 +20154,10 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="F705" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="706">
@@ -20182,10 +20182,10 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="F706" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="707">
@@ -20213,7 +20213,7 @@
         <v>18.4</v>
       </c>
       <c r="F707" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="708">
@@ -20238,7 +20238,7 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="F708" t="n">
         <v>51.6</v>
@@ -20266,10 +20266,10 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F709" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="710">
@@ -20294,10 +20294,10 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="F710" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="711">
@@ -20353,7 +20353,7 @@
         <v>14.5</v>
       </c>
       <c r="F712" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="713">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="F713" t="n">
         <v>52</v>
@@ -20434,10 +20434,10 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="F715" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="716">
@@ -20465,7 +20465,7 @@
         <v>11.3</v>
       </c>
       <c r="F716" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="717">
@@ -20493,7 +20493,7 @@
         <v>11.2</v>
       </c>
       <c r="F717" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="718">
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F719" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="720">
@@ -20577,7 +20577,7 @@
         <v>9.5</v>
       </c>
       <c r="F720" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="721">
@@ -20593,19 +20593,19 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F721" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="722">
@@ -20621,19 +20621,19 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F722" t="n">
-        <v>54.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="723">
@@ -20686,7 +20686,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F724" t="n">
         <v>49.3</v>
@@ -20717,7 +20717,7 @@
         <v>8.4</v>
       </c>
       <c r="F725" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="726">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F726" t="n">
         <v>51.8</v>
@@ -20773,7 +20773,7 @@
         <v>8.1</v>
       </c>
       <c r="F727" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="728">
@@ -20801,7 +20801,7 @@
         <v>7.9</v>
       </c>
       <c r="F728" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="729">
@@ -20829,7 +20829,7 @@
         <v>7.8</v>
       </c>
       <c r="F729" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="730">
@@ -20885,7 +20885,7 @@
         <v>7.2</v>
       </c>
       <c r="F731" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="732">
@@ -20913,7 +20913,7 @@
         <v>7</v>
       </c>
       <c r="F732" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="733">
@@ -20969,7 +20969,7 @@
         <v>6.3</v>
       </c>
       <c r="F734" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="735">
@@ -20997,7 +20997,7 @@
         <v>6.1</v>
       </c>
       <c r="F735" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="736">
@@ -21025,7 +21025,7 @@
         <v>5.9</v>
       </c>
       <c r="F736" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="737">
@@ -21053,7 +21053,7 @@
         <v>5.5</v>
       </c>
       <c r="F737" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="738">
@@ -21081,7 +21081,7 @@
         <v>4.7</v>
       </c>
       <c r="F738" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="739">
@@ -21109,7 +21109,7 @@
         <v>4.4</v>
       </c>
       <c r="F739" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="740">
@@ -21209,19 +21209,19 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E743" t="n">
         <v>3.7</v>
       </c>
       <c r="F743" t="n">
-        <v>53.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="744">
@@ -21237,19 +21237,19 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F744" t="n">
-        <v>46.2</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="745">
@@ -21277,7 +21277,7 @@
         <v>3.6</v>
       </c>
       <c r="F745" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="746">
@@ -21305,7 +21305,7 @@
         <v>3.6</v>
       </c>
       <c r="F746" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="747">
@@ -21361,7 +21361,7 @@
         <v>3.3</v>
       </c>
       <c r="F748" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="749">
@@ -21389,7 +21389,7 @@
         <v>3.2</v>
       </c>
       <c r="F749" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="750">
@@ -21417,7 +21417,7 @@
         <v>2.8</v>
       </c>
       <c r="F750" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="751">
@@ -21445,7 +21445,7 @@
         <v>2.7</v>
       </c>
       <c r="F751" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="752">
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="F802" t="n">
         <v>53.3</v>
@@ -22898,7 +22898,7 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F803" t="n">
         <v>47.8</v>
@@ -23029,19 +23029,19 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E808" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="F808" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="809">
@@ -23057,19 +23057,19 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E809" t="n">
         <v>17.2</v>
       </c>
       <c r="F809" t="n">
-        <v>47.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="810">
@@ -23150,10 +23150,10 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F812" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="813">
@@ -23265,7 +23265,7 @@
         <v>12.7</v>
       </c>
       <c r="F816" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="817">
@@ -23321,7 +23321,7 @@
         <v>11.1</v>
       </c>
       <c r="F818" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="819">
@@ -23346,10 +23346,10 @@
         </is>
       </c>
       <c r="E819" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F819" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="820">
@@ -23374,7 +23374,7 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="F820" t="n">
         <v>53.3</v>
@@ -23514,7 +23514,7 @@
         </is>
       </c>
       <c r="E825" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F825" t="n">
         <v>48.2</v>
@@ -23713,7 +23713,7 @@
         <v>6.1</v>
       </c>
       <c r="F832" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="833">
@@ -23769,7 +23769,7 @@
         <v>6</v>
       </c>
       <c r="F834" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="835">
@@ -23850,7 +23850,7 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F837" t="n">
         <v>50.2</v>
@@ -23897,19 +23897,19 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E839" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F839" t="n">
-        <v>54.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="840">
@@ -23925,19 +23925,19 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E840" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F840" t="n">
-        <v>52.1</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="841">
@@ -23965,7 +23965,7 @@
         <v>4.5</v>
       </c>
       <c r="F841" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="842">
@@ -24077,7 +24077,7 @@
         <v>3.7</v>
       </c>
       <c r="F845" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="846">
@@ -24133,7 +24133,7 @@
         <v>3.4</v>
       </c>
       <c r="F847" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="848">
@@ -24189,7 +24189,7 @@
         <v>2.7</v>
       </c>
       <c r="F849" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="850">
@@ -24245,7 +24245,7 @@
         <v>1.8</v>
       </c>
       <c r="F851" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="852">
@@ -24485,19 +24485,19 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E860" t="n">
         <v>14.6</v>
       </c>
       <c r="F860" t="n">
-        <v>50.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="861">
@@ -24513,19 +24513,19 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E861" t="n">
         <v>14.6</v>
       </c>
       <c r="F861" t="n">
-        <v>45</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="862">
@@ -24625,19 +24625,19 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E865" t="n">
         <v>12.6</v>
       </c>
       <c r="F865" t="n">
-        <v>47</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="866">
@@ -24653,19 +24653,19 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E866" t="n">
         <v>12.6</v>
       </c>
       <c r="F866" t="n">
-        <v>53.3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="867">
@@ -24709,19 +24709,19 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E868" t="n">
         <v>11.6</v>
       </c>
       <c r="F868" t="n">
-        <v>49.9</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="869">
@@ -24737,19 +24737,19 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E869" t="n">
         <v>11.6</v>
       </c>
       <c r="F869" t="n">
-        <v>54.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="870">
@@ -25017,19 +25017,19 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E879" t="n">
         <v>6.1</v>
       </c>
       <c r="F879" t="n">
-        <v>45.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="880">
@@ -25045,19 +25045,19 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E880" t="n">
         <v>6.1</v>
       </c>
       <c r="F880" t="n">
-        <v>50.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="881">
@@ -25073,19 +25073,19 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E881" t="n">
         <v>6.1</v>
       </c>
       <c r="F881" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="882">
@@ -25213,19 +25213,19 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E886" t="n">
         <v>5.4</v>
       </c>
       <c r="F886" t="n">
-        <v>53.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="887">
@@ -25241,19 +25241,19 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E887" t="n">
         <v>5.4</v>
       </c>
       <c r="F887" t="n">
-        <v>44</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="888">
@@ -25829,19 +25829,19 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E908" t="n">
         <v>17.5</v>
       </c>
       <c r="F908" t="n">
-        <v>50.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="909">
@@ -25857,19 +25857,19 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E909" t="n">
         <v>17.5</v>
       </c>
       <c r="F909" t="n">
-        <v>46.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="910">
@@ -28265,19 +28265,19 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E995" t="n">
         <v>3.7</v>
       </c>
       <c r="F995" t="n">
-        <v>51.9</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="996">
@@ -28293,19 +28293,19 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E996" t="n">
         <v>3.7</v>
       </c>
       <c r="F996" t="n">
-        <v>48.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="997">
@@ -29301,19 +29301,19 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1032" t="n">
         <v>6.6</v>
       </c>
       <c r="F1032" t="n">
-        <v>49.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1033">
@@ -29329,19 +29329,19 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1033" t="n">
         <v>6.6</v>
       </c>
       <c r="F1033" t="n">
-        <v>44.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1034">
@@ -29873,7 +29873,7 @@
         <v>36.6</v>
       </c>
       <c r="F1052" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1053">
@@ -29898,7 +29898,7 @@
         </is>
       </c>
       <c r="E1053" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="F1053" t="n">
         <v>45.1</v>
@@ -29954,10 +29954,10 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="F1055" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1056">
@@ -30038,10 +30038,10 @@
         </is>
       </c>
       <c r="E1058" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="F1058" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1059">
@@ -30153,7 +30153,7 @@
         <v>14.4</v>
       </c>
       <c r="F1062" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1063">
@@ -30178,7 +30178,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="F1063" t="n">
         <v>46.7</v>
@@ -30234,7 +30234,7 @@
         </is>
       </c>
       <c r="E1065" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F1065" t="n">
         <v>50.2</v>
@@ -30281,19 +30281,19 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="F1067" t="n">
-        <v>53.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1068">
@@ -30309,19 +30309,19 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1068" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="F1068" t="n">
-        <v>48.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1069">
@@ -30337,19 +30337,19 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F1069" t="n">
-        <v>54.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1070">
@@ -30365,19 +30365,19 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F1070" t="n">
-        <v>46.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1071">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -30405,7 +30405,7 @@
         <v>10</v>
       </c>
       <c r="F1071" t="n">
-        <v>52.9</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1072">
@@ -30461,7 +30461,7 @@
         <v>9.1</v>
       </c>
       <c r="F1073" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1074">
@@ -30477,19 +30477,19 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F1074" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1075">
@@ -30505,19 +30505,19 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1075" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="F1075" t="n">
-        <v>51.6</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1076">
@@ -30601,7 +30601,7 @@
         <v>8.1</v>
       </c>
       <c r="F1078" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1079">
@@ -30645,19 +30645,19 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1080" t="n">
         <v>6.9</v>
       </c>
       <c r="F1080" t="n">
-        <v>51.4</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1081">
@@ -30673,19 +30673,19 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1081" t="n">
         <v>6.9</v>
       </c>
       <c r="F1081" t="n">
-        <v>44.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1082">
@@ -30797,7 +30797,7 @@
         <v>5.6</v>
       </c>
       <c r="F1085" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1086">
@@ -30825,7 +30825,7 @@
         <v>5.3</v>
       </c>
       <c r="F1086" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1087">
@@ -30853,7 +30853,7 @@
         <v>5</v>
       </c>
       <c r="F1087" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1088">
@@ -30909,7 +30909,7 @@
         <v>5</v>
       </c>
       <c r="F1089" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1090">
@@ -30993,7 +30993,7 @@
         <v>4.4</v>
       </c>
       <c r="F1092" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1093">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -31021,7 +31021,7 @@
         <v>4.1</v>
       </c>
       <c r="F1093" t="n">
-        <v>46</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1094">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -31049,7 +31049,7 @@
         <v>4.1</v>
       </c>
       <c r="F1094" t="n">
-        <v>46.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1095">
@@ -31077,7 +31077,7 @@
         <v>4</v>
       </c>
       <c r="F1095" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1096">
@@ -31105,7 +31105,7 @@
         <v>3.9</v>
       </c>
       <c r="F1096" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1097">
@@ -31133,7 +31133,7 @@
         <v>3.3</v>
       </c>
       <c r="F1097" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1098">
@@ -31161,7 +31161,7 @@
         <v>3.2</v>
       </c>
       <c r="F1098" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1099">
@@ -31217,7 +31217,7 @@
         <v>2.7</v>
       </c>
       <c r="F1100" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1101">
@@ -32073,19 +32073,19 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1131" t="n">
         <v>6.8</v>
       </c>
       <c r="F1131" t="n">
-        <v>50.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1132">
@@ -32101,19 +32101,19 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1132" t="n">
         <v>6.8</v>
       </c>
       <c r="F1132" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1133">
@@ -32129,19 +32129,19 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1133" t="n">
         <v>6.8</v>
       </c>
       <c r="F1133" t="n">
-        <v>49.2</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1134">
@@ -32157,19 +32157,19 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1134" t="n">
         <v>6.5</v>
       </c>
       <c r="F1134" t="n">
-        <v>46.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1135">
@@ -32185,19 +32185,19 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1135" t="n">
         <v>6.5</v>
       </c>
       <c r="F1135" t="n">
-        <v>49.2</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1136">
@@ -33137,19 +33137,19 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1169" t="n">
         <v>11.1</v>
       </c>
       <c r="F1169" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1170">
@@ -33165,19 +33165,19 @@
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1170" t="n">
         <v>11.1</v>
       </c>
       <c r="F1170" t="n">
-        <v>51.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1171">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
@@ -33485,7 +33485,7 @@
         <v>6</v>
       </c>
       <c r="F1181" t="n">
-        <v>44.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1182">
@@ -33501,7 +33501,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -33513,7 +33513,7 @@
         <v>6</v>
       </c>
       <c r="F1182" t="n">
-        <v>46.2</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1183">
@@ -33669,19 +33669,19 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1188" t="n">
         <v>4.6</v>
       </c>
       <c r="F1188" t="n">
-        <v>52.9</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1189">
@@ -33697,19 +33697,19 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1189" t="n">
         <v>4.6</v>
       </c>
       <c r="F1189" t="n">
-        <v>45.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1190">
@@ -34686,7 +34686,7 @@
         </is>
       </c>
       <c r="E1224" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1224" t="n">
         <v>49</v>
@@ -34773,7 +34773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1227" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1228">
@@ -34857,7 +34857,7 @@
         <v>1.4</v>
       </c>
       <c r="F1230" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1231">
@@ -34913,7 +34913,7 @@
         <v>1.2</v>
       </c>
       <c r="F1232" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1233">
@@ -35125,19 +35125,19 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1240" t="n">
         <v>1.1</v>
       </c>
       <c r="F1240" t="n">
-        <v>50.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1241">
@@ -35153,19 +35153,19 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1241" t="n">
         <v>1.1</v>
       </c>
       <c r="F1241" t="n">
-        <v>46.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1242">
@@ -35277,7 +35277,7 @@
         <v>0.9</v>
       </c>
       <c r="F1245" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1246">
@@ -35501,7 +35501,7 @@
         <v>5.1</v>
       </c>
       <c r="F1253" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1254">
@@ -35585,7 +35585,7 @@
         <v>4</v>
       </c>
       <c r="F1256" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1257">
@@ -35865,7 +35865,7 @@
         <v>2.7</v>
       </c>
       <c r="F1266" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1267">
@@ -36061,7 +36061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1273" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1274">
@@ -36089,7 +36089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1274" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1275">
@@ -36173,7 +36173,7 @@
         <v>1.7</v>
       </c>
       <c r="F1277" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1278">
@@ -36201,7 +36201,7 @@
         <v>1.6</v>
       </c>
       <c r="F1278" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1279">
@@ -36257,7 +36257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1280" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1281">
@@ -36341,7 +36341,7 @@
         <v>1.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1284">
@@ -36441,19 +36441,19 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1287" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1287" t="n">
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>44.2</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1288">
@@ -36469,19 +36469,19 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1288" t="n">
         <v>1.1</v>
       </c>
       <c r="F1288" t="n">
-        <v>53.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1289">
@@ -36621,7 +36621,7 @@
         <v>0.9</v>
       </c>
       <c r="F1293" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1294">
@@ -36733,7 +36733,7 @@
         <v>0.6</v>
       </c>
       <c r="F1297" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1298">
@@ -36817,7 +36817,7 @@
         <v>0.4</v>
       </c>
       <c r="F1300" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="1301">
@@ -36985,7 +36985,7 @@
         <v>4</v>
       </c>
       <c r="F1306" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1307">
@@ -37066,7 +37066,7 @@
         </is>
       </c>
       <c r="E1309" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1309" t="n">
         <v>48.2</v>
@@ -37097,7 +37097,7 @@
         <v>3.2</v>
       </c>
       <c r="F1310" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1311">
@@ -37181,7 +37181,7 @@
         <v>3</v>
       </c>
       <c r="F1313" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1314">
@@ -37265,7 +37265,7 @@
         <v>2.4</v>
       </c>
       <c r="F1316" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1317">
@@ -37349,7 +37349,7 @@
         <v>2.1</v>
       </c>
       <c r="F1319" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1320">
@@ -37433,7 +37433,7 @@
         <v>1.8</v>
       </c>
       <c r="F1322" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1323">
@@ -37449,19 +37449,19 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1323" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1323" t="n">
         <v>1.8</v>
       </c>
       <c r="F1323" t="n">
-        <v>53.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1324">
@@ -37477,19 +37477,19 @@
       </c>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1324" t="n">
         <v>1.8</v>
       </c>
       <c r="F1324" t="n">
-        <v>43.8</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1325">
@@ -37713,7 +37713,7 @@
         <v>1.3</v>
       </c>
       <c r="F1332" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1333">
@@ -37785,19 +37785,19 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1335" t="n">
         <v>1.2</v>
       </c>
       <c r="F1335" t="n">
-        <v>47.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1336">
@@ -37813,19 +37813,19 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1336" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1336" t="n">
         <v>1.2</v>
       </c>
       <c r="F1336" t="n">
-        <v>45.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1337">
@@ -37841,19 +37841,19 @@
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1337" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1337" t="n">
         <v>1.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>50.7</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1338">
@@ -37869,19 +37869,19 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1338" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1338" t="n">
         <v>1.1</v>
       </c>
       <c r="F1338" t="n">
-        <v>51.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1339">
@@ -37909,7 +37909,7 @@
         <v>1.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1340">
@@ -38077,7 +38077,7 @@
         <v>0.8</v>
       </c>
       <c r="F1345" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1346">
@@ -38410,7 +38410,7 @@
         </is>
       </c>
       <c r="E1357" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F1357" t="n">
         <v>49.7</v>
@@ -38961,19 +38961,19 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1377" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1377" t="n">
         <v>1.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1378">
@@ -38989,12 +38989,12 @@
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1378" t="n">
@@ -39157,19 +39157,19 @@
       </c>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1384" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1384" t="n">
         <v>1.1</v>
       </c>
       <c r="F1384" t="n">
-        <v>49.6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1385">
@@ -39185,19 +39185,19 @@
       </c>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1385" t="n">
         <v>1.1</v>
       </c>
       <c r="F1385" t="n">
-        <v>51</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1386">
@@ -39225,7 +39225,7 @@
         <v>1.1</v>
       </c>
       <c r="F1386" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1387">
@@ -39465,19 +39465,19 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1395" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1395" t="n">
         <v>0.9</v>
       </c>
       <c r="F1395" t="n">
-        <v>50.6</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1396">
@@ -39493,19 +39493,19 @@
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1396" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1396" t="n">
         <v>0.9</v>
       </c>
       <c r="F1396" t="n">
-        <v>47.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1397">
@@ -39533,7 +39533,7 @@
         <v>0.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1398">
@@ -39645,7 +39645,7 @@
         <v>0.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1402">
@@ -39673,7 +39673,7 @@
         <v>6.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1403">
@@ -39813,7 +39813,7 @@
         <v>3.3</v>
       </c>
       <c r="F1407" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1408">
@@ -39869,7 +39869,7 @@
         <v>3</v>
       </c>
       <c r="F1409" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1410">
@@ -40009,7 +40009,7 @@
         <v>2.5</v>
       </c>
       <c r="F1414" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1415">
@@ -40233,7 +40233,7 @@
         <v>2</v>
       </c>
       <c r="F1422" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1423">
@@ -40345,7 +40345,7 @@
         <v>1.6</v>
       </c>
       <c r="F1426" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1427">
@@ -40401,7 +40401,7 @@
         <v>1.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1429">
@@ -40457,7 +40457,7 @@
         <v>1.4</v>
       </c>
       <c r="F1430" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1431">
@@ -40557,19 +40557,19 @@
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1434" t="n">
         <v>1.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>51.6</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1435">
@@ -40585,19 +40585,19 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1435" t="n">
         <v>1.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>43.6</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1436">
@@ -40625,7 +40625,7 @@
         <v>1.2</v>
       </c>
       <c r="F1436" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="1437">
@@ -40737,7 +40737,7 @@
         <v>0.9</v>
       </c>
       <c r="F1440" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1441">
@@ -40793,7 +40793,7 @@
         <v>0.9</v>
       </c>
       <c r="F1442" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1443">
@@ -40821,7 +40821,7 @@
         <v>0.9</v>
       </c>
       <c r="F1443" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1444">
@@ -41185,7 +41185,7 @@
         <v>3.8</v>
       </c>
       <c r="F1456" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1457">
@@ -41241,7 +41241,7 @@
         <v>3.2</v>
       </c>
       <c r="F1458" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1459">
@@ -41325,7 +41325,7 @@
         <v>2.9</v>
       </c>
       <c r="F1461" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1462">
@@ -41353,7 +41353,7 @@
         <v>2.7</v>
       </c>
       <c r="F1462" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1463">
@@ -41381,7 +41381,7 @@
         <v>2.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1464">
@@ -41409,7 +41409,7 @@
         <v>2.6</v>
       </c>
       <c r="F1464" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1465">
@@ -41425,19 +41425,19 @@
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1465" t="n">
         <v>2.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>48.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1466">
@@ -41453,19 +41453,19 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1466" t="n">
         <v>2.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>53.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1467">
@@ -41481,19 +41481,19 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1467" t="n">
         <v>2.3</v>
       </c>
       <c r="F1467" t="n">
-        <v>52.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1468">
@@ -41509,19 +41509,19 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1468" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1468" t="n">
-        <v>49.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1469">
@@ -41549,7 +41549,7 @@
         <v>2.2</v>
       </c>
       <c r="F1469" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1470">
@@ -41605,7 +41605,7 @@
         <v>2.1</v>
       </c>
       <c r="F1471" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1472">
@@ -41689,7 +41689,7 @@
         <v>1.9</v>
       </c>
       <c r="F1474" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1475">
@@ -41717,7 +41717,7 @@
         <v>1.8</v>
       </c>
       <c r="F1475" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1476">
@@ -41745,7 +41745,7 @@
         <v>1.8</v>
       </c>
       <c r="F1476" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1477">
@@ -41801,7 +41801,7 @@
         <v>1.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1479">
@@ -41829,7 +41829,7 @@
         <v>1.5</v>
       </c>
       <c r="F1479" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1480">
@@ -41857,7 +41857,7 @@
         <v>1.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1481">
@@ -41873,19 +41873,19 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1481" t="n">
         <v>1.4</v>
       </c>
       <c r="F1481" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1482">
@@ -41901,19 +41901,19 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1482" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1483">
@@ -41941,7 +41941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1484">
@@ -41957,7 +41957,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -41969,7 +41969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1484" t="n">
-        <v>51.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1485">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -41997,7 +41997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1485" t="n">
-        <v>46</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1486">
@@ -42025,7 +42025,7 @@
         <v>1.1</v>
       </c>
       <c r="F1486" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1487">
@@ -42053,7 +42053,7 @@
         <v>1</v>
       </c>
       <c r="F1487" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1488">
@@ -42081,7 +42081,7 @@
         <v>1</v>
       </c>
       <c r="F1488" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1489">
@@ -42109,7 +42109,7 @@
         <v>0.9</v>
       </c>
       <c r="F1489" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1490">
@@ -42125,19 +42125,19 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1490" t="n">
         <v>0.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>41.3</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="1491">
@@ -42153,19 +42153,19 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1491" t="n">
         <v>0.8</v>
       </c>
       <c r="F1491" t="n">
-        <v>37.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1492">
@@ -42193,7 +42193,7 @@
         <v>0.8</v>
       </c>
       <c r="F1492" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1493">
@@ -42221,7 +42221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1493" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1494">
@@ -42249,7 +42249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1495">
@@ -42277,7 +42277,7 @@
         <v>0.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1496">
@@ -42305,7 +42305,7 @@
         <v>0.5</v>
       </c>
       <c r="F1496" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>0.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1498">
@@ -42389,7 +42389,7 @@
         <v>0.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>0.4</v>
       </c>
       <c r="F1500" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1501">
@@ -42445,7 +42445,7 @@
         <v>0.4</v>
       </c>
       <c r="F1501" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="1502">
@@ -42501,7 +42501,7 @@
         <v>6</v>
       </c>
       <c r="F1503" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1504">
@@ -42529,7 +42529,7 @@
         <v>5.5</v>
       </c>
       <c r="F1504" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1505">
@@ -42554,10 +42554,10 @@
         </is>
       </c>
       <c r="E1505" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1506">
@@ -42585,7 +42585,7 @@
         <v>4.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1507">
@@ -42610,10 +42610,10 @@
         </is>
       </c>
       <c r="E1507" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1507" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1508">
@@ -42641,7 +42641,7 @@
         <v>4</v>
       </c>
       <c r="F1508" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1509">
@@ -42669,7 +42669,7 @@
         <v>3.9</v>
       </c>
       <c r="F1509" t="n">
-        <v>38.6</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="1510">
@@ -42725,7 +42725,7 @@
         <v>3.5</v>
       </c>
       <c r="F1511" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1512">
@@ -42753,7 +42753,7 @@
         <v>3.2</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1513">
@@ -42781,7 +42781,7 @@
         <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1514">
@@ -42809,7 +42809,7 @@
         <v>2.6</v>
       </c>
       <c r="F1514" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1515">
@@ -42865,7 +42865,7 @@
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1517" t="n">
         <v>2.3</v>
       </c>
       <c r="F1517" t="n">
-        <v>50.7</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1518">
@@ -42909,19 +42909,19 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1518" t="n">
         <v>2.3</v>
       </c>
       <c r="F1518" t="n">
-        <v>44.5</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1519">
@@ -42949,7 +42949,7 @@
         <v>2.1</v>
       </c>
       <c r="F1519" t="n">
-        <v>46.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1521">
@@ -43005,7 +43005,7 @@
         <v>2</v>
       </c>
       <c r="F1521" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1522">
@@ -43021,19 +43021,19 @@
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1522" t="n">
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>45</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1523">
@@ -43049,19 +43049,19 @@
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1523" t="n">
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>51.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1524">
@@ -43089,7 +43089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1524" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1525">
@@ -43117,7 +43117,7 @@
         <v>1.8</v>
       </c>
       <c r="F1525" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1526">
@@ -43198,10 +43198,10 @@
         </is>
       </c>
       <c r="E1528" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1529">
@@ -43285,7 +43285,7 @@
         <v>1.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1532">
@@ -43301,19 +43301,19 @@
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1532" t="n">
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1533">
@@ -43329,19 +43329,19 @@
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1533" t="n">
         <v>1.3</v>
       </c>
       <c r="F1533" t="n">
-        <v>50.6</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>1</v>
       </c>
       <c r="F1534" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1535">
@@ -43413,19 +43413,19 @@
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1536" t="n">
         <v>0.9</v>
       </c>
       <c r="F1536" t="n">
-        <v>49.3</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1537">
@@ -43441,19 +43441,19 @@
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1537" t="n">
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>43.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1538">
@@ -43509,7 +43509,7 @@
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="1540">
@@ -43537,7 +43537,7 @@
         <v>0.8</v>
       </c>
       <c r="F1540" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="1541">
@@ -43565,7 +43565,7 @@
         <v>0.7</v>
       </c>
       <c r="F1541" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="1542">
@@ -43621,7 +43621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1543" t="n">
-        <v>52.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1544">
@@ -43649,7 +43649,7 @@
         <v>0.5</v>
       </c>
       <c r="F1544" t="n">
-        <v>39.2</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="1545">
@@ -43674,10 +43674,10 @@
         </is>
       </c>
       <c r="E1545" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>41</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="1546">
@@ -43702,10 +43702,10 @@
         </is>
       </c>
       <c r="E1546" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1546" t="n">
-        <v>47.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1547">
@@ -43761,7 +43761,7 @@
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="1549">
@@ -43789,7 +43789,7 @@
         <v>0.3</v>
       </c>
       <c r="F1549" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="1550">
@@ -44253,19 +44253,19 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1566" t="n">
         <v>1.2</v>
       </c>
       <c r="F1566" t="n">
-        <v>62.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1567">
@@ -44281,12 +44281,12 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1567" t="n">
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1568" t="n">
         <v>1.2</v>
       </c>
       <c r="F1568" t="n">
-        <v>100</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="1569">
@@ -44337,12 +44337,12 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1569" t="n">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1573" t="n">
         <v>0.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1574" t="n">
         <v>0.6</v>
       </c>
       <c r="F1574" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1575">
@@ -44505,7 +44505,7 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1576" t="n">
         <v>0.6</v>
       </c>
       <c r="F1576" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1577">
@@ -44561,19 +44561,19 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1577" t="n">
         <v>0.6</v>
       </c>
       <c r="F1577" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -34378,7 +34378,7 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F1213" t="n">
         <v>52.3</v>
@@ -34549,7 +34549,7 @@
         <v>2.2</v>
       </c>
       <c r="F1219" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1220">
@@ -34761,19 +34761,19 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1227" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1227" t="n">
         <v>1.6</v>
       </c>
       <c r="F1227" t="n">
-        <v>50.3</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1228">
@@ -34789,19 +34789,19 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1228" t="n">
         <v>1.6</v>
       </c>
       <c r="F1228" t="n">
-        <v>43.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1229">
@@ -35013,19 +35013,19 @@
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1236" t="n">
         <v>1.1</v>
       </c>
       <c r="F1236" t="n">
-        <v>51</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1237">
@@ -35041,19 +35041,19 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1237" t="n">
         <v>1.1</v>
       </c>
       <c r="F1237" t="n">
-        <v>43.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1238">
@@ -35125,19 +35125,19 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1240" t="n">
         <v>1.1</v>
       </c>
       <c r="F1240" t="n">
-        <v>50.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1241">
@@ -35153,19 +35153,19 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1241" t="n">
         <v>1.1</v>
       </c>
       <c r="F1241" t="n">
-        <v>46.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1242">
@@ -35265,19 +35265,19 @@
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1245" t="n">
         <v>0.9</v>
       </c>
       <c r="F1245" t="n">
-        <v>47.4</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="1246">
@@ -35293,19 +35293,19 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1246" t="n">
         <v>0.9</v>
       </c>
       <c r="F1246" t="n">
-        <v>39.9</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1247">
@@ -35333,7 +35333,7 @@
         <v>0.8</v>
       </c>
       <c r="F1247" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1248">
@@ -35389,7 +35389,7 @@
         <v>0.6</v>
       </c>
       <c r="F1249" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1250">
@@ -35498,7 +35498,7 @@
         </is>
       </c>
       <c r="E1253" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F1253" t="n">
         <v>51.4</v>
@@ -35585,7 +35585,7 @@
         <v>4</v>
       </c>
       <c r="F1256" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1257">
@@ -35613,7 +35613,7 @@
         <v>3.9</v>
       </c>
       <c r="F1257" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1258">
@@ -35697,7 +35697,7 @@
         <v>3.1</v>
       </c>
       <c r="F1260" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1261">
@@ -35781,7 +35781,7 @@
         <v>2.9</v>
       </c>
       <c r="F1263" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1264">
@@ -36173,7 +36173,7 @@
         <v>1.7</v>
       </c>
       <c r="F1277" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1278">
@@ -36201,7 +36201,7 @@
         <v>1.7</v>
       </c>
       <c r="F1278" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1279">
@@ -36229,7 +36229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1279" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1280">
@@ -36257,7 +36257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1280" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1281">
@@ -36285,7 +36285,7 @@
         <v>1.3</v>
       </c>
       <c r="F1281" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1282">
@@ -36397,7 +36397,7 @@
         <v>1.1</v>
       </c>
       <c r="F1285" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1286">
@@ -36453,7 +36453,7 @@
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1288">
@@ -36649,7 +36649,7 @@
         <v>0.8</v>
       </c>
       <c r="F1294" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1295">
@@ -36705,7 +36705,7 @@
         <v>0.7</v>
       </c>
       <c r="F1296" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1297">
@@ -36817,7 +36817,7 @@
         <v>0.4</v>
       </c>
       <c r="F1300" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="1301">
@@ -36873,7 +36873,7 @@
         <v>5.4</v>
       </c>
       <c r="F1302" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1303">
@@ -37321,7 +37321,7 @@
         <v>2.2</v>
       </c>
       <c r="F1318" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1319">
@@ -37545,7 +37545,7 @@
         <v>1.7</v>
       </c>
       <c r="F1326" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1327">
@@ -37573,7 +37573,7 @@
         <v>1.7</v>
       </c>
       <c r="F1327" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1328">
@@ -37629,7 +37629,7 @@
         <v>1.5</v>
       </c>
       <c r="F1329" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1330">
@@ -37713,7 +37713,7 @@
         <v>1.3</v>
       </c>
       <c r="F1332" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1333">
@@ -37741,7 +37741,7 @@
         <v>1.2</v>
       </c>
       <c r="F1333" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1334">
@@ -37785,19 +37785,19 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1335" t="n">
         <v>1.2</v>
       </c>
       <c r="F1335" t="n">
-        <v>47.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1336">
@@ -37813,19 +37813,19 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1336" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1336" t="n">
         <v>1.2</v>
       </c>
       <c r="F1336" t="n">
-        <v>45.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1337">
@@ -37853,7 +37853,7 @@
         <v>1.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1338">
@@ -37909,7 +37909,7 @@
         <v>1.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1340">
@@ -37965,7 +37965,7 @@
         <v>1</v>
       </c>
       <c r="F1341" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1342">
@@ -38021,7 +38021,7 @@
         <v>1</v>
       </c>
       <c r="F1343" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1344">
@@ -38049,7 +38049,7 @@
         <v>0.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1345">
@@ -38077,7 +38077,7 @@
         <v>0.8</v>
       </c>
       <c r="F1345" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="1346">
@@ -38105,7 +38105,7 @@
         <v>0.7</v>
       </c>
       <c r="F1346" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1347">
@@ -38189,7 +38189,7 @@
         <v>0.6</v>
       </c>
       <c r="F1349" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1350">
@@ -38354,7 +38354,7 @@
         </is>
       </c>
       <c r="E1355" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F1355" t="n">
         <v>51.5</v>
@@ -38413,7 +38413,7 @@
         <v>3.3</v>
       </c>
       <c r="F1357" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1358">
@@ -38485,19 +38485,19 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1360" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1360" t="n">
         <v>3</v>
       </c>
       <c r="F1360" t="n">
-        <v>52.4</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1361">
@@ -38513,19 +38513,19 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1361" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1361" t="n">
         <v>3</v>
       </c>
       <c r="F1361" t="n">
-        <v>50.8</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1362">
@@ -39169,7 +39169,7 @@
         <v>1.1</v>
       </c>
       <c r="F1384" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1385">
@@ -39309,7 +39309,7 @@
         <v>1.1</v>
       </c>
       <c r="F1389" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1390">
@@ -39365,7 +39365,7 @@
         <v>1.1</v>
       </c>
       <c r="F1391" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1392">
@@ -39465,19 +39465,19 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1395" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1395" t="n">
         <v>0.9</v>
       </c>
       <c r="F1395" t="n">
-        <v>50.6</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1396">
@@ -39493,19 +39493,19 @@
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1396" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1396" t="n">
         <v>0.9</v>
       </c>
       <c r="F1396" t="n">
-        <v>47.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1397">
@@ -39533,7 +39533,7 @@
         <v>0.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1398">
@@ -39841,7 +39841,7 @@
         <v>3.1</v>
       </c>
       <c r="F1408" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1409">
@@ -39869,7 +39869,7 @@
         <v>3</v>
       </c>
       <c r="F1409" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1410">
@@ -40177,7 +40177,7 @@
         <v>2.1</v>
       </c>
       <c r="F1420" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1421">
@@ -40233,7 +40233,7 @@
         <v>2</v>
       </c>
       <c r="F1422" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1423">
@@ -40289,7 +40289,7 @@
         <v>1.8</v>
       </c>
       <c r="F1424" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1425">
@@ -40373,7 +40373,7 @@
         <v>1.6</v>
       </c>
       <c r="F1427" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1428">
@@ -40457,7 +40457,7 @@
         <v>1.4</v>
       </c>
       <c r="F1430" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1431">
@@ -40625,7 +40625,7 @@
         <v>1.2</v>
       </c>
       <c r="F1436" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1437">
@@ -40737,7 +40737,7 @@
         <v>0.9</v>
       </c>
       <c r="F1440" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1441">
@@ -40989,7 +40989,7 @@
         <v>0.7</v>
       </c>
       <c r="F1449" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1450">
@@ -41045,7 +41045,7 @@
         <v>0.6</v>
       </c>
       <c r="F1451" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1452">
@@ -41101,7 +41101,7 @@
         <v>6.5</v>
       </c>
       <c r="F1453" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1454">
@@ -41157,7 +41157,7 @@
         <v>4</v>
       </c>
       <c r="F1455" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1456">
@@ -41353,7 +41353,7 @@
         <v>2.7</v>
       </c>
       <c r="F1462" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1463">
@@ -41381,7 +41381,7 @@
         <v>2.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1464">
@@ -41493,7 +41493,7 @@
         <v>2.3</v>
       </c>
       <c r="F1467" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1468">
@@ -41521,7 +41521,7 @@
         <v>2.2</v>
       </c>
       <c r="F1468" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1469">
@@ -41633,7 +41633,7 @@
         <v>2</v>
       </c>
       <c r="F1472" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1473">
@@ -41773,7 +41773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1478">
@@ -41801,7 +41801,7 @@
         <v>1.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1479">
@@ -41913,7 +41913,7 @@
         <v>1.3</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1483">
@@ -41941,7 +41941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1484">
@@ -42025,7 +42025,7 @@
         <v>1.1</v>
       </c>
       <c r="F1486" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1487">
@@ -42053,7 +42053,7 @@
         <v>1</v>
       </c>
       <c r="F1487" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1488">
@@ -42137,7 +42137,7 @@
         <v>0.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="1491">
@@ -42165,7 +42165,7 @@
         <v>0.8</v>
       </c>
       <c r="F1491" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1492">
@@ -42221,7 +42221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1493" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1494">
@@ -42249,7 +42249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1495">
@@ -42293,19 +42293,19 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1496" t="n">
         <v>0.5</v>
       </c>
       <c r="F1496" t="n">
-        <v>49.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1497">
@@ -42321,19 +42321,19 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1497" t="n">
         <v>0.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>0.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="1500">
@@ -42445,7 +42445,7 @@
         <v>0.4</v>
       </c>
       <c r="F1501" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>6.5</v>
       </c>
       <c r="F1502" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1503">
@@ -42498,10 +42498,10 @@
         </is>
       </c>
       <c r="E1503" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F1503" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1504">
@@ -42529,7 +42529,7 @@
         <v>5.5</v>
       </c>
       <c r="F1504" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1505">
@@ -42557,7 +42557,7 @@
         <v>4.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1506">
@@ -42585,7 +42585,7 @@
         <v>4.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1507">
@@ -42613,7 +42613,7 @@
         <v>4.2</v>
       </c>
       <c r="F1507" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1508">
@@ -42641,7 +42641,7 @@
         <v>4</v>
       </c>
       <c r="F1508" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1509">
@@ -42669,7 +42669,7 @@
         <v>3.9</v>
       </c>
       <c r="F1509" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="1510">
@@ -42697,7 +42697,7 @@
         <v>3.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1511">
@@ -42722,7 +42722,7 @@
         </is>
       </c>
       <c r="E1511" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F1511" t="n">
         <v>45.5</v>
@@ -42781,7 +42781,7 @@
         <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1514">
@@ -42806,10 +42806,10 @@
         </is>
       </c>
       <c r="E1514" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1514" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1515">
@@ -42837,7 +42837,7 @@
         <v>2.4</v>
       </c>
       <c r="F1515" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1516">
@@ -42865,7 +42865,7 @@
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1517">
@@ -42893,7 +42893,7 @@
         <v>2.3</v>
       </c>
       <c r="F1517" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1518">
@@ -42921,7 +42921,7 @@
         <v>2.2</v>
       </c>
       <c r="F1518" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1519">
@@ -42949,7 +42949,7 @@
         <v>2.1</v>
       </c>
       <c r="F1519" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1521">
@@ -43005,7 +43005,7 @@
         <v>2</v>
       </c>
       <c r="F1521" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1522">
@@ -43033,7 +43033,7 @@
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1524">
@@ -43117,7 +43117,7 @@
         <v>1.7</v>
       </c>
       <c r="F1525" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1526">
@@ -43145,7 +43145,7 @@
         <v>1.7</v>
       </c>
       <c r="F1526" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1527">
@@ -43201,7 +43201,7 @@
         <v>1.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1529">
@@ -43229,7 +43229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="1530">
@@ -43245,19 +43245,19 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1530" t="n">
         <v>1.3</v>
       </c>
       <c r="F1530" t="n">
-        <v>44.6</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1531">
@@ -43273,19 +43273,19 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1531" t="n">
         <v>1.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>46.2</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1532">
@@ -43341,7 +43341,7 @@
         <v>1.3</v>
       </c>
       <c r="F1533" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>1</v>
       </c>
       <c r="F1534" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1535">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>39.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>0.9</v>
       </c>
       <c r="F1536" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>44</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1538">
@@ -43481,7 +43481,7 @@
         <v>0.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="1539">
@@ -43509,7 +43509,7 @@
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1540">
@@ -43534,7 +43534,7 @@
         </is>
       </c>
       <c r="E1540" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1540" t="n">
         <v>41.7</v>
@@ -43565,7 +43565,7 @@
         <v>0.7</v>
       </c>
       <c r="F1541" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="1542">
@@ -43646,7 +43646,7 @@
         </is>
       </c>
       <c r="E1544" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1544" t="n">
         <v>42.3</v>
@@ -43665,19 +43665,19 @@
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1545" t="n">
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>40.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1546">
@@ -43693,19 +43693,19 @@
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1546" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>47.5</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1547">
@@ -43733,7 +43733,7 @@
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="1548">
@@ -43789,7 +43789,7 @@
         <v>0.3</v>
       </c>
       <c r="F1549" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="1550">
@@ -43817,7 +43817,7 @@
         <v>0.3</v>
       </c>
       <c r="F1550" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="1551">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="F52" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="53">
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26</v>
+        <v>26.7</v>
       </c>
       <c r="F53" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="54">
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>25.3</v>
+        <v>24.7</v>
       </c>
       <c r="F54" t="n">
-        <v>49.2</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="55">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="F55" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="56">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>21.4</v>
+        <v>20.4</v>
       </c>
       <c r="F56" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="57">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="F57" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="F58" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="F59" t="n">
-        <v>55.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="60">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="F60" t="n">
-        <v>47.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="61">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="F61" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="62">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="F62" t="n">
-        <v>49.5</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="63">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
-        <v>47.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="64">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F64" t="n">
-        <v>51.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="65">
@@ -2225,19 +2225,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="F65" t="n">
-        <v>52.6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
@@ -2253,19 +2253,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="F66" t="n">
-        <v>50.7</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="67">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="F67" t="n">
-        <v>52.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="68">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F68" t="n">
-        <v>55.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
@@ -2337,19 +2337,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="F69" t="n">
-        <v>47.3</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="70">
@@ -2365,19 +2365,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F70" t="n">
-        <v>45.7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -2393,19 +2393,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="F71" t="n">
-        <v>49.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="72">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>51.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="F73" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="74">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="F74" t="n">
-        <v>46.9</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="75">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="76">
@@ -2545,7 +2545,7 @@
         <v>7.8</v>
       </c>
       <c r="F76" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="77">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>7.4</v>
       </c>
       <c r="F77" t="n">
-        <v>52.3</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="78">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>45.7</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="80">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="F80" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="81">
@@ -2685,7 +2685,7 @@
         <v>5.9</v>
       </c>
       <c r="F81" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="82">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="F82" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="83">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F83" t="n">
         <v>52</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F84" t="n">
-        <v>46.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="85">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="F85" t="n">
-        <v>44.9</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="86">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F86" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="87">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F87" t="n">
-        <v>46</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="88">
@@ -2869,19 +2869,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F88" t="n">
-        <v>49.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="89">
@@ -2897,19 +2897,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>4.4</v>
       </c>
       <c r="F89" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="90">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="F90" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="91">
@@ -2953,19 +2953,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F91" t="n">
-        <v>40.9</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="92">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F92" t="n">
-        <v>45.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="93">
@@ -3009,19 +3009,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F93" t="n">
-        <v>55.8</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="94">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="95">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="F95" t="n">
-        <v>53</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="96">
@@ -3093,19 +3093,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F96" t="n">
-        <v>48.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="97">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>2.6</v>
       </c>
       <c r="F97" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="98">
@@ -3149,19 +3149,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F98" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="99">
@@ -3177,19 +3177,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F99" t="n">
-        <v>49.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="100">
@@ -3205,19 +3205,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F100" t="n">
-        <v>45.7</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="101">
@@ -3245,7 +3245,7 @@
         <v>2.1</v>
       </c>
       <c r="F101" t="n">
-        <v>48.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="102">
@@ -34241,7 +34241,7 @@
         <v>3.1</v>
       </c>
       <c r="F1208" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1209">
@@ -34521,7 +34521,7 @@
         <v>2.3</v>
       </c>
       <c r="F1218" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1219">
@@ -34677,7 +34677,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -34689,7 +34689,7 @@
         <v>1.8</v>
       </c>
       <c r="F1224" t="n">
-        <v>49.1</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1225">
@@ -34705,7 +34705,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -34714,10 +34714,10 @@
         </is>
       </c>
       <c r="E1225" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F1225" t="n">
-        <v>53.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1226">
@@ -34885,7 +34885,7 @@
         <v>1.4</v>
       </c>
       <c r="F1231" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1232">
@@ -35249,7 +35249,7 @@
         <v>0.9</v>
       </c>
       <c r="F1244" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="1245">
@@ -35361,7 +35361,7 @@
         <v>0.7</v>
       </c>
       <c r="F1248" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1249">
@@ -35417,7 +35417,7 @@
         <v>0.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1251">
@@ -35557,7 +35557,7 @@
         <v>4.1</v>
       </c>
       <c r="F1255" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1256">
@@ -35697,7 +35697,7 @@
         <v>3.1</v>
       </c>
       <c r="F1260" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1261">
@@ -35781,7 +35781,7 @@
         <v>2.9</v>
       </c>
       <c r="F1263" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1264">
@@ -35865,7 +35865,7 @@
         <v>2.7</v>
       </c>
       <c r="F1266" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1267">
@@ -36257,7 +36257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1280" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1281">
@@ -36301,19 +36301,19 @@
       </c>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1282" t="n">
         <v>1.2</v>
       </c>
       <c r="F1282" t="n">
-        <v>51.1</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1283">
@@ -36329,19 +36329,19 @@
       </c>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1283" t="n">
         <v>1.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>46.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1284">
@@ -36369,7 +36369,7 @@
         <v>1.2</v>
       </c>
       <c r="F1284" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1285">
@@ -36397,7 +36397,7 @@
         <v>1.1</v>
       </c>
       <c r="F1285" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1286">
@@ -36453,7 +36453,7 @@
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1288">
@@ -36593,7 +36593,7 @@
         <v>0.9</v>
       </c>
       <c r="F1292" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1293">
@@ -36649,7 +36649,7 @@
         <v>0.8</v>
       </c>
       <c r="F1294" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1295">
@@ -36814,7 +36814,7 @@
         </is>
       </c>
       <c r="E1300" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F1300" t="n">
         <v>56.4</v>
@@ -37377,7 +37377,7 @@
         <v>2.1</v>
       </c>
       <c r="F1320" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1321">
@@ -37545,7 +37545,7 @@
         <v>1.7</v>
       </c>
       <c r="F1326" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1327">
@@ -37769,7 +37769,7 @@
         <v>1.2</v>
       </c>
       <c r="F1334" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1335">
@@ -37785,19 +37785,19 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1335" t="n">
         <v>1.2</v>
       </c>
       <c r="F1335" t="n">
-        <v>51</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1336">
@@ -37813,19 +37813,19 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1336" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1336" t="n">
         <v>1.2</v>
       </c>
       <c r="F1336" t="n">
-        <v>47.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1337">
@@ -37897,19 +37897,19 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1339" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1339" t="n">
         <v>1.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>47.1</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1340">
@@ -37925,19 +37925,19 @@
       </c>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1340" t="n">
         <v>1.1</v>
       </c>
       <c r="F1340" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1341">
@@ -37993,7 +37993,7 @@
         <v>1</v>
       </c>
       <c r="F1342" t="n">
-        <v>54.6</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1343">
@@ -38049,7 +38049,7 @@
         <v>0.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="1345">
@@ -38133,7 +38133,7 @@
         <v>0.7</v>
       </c>
       <c r="F1347" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1348">
@@ -38522,7 +38522,7 @@
         </is>
       </c>
       <c r="E1361" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F1361" t="n">
         <v>52.4</v>
@@ -38637,7 +38637,7 @@
         <v>2.6</v>
       </c>
       <c r="F1365" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1366">
@@ -38989,19 +38989,19 @@
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1378" t="n">
         <v>1.5</v>
       </c>
       <c r="F1378" t="n">
-        <v>49.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="1379">
@@ -39017,19 +39017,19 @@
       </c>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1379" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1379" t="n">
         <v>1.5</v>
       </c>
       <c r="F1379" t="n">
-        <v>43.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1380">
@@ -39169,7 +39169,7 @@
         <v>1.1</v>
       </c>
       <c r="F1384" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1385">
@@ -39253,7 +39253,7 @@
         <v>1.1</v>
       </c>
       <c r="F1387" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1388">
@@ -39297,19 +39297,19 @@
       </c>
       <c r="C1389" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1389" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1389" t="n">
         <v>1.1</v>
       </c>
       <c r="F1389" t="n">
-        <v>46.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1390">
@@ -39325,19 +39325,19 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1390" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1390" t="n">
         <v>1.1</v>
       </c>
       <c r="F1390" t="n">
-        <v>51.9</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1391">
@@ -39353,19 +39353,19 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1391" t="n">
         <v>1.1</v>
       </c>
       <c r="F1391" t="n">
-        <v>42.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1392">
@@ -39393,7 +39393,7 @@
         <v>1</v>
       </c>
       <c r="F1392" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="1393">
@@ -39477,7 +39477,7 @@
         <v>0.9</v>
       </c>
       <c r="F1395" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1396">
@@ -39505,7 +39505,7 @@
         <v>0.8</v>
       </c>
       <c r="F1396" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1397">
@@ -39589,7 +39589,7 @@
         <v>0.7</v>
       </c>
       <c r="F1399" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1400">
@@ -39673,7 +39673,7 @@
         <v>6.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1403">
@@ -40317,7 +40317,7 @@
         <v>1.7</v>
       </c>
       <c r="F1425" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1426">
@@ -40485,7 +40485,7 @@
         <v>1.4</v>
       </c>
       <c r="F1431" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1432">
@@ -40541,7 +40541,7 @@
         <v>1.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1434">
@@ -40653,7 +40653,7 @@
         <v>1.1</v>
       </c>
       <c r="F1437" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1438">
@@ -40681,7 +40681,7 @@
         <v>1</v>
       </c>
       <c r="F1438" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="1439">
@@ -40793,7 +40793,7 @@
         <v>0.9</v>
       </c>
       <c r="F1442" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1443">
@@ -40905,7 +40905,7 @@
         <v>0.8</v>
       </c>
       <c r="F1446" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1447">
@@ -40933,7 +40933,7 @@
         <v>0.8</v>
       </c>
       <c r="F1447" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1448">
@@ -40989,7 +40989,7 @@
         <v>0.7</v>
       </c>
       <c r="F1449" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1450">
@@ -41409,7 +41409,7 @@
         <v>2.6</v>
       </c>
       <c r="F1464" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1465">
@@ -41465,7 +41465,7 @@
         <v>2.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1467">
@@ -41490,10 +41490,10 @@
         </is>
       </c>
       <c r="E1467" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F1467" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1468">
@@ -41521,7 +41521,7 @@
         <v>2.2</v>
       </c>
       <c r="F1468" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1469">
@@ -41549,7 +41549,7 @@
         <v>2.2</v>
       </c>
       <c r="F1469" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1470">
@@ -41689,7 +41689,7 @@
         <v>1.9</v>
       </c>
       <c r="F1474" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1475">
@@ -41745,7 +41745,7 @@
         <v>1.8</v>
       </c>
       <c r="F1476" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1477">
@@ -41773,7 +41773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1478">
@@ -41829,7 +41829,7 @@
         <v>1.5</v>
       </c>
       <c r="F1479" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1480">
@@ -41857,7 +41857,7 @@
         <v>1.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1481">
@@ -42109,7 +42109,7 @@
         <v>0.9</v>
       </c>
       <c r="F1489" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1490">
@@ -42137,7 +42137,7 @@
         <v>0.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1491">
@@ -42193,7 +42193,7 @@
         <v>0.8</v>
       </c>
       <c r="F1492" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1493">
@@ -42221,7 +42221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1493" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1494">
@@ -42305,7 +42305,7 @@
         <v>0.6</v>
       </c>
       <c r="F1496" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1497">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>0.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>0.4</v>
       </c>
       <c r="F1500" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1501">
@@ -42473,7 +42473,7 @@
         <v>6.5</v>
       </c>
       <c r="F1502" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1503">
@@ -42501,7 +42501,7 @@
         <v>6.1</v>
       </c>
       <c r="F1503" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1504">
@@ -42526,10 +42526,10 @@
         </is>
       </c>
       <c r="E1504" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="F1504" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1505">
@@ -42557,7 +42557,7 @@
         <v>4.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1506">
@@ -42582,10 +42582,10 @@
         </is>
       </c>
       <c r="E1506" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1506" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1507">
@@ -42613,7 +42613,7 @@
         <v>4.2</v>
       </c>
       <c r="F1507" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1508">
@@ -42641,7 +42641,7 @@
         <v>4</v>
       </c>
       <c r="F1508" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1509">
@@ -42657,19 +42657,19 @@
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1509" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F1509" t="n">
-        <v>46.8</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="1510">
@@ -42685,19 +42685,19 @@
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1510" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>37.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1511">
@@ -42753,7 +42753,7 @@
         <v>3.1</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1513">
@@ -42781,7 +42781,7 @@
         <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1514">
@@ -42806,10 +42806,10 @@
         </is>
       </c>
       <c r="E1514" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1514" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1515">
@@ -42825,19 +42825,19 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1515" t="n">
         <v>2.4</v>
       </c>
       <c r="F1515" t="n">
-        <v>47.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1516">
@@ -42853,19 +42853,19 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1516" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>45.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1517">
@@ -42921,7 +42921,7 @@
         <v>2.2</v>
       </c>
       <c r="F1518" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1519">
@@ -42949,7 +42949,7 @@
         <v>2.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>45.1</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1521">
@@ -43005,7 +43005,7 @@
         <v>2</v>
       </c>
       <c r="F1521" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1522">
@@ -43033,7 +43033,7 @@
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1524">
@@ -43089,7 +43089,7 @@
         <v>1.8</v>
       </c>
       <c r="F1524" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1525">
@@ -43117,7 +43117,7 @@
         <v>1.8</v>
       </c>
       <c r="F1525" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1526">
@@ -43145,7 +43145,7 @@
         <v>1.7</v>
       </c>
       <c r="F1526" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1527">
@@ -43170,10 +43170,10 @@
         </is>
       </c>
       <c r="E1527" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1527" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1528">
@@ -43201,7 +43201,7 @@
         <v>1.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1529">
@@ -43229,7 +43229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="1530">
@@ -43245,19 +43245,19 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1530" t="n">
         <v>1.3</v>
       </c>
       <c r="F1530" t="n">
-        <v>45</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1531">
@@ -43273,19 +43273,19 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1531" t="n">
         <v>1.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>48.2</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1532">
@@ -43313,7 +43313,7 @@
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1533">
@@ -43338,10 +43338,10 @@
         </is>
       </c>
       <c r="E1533" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1533" t="n">
-        <v>35.6</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>1</v>
       </c>
       <c r="F1534" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1535">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>0.9</v>
       </c>
       <c r="F1536" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>45.2</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1538">
@@ -43481,7 +43481,7 @@
         <v>0.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>41.8</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="1539">
@@ -43509,7 +43509,7 @@
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="1540">
@@ -43537,7 +43537,7 @@
         <v>0.7</v>
       </c>
       <c r="F1540" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1541">
@@ -43565,7 +43565,7 @@
         <v>0.7</v>
       </c>
       <c r="F1541" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="1542">
@@ -43593,7 +43593,7 @@
         <v>0.6</v>
       </c>
       <c r="F1542" t="n">
-        <v>37.4</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="1543">
@@ -43621,7 +43621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1543" t="n">
-        <v>49.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1544">
@@ -43646,7 +43646,7 @@
         </is>
       </c>
       <c r="E1544" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1544" t="n">
         <v>42.7</v>
@@ -43677,7 +43677,7 @@
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1546">
@@ -43705,7 +43705,7 @@
         <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="1547">
@@ -43733,7 +43733,7 @@
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="1548">
@@ -43761,7 +43761,7 @@
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>32.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="1549">
@@ -43789,7 +43789,7 @@
         <v>0.3</v>
       </c>
       <c r="F1549" t="n">
-        <v>32.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1550">
@@ -43845,7 +43845,7 @@
         <v>0.3</v>
       </c>
       <c r="F1551" t="n">
-        <v>44.3</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1552">
@@ -43861,7 +43861,7 @@
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
@@ -43870,10 +43870,10 @@
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="F1552" t="n">
-        <v>43.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1553">
@@ -43889,7 +43889,7 @@
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
@@ -43898,10 +43898,10 @@
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="F1553" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1554">
@@ -43926,10 +43926,10 @@
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="F1554" t="n">
-        <v>35.6</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1555">
@@ -43954,7 +43954,7 @@
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="F1555" t="n">
         <v>48.4</v>
@@ -43973,7 +43973,7 @@
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
@@ -43982,10 +43982,10 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="F1556" t="n">
-        <v>63.5</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="1557">
@@ -44001,7 +44001,7 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
@@ -44010,10 +44010,10 @@
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F1557" t="n">
-        <v>3.8</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="1558">
@@ -44038,7 +44038,7 @@
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="F1558" t="n">
         <v>22.2</v>
@@ -44066,10 +44066,10 @@
         </is>
       </c>
       <c r="E1559" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F1559" t="n">
-        <v>20.7</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="1560">
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F1560" t="n">
         <v>62.9</v>
@@ -44122,10 +44122,10 @@
         </is>
       </c>
       <c r="E1561" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="F1561" t="n">
-        <v>29.1</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1562">
@@ -44141,19 +44141,19 @@
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="F1562" t="n">
-        <v>28.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F1563" t="n">
-        <v>85.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="1564">
@@ -44197,19 +44197,19 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F1564" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="1565">
@@ -44225,19 +44225,19 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F1565" t="n">
-        <v>56</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="1566">
@@ -44253,7 +44253,7 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
@@ -44262,10 +44262,10 @@
         </is>
       </c>
       <c r="E1566" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F1566" t="n">
-        <v>66.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="1567">
@@ -44281,16 +44281,16 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F1567" t="n">
         <v>0</v>
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1568" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F1568" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1569">
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="E1569" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F1569" t="n">
         <v>79.2</v>
@@ -44374,7 +44374,7 @@
         </is>
       </c>
       <c r="E1570" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F1570" t="n">
         <v>41.8</v>
@@ -44402,7 +44402,7 @@
         </is>
       </c>
       <c r="E1571" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F1571" t="n">
         <v>62.7</v>
@@ -44430,7 +44430,7 @@
         </is>
       </c>
       <c r="E1572" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F1572" t="n">
         <v>0</v>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1578"/>
+  <dimension ref="A1:F1580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34213,7 +34213,7 @@
         <v>3.1</v>
       </c>
       <c r="F1207" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1208">
@@ -34649,19 +34649,19 @@
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1223" t="n">
         <v>1.8</v>
       </c>
       <c r="F1223" t="n">
-        <v>49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1224">
@@ -34677,19 +34677,19 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1224" t="n">
         <v>1.8</v>
       </c>
       <c r="F1224" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1225">
@@ -34941,7 +34941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1233" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1234">
@@ -34969,7 +34969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1234" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1235">
@@ -34997,7 +34997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1235" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1236">
@@ -35053,7 +35053,7 @@
         <v>1.1</v>
       </c>
       <c r="F1237" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1238">
@@ -35221,7 +35221,7 @@
         <v>1</v>
       </c>
       <c r="F1243" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1244">
@@ -35249,7 +35249,7 @@
         <v>0.9</v>
       </c>
       <c r="F1244" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1245">
@@ -35417,7 +35417,7 @@
         <v>0.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1251">
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="E1262" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F1262" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1263">
@@ -35778,7 +35778,7 @@
         </is>
       </c>
       <c r="E1263" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F1263" t="n">
         <v>51.5</v>
@@ -35809,7 +35809,7 @@
         <v>2.8</v>
       </c>
       <c r="F1264" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1265">
@@ -35890,7 +35890,7 @@
         </is>
       </c>
       <c r="E1267" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1267" t="n">
         <v>47.8</v>
@@ -35921,7 +35921,7 @@
         <v>2.5</v>
       </c>
       <c r="F1268" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1269">
@@ -35949,7 +35949,7 @@
         <v>2.5</v>
       </c>
       <c r="F1269" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1270">
@@ -35977,7 +35977,7 @@
         <v>2.3</v>
       </c>
       <c r="F1270" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1271">
@@ -36005,7 +36005,7 @@
         <v>2</v>
       </c>
       <c r="F1271" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1272">
@@ -36061,7 +36061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1273" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1274">
@@ -36117,7 +36117,7 @@
         <v>1.8</v>
       </c>
       <c r="F1275" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1276">
@@ -36145,7 +36145,7 @@
         <v>1.8</v>
       </c>
       <c r="F1276" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1277">
@@ -36257,7 +36257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1280" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1281">
@@ -36397,7 +36397,7 @@
         <v>1.1</v>
       </c>
       <c r="F1285" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1286">
@@ -36425,7 +36425,7 @@
         <v>1.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1287">
@@ -36441,19 +36441,19 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1287" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1287" t="n">
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>44.5</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1288">
@@ -36469,19 +36469,19 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1288" t="n">
         <v>1.1</v>
       </c>
       <c r="F1288" t="n">
-        <v>53.2</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1289">
@@ -36509,7 +36509,7 @@
         <v>1</v>
       </c>
       <c r="F1289" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1290">
@@ -36565,7 +36565,7 @@
         <v>1</v>
       </c>
       <c r="F1291" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1292">
@@ -36581,19 +36581,19 @@
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1292" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1292" t="n">
         <v>0.9</v>
       </c>
       <c r="F1292" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1293">
@@ -36609,19 +36609,19 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1293" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1293" t="n">
         <v>0.9</v>
       </c>
       <c r="F1293" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1294">
@@ -36649,7 +36649,7 @@
         <v>0.8</v>
       </c>
       <c r="F1294" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1295">
@@ -36665,19 +36665,19 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1295" t="n">
         <v>0.7</v>
       </c>
       <c r="F1295" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1296">
@@ -36693,19 +36693,19 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1296" t="n">
         <v>0.7</v>
       </c>
       <c r="F1296" t="n">
-        <v>48.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1297">
@@ -36733,7 +36733,7 @@
         <v>0.6</v>
       </c>
       <c r="F1297" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1298">
@@ -36789,7 +36789,7 @@
         <v>0.5</v>
       </c>
       <c r="F1299" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1300">
@@ -36814,7 +36814,7 @@
         </is>
       </c>
       <c r="E1300" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1300" t="n">
         <v>56.4</v>
@@ -36985,7 +36985,7 @@
         <v>4</v>
       </c>
       <c r="F1306" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1307">
@@ -37545,7 +37545,7 @@
         <v>1.7</v>
       </c>
       <c r="F1326" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1327">
@@ -37657,7 +37657,7 @@
         <v>1.4</v>
       </c>
       <c r="F1330" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1331">
@@ -37981,19 +37981,19 @@
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1342" t="n">
         <v>1</v>
       </c>
       <c r="F1342" t="n">
-        <v>54.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1343">
@@ -38009,19 +38009,19 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1343" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1343" t="n">
         <v>1</v>
       </c>
       <c r="F1343" t="n">
-        <v>43.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1344">
@@ -38049,7 +38049,7 @@
         <v>0.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1345">
@@ -38889,7 +38889,7 @@
         <v>1.7</v>
       </c>
       <c r="F1374" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1375">
@@ -38973,7 +38973,7 @@
         <v>1.6</v>
       </c>
       <c r="F1377" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1378">
@@ -39113,7 +39113,7 @@
         <v>1.2</v>
       </c>
       <c r="F1382" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1383">
@@ -39241,19 +39241,19 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1387" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1387" t="n">
         <v>1.1</v>
       </c>
       <c r="F1387" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1388">
@@ -39269,19 +39269,19 @@
       </c>
       <c r="C1388" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1388" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1388" t="n">
         <v>1.1</v>
       </c>
       <c r="F1388" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1389">
@@ -39309,7 +39309,7 @@
         <v>1.1</v>
       </c>
       <c r="F1389" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1390">
@@ -39393,7 +39393,7 @@
         <v>1</v>
       </c>
       <c r="F1392" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1393">
@@ -39561,7 +39561,7 @@
         <v>0.8</v>
       </c>
       <c r="F1398" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1399">
@@ -39701,7 +39701,7 @@
         <v>6.1</v>
       </c>
       <c r="F1403" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1404">
@@ -40261,7 +40261,7 @@
         <v>1.9</v>
       </c>
       <c r="F1423" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1424">
@@ -40401,7 +40401,7 @@
         <v>1.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1429">
@@ -40429,7 +40429,7 @@
         <v>1.6</v>
       </c>
       <c r="F1429" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1430">
@@ -40485,7 +40485,7 @@
         <v>1.4</v>
       </c>
       <c r="F1431" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1432">
@@ -40597,7 +40597,7 @@
         <v>1.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1436">
@@ -40681,7 +40681,7 @@
         <v>1</v>
       </c>
       <c r="F1438" t="n">
-        <v>38.5</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="1439">
@@ -40877,7 +40877,7 @@
         <v>0.8</v>
       </c>
       <c r="F1445" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1446">
@@ -40905,7 +40905,7 @@
         <v>0.8</v>
       </c>
       <c r="F1446" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1447">
@@ -40989,7 +40989,7 @@
         <v>0.7</v>
       </c>
       <c r="F1449" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1450">
@@ -41269,7 +41269,7 @@
         <v>3.2</v>
       </c>
       <c r="F1459" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1460">
@@ -41325,7 +41325,7 @@
         <v>2.9</v>
       </c>
       <c r="F1461" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1462">
@@ -41381,7 +41381,7 @@
         <v>2.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1464">
@@ -41490,7 +41490,7 @@
         </is>
       </c>
       <c r="E1467" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1467" t="n">
         <v>50</v>
@@ -41521,7 +41521,7 @@
         <v>2.2</v>
       </c>
       <c r="F1468" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1469">
@@ -41537,19 +41537,19 @@
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1469" t="n">
         <v>2.2</v>
       </c>
       <c r="F1469" t="n">
-        <v>52.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1470">
@@ -41565,19 +41565,19 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1470" t="n">
         <v>2.2</v>
       </c>
       <c r="F1470" t="n">
-        <v>49.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1471">
@@ -41633,7 +41633,7 @@
         <v>2</v>
       </c>
       <c r="F1472" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1473">
@@ -41773,7 +41773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1478">
@@ -41913,7 +41913,7 @@
         <v>1.3</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1483">
@@ -41969,7 +41969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1484" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1485">
@@ -41997,7 +41997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1485" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1486">
@@ -42081,7 +42081,7 @@
         <v>1</v>
       </c>
       <c r="F1488" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1489">
@@ -42109,7 +42109,7 @@
         <v>0.9</v>
       </c>
       <c r="F1489" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1490">
@@ -42137,7 +42137,7 @@
         <v>0.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="1491">
@@ -42165,7 +42165,7 @@
         <v>0.8</v>
       </c>
       <c r="F1491" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1492">
@@ -42249,7 +42249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1495">
@@ -42277,7 +42277,7 @@
         <v>0.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1496">
@@ -42305,7 +42305,7 @@
         <v>0.6</v>
       </c>
       <c r="F1496" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>0.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1498">
@@ -42389,7 +42389,7 @@
         <v>0.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>0.4</v>
       </c>
       <c r="F1500" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1501">
@@ -42473,7 +42473,7 @@
         <v>6.5</v>
       </c>
       <c r="F1502" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1503">
@@ -42498,7 +42498,7 @@
         </is>
       </c>
       <c r="E1503" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="F1503" t="n">
         <v>45.2</v>
@@ -42529,7 +42529,7 @@
         <v>5.4</v>
       </c>
       <c r="F1504" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1505">
@@ -42557,7 +42557,7 @@
         <v>4.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1506">
@@ -42573,19 +42573,19 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1506" t="n">
         <v>4.2</v>
       </c>
       <c r="F1506" t="n">
-        <v>48.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1507">
@@ -42601,19 +42601,19 @@
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1507" t="n">
         <v>4.2</v>
       </c>
       <c r="F1507" t="n">
-        <v>49.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1508">
@@ -42638,7 +42638,7 @@
         </is>
       </c>
       <c r="E1508" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1508" t="n">
         <v>44.6</v>
@@ -42697,7 +42697,7 @@
         <v>3.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1511">
@@ -42725,7 +42725,7 @@
         <v>3.4</v>
       </c>
       <c r="F1511" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1512">
@@ -42753,7 +42753,7 @@
         <v>3.1</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1513">
@@ -42781,7 +42781,7 @@
         <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1514">
@@ -42809,7 +42809,7 @@
         <v>2.5</v>
       </c>
       <c r="F1514" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1515">
@@ -42837,7 +42837,7 @@
         <v>2.4</v>
       </c>
       <c r="F1515" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1516">
@@ -42865,7 +42865,7 @@
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1517">
@@ -42893,7 +42893,7 @@
         <v>2.3</v>
       </c>
       <c r="F1517" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1518">
@@ -42909,19 +42909,19 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1518" t="n">
         <v>2.2</v>
       </c>
       <c r="F1518" t="n">
-        <v>50.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>2.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>45.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1520">
@@ -43033,7 +43033,7 @@
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>52.6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1523">
@@ -43117,7 +43117,7 @@
         <v>1.8</v>
       </c>
       <c r="F1525" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1526">
@@ -43145,7 +43145,7 @@
         <v>1.7</v>
       </c>
       <c r="F1526" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1527">
@@ -43170,10 +43170,10 @@
         </is>
       </c>
       <c r="E1527" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F1527" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1528">
@@ -43201,7 +43201,7 @@
         <v>1.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1529">
@@ -43229,7 +43229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>1.3</v>
       </c>
       <c r="F1530" t="n">
-        <v>47.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1531">
@@ -43285,7 +43285,7 @@
         <v>1.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1532">
@@ -43301,19 +43301,19 @@
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1532" t="n">
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>44.8</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="1533">
@@ -43329,19 +43329,19 @@
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1533" t="n">
         <v>1.3</v>
       </c>
       <c r="F1533" t="n">
-        <v>36.5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>1</v>
       </c>
       <c r="F1534" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="1535">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1536">
@@ -43413,19 +43413,19 @@
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1536" t="n">
         <v>0.9</v>
       </c>
       <c r="F1536" t="n">
-        <v>49.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1537">
@@ -43441,19 +43441,19 @@
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1537" t="n">
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>45.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1538">
@@ -43481,7 +43481,7 @@
         <v>0.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1539">
@@ -43537,7 +43537,7 @@
         <v>0.7</v>
       </c>
       <c r="F1540" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1541">
@@ -43565,7 +43565,7 @@
         <v>0.7</v>
       </c>
       <c r="F1541" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="1542">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
@@ -43590,10 +43590,10 @@
         </is>
       </c>
       <c r="E1542" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F1542" t="n">
-        <v>37.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1543">
@@ -43609,7 +43609,7 @@
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
@@ -43621,7 +43621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1543" t="n">
-        <v>51.2</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="1544">
@@ -43677,7 +43677,7 @@
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>47.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1546">
@@ -43721,19 +43721,19 @@
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1547" t="n">
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>34.6</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="1548">
@@ -43749,19 +43749,19 @@
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1548" t="n">
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>31.8</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="1549">
@@ -43789,7 +43789,7 @@
         <v>0.3</v>
       </c>
       <c r="F1549" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="1550">
@@ -43817,7 +43817,7 @@
         <v>0.3</v>
       </c>
       <c r="F1550" t="n">
-        <v>39.8</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1551">
@@ -43861,7 +43861,7 @@
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
@@ -43870,10 +43870,10 @@
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="F1552" t="n">
-        <v>44.9</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="1553">
@@ -43889,7 +43889,7 @@
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
@@ -43898,10 +43898,10 @@
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>17.2</v>
+        <v>16.2</v>
       </c>
       <c r="F1553" t="n">
-        <v>41.9</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1554">
@@ -43926,7 +43926,7 @@
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="F1554" t="n">
         <v>40.6</v>
@@ -43954,10 +43954,10 @@
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="F1555" t="n">
-        <v>48.4</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1556">
@@ -43982,7 +43982,7 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="F1556" t="n">
         <v>20.4</v>
@@ -44001,19 +44001,19 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F1557" t="n">
-        <v>63.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="1558">
@@ -44029,19 +44029,19 @@
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F1558" t="n">
-        <v>22.2</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="1559">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="E1559" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F1559" t="n">
         <v>17.8</v>
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F1560" t="n">
         <v>62.9</v>
@@ -44122,7 +44122,7 @@
         </is>
       </c>
       <c r="E1561" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F1561" t="n">
         <v>40.9</v>
@@ -44150,10 +44150,10 @@
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="F1562" t="n">
-        <v>6</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="1563">
@@ -44178,10 +44178,10 @@
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="F1563" t="n">
-        <v>73.90000000000001</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="1564">
@@ -44206,7 +44206,7 @@
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1564" t="n">
         <v>28.8</v>
@@ -44234,7 +44234,7 @@
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1565" t="n">
         <v>85.7</v>
@@ -44262,7 +44262,7 @@
         </is>
       </c>
       <c r="E1566" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1566" t="n">
         <v>11.1</v>
@@ -44290,7 +44290,7 @@
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1567" t="n">
         <v>0</v>
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="E1568" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1568" t="n">
         <v>56</v>
@@ -44337,19 +44337,19 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1569" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F1569" t="n">
-        <v>79.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1570">
@@ -44365,19 +44365,19 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1570" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F1570" t="n">
-        <v>41.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1571" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F1571" t="n">
-        <v>62.7</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,16 +44421,16 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1572" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F1572" t="n">
         <v>0</v>
@@ -44449,7 +44449,7 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
@@ -44458,10 +44458,10 @@
         </is>
       </c>
       <c r="E1573" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F1573" t="n">
-        <v>100</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1574" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F1574" t="n">
-        <v>0</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="1575">
@@ -44505,7 +44505,7 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1576" t="n">
         <v>0.5</v>
       </c>
       <c r="F1576" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1577">
@@ -44561,12 +44561,12 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1577" t="n">
@@ -44589,18 +44589,74 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1578" t="n">
         <v>0.5</v>
       </c>
       <c r="F1578" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>프레야</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>공격 · 수색가</t>
+        </is>
+      </c>
+      <c r="E1579" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>안란</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>공격 · 측면 공격가</t>
+        </is>
+      </c>
+      <c r="E1580" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1580" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>52.8</v>
+        <v>53.9</v>
       </c>
       <c r="F202" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="203">
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>41.1</v>
+        <v>39.8</v>
       </c>
       <c r="F203" t="n">
-        <v>48.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="204">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="F204" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="205">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="F205" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="206">
@@ -6173,19 +6173,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E206" t="n">
         <v>16</v>
       </c>
       <c r="F206" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="207">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="F207" t="n">
         <v>52</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="F208" t="n">
         <v>53</v>
@@ -6257,19 +6257,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E209" t="n">
         <v>14.4</v>
       </c>
       <c r="F209" t="n">
-        <v>45.4</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="210">
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="F210" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="211">
@@ -6313,19 +6313,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="F211" t="n">
-        <v>47.8</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="212">
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="F212" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="213">
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F213" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="214">
@@ -6409,7 +6409,7 @@
         <v>12.6</v>
       </c>
       <c r="F214" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="215">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F215" t="n">
-        <v>51.3</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="216">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F216" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="217">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="F217" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="218">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F218" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="219">
@@ -6549,7 +6549,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F219" t="n">
-        <v>46.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="220">
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F220" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="221">
@@ -6605,7 +6605,7 @@
         <v>8.6</v>
       </c>
       <c r="F221" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="222">
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F222" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="223">
@@ -6649,19 +6649,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="F223" t="n">
-        <v>53.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="224">
@@ -6677,19 +6677,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F224" t="n">
-        <v>51</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="225">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F225" t="n">
-        <v>48.5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="226">
@@ -6733,19 +6733,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F226" t="n">
-        <v>45.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="227">
@@ -6761,19 +6761,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E227" t="n">
         <v>7.3</v>
       </c>
       <c r="F227" t="n">
-        <v>49.6</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="228">
@@ -6789,19 +6789,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="F228" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="229">
@@ -6817,19 +6817,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="F229" t="n">
-        <v>48.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="230">
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F230" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="231">
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="F231" t="n">
-        <v>50.3</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="232">
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="F232" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="233">
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="F233" t="n">
-        <v>45.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="234">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="F234" t="n">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="235">
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F235" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="236">
@@ -7013,19 +7013,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E236" t="n">
         <v>4.6</v>
       </c>
       <c r="F236" t="n">
-        <v>51</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="237">
@@ -7041,19 +7041,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F237" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="238">
@@ -7069,19 +7069,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F238" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="239">
@@ -7097,19 +7097,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F239" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="240">
@@ -7125,19 +7125,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E240" t="n">
         <v>4.2</v>
       </c>
       <c r="F240" t="n">
-        <v>53.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="241">
@@ -7153,19 +7153,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F241" t="n">
-        <v>50.3</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="242">
@@ -7181,19 +7181,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E242" t="n">
         <v>4</v>
       </c>
       <c r="F242" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="243">
@@ -7209,19 +7209,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E243" t="n">
         <v>3.9</v>
       </c>
       <c r="F243" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="244">
@@ -7249,7 +7249,7 @@
         <v>3.8</v>
       </c>
       <c r="F244" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="245">
@@ -7265,19 +7265,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E245" t="n">
         <v>3.7</v>
       </c>
       <c r="F245" t="n">
-        <v>50.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="246">
@@ -7305,7 +7305,7 @@
         <v>3.7</v>
       </c>
       <c r="F246" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="247">
@@ -7333,7 +7333,7 @@
         <v>3.5</v>
       </c>
       <c r="F247" t="n">
-        <v>48.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="248">
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F248" t="n">
         <v>51.7</v>
@@ -7389,7 +7389,7 @@
         <v>3.3</v>
       </c>
       <c r="F249" t="n">
-        <v>45.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="250">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7414,10 +7414,10 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F250" t="n">
-        <v>50.2</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="251">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7442,10 +7442,10 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F251" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="252">
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>50.3</v>
+        <v>51.5</v>
       </c>
       <c r="F302" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="303">
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>39.6</v>
+        <v>40.2</v>
       </c>
       <c r="F303" t="n">
-        <v>47.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="304">
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>26.7</v>
+        <v>27.6</v>
       </c>
       <c r="F304" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="305">
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="F305" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="306">
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="F306" t="n">
-        <v>53.3</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="307">
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="F307" t="n">
-        <v>53.4</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="308">
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="F308" t="n">
-        <v>50.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="309">
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>18.9</v>
+        <v>17.7</v>
       </c>
       <c r="F309" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="310">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="F310" t="n">
-        <v>49.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="311">
@@ -9113,19 +9113,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="F311" t="n">
-        <v>54.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="312">
@@ -9141,19 +9141,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="F312" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="313">
@@ -9169,19 +9169,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="F313" t="n">
-        <v>51.6</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="314">
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="F314" t="n">
-        <v>47.8</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="315">
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="F315" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="316">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F316" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="317">
@@ -9293,7 +9293,7 @@
         <v>9.4</v>
       </c>
       <c r="F317" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="318">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F318" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="319">
@@ -9337,19 +9337,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F319" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="320">
@@ -9377,7 +9377,7 @@
         <v>7.9</v>
       </c>
       <c r="F320" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="321">
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F321" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="322">
@@ -9421,19 +9421,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F322" t="n">
-        <v>47</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="323">
@@ -9449,19 +9449,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="F323" t="n">
-        <v>48.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="324">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F324" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="325">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="F325" t="n">
-        <v>48.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="326">
@@ -9533,19 +9533,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="F326" t="n">
-        <v>52.3</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="327">
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="F327" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="328">
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="F328" t="n">
         <v>48.4</v>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="F329" t="n">
-        <v>49.3</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="330">
@@ -9645,19 +9645,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="F330" t="n">
-        <v>42.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="331">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9682,10 +9682,10 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="F331" t="n">
-        <v>45.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="332">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F332" t="n">
-        <v>49.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="333">
@@ -9729,19 +9729,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F333" t="n">
-        <v>54.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="334">
@@ -9757,19 +9757,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="F334" t="n">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="335">
@@ -9794,10 +9794,10 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F335" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="336">
@@ -9813,19 +9813,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="F336" t="n">
-        <v>45.2</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="337">
@@ -9841,19 +9841,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F337" t="n">
-        <v>43.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="338">
@@ -9869,19 +9869,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F338" t="n">
-        <v>47.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="339">
@@ -9906,10 +9906,10 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="F339" t="n">
-        <v>51.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="340">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="F340" t="n">
-        <v>46.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="341">
@@ -9953,19 +9953,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F341" t="n">
-        <v>44.7</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="342">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9993,7 +9993,7 @@
         <v>3.4</v>
       </c>
       <c r="F342" t="n">
-        <v>49.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="343">
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="F343" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="344">
@@ -10037,19 +10037,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F344" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="345">
@@ -10065,19 +10065,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="F345" t="n">
-        <v>44.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="346">
@@ -10105,7 +10105,7 @@
         <v>2.7</v>
       </c>
       <c r="F346" t="n">
-        <v>37.2</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="347">
@@ -10121,19 +10121,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F347" t="n">
-        <v>42.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="348">
@@ -10161,7 +10161,7 @@
         <v>2.5</v>
       </c>
       <c r="F348" t="n">
-        <v>50</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="349">
@@ -10177,19 +10177,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E349" t="n">
         <v>2.4</v>
       </c>
       <c r="F349" t="n">
-        <v>47.3</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="350">
@@ -10217,7 +10217,7 @@
         <v>2.4</v>
       </c>
       <c r="F350" t="n">
-        <v>43.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="351">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F351" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="352">
@@ -20070,7 +20070,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>42.3</v>
+        <v>41.2</v>
       </c>
       <c r="F702" t="n">
         <v>47.5</v>
@@ -20098,10 +20098,10 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>30</v>
+        <v>30.7</v>
       </c>
       <c r="F703" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="704">
@@ -20126,10 +20126,10 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="F704" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="705">
@@ -20154,10 +20154,10 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="F705" t="n">
-        <v>53.1</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="706">
@@ -20182,10 +20182,10 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="F706" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="707">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="F707" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="708">
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="F708" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="709">
@@ -20266,10 +20266,10 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="F709" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="710">
@@ -20294,10 +20294,10 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F710" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="711">
@@ -20322,10 +20322,10 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="F711" t="n">
-        <v>51.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="712">
@@ -20350,10 +20350,10 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="F712" t="n">
-        <v>49.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="713">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="F713" t="n">
         <v>51.4</v>
@@ -20406,10 +20406,10 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F714" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="715">
@@ -20434,10 +20434,10 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F715" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="716">
@@ -20453,19 +20453,19 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E716" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="F716" t="n">
-        <v>47.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="717">
@@ -20481,19 +20481,19 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E717" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F717" t="n">
-        <v>52.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="718">
@@ -20509,19 +20509,19 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="F718" t="n">
-        <v>50.6</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="719">
@@ -20537,19 +20537,19 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E719" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="F719" t="n">
-        <v>53.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="720">
@@ -20565,19 +20565,19 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E720" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="F720" t="n">
-        <v>54.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="721">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F721" t="n">
-        <v>48</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="722">
@@ -20621,19 +20621,19 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E722" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>47.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="723">
@@ -20658,10 +20658,10 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F723" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="724">
@@ -20686,10 +20686,10 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F724" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="725">
@@ -20714,10 +20714,10 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F725" t="n">
-        <v>48</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="726">
@@ -20733,19 +20733,19 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E726" t="n">
         <v>7.3</v>
       </c>
       <c r="F726" t="n">
-        <v>53.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="727">
@@ -20761,19 +20761,19 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F727" t="n">
-        <v>52.6</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="728">
@@ -20789,19 +20789,19 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F728" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="729">
@@ -20817,19 +20817,19 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E729" t="n">
         <v>7</v>
       </c>
       <c r="F729" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="730">
@@ -20845,19 +20845,19 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E730" t="n">
         <v>6.9</v>
       </c>
       <c r="F730" t="n">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="731">
@@ -20873,19 +20873,19 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="F731" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="732">
@@ -20913,7 +20913,7 @@
         <v>6.7</v>
       </c>
       <c r="F732" t="n">
-        <v>49.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="733">
@@ -20938,10 +20938,10 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="F733" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="734">
@@ -20966,10 +20966,10 @@
         </is>
       </c>
       <c r="E734" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F734" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="735">
@@ -20985,19 +20985,19 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F735" t="n">
-        <v>48.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="736">
@@ -21013,19 +21013,19 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E736" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F736" t="n">
-        <v>49.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="737">
@@ -21050,10 +21050,10 @@
         </is>
       </c>
       <c r="E737" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="F737" t="n">
-        <v>43.5</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="738">
@@ -21069,19 +21069,19 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E738" t="n">
         <v>5</v>
       </c>
       <c r="F738" t="n">
-        <v>54.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="739">
@@ -21097,19 +21097,19 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E739" t="n">
         <v>4.9</v>
       </c>
       <c r="F739" t="n">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="740">
@@ -21125,19 +21125,19 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F740" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="741">
@@ -21162,10 +21162,10 @@
         </is>
       </c>
       <c r="E741" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F741" t="n">
-        <v>53.7</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="742">
@@ -21181,19 +21181,19 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F742" t="n">
-        <v>52.8</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="743">
@@ -21218,10 +21218,10 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F743" t="n">
-        <v>46.6</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="744">
@@ -21249,7 +21249,7 @@
         <v>4</v>
       </c>
       <c r="F744" t="n">
-        <v>52.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="745">
@@ -21265,19 +21265,19 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="F745" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="746">
@@ -21293,19 +21293,19 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="F746" t="n">
-        <v>56.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="747">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -21330,10 +21330,10 @@
         </is>
       </c>
       <c r="E747" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F747" t="n">
-        <v>48.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="748">
@@ -21349,19 +21349,19 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F748" t="n">
-        <v>46.2</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="749">
@@ -21377,19 +21377,19 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="F749" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="750">
@@ -21405,19 +21405,19 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F750" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="751">
@@ -21442,10 +21442,10 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F751" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="752">
@@ -22870,10 +22870,10 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="F802" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="803">
@@ -22898,7 +22898,7 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="F803" t="n">
         <v>47.7</v>
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F804" t="n">
         <v>47.3</v>
@@ -22954,7 +22954,7 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F805" t="n">
         <v>49.9</v>
@@ -22982,7 +22982,7 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="F806" t="n">
         <v>48.4</v>
@@ -23010,10 +23010,10 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F807" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="808">
@@ -23038,10 +23038,10 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="F808" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="809">
@@ -23066,10 +23066,10 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="F809" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="810">
@@ -23094,10 +23094,10 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="F810" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="811">
@@ -23125,7 +23125,7 @@
         <v>15.5</v>
       </c>
       <c r="F811" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="812">
@@ -23141,19 +23141,19 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E812" t="n">
         <v>13.9</v>
       </c>
       <c r="F812" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="813">
@@ -23169,19 +23169,19 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E813" t="n">
         <v>13.8</v>
       </c>
       <c r="F813" t="n">
-        <v>50.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="814">
@@ -23197,19 +23197,19 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E814" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F814" t="n">
-        <v>51.7</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="815">
@@ -23225,19 +23225,19 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E815" t="n">
         <v>12.6</v>
       </c>
       <c r="F815" t="n">
-        <v>45.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="816">
@@ -23265,7 +23265,7 @@
         <v>12.1</v>
       </c>
       <c r="F816" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="817">
@@ -23309,19 +23309,19 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E818" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="F818" t="n">
-        <v>52.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="819">
@@ -23337,19 +23337,19 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E819" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="F819" t="n">
-        <v>53.2</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="820">
@@ -23377,7 +23377,7 @@
         <v>10.6</v>
       </c>
       <c r="F820" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="821">
@@ -23402,10 +23402,10 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F821" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="822">
@@ -23421,19 +23421,19 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E822" t="n">
         <v>9.4</v>
       </c>
       <c r="F822" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="823">
@@ -23449,19 +23449,19 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E823" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="F823" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="824">
@@ -23477,19 +23477,19 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E824" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="F824" t="n">
-        <v>51.9</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="825">
@@ -23505,19 +23505,19 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E825" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="F825" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="826">
@@ -23542,10 +23542,10 @@
         </is>
       </c>
       <c r="E826" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="F826" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="827">
@@ -23561,19 +23561,19 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E827" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F827" t="n">
-        <v>51.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="828">
@@ -23589,19 +23589,19 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E828" t="n">
         <v>7.8</v>
       </c>
       <c r="F828" t="n">
-        <v>47.5</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="829">
@@ -23617,19 +23617,19 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E829" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F829" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="830">
@@ -23654,10 +23654,10 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F830" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="831">
@@ -23682,7 +23682,7 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F831" t="n">
         <v>46.7</v>
@@ -23701,19 +23701,19 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E832" t="n">
         <v>5.7</v>
       </c>
       <c r="F832" t="n">
-        <v>50.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="833">
@@ -23729,19 +23729,19 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E833" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F833" t="n">
-        <v>50.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="834">
@@ -23757,19 +23757,19 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E834" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F834" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="835">
@@ -23785,19 +23785,19 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E835" t="n">
         <v>5.6</v>
       </c>
       <c r="F835" t="n">
-        <v>52.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="836">
@@ -23813,19 +23813,19 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E836" t="n">
         <v>5.6</v>
       </c>
       <c r="F836" t="n">
-        <v>47.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="837">
@@ -23853,7 +23853,7 @@
         <v>5.4</v>
       </c>
       <c r="F837" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="838">
@@ -23878,10 +23878,10 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="F838" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="839">
@@ -23906,10 +23906,10 @@
         </is>
       </c>
       <c r="E839" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F839" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="840">
@@ -23934,10 +23934,10 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F840" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="841">
@@ -23965,7 +23965,7 @@
         <v>4.9</v>
       </c>
       <c r="F841" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="842">
@@ -23981,19 +23981,19 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E842" t="n">
         <v>4.6</v>
       </c>
       <c r="F842" t="n">
-        <v>53.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="843">
@@ -24009,19 +24009,19 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E843" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F843" t="n">
-        <v>51.6</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="844">
@@ -24037,19 +24037,19 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E844" t="n">
         <v>4.3</v>
       </c>
       <c r="F844" t="n">
-        <v>46.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="845">
@@ -24077,7 +24077,7 @@
         <v>3.8</v>
       </c>
       <c r="F845" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="846">
@@ -24130,10 +24130,10 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F847" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="848">
@@ -24217,7 +24217,7 @@
         <v>2.8</v>
       </c>
       <c r="F850" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="851">
@@ -24242,10 +24242,10 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="F851" t="n">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="852">
@@ -25670,10 +25670,10 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="F902" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="903">
@@ -25698,7 +25698,7 @@
         </is>
       </c>
       <c r="E903" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F903" t="n">
         <v>47.7</v>
@@ -25726,10 +25726,10 @@
         </is>
       </c>
       <c r="E904" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="F904" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="905">
@@ -25754,10 +25754,10 @@
         </is>
       </c>
       <c r="E905" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="F905" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="906">
@@ -25782,10 +25782,10 @@
         </is>
       </c>
       <c r="E906" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="F906" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="907">
@@ -25810,10 +25810,10 @@
         </is>
       </c>
       <c r="E907" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="F907" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="908">
@@ -25838,10 +25838,10 @@
         </is>
       </c>
       <c r="E908" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="F908" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="909">
@@ -25869,7 +25869,7 @@
         <v>16.8</v>
       </c>
       <c r="F909" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="910">
@@ -25894,7 +25894,7 @@
         </is>
       </c>
       <c r="E910" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="F910" t="n">
         <v>49.4</v>
@@ -25922,10 +25922,10 @@
         </is>
       </c>
       <c r="E911" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="F911" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="912">
@@ -25953,7 +25953,7 @@
         <v>14.1</v>
       </c>
       <c r="F912" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="913">
@@ -25978,10 +25978,10 @@
         </is>
       </c>
       <c r="E913" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="F913" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="914">
@@ -26006,10 +26006,10 @@
         </is>
       </c>
       <c r="E914" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F914" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="915">
@@ -26025,19 +26025,19 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E915" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F915" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="916">
@@ -26053,19 +26053,19 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E916" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="F916" t="n">
-        <v>48.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="917">
@@ -26090,10 +26090,10 @@
         </is>
       </c>
       <c r="E917" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="F917" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="918">
@@ -26118,10 +26118,10 @@
         </is>
       </c>
       <c r="E918" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="F918" t="n">
-        <v>44.9</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="919">
@@ -26149,7 +26149,7 @@
         <v>11.7</v>
       </c>
       <c r="F919" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="920">
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="E920" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="F920" t="n">
         <v>53.3</v>
@@ -26205,7 +26205,7 @@
         <v>10.7</v>
       </c>
       <c r="F921" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="922">
@@ -26221,19 +26221,19 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E922" t="n">
         <v>9.6</v>
       </c>
       <c r="F922" t="n">
-        <v>52.1</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="923">
@@ -26249,19 +26249,19 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E923" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="F923" t="n">
-        <v>45.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="924">
@@ -26277,19 +26277,19 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E924" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F924" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="925">
@@ -26305,19 +26305,19 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E925" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="F925" t="n">
-        <v>50.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="926">
@@ -26333,19 +26333,19 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E926" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="F926" t="n">
-        <v>48.8</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="927">
@@ -26373,7 +26373,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F927" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="928">
@@ -26398,10 +26398,10 @@
         </is>
       </c>
       <c r="E928" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="F928" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="929">
@@ -26417,19 +26417,19 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E929" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F929" t="n">
-        <v>47.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="930">
@@ -26445,19 +26445,19 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E930" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="F930" t="n">
-        <v>50.3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="931">
@@ -26473,19 +26473,19 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E931" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F931" t="n">
-        <v>44.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="932">
@@ -26501,19 +26501,19 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E932" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F932" t="n">
-        <v>49.3</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="933">
@@ -26541,7 +26541,7 @@
         <v>5.9</v>
       </c>
       <c r="F933" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="934">
@@ -26594,10 +26594,10 @@
         </is>
       </c>
       <c r="E935" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F935" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="936">
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="E936" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F936" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="937">
@@ -26641,19 +26641,19 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E937" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F937" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="938">
@@ -26669,19 +26669,19 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E938" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F938" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="939">
@@ -26697,19 +26697,19 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E939" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F939" t="n">
-        <v>54.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="940">
@@ -26725,19 +26725,19 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E940" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F940" t="n">
-        <v>48.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="941">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -26762,10 +26762,10 @@
         </is>
       </c>
       <c r="E941" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F941" t="n">
-        <v>51.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="942">
@@ -26781,19 +26781,19 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E942" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F942" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="943">
@@ -26809,16 +26809,16 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E943" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F943" t="n">
         <v>51.7</v>
@@ -26849,7 +26849,7 @@
         <v>3.9</v>
       </c>
       <c r="F944" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="945">
@@ -26877,7 +26877,7 @@
         <v>3.7</v>
       </c>
       <c r="F945" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="946">
@@ -26905,7 +26905,7 @@
         <v>3.3</v>
       </c>
       <c r="F946" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="947">
@@ -26933,7 +26933,7 @@
         <v>3.2</v>
       </c>
       <c r="F947" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="948">
@@ -26961,7 +26961,7 @@
         <v>3.1</v>
       </c>
       <c r="F948" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="949">
@@ -27014,10 +27014,10 @@
         </is>
       </c>
       <c r="E950" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F950" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="951">
@@ -27045,7 +27045,7 @@
         <v>1.8</v>
       </c>
       <c r="F951" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="952">
@@ -28461,19 +28461,19 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1002" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="F1002" t="n">
-        <v>46.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1003">
@@ -28489,19 +28489,19 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1003" t="n">
         <v>31.2</v>
       </c>
       <c r="F1003" t="n">
-        <v>47.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1004">
@@ -28526,10 +28526,10 @@
         </is>
       </c>
       <c r="E1004" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="F1004" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1005">
@@ -28545,19 +28545,19 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1005" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="F1005" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1006">
@@ -28573,19 +28573,19 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1006" t="n">
         <v>20.2</v>
       </c>
       <c r="F1006" t="n">
-        <v>47.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1007">
@@ -28638,10 +28638,10 @@
         </is>
       </c>
       <c r="E1008" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="F1008" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1009">
@@ -28666,10 +28666,10 @@
         </is>
       </c>
       <c r="E1009" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="F1009" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1010">
@@ -28694,10 +28694,10 @@
         </is>
       </c>
       <c r="E1010" t="n">
-        <v>15.4</v>
+        <v>15.9</v>
       </c>
       <c r="F1010" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1011">
@@ -28750,10 +28750,10 @@
         </is>
       </c>
       <c r="E1012" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="F1012" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1013">
@@ -28778,7 +28778,7 @@
         </is>
       </c>
       <c r="E1013" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="F1013" t="n">
         <v>46.8</v>
@@ -28797,19 +28797,19 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1014" t="n">
         <v>12.6</v>
       </c>
       <c r="F1014" t="n">
-        <v>50.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1015">
@@ -28825,19 +28825,19 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1015" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="F1015" t="n">
-        <v>46</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1016">
@@ -28865,7 +28865,7 @@
         <v>12</v>
       </c>
       <c r="F1016" t="n">
-        <v>51.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1017">
@@ -28890,10 +28890,10 @@
         </is>
       </c>
       <c r="E1017" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F1017" t="n">
-        <v>49.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1018">
@@ -28918,10 +28918,10 @@
         </is>
       </c>
       <c r="E1018" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="F1018" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1019">
@@ -28949,7 +28949,7 @@
         <v>10.7</v>
       </c>
       <c r="F1019" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1020">
@@ -28977,7 +28977,7 @@
         <v>10.7</v>
       </c>
       <c r="F1020" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1021">
@@ -28993,19 +28993,19 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F1021" t="n">
-        <v>50.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1022">
@@ -29021,19 +29021,19 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1022" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F1022" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1023">
@@ -29049,19 +29049,19 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1023" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F1023" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1024">
@@ -29077,19 +29077,19 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1024" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F1024" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1025">
@@ -29117,7 +29117,7 @@
         <v>8.4</v>
       </c>
       <c r="F1025" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1026">
@@ -29133,19 +29133,19 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1026" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F1026" t="n">
-        <v>51.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1027">
@@ -29161,19 +29161,19 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1027" t="n">
         <v>7.8</v>
       </c>
       <c r="F1027" t="n">
-        <v>49</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1028">
@@ -29189,19 +29189,19 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1028" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="F1028" t="n">
-        <v>47.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1029">
@@ -29217,19 +29217,19 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1029" t="n">
         <v>7.3</v>
       </c>
       <c r="F1029" t="n">
-        <v>46.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1030">
@@ -29254,10 +29254,10 @@
         </is>
       </c>
       <c r="E1030" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F1030" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1031">
@@ -29285,7 +29285,7 @@
         <v>6.5</v>
       </c>
       <c r="F1031" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1032">
@@ -29310,10 +29310,10 @@
         </is>
       </c>
       <c r="E1032" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F1032" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1033">
@@ -29338,10 +29338,10 @@
         </is>
       </c>
       <c r="E1033" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F1033" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1034">
@@ -29366,10 +29366,10 @@
         </is>
       </c>
       <c r="E1034" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="F1034" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1035">
@@ -29397,7 +29397,7 @@
         <v>5.8</v>
       </c>
       <c r="F1035" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1036">
@@ -29425,7 +29425,7 @@
         <v>5.7</v>
       </c>
       <c r="F1036" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1037">
@@ -29453,7 +29453,7 @@
         <v>5.6</v>
       </c>
       <c r="F1037" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1038">
@@ -29478,10 +29478,10 @@
         </is>
       </c>
       <c r="E1038" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F1038" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1039">
@@ -29506,10 +29506,10 @@
         </is>
       </c>
       <c r="E1039" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F1039" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1040">
@@ -29534,10 +29534,10 @@
         </is>
       </c>
       <c r="E1040" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F1040" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1041">
@@ -29553,19 +29553,19 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1041" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F1041" t="n">
-        <v>53.5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1042">
@@ -29581,19 +29581,19 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1042" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1042" t="n">
-        <v>52.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1043">
@@ -29637,19 +29637,19 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1044" t="n">
         <v>4.1</v>
       </c>
       <c r="F1044" t="n">
-        <v>51.6</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1045">
@@ -29665,19 +29665,19 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1045" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F1045" t="n">
-        <v>47.8</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1046">
@@ -29693,7 +29693,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -29702,10 +29702,10 @@
         </is>
       </c>
       <c r="E1046" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1046" t="n">
-        <v>46.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1047">
@@ -29730,7 +29730,7 @@
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1047" t="n">
         <v>50.4</v>
@@ -29758,10 +29758,10 @@
         </is>
       </c>
       <c r="E1048" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F1048" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1049">
@@ -29805,19 +29805,19 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1050" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F1050" t="n">
-        <v>50.8</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="1051">
@@ -29833,19 +29833,19 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1051" t="n">
         <v>2.8</v>
       </c>
       <c r="F1051" t="n">
-        <v>53.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1052">
@@ -34157,7 +34157,7 @@
         <v>4.7</v>
       </c>
       <c r="F1205" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1206">
@@ -34565,19 +34565,19 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1220" t="n">
         <v>2</v>
       </c>
       <c r="F1220" t="n">
-        <v>46.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1221">
@@ -34593,19 +34593,19 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1221" t="n">
         <v>2</v>
       </c>
       <c r="F1221" t="n">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1222">
@@ -34941,7 +34941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1233" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1234">
@@ -34969,7 +34969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1234" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1235">
@@ -35053,7 +35053,7 @@
         <v>1.1</v>
       </c>
       <c r="F1237" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1238">
@@ -35165,7 +35165,7 @@
         <v>1.1</v>
       </c>
       <c r="F1241" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1242">
@@ -35221,7 +35221,7 @@
         <v>1</v>
       </c>
       <c r="F1243" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1244">
@@ -35246,10 +35246,10 @@
         </is>
       </c>
       <c r="E1244" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F1244" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1245">
@@ -35305,7 +35305,7 @@
         <v>0.9</v>
       </c>
       <c r="F1246" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1247">
@@ -35361,7 +35361,7 @@
         <v>0.7</v>
       </c>
       <c r="F1248" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1249">
@@ -35417,7 +35417,7 @@
         <v>0.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1251">
@@ -35498,7 +35498,7 @@
         </is>
       </c>
       <c r="E1253" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F1253" t="n">
         <v>51.4</v>
@@ -35613,7 +35613,7 @@
         <v>3.9</v>
       </c>
       <c r="F1257" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1258">
@@ -35809,7 +35809,7 @@
         <v>2.8</v>
       </c>
       <c r="F1264" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1265">
@@ -35921,7 +35921,7 @@
         <v>2.5</v>
       </c>
       <c r="F1268" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1269">
@@ -35949,7 +35949,7 @@
         <v>2.5</v>
       </c>
       <c r="F1269" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1270">
@@ -35977,7 +35977,7 @@
         <v>2.3</v>
       </c>
       <c r="F1270" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1271">
@@ -36005,7 +36005,7 @@
         <v>2</v>
       </c>
       <c r="F1271" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1272">
@@ -36089,7 +36089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1274" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1275">
@@ -36161,19 +36161,19 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1277" t="n">
         <v>1.7</v>
       </c>
       <c r="F1277" t="n">
-        <v>47.8</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1278">
@@ -36189,19 +36189,19 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1278" t="n">
         <v>1.7</v>
       </c>
       <c r="F1278" t="n">
-        <v>45.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1279">
@@ -36341,7 +36341,7 @@
         <v>1.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1284">
@@ -36453,7 +36453,7 @@
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1288">
@@ -36565,7 +36565,7 @@
         <v>1</v>
       </c>
       <c r="F1291" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1292">
@@ -36649,7 +36649,7 @@
         <v>0.8</v>
       </c>
       <c r="F1294" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1295">
@@ -36677,7 +36677,7 @@
         <v>0.7</v>
       </c>
       <c r="F1295" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1296">
@@ -36761,7 +36761,7 @@
         <v>0.5</v>
       </c>
       <c r="F1298" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1299">
@@ -36789,7 +36789,7 @@
         <v>0.5</v>
       </c>
       <c r="F1299" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1300">
@@ -36985,7 +36985,7 @@
         <v>4</v>
       </c>
       <c r="F1306" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1307">
@@ -37377,7 +37377,7 @@
         <v>2.1</v>
       </c>
       <c r="F1320" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1321">
@@ -37461,7 +37461,7 @@
         <v>1.8</v>
       </c>
       <c r="F1323" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1324">
@@ -37489,7 +37489,7 @@
         <v>1.8</v>
       </c>
       <c r="F1324" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1325">
@@ -37545,7 +37545,7 @@
         <v>1.7</v>
       </c>
       <c r="F1326" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1327">
@@ -38049,7 +38049,7 @@
         <v>0.9</v>
       </c>
       <c r="F1344" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="1345">
@@ -38077,7 +38077,7 @@
         <v>0.8</v>
       </c>
       <c r="F1345" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1346">
@@ -38189,7 +38189,7 @@
         <v>0.6</v>
       </c>
       <c r="F1349" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1350">
@@ -38245,7 +38245,7 @@
         <v>0.4</v>
       </c>
       <c r="F1351" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1352">
@@ -38525,7 +38525,7 @@
         <v>2.9</v>
       </c>
       <c r="F1361" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1362">
@@ -38877,19 +38877,19 @@
       </c>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1374" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F1374" t="n">
-        <v>50.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1375">
@@ -38905,19 +38905,19 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1375" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1375" t="n">
         <v>1.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>54</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1376">
@@ -39169,7 +39169,7 @@
         <v>1.1</v>
       </c>
       <c r="F1384" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1385">
@@ -39297,19 +39297,19 @@
       </c>
       <c r="C1389" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1389" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1389" t="n">
         <v>1.1</v>
       </c>
       <c r="F1389" t="n">
-        <v>42.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1390">
@@ -39325,19 +39325,19 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1390" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1390" t="n">
         <v>1.1</v>
       </c>
       <c r="F1390" t="n">
-        <v>46.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1391">
@@ -39393,7 +39393,7 @@
         <v>1</v>
       </c>
       <c r="F1392" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1393">
@@ -39561,7 +39561,7 @@
         <v>0.8</v>
       </c>
       <c r="F1398" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1399">
@@ -40034,10 +40034,10 @@
         </is>
       </c>
       <c r="E1415" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1415" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1416">
@@ -40081,19 +40081,19 @@
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1417" t="n">
         <v>2.2</v>
       </c>
       <c r="F1417" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1418">
@@ -40109,19 +40109,19 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1418" t="n">
         <v>2.2</v>
       </c>
       <c r="F1418" t="n">
-        <v>47.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1419">
@@ -40177,7 +40177,7 @@
         <v>2.1</v>
       </c>
       <c r="F1420" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1421">
@@ -40286,7 +40286,7 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F1424" t="n">
         <v>50.6</v>
@@ -40305,19 +40305,19 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1425" t="n">
         <v>1.7</v>
       </c>
       <c r="F1425" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1426">
@@ -40333,19 +40333,19 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1426" t="n">
         <v>1.7</v>
       </c>
       <c r="F1426" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1427">
@@ -40429,7 +40429,7 @@
         <v>1.6</v>
       </c>
       <c r="F1429" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1430">
@@ -40445,19 +40445,19 @@
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1430" t="n">
         <v>1.4</v>
       </c>
       <c r="F1430" t="n">
-        <v>49.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1431">
@@ -40473,19 +40473,19 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1431" t="n">
         <v>1.4</v>
       </c>
       <c r="F1431" t="n">
-        <v>51.2</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1432">
@@ -40541,7 +40541,7 @@
         <v>1.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1434">
@@ -40557,19 +40557,19 @@
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1434" t="n">
         <v>1.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>44.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1435">
@@ -40585,19 +40585,19 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1435" t="n">
         <v>1.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>51.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1436">
@@ -40641,19 +40641,19 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1437" t="n">
         <v>1.1</v>
       </c>
       <c r="F1437" t="n">
-        <v>48.1</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="1438">
@@ -40669,19 +40669,19 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1438" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1438" t="n">
-        <v>38.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1439">
@@ -40765,7 +40765,7 @@
         <v>0.9</v>
       </c>
       <c r="F1441" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1442">
@@ -40821,7 +40821,7 @@
         <v>0.9</v>
       </c>
       <c r="F1443" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1444">
@@ -41101,7 +41101,7 @@
         <v>6.5</v>
       </c>
       <c r="F1453" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1454">
@@ -41241,7 +41241,7 @@
         <v>3.2</v>
       </c>
       <c r="F1458" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1459">
@@ -41325,7 +41325,7 @@
         <v>2.9</v>
       </c>
       <c r="F1461" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1462">
@@ -41633,7 +41633,7 @@
         <v>2</v>
       </c>
       <c r="F1472" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1473">
@@ -41661,7 +41661,7 @@
         <v>2</v>
       </c>
       <c r="F1473" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1474">
@@ -41885,7 +41885,7 @@
         <v>1.3</v>
       </c>
       <c r="F1481" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1482">
@@ -41941,7 +41941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1484">
@@ -42025,7 +42025,7 @@
         <v>1.1</v>
       </c>
       <c r="F1486" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1487">
@@ -42053,7 +42053,7 @@
         <v>1</v>
       </c>
       <c r="F1487" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1488">
@@ -42081,7 +42081,7 @@
         <v>1</v>
       </c>
       <c r="F1488" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1489">
@@ -42134,10 +42134,10 @@
         </is>
       </c>
       <c r="E1490" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1490" t="n">
-        <v>38.6</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="1491">
@@ -42221,7 +42221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1493" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1494">
@@ -42277,7 +42277,7 @@
         <v>0.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1496">
@@ -42333,7 +42333,7 @@
         <v>0.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1499">
@@ -42445,7 +42445,7 @@
         <v>0.4</v>
       </c>
       <c r="F1501" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1502">
@@ -42498,10 +42498,10 @@
         </is>
       </c>
       <c r="E1503" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="F1503" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1504">
@@ -42529,7 +42529,7 @@
         <v>5.4</v>
       </c>
       <c r="F1504" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1505">
@@ -42585,7 +42585,7 @@
         <v>4.2</v>
       </c>
       <c r="F1506" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1507">
@@ -42641,7 +42641,7 @@
         <v>3.9</v>
       </c>
       <c r="F1508" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1509">
@@ -42669,7 +42669,7 @@
         <v>3.8</v>
       </c>
       <c r="F1509" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="1510">
@@ -42697,7 +42697,7 @@
         <v>3.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1511">
@@ -42725,7 +42725,7 @@
         <v>3.4</v>
       </c>
       <c r="F1511" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1512">
@@ -42753,7 +42753,7 @@
         <v>3.1</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1513">
@@ -42781,7 +42781,7 @@
         <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1514">
@@ -42809,7 +42809,7 @@
         <v>2.5</v>
       </c>
       <c r="F1514" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1515">
@@ -42837,7 +42837,7 @@
         <v>2.4</v>
       </c>
       <c r="F1515" t="n">
-        <v>45.4</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1516">
@@ -42853,19 +42853,19 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1516" t="n">
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>47.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1517" t="n">
         <v>2.4</v>
       </c>
       <c r="F1517" t="n">
-        <v>49.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1518">
@@ -42921,7 +42921,7 @@
         <v>2.2</v>
       </c>
       <c r="F1518" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>2.1</v>
       </c>
       <c r="F1519" t="n">
-        <v>50.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1520">
@@ -42965,19 +42965,19 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1520" t="n">
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>45.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1521">
@@ -43033,7 +43033,7 @@
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1524">
@@ -43086,10 +43086,10 @@
         </is>
       </c>
       <c r="E1524" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F1524" t="n">
-        <v>46.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1525">
@@ -43170,10 +43170,10 @@
         </is>
       </c>
       <c r="E1527" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1527" t="n">
-        <v>46.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1528">
@@ -43229,7 +43229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1531">
@@ -43285,7 +43285,7 @@
         <v>1.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1532">
@@ -43313,7 +43313,7 @@
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>37.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="1533">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>0.9</v>
       </c>
       <c r="F1536" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1538">
@@ -43481,7 +43481,7 @@
         <v>0.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>42.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="1539">
@@ -43534,10 +43534,10 @@
         </is>
       </c>
       <c r="E1540" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F1540" t="n">
-        <v>42</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1541">
@@ -43565,7 +43565,7 @@
         <v>0.7</v>
       </c>
       <c r="F1541" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1542">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
@@ -43593,7 +43593,7 @@
         <v>0.7</v>
       </c>
       <c r="F1542" t="n">
-        <v>51.1</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="1543">
@@ -43609,7 +43609,7 @@
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
@@ -43618,10 +43618,10 @@
         </is>
       </c>
       <c r="E1543" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F1543" t="n">
-        <v>37.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1544">
@@ -43677,7 +43677,7 @@
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>45.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1546">
@@ -43705,7 +43705,7 @@
         <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>40.4</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1547">
@@ -43721,19 +43721,19 @@
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1547" t="n">
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>33.6</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="1548">
@@ -43749,19 +43749,19 @@
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1548" t="n">
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>34.6</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="1549">
@@ -43789,7 +43789,7 @@
         <v>0.3</v>
       </c>
       <c r="F1549" t="n">
-        <v>36.1</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="1550">
@@ -43817,7 +43817,7 @@
         <v>0.3</v>
       </c>
       <c r="F1550" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="1551">
@@ -43845,7 +43845,7 @@
         <v>0.3</v>
       </c>
       <c r="F1551" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1552">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1586"/>
+  <dimension ref="A1:F1588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="F52" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="53">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="F53" t="n">
         <v>49.1</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="F54" t="n">
         <v>48.5</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="F55" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="56">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F56" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
@@ -2013,7 +2013,7 @@
         <v>19.4</v>
       </c>
       <c r="F57" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="58">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F58" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="59">
@@ -2069,7 +2069,7 @@
         <v>18.2</v>
       </c>
       <c r="F59" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="60">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="F61" t="n">
         <v>52.5</v>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="F62" t="n">
         <v>46.3</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F63" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="64">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="F64" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="65">
@@ -2237,7 +2237,7 @@
         <v>13.5</v>
       </c>
       <c r="F65" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F66" t="n">
         <v>53.1</v>
@@ -2293,7 +2293,7 @@
         <v>12.2</v>
       </c>
       <c r="F67" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="68">
@@ -2309,19 +2309,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F68" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
@@ -2337,19 +2337,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>10.8</v>
       </c>
       <c r="F69" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="70">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="F70" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="71">
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F71" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="72">
@@ -2433,7 +2433,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="73">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F73" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="74">
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="75">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F75" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="76">
@@ -2545,7 +2545,7 @@
         <v>7.9</v>
       </c>
       <c r="F76" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="77">
@@ -2573,7 +2573,7 @@
         <v>7.6</v>
       </c>
       <c r="F77" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="78">
@@ -2601,7 +2601,7 @@
         <v>7.1</v>
       </c>
       <c r="F78" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="79">
@@ -2629,7 +2629,7 @@
         <v>6.9</v>
       </c>
       <c r="F79" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="80">
@@ -2657,7 +2657,7 @@
         <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="81">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F81" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="82">
@@ -2713,7 +2713,7 @@
         <v>5.9</v>
       </c>
       <c r="F82" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="83">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F83" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="84">
@@ -2797,7 +2797,7 @@
         <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="86">
@@ -2825,7 +2825,7 @@
         <v>5</v>
       </c>
       <c r="F86" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="87">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="88">
@@ -2869,19 +2869,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>4.9</v>
       </c>
       <c r="F88" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="89">
@@ -2909,7 +2909,7 @@
         <v>4.5</v>
       </c>
       <c r="F89" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="90">
@@ -2937,7 +2937,7 @@
         <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>54.9</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="91">
@@ -2965,7 +2965,7 @@
         <v>3.8</v>
       </c>
       <c r="F91" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="92">
@@ -2993,7 +2993,7 @@
         <v>3.6</v>
       </c>
       <c r="F92" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="93">
@@ -3021,7 +3021,7 @@
         <v>3.5</v>
       </c>
       <c r="F93" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="94">
@@ -3037,19 +3037,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>3.2</v>
       </c>
       <c r="F94" t="n">
-        <v>52.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95">
@@ -3065,19 +3065,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F95" t="n">
-        <v>49.7</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="96">
@@ -3093,19 +3093,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>2.9</v>
       </c>
       <c r="F96" t="n">
-        <v>50.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F97" t="n">
-        <v>54.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="98">
@@ -3161,7 +3161,7 @@
         <v>2.5</v>
       </c>
       <c r="F98" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="99">
@@ -3189,7 +3189,7 @@
         <v>2.3</v>
       </c>
       <c r="F99" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="100">
@@ -3217,7 +3217,7 @@
         <v>2.3</v>
       </c>
       <c r="F100" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="101">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="F102" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="103">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="F103" t="n">
         <v>48.7</v>
@@ -3329,7 +3329,7 @@
         <v>24.4</v>
       </c>
       <c r="F104" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105">
@@ -3385,7 +3385,7 @@
         <v>19.7</v>
       </c>
       <c r="F106" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="107">
@@ -3469,7 +3469,7 @@
         <v>15.9</v>
       </c>
       <c r="F109" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="110">
@@ -3553,7 +3553,7 @@
         <v>14.7</v>
       </c>
       <c r="F112" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="113">
@@ -3581,7 +3581,7 @@
         <v>13.3</v>
       </c>
       <c r="F113" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="114">
@@ -3609,7 +3609,7 @@
         <v>12.5</v>
       </c>
       <c r="F114" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="115">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F117" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118">
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F119" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="120">
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="F120" t="n">
         <v>52.3</v>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F123" t="n">
         <v>53.1</v>
@@ -3889,7 +3889,7 @@
         <v>8.1</v>
       </c>
       <c r="F124" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="125">
@@ -3905,19 +3905,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E125" t="n">
         <v>8</v>
       </c>
       <c r="F125" t="n">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="126">
@@ -3933,19 +3933,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F126" t="n">
-        <v>50.8</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="127">
@@ -4001,7 +4001,7 @@
         <v>7.6</v>
       </c>
       <c r="F128" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="129">
@@ -4057,7 +4057,7 @@
         <v>6.7</v>
       </c>
       <c r="F130" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="131">
@@ -4085,7 +4085,7 @@
         <v>6.6</v>
       </c>
       <c r="F131" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="132">
@@ -4113,7 +4113,7 @@
         <v>6.6</v>
       </c>
       <c r="F132" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="133">
@@ -4169,7 +4169,7 @@
         <v>6.4</v>
       </c>
       <c r="F134" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="135">
@@ -4241,19 +4241,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F137" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="138">
@@ -4269,19 +4269,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E138" t="n">
         <v>4.5</v>
       </c>
       <c r="F138" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="139">
@@ -4309,7 +4309,7 @@
         <v>4.2</v>
       </c>
       <c r="F139" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140">
@@ -4337,7 +4337,7 @@
         <v>4.2</v>
       </c>
       <c r="F140" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="141">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F141" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="142">
@@ -4393,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="143">
@@ -4421,7 +4421,7 @@
         <v>3.8</v>
       </c>
       <c r="F143" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="144">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F145" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="146">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4505,7 +4505,7 @@
         <v>3.3</v>
       </c>
       <c r="F146" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="147">
@@ -4533,7 +4533,7 @@
         <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="148">
@@ -4561,7 +4561,7 @@
         <v>2.6</v>
       </c>
       <c r="F148" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="149">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F151" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="152">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="F152" t="n">
         <v>49.1</v>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="F153" t="n">
         <v>48</v>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="F155" t="n">
         <v>50.6</v>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="F157" t="n">
         <v>48</v>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F159" t="n">
         <v>52.8</v>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F161" t="n">
         <v>50.8</v>
@@ -5093,7 +5093,7 @@
         <v>11.4</v>
       </c>
       <c r="F167" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168">
@@ -5233,7 +5233,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="173">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F174" t="n">
         <v>48</v>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -5333,19 +5333,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E176" t="n">
         <v>8</v>
       </c>
       <c r="F176" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="177">
@@ -5401,7 +5401,7 @@
         <v>7.8</v>
       </c>
       <c r="F178" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="179">
@@ -5429,7 +5429,7 @@
         <v>7.4</v>
       </c>
       <c r="F179" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="180">
@@ -5457,7 +5457,7 @@
         <v>7.1</v>
       </c>
       <c r="F180" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="181">
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F181" t="n">
         <v>50</v>
@@ -5541,7 +5541,7 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="184">
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F185" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="186">
@@ -5669,19 +5669,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E188" t="n">
         <v>4.5</v>
       </c>
       <c r="F188" t="n">
-        <v>47.4</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="189">
@@ -5697,19 +5697,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F189" t="n">
-        <v>54.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="190">
@@ -5753,19 +5753,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F191" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="192">
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>4.1</v>
       </c>
       <c r="F192" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="193">
@@ -5821,7 +5821,7 @@
         <v>4</v>
       </c>
       <c r="F193" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="194">
@@ -5837,19 +5837,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E194" t="n">
         <v>3.8</v>
       </c>
       <c r="F194" t="n">
-        <v>52.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="195">
@@ -5865,19 +5865,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F195" t="n">
-        <v>47</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="196">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F196" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="197">
@@ -5989,7 +5989,7 @@
         <v>3</v>
       </c>
       <c r="F199" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="200">
@@ -6045,7 +6045,7 @@
         <v>2.6</v>
       </c>
       <c r="F201" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="202">
@@ -8901,7 +8901,7 @@
         <v>40.3</v>
       </c>
       <c r="F303" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="304">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="F304" t="n">
         <v>46.2</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="F305" t="n">
         <v>52.1</v>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="F306" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="307">
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="F308" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="309">
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F309" t="n">
         <v>54.6</v>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="F310" t="n">
         <v>47.6</v>
@@ -9125,7 +9125,7 @@
         <v>15.6</v>
       </c>
       <c r="F311" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="312">
@@ -9153,7 +9153,7 @@
         <v>13.9</v>
       </c>
       <c r="F312" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="313">
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="F313" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="314">
@@ -9209,7 +9209,7 @@
         <v>10.4</v>
       </c>
       <c r="F314" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="315">
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F315" t="n">
         <v>48.3</v>
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F316" t="n">
         <v>50.7</v>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F317" t="n">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="318">
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F318" t="n">
         <v>44.8</v>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F319" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="320">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="F320" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="321">
@@ -9405,7 +9405,7 @@
         <v>7.7</v>
       </c>
       <c r="F321" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="322">
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F322" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="323">
@@ -9477,19 +9477,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F324" t="n">
-        <v>46.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="325">
@@ -9505,19 +9505,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E325" t="n">
         <v>6.9</v>
       </c>
       <c r="F325" t="n">
-        <v>47.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="326">
@@ -9533,19 +9533,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E326" t="n">
         <v>6.9</v>
       </c>
       <c r="F326" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="327">
@@ -9573,7 +9573,7 @@
         <v>6.3</v>
       </c>
       <c r="F327" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="328">
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="F328" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="329">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F329" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="330">
@@ -9657,7 +9657,7 @@
         <v>5.3</v>
       </c>
       <c r="F330" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="331">
@@ -9685,7 +9685,7 @@
         <v>5.3</v>
       </c>
       <c r="F331" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="332">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F332" t="n">
         <v>46.3</v>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F333" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="334">
@@ -9757,19 +9757,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F334" t="n">
-        <v>41.8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="335">
@@ -9785,19 +9785,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E335" t="n">
         <v>4.9</v>
       </c>
       <c r="F335" t="n">
-        <v>54.4</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="336">
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F336" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="337">
@@ -9841,19 +9841,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F337" t="n">
-        <v>48.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="338">
@@ -9869,19 +9869,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F338" t="n">
-        <v>46.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="339">
@@ -9897,19 +9897,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F339" t="n">
-        <v>51.7</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="340">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9937,7 +9937,7 @@
         <v>4</v>
       </c>
       <c r="F340" t="n">
-        <v>48.6</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="341">
@@ -9953,19 +9953,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E341" t="n">
         <v>3.9</v>
       </c>
       <c r="F341" t="n">
-        <v>54</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="342">
@@ -9993,7 +9993,7 @@
         <v>3.3</v>
       </c>
       <c r="F342" t="n">
-        <v>50.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="343">
@@ -10021,7 +10021,7 @@
         <v>3.2</v>
       </c>
       <c r="F343" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="344">
@@ -10049,7 +10049,7 @@
         <v>3.2</v>
       </c>
       <c r="F344" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="345">
@@ -10065,19 +10065,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E345" t="n">
         <v>2.8</v>
       </c>
       <c r="F345" t="n">
-        <v>47.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="346">
@@ -10093,19 +10093,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F346" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="347">
@@ -10121,19 +10121,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="F347" t="n">
-        <v>46.4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="348">
@@ -10149,19 +10149,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E348" t="n">
         <v>2.6</v>
       </c>
       <c r="F348" t="n">
-        <v>36.5</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="349">
@@ -10186,10 +10186,10 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F349" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="350">
@@ -10217,7 +10217,7 @@
         <v>2.5</v>
       </c>
       <c r="F350" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="351">
@@ -10245,7 +10245,7 @@
         <v>2</v>
       </c>
       <c r="F351" t="n">
-        <v>49.3</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="352">
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="F602" t="n">
         <v>46.2</v>
@@ -17354,7 +17354,7 @@
         </is>
       </c>
       <c r="E605" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="F605" t="n">
         <v>46.8</v>
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="F607" t="n">
         <v>52.9</v>
@@ -17457,19 +17457,19 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="F609" t="n">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="610">
@@ -17485,19 +17485,19 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E610" t="n">
         <v>17.3</v>
       </c>
       <c r="F610" t="n">
-        <v>50.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="611">
@@ -17609,7 +17609,7 @@
         <v>13</v>
       </c>
       <c r="F614" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="615">
@@ -17637,7 +17637,7 @@
         <v>12.9</v>
       </c>
       <c r="F615" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="616">
@@ -17765,19 +17765,19 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F620" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="621">
@@ -17793,19 +17793,19 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E621" t="n">
         <v>9.5</v>
       </c>
       <c r="F621" t="n">
-        <v>51.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="622">
@@ -17821,19 +17821,19 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E622" t="n">
         <v>9.5</v>
       </c>
       <c r="F622" t="n">
-        <v>43.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="623">
@@ -17858,7 +17858,7 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F623" t="n">
         <v>52.8</v>
@@ -17886,7 +17886,7 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F624" t="n">
         <v>45.2</v>
@@ -17917,7 +17917,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F625" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="626">
@@ -17945,7 +17945,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F626" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="627">
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F627" t="n">
         <v>51.9</v>
@@ -18001,7 +18001,7 @@
         <v>7.5</v>
       </c>
       <c r="F628" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="629">
@@ -18029,7 +18029,7 @@
         <v>7.1</v>
       </c>
       <c r="F629" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="630">
@@ -18169,7 +18169,7 @@
         <v>6.5</v>
       </c>
       <c r="F634" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="635">
@@ -18197,7 +18197,7 @@
         <v>6.1</v>
       </c>
       <c r="F635" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="636">
@@ -18225,7 +18225,7 @@
         <v>5.8</v>
       </c>
       <c r="F636" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="637">
@@ -18309,7 +18309,7 @@
         <v>4.9</v>
       </c>
       <c r="F639" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="640">
@@ -18337,7 +18337,7 @@
         <v>4.6</v>
       </c>
       <c r="F640" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="641">
@@ -18362,7 +18362,7 @@
         </is>
       </c>
       <c r="E641" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F641" t="n">
         <v>51.7</v>
@@ -18393,7 +18393,7 @@
         <v>4.2</v>
       </c>
       <c r="F642" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="643">
@@ -18421,7 +18421,7 @@
         <v>4.1</v>
       </c>
       <c r="F643" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="644">
@@ -18521,19 +18521,19 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F647" t="n">
-        <v>53.4</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="648">
@@ -18549,19 +18549,19 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E648" t="n">
         <v>3.5</v>
       </c>
       <c r="F648" t="n">
-        <v>46.1</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="649">
@@ -18589,7 +18589,7 @@
         <v>3.3</v>
       </c>
       <c r="F649" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="650">
@@ -18645,7 +18645,7 @@
         <v>3</v>
       </c>
       <c r="F651" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="652">
@@ -21470,10 +21470,10 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F752" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="753">
@@ -21498,10 +21498,10 @@
         </is>
       </c>
       <c r="E753" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="F753" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="754">
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="E754" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="F754" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="755">
@@ -21554,7 +21554,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="F755" t="n">
         <v>47.2</v>
@@ -21582,7 +21582,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="F756" t="n">
         <v>49.1</v>
@@ -21613,7 +21613,7 @@
         <v>18.3</v>
       </c>
       <c r="F757" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="758">
@@ -21638,10 +21638,10 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F758" t="n">
-        <v>51.3</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="759">
@@ -21666,7 +21666,7 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="F759" t="n">
         <v>48.6</v>
@@ -21694,10 +21694,10 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="F760" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="761">
@@ -21722,10 +21722,10 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F761" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="762">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F762" t="n">
-        <v>51.3</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="763">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -21781,7 +21781,7 @@
         <v>12.1</v>
       </c>
       <c r="F763" t="n">
-        <v>55.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="764">
@@ -21806,10 +21806,10 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F764" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="765">
@@ -21834,10 +21834,10 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F765" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="766">
@@ -21865,7 +21865,7 @@
         <v>10.8</v>
       </c>
       <c r="F766" t="n">
-        <v>48.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="767">
@@ -21893,7 +21893,7 @@
         <v>10.5</v>
       </c>
       <c r="F767" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="768">
@@ -21918,10 +21918,10 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="F768" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="769">
@@ -21949,7 +21949,7 @@
         <v>9.4</v>
       </c>
       <c r="F769" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="770">
@@ -22005,7 +22005,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F771" t="n">
-        <v>53.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="772">
@@ -22030,10 +22030,10 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F772" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="773">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="F773" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="774">
@@ -22086,10 +22086,10 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F774" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="775">
@@ -22105,19 +22105,19 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E775" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="F775" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="776">
@@ -22133,19 +22133,19 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E776" t="n">
         <v>7.4</v>
       </c>
       <c r="F776" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="777">
@@ -22173,7 +22173,7 @@
         <v>7.4</v>
       </c>
       <c r="F777" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="778">
@@ -22189,19 +22189,19 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E778" t="n">
         <v>7.1</v>
       </c>
       <c r="F778" t="n">
-        <v>46.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="779">
@@ -22217,19 +22217,19 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E779" t="n">
         <v>7</v>
       </c>
       <c r="F779" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="780">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F780" t="n">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="781">
@@ -22282,10 +22282,10 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F781" t="n">
-        <v>54.7</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="782">
@@ -22301,19 +22301,19 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E782" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F782" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="783">
@@ -22329,19 +22329,19 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E783" t="n">
         <v>6.4</v>
       </c>
       <c r="F783" t="n">
-        <v>47.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="784">
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="F784" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="785">
@@ -22397,7 +22397,7 @@
         <v>6</v>
       </c>
       <c r="F785" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="786">
@@ -22422,10 +22422,10 @@
         </is>
       </c>
       <c r="E786" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F786" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="787">
@@ -22441,19 +22441,19 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E787" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F787" t="n">
-        <v>53</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="788">
@@ -22469,19 +22469,19 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E788" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F788" t="n">
-        <v>49.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="789">
@@ -22509,7 +22509,7 @@
         <v>4.9</v>
       </c>
       <c r="F789" t="n">
-        <v>45.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="790">
@@ -22534,10 +22534,10 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F790" t="n">
-        <v>46.4</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="791">
@@ -22562,10 +22562,10 @@
         </is>
       </c>
       <c r="E791" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F791" t="n">
-        <v>46.6</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="792">
@@ -22593,7 +22593,7 @@
         <v>4.2</v>
       </c>
       <c r="F792" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="793">
@@ -22618,10 +22618,10 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F793" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="794">
@@ -22646,10 +22646,10 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F794" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="795">
@@ -22665,19 +22665,19 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E795" t="n">
         <v>3.7</v>
       </c>
       <c r="F795" t="n">
-        <v>53.1</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="796">
@@ -22693,19 +22693,19 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E796" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F796" t="n">
-        <v>49.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="797">
@@ -22730,10 +22730,10 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F797" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="798">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F798" t="n">
-        <v>49.6</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="799">
@@ -22786,7 +22786,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F799" t="n">
         <v>53.4</v>
@@ -22817,7 +22817,7 @@
         <v>2.4</v>
       </c>
       <c r="F800" t="n">
-        <v>45.4</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="801">
@@ -22842,10 +22842,10 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F801" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="802">
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="F852" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="853">
@@ -24301,7 +24301,7 @@
         <v>26.5</v>
       </c>
       <c r="F853" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="854">
@@ -24326,10 +24326,10 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="F854" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="855">
@@ -24357,7 +24357,7 @@
         <v>21.3</v>
       </c>
       <c r="F855" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="856">
@@ -24413,7 +24413,7 @@
         <v>19.3</v>
       </c>
       <c r="F857" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="858">
@@ -24441,7 +24441,7 @@
         <v>18.8</v>
       </c>
       <c r="F858" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="859">
@@ -24469,7 +24469,7 @@
         <v>15.5</v>
       </c>
       <c r="F859" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="860">
@@ -24494,10 +24494,10 @@
         </is>
       </c>
       <c r="E860" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="F860" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="861">
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F861" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="862">
@@ -24550,10 +24550,10 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="F862" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="863">
@@ -24578,7 +24578,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="F863" t="n">
         <v>53.4</v>
@@ -24606,10 +24606,10 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F864" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="865">
@@ -24634,10 +24634,10 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F865" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="866">
@@ -24665,7 +24665,7 @@
         <v>12.2</v>
       </c>
       <c r="F866" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="867">
@@ -24693,7 +24693,7 @@
         <v>12.2</v>
       </c>
       <c r="F867" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="868">
@@ -24721,7 +24721,7 @@
         <v>11.8</v>
       </c>
       <c r="F868" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="869">
@@ -24749,7 +24749,7 @@
         <v>11.5</v>
       </c>
       <c r="F869" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="870">
@@ -24777,7 +24777,7 @@
         <v>11.3</v>
       </c>
       <c r="F870" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="871">
@@ -24805,7 +24805,7 @@
         <v>11.1</v>
       </c>
       <c r="F871" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="872">
@@ -24833,7 +24833,7 @@
         <v>11.1</v>
       </c>
       <c r="F872" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="873">
@@ -24849,19 +24849,19 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E873" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="F873" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="874">
@@ -24877,19 +24877,19 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E874" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F874" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="875">
@@ -24942,10 +24942,10 @@
         </is>
       </c>
       <c r="E876" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F876" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="877">
@@ -24973,7 +24973,7 @@
         <v>7.8</v>
       </c>
       <c r="F877" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="878">
@@ -25001,7 +25001,7 @@
         <v>7.4</v>
       </c>
       <c r="F878" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="879">
@@ -25029,7 +25029,7 @@
         <v>7.2</v>
       </c>
       <c r="F879" t="n">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="880">
@@ -25057,7 +25057,7 @@
         <v>7.1</v>
       </c>
       <c r="F880" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="881">
@@ -25085,7 +25085,7 @@
         <v>7</v>
       </c>
       <c r="F881" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="882">
@@ -25110,10 +25110,10 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F882" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="883">
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="E883" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F883" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="884">
@@ -25169,7 +25169,7 @@
         <v>6</v>
       </c>
       <c r="F884" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="885">
@@ -25197,7 +25197,7 @@
         <v>5.5</v>
       </c>
       <c r="F885" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="886">
@@ -25225,7 +25225,7 @@
         <v>5.4</v>
       </c>
       <c r="F886" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="887">
@@ -25241,19 +25241,19 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E887" t="n">
         <v>5.3</v>
       </c>
       <c r="F887" t="n">
-        <v>48.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="888">
@@ -25269,19 +25269,19 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E888" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F888" t="n">
-        <v>50.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="889">
@@ -25309,7 +25309,7 @@
         <v>4.1</v>
       </c>
       <c r="F889" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="890">
@@ -25334,10 +25334,10 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F890" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="891">
@@ -25365,7 +25365,7 @@
         <v>3.7</v>
       </c>
       <c r="F891" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="892">
@@ -25393,7 +25393,7 @@
         <v>3.6</v>
       </c>
       <c r="F892" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="893">
@@ -25421,7 +25421,7 @@
         <v>3.4</v>
       </c>
       <c r="F893" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="894">
@@ -25449,7 +25449,7 @@
         <v>3.3</v>
       </c>
       <c r="F894" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="895">
@@ -25477,7 +25477,7 @@
         <v>3.3</v>
       </c>
       <c r="F895" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="896">
@@ -25505,7 +25505,7 @@
         <v>3.2</v>
       </c>
       <c r="F896" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="897">
@@ -25533,7 +25533,7 @@
         <v>3.1</v>
       </c>
       <c r="F897" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="898">
@@ -25561,7 +25561,7 @@
         <v>2.8</v>
       </c>
       <c r="F898" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="899">
@@ -25589,7 +25589,7 @@
         <v>2.6</v>
       </c>
       <c r="F899" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="900">
@@ -25617,7 +25617,7 @@
         <v>2</v>
       </c>
       <c r="F900" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="901">
@@ -25645,7 +25645,7 @@
         <v>1.9</v>
       </c>
       <c r="F901" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="902">
@@ -27098,7 +27098,7 @@
         </is>
       </c>
       <c r="E953" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="F953" t="n">
         <v>46.9</v>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="E954" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="F954" t="n">
         <v>47.3</v>
@@ -27157,7 +27157,7 @@
         <v>21.5</v>
       </c>
       <c r="F955" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="956">
@@ -27210,10 +27210,10 @@
         </is>
       </c>
       <c r="E957" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="F957" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="958">
@@ -27238,7 +27238,7 @@
         </is>
       </c>
       <c r="E958" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="F958" t="n">
         <v>47.1</v>
@@ -27266,7 +27266,7 @@
         </is>
       </c>
       <c r="E959" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="F959" t="n">
         <v>48.2</v>
@@ -27297,7 +27297,7 @@
         <v>16.1</v>
       </c>
       <c r="F960" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="961">
@@ -27462,7 +27462,7 @@
         </is>
       </c>
       <c r="E966" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F966" t="n">
         <v>45.5</v>
@@ -27518,10 +27518,10 @@
         </is>
       </c>
       <c r="E968" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F968" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="969">
@@ -27546,10 +27546,10 @@
         </is>
       </c>
       <c r="E969" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F969" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="970">
@@ -27621,19 +27621,19 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E972" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F972" t="n">
-        <v>52.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="973">
@@ -27649,19 +27649,19 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E973" t="n">
         <v>9.5</v>
       </c>
       <c r="F973" t="n">
-        <v>50.7</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="974">
@@ -27686,7 +27686,7 @@
         </is>
       </c>
       <c r="E974" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F974" t="n">
         <v>51.4</v>
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="E975" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F975" t="n">
         <v>48.8</v>
@@ -27829,7 +27829,7 @@
         <v>7.5</v>
       </c>
       <c r="F979" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="980">
@@ -27857,7 +27857,7 @@
         <v>7.1</v>
       </c>
       <c r="F980" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="981">
@@ -27997,7 +27997,7 @@
         <v>5</v>
       </c>
       <c r="F985" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="986">
@@ -28041,19 +28041,19 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E987" t="n">
         <v>4.9</v>
       </c>
       <c r="F987" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="988">
@@ -28069,19 +28069,19 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E988" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F988" t="n">
-        <v>52.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="989">
@@ -28097,19 +28097,19 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E989" t="n">
         <v>4.8</v>
       </c>
       <c r="F989" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="990">
@@ -28193,7 +28193,7 @@
         <v>4.3</v>
       </c>
       <c r="F992" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="993">
@@ -28249,7 +28249,7 @@
         <v>4.2</v>
       </c>
       <c r="F994" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="995">
@@ -28277,7 +28277,7 @@
         <v>3.7</v>
       </c>
       <c r="F995" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="996">
@@ -28305,7 +28305,7 @@
         <v>3.5</v>
       </c>
       <c r="F996" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="997">
@@ -28321,19 +28321,19 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E997" t="n">
         <v>3.3</v>
       </c>
       <c r="F997" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="998">
@@ -28349,19 +28349,19 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E998" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F998" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="999">
@@ -28389,7 +28389,7 @@
         <v>2.9</v>
       </c>
       <c r="F999" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1000">
@@ -28417,7 +28417,7 @@
         <v>2.5</v>
       </c>
       <c r="F1000" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1001">
@@ -28445,7 +28445,7 @@
         <v>2.2</v>
       </c>
       <c r="F1001" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1002">
@@ -28470,7 +28470,7 @@
         </is>
       </c>
       <c r="E1002" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="F1002" t="n">
         <v>47.3</v>
@@ -28498,7 +28498,7 @@
         </is>
       </c>
       <c r="E1003" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="F1003" t="n">
         <v>46.3</v>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="E1007" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="F1007" t="n">
         <v>51.4</v>
@@ -28638,10 +28638,10 @@
         </is>
       </c>
       <c r="E1008" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="F1008" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1009">
@@ -28669,7 +28669,7 @@
         <v>16.8</v>
       </c>
       <c r="F1009" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1010">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="E1010" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="F1010" t="n">
         <v>51.1</v>
@@ -28722,10 +28722,10 @@
         </is>
       </c>
       <c r="E1011" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="F1011" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1012">
@@ -28781,7 +28781,7 @@
         <v>13.5</v>
       </c>
       <c r="F1013" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1014">
@@ -28809,7 +28809,7 @@
         <v>12.7</v>
       </c>
       <c r="F1014" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1015">
@@ -28837,7 +28837,7 @@
         <v>12.5</v>
       </c>
       <c r="F1015" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1016">
@@ -28865,7 +28865,7 @@
         <v>12</v>
       </c>
       <c r="F1016" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1017">
@@ -28890,7 +28890,7 @@
         </is>
       </c>
       <c r="E1017" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="F1017" t="n">
         <v>50</v>
@@ -28918,7 +28918,7 @@
         </is>
       </c>
       <c r="E1018" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F1018" t="n">
         <v>53.5</v>
@@ -28946,10 +28946,10 @@
         </is>
       </c>
       <c r="E1019" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F1019" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1020">
@@ -29058,10 +29058,10 @@
         </is>
       </c>
       <c r="E1023" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F1023" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1024">
@@ -29077,19 +29077,19 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1024" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F1024" t="n">
-        <v>50.4</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1025">
@@ -29105,19 +29105,19 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1025" t="n">
         <v>8.5</v>
       </c>
       <c r="F1025" t="n">
-        <v>45.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1026">
@@ -29173,7 +29173,7 @@
         <v>7.7</v>
       </c>
       <c r="F1027" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1028">
@@ -29229,7 +29229,7 @@
         <v>7.2</v>
       </c>
       <c r="F1029" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1030">
@@ -29257,7 +29257,7 @@
         <v>6.8</v>
       </c>
       <c r="F1030" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1031">
@@ -29285,7 +29285,7 @@
         <v>6.5</v>
       </c>
       <c r="F1031" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1032">
@@ -29301,19 +29301,19 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1032" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F1032" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1033">
@@ -29329,19 +29329,19 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1033" t="n">
         <v>6.2</v>
       </c>
       <c r="F1033" t="n">
-        <v>45.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1034">
@@ -29369,7 +29369,7 @@
         <v>5.9</v>
       </c>
       <c r="F1034" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1035">
@@ -29397,7 +29397,7 @@
         <v>5.9</v>
       </c>
       <c r="F1035" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1036">
@@ -29425,7 +29425,7 @@
         <v>5.7</v>
       </c>
       <c r="F1036" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1037">
@@ -29453,7 +29453,7 @@
         <v>5.6</v>
       </c>
       <c r="F1037" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1038">
@@ -29481,7 +29481,7 @@
         <v>5.4</v>
       </c>
       <c r="F1038" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1039">
@@ -29506,10 +29506,10 @@
         </is>
       </c>
       <c r="E1039" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F1039" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1040">
@@ -29565,7 +29565,7 @@
         <v>4.3</v>
       </c>
       <c r="F1041" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1042">
@@ -29593,7 +29593,7 @@
         <v>4.2</v>
       </c>
       <c r="F1042" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1043">
@@ -29621,7 +29621,7 @@
         <v>4.1</v>
       </c>
       <c r="F1043" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1044">
@@ -29677,7 +29677,7 @@
         <v>3.9</v>
       </c>
       <c r="F1045" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1046">
@@ -29705,7 +29705,7 @@
         <v>3.9</v>
       </c>
       <c r="F1046" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1047">
@@ -29733,7 +29733,7 @@
         <v>3.4</v>
       </c>
       <c r="F1047" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1048">
@@ -29761,7 +29761,7 @@
         <v>3.2</v>
       </c>
       <c r="F1048" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1049">
@@ -29845,7 +29845,7 @@
         <v>2.8</v>
       </c>
       <c r="F1051" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1052">
@@ -34229,19 +34229,19 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1208" t="n">
         <v>3.1</v>
       </c>
       <c r="F1208" t="n">
-        <v>49.7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1209">
@@ -34257,19 +34257,19 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1209" t="n">
         <v>3.1</v>
       </c>
       <c r="F1209" t="n">
-        <v>52</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1210">
@@ -34294,7 +34294,7 @@
         </is>
       </c>
       <c r="E1210" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1210" t="n">
         <v>46.2</v>
@@ -34773,7 +34773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1227" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1228">
@@ -35165,7 +35165,7 @@
         <v>1.1</v>
       </c>
       <c r="F1241" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1242">
@@ -35193,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="F1242" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1243">
@@ -35249,7 +35249,7 @@
         <v>1</v>
       </c>
       <c r="F1244" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="1245">
@@ -35333,7 +35333,7 @@
         <v>0.8</v>
       </c>
       <c r="F1247" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1248">
@@ -35473,7 +35473,7 @@
         <v>5.9</v>
       </c>
       <c r="F1252" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1253">
@@ -35641,7 +35641,7 @@
         <v>3.3</v>
       </c>
       <c r="F1258" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1259">
@@ -35697,7 +35697,7 @@
         <v>3.1</v>
       </c>
       <c r="F1260" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1261">
@@ -35893,7 +35893,7 @@
         <v>2.7</v>
       </c>
       <c r="F1267" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1268">
@@ -35949,7 +35949,7 @@
         <v>2.5</v>
       </c>
       <c r="F1269" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1270">
@@ -36089,7 +36089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1274" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1275">
@@ -36117,7 +36117,7 @@
         <v>1.8</v>
       </c>
       <c r="F1275" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1276">
@@ -36649,7 +36649,7 @@
         <v>0.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1295">
@@ -36677,7 +36677,7 @@
         <v>0.7</v>
       </c>
       <c r="F1295" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1296">
@@ -36705,7 +36705,7 @@
         <v>0.7</v>
       </c>
       <c r="F1296" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="1297">
@@ -36789,7 +36789,7 @@
         <v>0.5</v>
       </c>
       <c r="F1299" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1300">
@@ -36817,7 +36817,7 @@
         <v>0.5</v>
       </c>
       <c r="F1300" t="n">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="1301">
@@ -37097,7 +37097,7 @@
         <v>3.2</v>
       </c>
       <c r="F1310" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1311">
@@ -37125,7 +37125,7 @@
         <v>3.2</v>
       </c>
       <c r="F1311" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1312">
@@ -37785,19 +37785,19 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1335" t="n">
         <v>1.2</v>
       </c>
       <c r="F1335" t="n">
-        <v>50.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1336">
@@ -37813,19 +37813,19 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1336" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1336" t="n">
         <v>1.2</v>
       </c>
       <c r="F1336" t="n">
-        <v>47.2</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1337">
@@ -37881,7 +37881,7 @@
         <v>1.1</v>
       </c>
       <c r="F1338" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1339">
@@ -38049,7 +38049,7 @@
         <v>0.9</v>
       </c>
       <c r="F1344" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1345">
@@ -38217,7 +38217,7 @@
         <v>0.5</v>
       </c>
       <c r="F1350" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1351">
@@ -38497,7 +38497,7 @@
         <v>3</v>
       </c>
       <c r="F1360" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1361">
@@ -38513,19 +38513,19 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1361" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1361" t="n">
         <v>2.9</v>
       </c>
       <c r="F1361" t="n">
-        <v>52.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1362">
@@ -38541,19 +38541,19 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1362" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1362" t="n">
         <v>2.9</v>
       </c>
       <c r="F1362" t="n">
-        <v>46</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1363">
@@ -38945,7 +38945,7 @@
         <v>1.6</v>
       </c>
       <c r="F1376" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1377">
@@ -39213,19 +39213,19 @@
       </c>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1386" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1386" t="n">
         <v>1.1</v>
       </c>
       <c r="F1386" t="n">
-        <v>47.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1387">
@@ -39241,19 +39241,19 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1387" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1387" t="n">
         <v>1.1</v>
       </c>
       <c r="F1387" t="n">
-        <v>50.5</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1388">
@@ -39269,19 +39269,19 @@
       </c>
       <c r="C1388" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1388" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1388" t="n">
         <v>1.1</v>
       </c>
       <c r="F1388" t="n">
-        <v>46.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1389">
@@ -39297,19 +39297,19 @@
       </c>
       <c r="C1389" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1389" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1389" t="n">
         <v>1.1</v>
       </c>
       <c r="F1389" t="n">
-        <v>42.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1390">
@@ -39390,10 +39390,10 @@
         </is>
       </c>
       <c r="E1392" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1393">
@@ -39421,7 +39421,7 @@
         <v>1</v>
       </c>
       <c r="F1393" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1394">
@@ -39925,7 +39925,7 @@
         <v>2.8</v>
       </c>
       <c r="F1411" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>2.8</v>
       </c>
       <c r="F1412" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1413">
@@ -40081,19 +40081,19 @@
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1417" t="n">
         <v>2.2</v>
       </c>
       <c r="F1417" t="n">
-        <v>47.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1418">
@@ -40109,19 +40109,19 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1418" t="n">
         <v>2.2</v>
       </c>
       <c r="F1418" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1419">
@@ -40205,7 +40205,7 @@
         <v>2</v>
       </c>
       <c r="F1421" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1422">
@@ -40653,7 +40653,7 @@
         <v>1.1</v>
       </c>
       <c r="F1437" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1438">
@@ -40681,7 +40681,7 @@
         <v>1</v>
       </c>
       <c r="F1438" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1439">
@@ -40709,7 +40709,7 @@
         <v>1</v>
       </c>
       <c r="F1439" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1440">
@@ -40818,7 +40818,7 @@
         </is>
       </c>
       <c r="E1443" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1443" t="n">
         <v>47.7</v>
@@ -40989,7 +40989,7 @@
         <v>0.7</v>
       </c>
       <c r="F1449" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1450">
@@ -41129,7 +41129,7 @@
         <v>6.5</v>
       </c>
       <c r="F1454" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1455">
@@ -41269,7 +41269,7 @@
         <v>3.2</v>
       </c>
       <c r="F1459" t="n">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1460">
@@ -41381,7 +41381,7 @@
         <v>2.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1464">
@@ -41437,7 +41437,7 @@
         <v>2.4</v>
       </c>
       <c r="F1465" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1466">
@@ -41521,7 +41521,7 @@
         <v>2.2</v>
       </c>
       <c r="F1468" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1469">
@@ -41549,7 +41549,7 @@
         <v>2.2</v>
       </c>
       <c r="F1469" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1470">
@@ -41605,7 +41605,7 @@
         <v>2.1</v>
       </c>
       <c r="F1471" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1472">
@@ -41801,7 +41801,7 @@
         <v>1.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1479">
@@ -41829,7 +41829,7 @@
         <v>1.5</v>
       </c>
       <c r="F1479" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1480">
@@ -41997,7 +41997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1485" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1486">
@@ -42109,7 +42109,7 @@
         <v>0.9</v>
       </c>
       <c r="F1489" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="1490">
@@ -42190,7 +42190,7 @@
         </is>
       </c>
       <c r="E1492" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1492" t="n">
         <v>50.6</v>
@@ -42221,7 +42221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1493" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1494">
@@ -42277,7 +42277,7 @@
         <v>0.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1496">
@@ -42305,7 +42305,7 @@
         <v>0.6</v>
       </c>
       <c r="F1496" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>0.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>0.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="1500">
@@ -42473,7 +42473,7 @@
         <v>6.4</v>
       </c>
       <c r="F1502" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1503">
@@ -42501,7 +42501,7 @@
         <v>6</v>
       </c>
       <c r="F1503" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1504">
@@ -42526,10 +42526,10 @@
         </is>
       </c>
       <c r="E1504" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F1504" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1505">
@@ -42557,7 +42557,7 @@
         <v>4.6</v>
       </c>
       <c r="F1505" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1506">
@@ -42585,7 +42585,7 @@
         <v>4.2</v>
       </c>
       <c r="F1506" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1507">
@@ -42613,7 +42613,7 @@
         <v>4.2</v>
       </c>
       <c r="F1507" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1508">
@@ -42641,7 +42641,7 @@
         <v>3.9</v>
       </c>
       <c r="F1508" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1509">
@@ -42669,7 +42669,7 @@
         <v>3.8</v>
       </c>
       <c r="F1509" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1510">
@@ -42697,7 +42697,7 @@
         <v>3.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1511">
@@ -42725,7 +42725,7 @@
         <v>3.4</v>
       </c>
       <c r="F1511" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1512">
@@ -42753,7 +42753,7 @@
         <v>3</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1513">
@@ -42769,19 +42769,19 @@
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1513" t="n">
         <v>2.5</v>
       </c>
       <c r="F1513" t="n">
-        <v>42.9</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1514">
@@ -42797,19 +42797,19 @@
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1514" t="n">
         <v>2.5</v>
       </c>
       <c r="F1514" t="n">
-        <v>52</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1515">
@@ -42825,19 +42825,19 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1515" t="n">
         <v>2.5</v>
       </c>
       <c r="F1515" t="n">
-        <v>44.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1516">
@@ -42865,7 +42865,7 @@
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1517">
@@ -42893,7 +42893,7 @@
         <v>2.4</v>
       </c>
       <c r="F1517" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1518">
@@ -42949,7 +42949,7 @@
         <v>2.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>45.6</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1521">
@@ -43005,7 +43005,7 @@
         <v>2</v>
       </c>
       <c r="F1521" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1522">
@@ -43033,7 +43033,7 @@
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>53.1</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1524">
@@ -43089,7 +43089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1524" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1525">
@@ -43145,7 +43145,7 @@
         <v>1.8</v>
       </c>
       <c r="F1526" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1527">
@@ -43173,7 +43173,7 @@
         <v>1.7</v>
       </c>
       <c r="F1527" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1528">
@@ -43201,7 +43201,7 @@
         <v>1.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1529">
@@ -43229,7 +43229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>49.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="1531">
@@ -43282,10 +43282,10 @@
         </is>
       </c>
       <c r="E1531" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1531" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="1532">
@@ -43369,7 +43369,7 @@
         <v>1.1</v>
       </c>
       <c r="F1534" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1535">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>0.9</v>
       </c>
       <c r="F1536" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1538">
@@ -43497,19 +43497,19 @@
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1539" t="n">
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>39.6</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1540">
@@ -43525,19 +43525,19 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1540" t="n">
         <v>0.8</v>
       </c>
       <c r="F1540" t="n">
-        <v>44.1</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="1541">
@@ -43593,7 +43593,7 @@
         <v>0.7</v>
       </c>
       <c r="F1542" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1543">
@@ -43621,7 +43621,7 @@
         <v>0.7</v>
       </c>
       <c r="F1543" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1544">
@@ -43677,7 +43677,7 @@
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1546">
@@ -43705,7 +43705,7 @@
         <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1547">
@@ -43733,7 +43733,7 @@
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="1548">
@@ -43761,7 +43761,7 @@
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>33.7</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="1549">
@@ -43789,7 +43789,7 @@
         <v>0.3</v>
       </c>
       <c r="F1549" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="1550">
@@ -43870,7 +43870,7 @@
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="F1552" t="n">
         <v>43.2</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="F1553" t="n">
         <v>40.5</v>
@@ -43926,7 +43926,7 @@
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="F1554" t="n">
         <v>39.5</v>
@@ -43954,7 +43954,7 @@
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="F1555" t="n">
         <v>40</v>
@@ -43982,7 +43982,7 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="F1556" t="n">
         <v>61.3</v>
@@ -44010,7 +44010,7 @@
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="F1557" t="n">
         <v>13.3</v>
@@ -44038,7 +44038,7 @@
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F1558" t="n">
         <v>15.6</v>
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="E1559" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F1559" t="n">
         <v>63.5</v>
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F1560" t="n">
         <v>44.6</v>
@@ -44113,19 +44113,19 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1561" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F1561" t="n">
-        <v>62.9</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="1562">
@@ -44141,19 +44141,19 @@
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F1562" t="n">
-        <v>40.9</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="F1563" t="n">
-        <v>77.59999999999999</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1564">
@@ -44197,19 +44197,19 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F1564" t="n">
-        <v>79.3</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1565">
@@ -44225,19 +44225,19 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="F1565" t="n">
-        <v>44.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1566">
@@ -44253,19 +44253,19 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1566" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1566" t="n">
-        <v>100</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="1567">
@@ -44281,19 +44281,19 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F1567" t="n">
-        <v>11.1</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1568">
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1568" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1568" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1569">
@@ -44337,19 +44337,19 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1569" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1569" t="n">
-        <v>56</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="1570">
@@ -44365,16 +44365,16 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1570" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1570" t="n">
         <v>0</v>
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1571" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F1571" t="n">
-        <v>0</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,19 +44421,19 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1572" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F1572" t="n">
-        <v>88.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1573">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1573" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F1573" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1574" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F1574" t="n">
-        <v>38.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1575">
@@ -44505,19 +44505,19 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1575" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F1575" t="n">
-        <v>68.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="1576">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1576" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F1576" t="n">
-        <v>57.8</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="1577">
@@ -44561,19 +44561,19 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1577" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F1577" t="n">
-        <v>72.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1578">
@@ -44589,19 +44589,19 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1578" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F1578" t="n">
-        <v>100</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="1579">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -44629,7 +44629,7 @@
         <v>0.8</v>
       </c>
       <c r="F1579" t="n">
-        <v>0</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="1580">
@@ -44645,7 +44645,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -44657,7 +44657,7 @@
         <v>0.8</v>
       </c>
       <c r="F1580" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1581">
@@ -44673,19 +44673,19 @@
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1581" t="n">
         <v>0.8</v>
       </c>
       <c r="F1581" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1582">
@@ -44701,19 +44701,19 @@
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1582" t="n">
         <v>0.8</v>
       </c>
       <c r="F1582" t="n">
-        <v>41.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1583">
@@ -44729,16 +44729,16 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F1583" t="n">
         <v>100</v>
@@ -44757,19 +44757,19 @@
       </c>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1584" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F1584" t="n">
-        <v>100</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1585">
@@ -44785,12 +44785,12 @@
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1585" t="n">
@@ -44813,18 +44813,74 @@
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1586" t="n">
         <v>0.4</v>
       </c>
       <c r="F1586" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>한조</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1587" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>트레이서</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>공격 · 측면 공격가</t>
+        </is>
+      </c>
+      <c r="E1588" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1588" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1588"/>
+  <dimension ref="A1:F1589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34297,7 +34297,7 @@
         <v>3.1</v>
       </c>
       <c r="F1210" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1211">
@@ -34325,7 +34325,7 @@
         <v>3</v>
       </c>
       <c r="F1211" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1212">
@@ -34745,7 +34745,7 @@
         <v>1.6</v>
       </c>
       <c r="F1226" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1227">
@@ -35081,7 +35081,7 @@
         <v>1.1</v>
       </c>
       <c r="F1238" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1239">
@@ -35137,7 +35137,7 @@
         <v>1.1</v>
       </c>
       <c r="F1240" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1241">
@@ -35193,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="F1242" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1243">
@@ -35249,7 +35249,7 @@
         <v>1</v>
       </c>
       <c r="F1244" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1245">
@@ -35417,7 +35417,7 @@
         <v>0.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1251">
@@ -35473,7 +35473,7 @@
         <v>5.9</v>
       </c>
       <c r="F1252" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1253">
@@ -35529,7 +35529,7 @@
         <v>4.4</v>
       </c>
       <c r="F1254" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1255">
@@ -35641,7 +35641,7 @@
         <v>3.3</v>
       </c>
       <c r="F1258" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1259">
@@ -35977,7 +35977,7 @@
         <v>2.3</v>
       </c>
       <c r="F1270" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1271">
@@ -36145,7 +36145,7 @@
         <v>1.8</v>
       </c>
       <c r="F1276" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1277">
@@ -36201,7 +36201,7 @@
         <v>1.7</v>
       </c>
       <c r="F1278" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1279">
@@ -36285,7 +36285,7 @@
         <v>1.3</v>
       </c>
       <c r="F1281" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1282">
@@ -36369,7 +36369,7 @@
         <v>1.2</v>
       </c>
       <c r="F1284" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1285">
@@ -36425,7 +36425,7 @@
         <v>1.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1287">
@@ -36453,7 +36453,7 @@
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1288">
@@ -36509,7 +36509,7 @@
         <v>1</v>
       </c>
       <c r="F1289" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1290">
@@ -36537,7 +36537,7 @@
         <v>1</v>
       </c>
       <c r="F1290" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1291">
@@ -36565,7 +36565,7 @@
         <v>1</v>
       </c>
       <c r="F1291" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1292">
@@ -36593,7 +36593,7 @@
         <v>0.9</v>
       </c>
       <c r="F1292" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1293">
@@ -36649,7 +36649,7 @@
         <v>0.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1295">
@@ -36733,7 +36733,7 @@
         <v>0.6</v>
       </c>
       <c r="F1297" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1298">
@@ -36789,7 +36789,7 @@
         <v>0.5</v>
       </c>
       <c r="F1299" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1300">
@@ -36845,7 +36845,7 @@
         <v>0.3</v>
       </c>
       <c r="F1301" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1302">
@@ -36889,19 +36889,19 @@
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1303" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1303" t="n">
         <v>4.9</v>
       </c>
       <c r="F1303" t="n">
-        <v>52</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1304">
@@ -36917,19 +36917,19 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1304" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1304" t="n">
         <v>4.9</v>
       </c>
       <c r="F1304" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1305">
@@ -36985,7 +36985,7 @@
         <v>4</v>
       </c>
       <c r="F1306" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1307">
@@ -37461,7 +37461,7 @@
         <v>1.8</v>
       </c>
       <c r="F1323" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1324">
@@ -37517,7 +37517,7 @@
         <v>1.7</v>
       </c>
       <c r="F1325" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1326">
@@ -37573,7 +37573,7 @@
         <v>1.7</v>
       </c>
       <c r="F1327" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1328">
@@ -37601,7 +37601,7 @@
         <v>1.6</v>
       </c>
       <c r="F1328" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1329">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="E1341" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1341" t="n">
         <v>54.5</v>
@@ -38049,7 +38049,7 @@
         <v>0.9</v>
       </c>
       <c r="F1344" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1345">
@@ -38133,7 +38133,7 @@
         <v>0.7</v>
       </c>
       <c r="F1347" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1348">
@@ -38217,7 +38217,7 @@
         <v>0.5</v>
       </c>
       <c r="F1350" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1351">
@@ -38245,7 +38245,7 @@
         <v>0.4</v>
       </c>
       <c r="F1351" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1352">
@@ -38690,7 +38690,7 @@
         </is>
       </c>
       <c r="E1367" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F1367" t="n">
         <v>49.7</v>
@@ -39129,19 +39129,19 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1383" t="n">
         <v>1.1</v>
       </c>
       <c r="F1383" t="n">
-        <v>47.4</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1384">
@@ -39157,19 +39157,19 @@
       </c>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1384" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1384" t="n">
         <v>1.1</v>
       </c>
       <c r="F1384" t="n">
-        <v>51.2</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1385">
@@ -39197,7 +39197,7 @@
         <v>1.1</v>
       </c>
       <c r="F1385" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1386">
@@ -39337,7 +39337,7 @@
         <v>1.1</v>
       </c>
       <c r="F1390" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1391">
@@ -39393,7 +39393,7 @@
         <v>1.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1393">
@@ -39533,7 +39533,7 @@
         <v>0.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1398">
@@ -39589,7 +39589,7 @@
         <v>0.7</v>
       </c>
       <c r="F1399" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1400">
@@ -39729,7 +39729,7 @@
         <v>5.8</v>
       </c>
       <c r="F1404" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1405">
@@ -39785,7 +39785,7 @@
         <v>3.7</v>
       </c>
       <c r="F1406" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1407">
@@ -39925,7 +39925,7 @@
         <v>2.8</v>
       </c>
       <c r="F1411" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>2.8</v>
       </c>
       <c r="F1412" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>2.7</v>
       </c>
       <c r="F1413" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1414">
@@ -40233,7 +40233,7 @@
         <v>2</v>
       </c>
       <c r="F1422" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1423">
@@ -40625,7 +40625,7 @@
         <v>1.2</v>
       </c>
       <c r="F1436" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1437">
@@ -40653,7 +40653,7 @@
         <v>1.1</v>
       </c>
       <c r="F1437" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1438">
@@ -40681,7 +40681,7 @@
         <v>1</v>
       </c>
       <c r="F1438" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1439">
@@ -41045,7 +41045,7 @@
         <v>0.6</v>
       </c>
       <c r="F1451" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1452">
@@ -41101,7 +41101,7 @@
         <v>6.5</v>
       </c>
       <c r="F1453" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1454">
@@ -41437,7 +41437,7 @@
         <v>2.4</v>
       </c>
       <c r="F1465" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1466">
@@ -41465,7 +41465,7 @@
         <v>2.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1467">
@@ -41493,7 +41493,7 @@
         <v>2.2</v>
       </c>
       <c r="F1467" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1468">
@@ -41521,7 +41521,7 @@
         <v>2.2</v>
       </c>
       <c r="F1468" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1469">
@@ -41549,7 +41549,7 @@
         <v>2.2</v>
       </c>
       <c r="F1469" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1470">
@@ -41577,7 +41577,7 @@
         <v>2.1</v>
       </c>
       <c r="F1470" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1471">
@@ -41705,19 +41705,19 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1475" t="n">
         <v>1.8</v>
       </c>
       <c r="F1475" t="n">
-        <v>49.4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1476">
@@ -41733,19 +41733,19 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1476" t="n">
         <v>1.8</v>
       </c>
       <c r="F1476" t="n">
-        <v>50.9</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1477">
@@ -41773,7 +41773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1478">
@@ -41857,7 +41857,7 @@
         <v>1.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1481">
@@ -41885,7 +41885,7 @@
         <v>1.3</v>
       </c>
       <c r="F1481" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1482">
@@ -41913,7 +41913,7 @@
         <v>1.3</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1483">
@@ -41941,7 +41941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1484">
@@ -41957,7 +41957,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -41969,7 +41969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1484" t="n">
-        <v>51.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1485">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -41997,7 +41997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1485" t="n">
-        <v>46</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1486">
@@ -42025,7 +42025,7 @@
         <v>1.1</v>
       </c>
       <c r="F1486" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1487">
@@ -42165,7 +42165,7 @@
         <v>0.8</v>
       </c>
       <c r="F1491" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1492">
@@ -42221,7 +42221,7 @@
         <v>0.6</v>
       </c>
       <c r="F1493" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1494">
@@ -42237,19 +42237,19 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1494" t="n">
         <v>0.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>45</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1495">
@@ -42265,19 +42265,19 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1495" t="n">
         <v>0.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>48.5</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1496">
@@ -42305,7 +42305,7 @@
         <v>0.6</v>
       </c>
       <c r="F1496" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>0.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1499">
@@ -42445,7 +42445,7 @@
         <v>0.4</v>
       </c>
       <c r="F1501" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1502">
@@ -42470,10 +42470,10 @@
         </is>
       </c>
       <c r="E1502" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F1502" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1503">
@@ -42529,7 +42529,7 @@
         <v>5.5</v>
       </c>
       <c r="F1504" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1505">
@@ -42557,7 +42557,7 @@
         <v>4.6</v>
       </c>
       <c r="F1505" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1506">
@@ -42582,10 +42582,10 @@
         </is>
       </c>
       <c r="E1506" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1507">
@@ -42613,7 +42613,7 @@
         <v>4.2</v>
       </c>
       <c r="F1507" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1508">
@@ -42641,7 +42641,7 @@
         <v>3.9</v>
       </c>
       <c r="F1508" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1509">
@@ -42669,7 +42669,7 @@
         <v>3.8</v>
       </c>
       <c r="F1509" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="1510">
@@ -42694,10 +42694,10 @@
         </is>
       </c>
       <c r="E1510" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1511">
@@ -42753,7 +42753,7 @@
         <v>3</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1513">
@@ -42778,10 +42778,10 @@
         </is>
       </c>
       <c r="E1513" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>44.9</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1514">
@@ -42837,7 +42837,7 @@
         <v>2.5</v>
       </c>
       <c r="F1515" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1516">
@@ -42865,7 +42865,7 @@
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1517">
@@ -42893,7 +42893,7 @@
         <v>2.4</v>
       </c>
       <c r="F1517" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1518">
@@ -42909,19 +42909,19 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1518" t="n">
         <v>2.2</v>
       </c>
       <c r="F1518" t="n">
-        <v>44.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>2.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>45.3</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1521">
@@ -43030,10 +43030,10 @@
         </is>
       </c>
       <c r="E1522" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1522" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1524">
@@ -43089,7 +43089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1524" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1525">
@@ -43117,7 +43117,7 @@
         <v>1.8</v>
       </c>
       <c r="F1525" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1526">
@@ -43133,19 +43133,19 @@
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1526" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F1526" t="n">
-        <v>48.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1527">
@@ -43161,19 +43161,19 @@
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1527" t="n">
         <v>1.7</v>
       </c>
       <c r="F1527" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1528">
@@ -43217,19 +43217,19 @@
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1529" t="n">
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>48.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="1530">
@@ -43245,19 +43245,19 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1530" t="n">
         <v>1.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>30.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1531">
@@ -43273,19 +43273,19 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1531" t="n">
         <v>1.4</v>
       </c>
       <c r="F1531" t="n">
-        <v>37.6</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="1532">
@@ -43313,7 +43313,7 @@
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1533">
@@ -43369,7 +43369,7 @@
         <v>1.1</v>
       </c>
       <c r="F1534" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1535">
@@ -43422,10 +43422,10 @@
         </is>
       </c>
       <c r="E1536" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F1536" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1538">
@@ -43481,7 +43481,7 @@
         <v>0.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>42.4</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1539">
@@ -43497,19 +43497,19 @@
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1539" t="n">
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>45.6</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="1540">
@@ -43525,19 +43525,19 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1540" t="n">
         <v>0.8</v>
       </c>
       <c r="F1540" t="n">
-        <v>39.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1541">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
@@ -43593,7 +43593,7 @@
         <v>0.7</v>
       </c>
       <c r="F1542" t="n">
-        <v>41.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1543">
@@ -43609,7 +43609,7 @@
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
@@ -43618,10 +43618,10 @@
         </is>
       </c>
       <c r="E1543" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F1543" t="n">
-        <v>50.8</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="1544">
@@ -43649,7 +43649,7 @@
         <v>0.5</v>
       </c>
       <c r="F1544" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="1545">
@@ -43677,7 +43677,7 @@
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>44.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1546">
@@ -43705,7 +43705,7 @@
         <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1547">
@@ -43733,7 +43733,7 @@
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="1548">
@@ -43761,7 +43761,7 @@
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>33.4</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="1549">
@@ -43870,7 +43870,7 @@
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="F1552" t="n">
         <v>43.2</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="F1553" t="n">
         <v>40.5</v>
@@ -43926,7 +43926,7 @@
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="F1554" t="n">
         <v>39.5</v>
@@ -43954,10 +43954,10 @@
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="F1555" t="n">
-        <v>40</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1556">
@@ -43982,7 +43982,7 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F1556" t="n">
         <v>61.3</v>
@@ -44010,10 +44010,10 @@
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F1557" t="n">
-        <v>13.3</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="1558">
@@ -44038,7 +44038,7 @@
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="F1558" t="n">
         <v>15.6</v>
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="E1559" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="F1559" t="n">
         <v>63.5</v>
@@ -44085,19 +44085,19 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="F1560" t="n">
-        <v>44.6</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1561">
@@ -44113,19 +44113,19 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1561" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1561" t="n">
-        <v>77.59999999999999</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1562">
@@ -44141,19 +44141,19 @@
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1562" t="n">
-        <v>62.9</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1563" t="n">
-        <v>43.4</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="1564">
@@ -44197,19 +44197,19 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1564" t="n">
-        <v>40.9</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1565">
@@ -44225,19 +44225,19 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F1565" t="n">
-        <v>100</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1566">
@@ -44253,19 +44253,19 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1566" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F1566" t="n">
-        <v>79.3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1567">
@@ -44290,10 +44290,10 @@
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F1567" t="n">
-        <v>44.7</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="1568">
@@ -44309,7 +44309,7 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="E1568" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F1568" t="n">
         <v>100</v>
@@ -44337,7 +44337,7 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
@@ -44346,10 +44346,10 @@
         </is>
       </c>
       <c r="E1569" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F1569" t="n">
-        <v>11.1</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="1570">
@@ -44365,19 +44365,19 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1570" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1570" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1571" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1571" t="n">
-        <v>57.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,16 +44421,16 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1572" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1572" t="n">
         <v>0</v>
@@ -44449,7 +44449,7 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
@@ -44458,10 +44458,10 @@
         </is>
       </c>
       <c r="E1573" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F1573" t="n">
-        <v>98.2</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,16 +44477,16 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1574" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F1574" t="n">
         <v>0</v>
@@ -44505,19 +44505,19 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1575" t="n">
         <v>1.1</v>
       </c>
       <c r="F1575" t="n">
-        <v>88.40000000000001</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="1576">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1576" t="n">
         <v>1.1</v>
       </c>
       <c r="F1576" t="n">
-        <v>38.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1577">
@@ -44561,19 +44561,19 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1577" t="n">
         <v>1.1</v>
       </c>
       <c r="F1577" t="n">
-        <v>100</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="1578">
@@ -44589,19 +44589,19 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1578" t="n">
         <v>1.1</v>
       </c>
       <c r="F1578" t="n">
-        <v>68.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1579">
@@ -44617,19 +44617,19 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1579" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F1579" t="n">
-        <v>72.5</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="1580">
@@ -44645,19 +44645,19 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1580" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1580" t="n">
-        <v>100</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="1581">
@@ -44682,7 +44682,7 @@
         </is>
       </c>
       <c r="E1581" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1581" t="n">
         <v>0</v>
@@ -44710,7 +44710,7 @@
         </is>
       </c>
       <c r="E1582" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1582" t="n">
         <v>50</v>
@@ -44738,7 +44738,7 @@
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1583" t="n">
         <v>100</v>
@@ -44766,7 +44766,7 @@
         </is>
       </c>
       <c r="E1584" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1584" t="n">
         <v>41.8</v>
@@ -44785,12 +44785,12 @@
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1585" t="n">
@@ -44813,19 +44813,19 @@
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1586" t="n">
         <v>0.4</v>
       </c>
       <c r="F1586" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1587">
@@ -44841,19 +44841,19 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1587" t="n">
         <v>0.4</v>
       </c>
       <c r="F1587" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1588">
@@ -44869,18 +44869,46 @@
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1588" t="n">
         <v>0.4</v>
       </c>
       <c r="F1588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>트레이서</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>공격 · 측면 공격가</t>
+        </is>
+      </c>
+      <c r="E1589" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1589" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1592"/>
+  <dimension ref="A1:F1593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="F2" t="n">
         <v>49.4</v>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="F3" t="n">
         <v>48</v>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="F6" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="7">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
         <v>52.1</v>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="F9" t="n">
         <v>45.2</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="F13" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="14">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="F14" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="15">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F16" t="n">
         <v>52</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="n">
         <v>46.4</v>
@@ -977,7 +977,7 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="21">
@@ -1033,7 +1033,7 @@
         <v>8.6</v>
       </c>
       <c r="F22" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="23">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>48.7</v>
@@ -1145,7 +1145,7 @@
         <v>7.7</v>
       </c>
       <c r="F26" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="27">
@@ -1453,7 +1453,7 @@
         <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="38">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F38" t="n">
         <v>54</v>
@@ -1649,7 +1649,7 @@
         <v>3.9</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="45">
@@ -1733,7 +1733,7 @@
         <v>3.5</v>
       </c>
       <c r="F47" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="48">
@@ -1929,7 +1929,7 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="55">
@@ -1985,7 +1985,7 @@
         <v>20.2</v>
       </c>
       <c r="F56" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="57">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="F58" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="59">
@@ -2097,7 +2097,7 @@
         <v>16.7</v>
       </c>
       <c r="F60" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="61">
@@ -2125,7 +2125,7 @@
         <v>15.9</v>
       </c>
       <c r="F61" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="62">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="F62" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="63">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="F63" t="n">
-        <v>52.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="64">
@@ -2197,19 +2197,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>13.7</v>
       </c>
       <c r="F64" t="n">
-        <v>48.3</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="65">
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="F66" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67">
@@ -2321,7 +2321,7 @@
         <v>11</v>
       </c>
       <c r="F68" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="69">
@@ -2349,7 +2349,7 @@
         <v>10.9</v>
       </c>
       <c r="F69" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="70">
@@ -2377,7 +2377,7 @@
         <v>10.5</v>
       </c>
       <c r="F70" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="71">
@@ -2405,7 +2405,7 @@
         <v>10.3</v>
       </c>
       <c r="F71" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="72">
@@ -2433,7 +2433,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F74" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="75">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F76" t="n">
         <v>50.6</v>
@@ -2601,7 +2601,7 @@
         <v>7.3</v>
       </c>
       <c r="F78" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="79">
@@ -2629,7 +2629,7 @@
         <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="80">
@@ -2657,7 +2657,7 @@
         <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="81">
@@ -2685,7 +2685,7 @@
         <v>6.1</v>
       </c>
       <c r="F81" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="82">
@@ -2713,7 +2713,7 @@
         <v>6.1</v>
       </c>
       <c r="F82" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="83">
@@ -2741,7 +2741,7 @@
         <v>5.7</v>
       </c>
       <c r="F83" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="84">
@@ -2769,7 +2769,7 @@
         <v>5.6</v>
       </c>
       <c r="F84" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="85">
@@ -2797,7 +2797,7 @@
         <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="86">
@@ -2825,7 +2825,7 @@
         <v>5.1</v>
       </c>
       <c r="F86" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="87">
@@ -2853,7 +2853,7 @@
         <v>5.1</v>
       </c>
       <c r="F87" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="88">
@@ -2881,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F89" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="90">
@@ -2965,7 +2965,7 @@
         <v>3.9</v>
       </c>
       <c r="F91" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="92">
@@ -2993,7 +2993,7 @@
         <v>3.6</v>
       </c>
       <c r="F92" t="n">
-        <v>44.2</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="93">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F93" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="94">
@@ -3049,7 +3049,7 @@
         <v>3.2</v>
       </c>
       <c r="F94" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="95">
@@ -3133,7 +3133,7 @@
         <v>2.8</v>
       </c>
       <c r="F97" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="98">
@@ -3161,7 +3161,7 @@
         <v>2.5</v>
       </c>
       <c r="F98" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="99">
@@ -3189,7 +3189,7 @@
         <v>2.3</v>
       </c>
       <c r="F99" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="100">
@@ -3245,7 +3245,7 @@
         <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="102">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="F102" t="n">
         <v>48.4</v>
@@ -3385,7 +3385,7 @@
         <v>19.8</v>
       </c>
       <c r="F106" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="107">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="F109" t="n">
         <v>44.5</v>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="F111" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="112">
@@ -3553,7 +3553,7 @@
         <v>14.4</v>
       </c>
       <c r="F112" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="113">
@@ -3609,7 +3609,7 @@
         <v>12.5</v>
       </c>
       <c r="F114" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="115">
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F115" t="n">
         <v>52.7</v>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F120" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="121">
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="123">
@@ -4029,7 +4029,7 @@
         <v>7.5</v>
       </c>
       <c r="F129" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="130">
@@ -4073,19 +4073,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E131" t="n">
         <v>6.7</v>
       </c>
       <c r="F131" t="n">
-        <v>51.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="132">
@@ -4101,19 +4101,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="F132" t="n">
-        <v>46.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="133">
@@ -4141,7 +4141,7 @@
         <v>6.5</v>
       </c>
       <c r="F133" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="134">
@@ -4169,7 +4169,7 @@
         <v>6.5</v>
       </c>
       <c r="F134" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="135">
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F137" t="n">
-        <v>51.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="138">
@@ -4337,7 +4337,7 @@
         <v>4.4</v>
       </c>
       <c r="F140" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="141">
@@ -4393,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="143">
@@ -4421,7 +4421,7 @@
         <v>3.8</v>
       </c>
       <c r="F143" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="144">
@@ -4477,7 +4477,7 @@
         <v>3.4</v>
       </c>
       <c r="F145" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="146">
@@ -4505,7 +4505,7 @@
         <v>3.3</v>
       </c>
       <c r="F146" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="147">
@@ -4561,7 +4561,7 @@
         <v>2.6</v>
       </c>
       <c r="F148" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="149">
@@ -4589,7 +4589,7 @@
         <v>2.5</v>
       </c>
       <c r="F149" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="150">
@@ -4645,7 +4645,7 @@
         <v>2.3</v>
       </c>
       <c r="F151" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="152">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="F153" t="n">
         <v>48</v>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F156" t="n">
         <v>48.2</v>
@@ -4813,7 +4813,7 @@
         <v>18.4</v>
       </c>
       <c r="F157" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="158">
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="F158" t="n">
         <v>52.2</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F160" t="n">
         <v>44.9</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="F161" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="162">
@@ -5009,7 +5009,7 @@
         <v>12.4</v>
       </c>
       <c r="F164" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="165">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F166" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="167">
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F169" t="n">
         <v>51.4</v>
@@ -5221,16 +5221,16 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F172" t="n">
         <v>48.2</v>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -5317,7 +5317,7 @@
         <v>8.1</v>
       </c>
       <c r="F175" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="176">
@@ -5373,7 +5373,7 @@
         <v>7.8</v>
       </c>
       <c r="F177" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="178">
@@ -5457,7 +5457,7 @@
         <v>7.1</v>
       </c>
       <c r="F180" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="181">
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F187" t="n">
         <v>51.3</v>
@@ -5681,7 +5681,7 @@
         <v>4.7</v>
       </c>
       <c r="F188" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="189">
@@ -5709,7 +5709,7 @@
         <v>4.4</v>
       </c>
       <c r="F189" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="190">
@@ -5765,7 +5765,7 @@
         <v>4.2</v>
       </c>
       <c r="F191" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="192">
@@ -5849,7 +5849,7 @@
         <v>3.9</v>
       </c>
       <c r="F194" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="195">
@@ -5877,7 +5877,7 @@
         <v>3.8</v>
       </c>
       <c r="F195" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196">
@@ -8873,7 +8873,7 @@
         <v>52.1</v>
       </c>
       <c r="F302" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="303">
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="F303" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="304">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="F305" t="n">
         <v>52.3</v>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="F306" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="307">
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F307" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="308">
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="F308" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="309">
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="F309" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="310">
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="F310" t="n">
         <v>47.8</v>
@@ -9122,10 +9122,10 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="F311" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="312">
@@ -9153,7 +9153,7 @@
         <v>13.6</v>
       </c>
       <c r="F312" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="313">
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F313" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="314">
@@ -9197,19 +9197,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F314" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="315">
@@ -9225,19 +9225,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E315" t="n">
         <v>10.3</v>
       </c>
       <c r="F315" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="316">
@@ -9265,7 +9265,7 @@
         <v>9.4</v>
       </c>
       <c r="F316" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="317">
@@ -9281,19 +9281,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F317" t="n">
-        <v>51.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="318">
@@ -9309,19 +9309,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F318" t="n">
-        <v>45.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="319">
@@ -9349,7 +9349,7 @@
         <v>8.4</v>
       </c>
       <c r="F319" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="320">
@@ -9377,7 +9377,7 @@
         <v>8.1</v>
       </c>
       <c r="F320" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="321">
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F321" t="n">
         <v>50.9</v>
@@ -9433,7 +9433,7 @@
         <v>7.4</v>
       </c>
       <c r="F322" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="323">
@@ -9449,19 +9449,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E323" t="n">
         <v>7</v>
       </c>
       <c r="F323" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="324">
@@ -9477,19 +9477,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E324" t="n">
         <v>6.9</v>
       </c>
       <c r="F324" t="n">
-        <v>49.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="325">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F325" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="326">
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F326" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="327">
@@ -9561,19 +9561,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F327" t="n">
-        <v>48.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="328">
@@ -9589,19 +9589,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E328" t="n">
         <v>6.1</v>
       </c>
       <c r="F328" t="n">
-        <v>46.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="329">
@@ -9629,7 +9629,7 @@
         <v>5.6</v>
       </c>
       <c r="F329" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="330">
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F330" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="331">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E332" t="n">
         <v>5</v>
       </c>
       <c r="F332" t="n">
-        <v>47.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="333">
@@ -9729,19 +9729,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F333" t="n">
-        <v>54.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="334">
@@ -9769,7 +9769,7 @@
         <v>4.8</v>
       </c>
       <c r="F334" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="335">
@@ -9797,7 +9797,7 @@
         <v>4.8</v>
       </c>
       <c r="F335" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="336">
@@ -9825,7 +9825,7 @@
         <v>4.6</v>
       </c>
       <c r="F336" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="337">
@@ -9881,7 +9881,7 @@
         <v>4.2</v>
       </c>
       <c r="F338" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="339">
@@ -9909,7 +9909,7 @@
         <v>4.2</v>
       </c>
       <c r="F339" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="340">
@@ -9965,7 +9965,7 @@
         <v>3.7</v>
       </c>
       <c r="F341" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="342">
@@ -9993,7 +9993,7 @@
         <v>3.6</v>
       </c>
       <c r="F342" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="343">
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F343" t="n">
-        <v>51.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="344">
@@ -10046,10 +10046,10 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F344" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="345">
@@ -10077,7 +10077,7 @@
         <v>2.9</v>
       </c>
       <c r="F345" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="346">
@@ -10105,7 +10105,7 @@
         <v>2.7</v>
       </c>
       <c r="F346" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="347">
@@ -10133,7 +10133,7 @@
         <v>2.7</v>
       </c>
       <c r="F347" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="348">
@@ -10161,7 +10161,7 @@
         <v>2.6</v>
       </c>
       <c r="F348" t="n">
-        <v>47.1</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="349">
@@ -10189,7 +10189,7 @@
         <v>2.5</v>
       </c>
       <c r="F349" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="350">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F351" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="352">
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="F352" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="353">
@@ -10298,10 +10298,10 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="F353" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="354">
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="F354" t="n">
-        <v>55.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="355">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="F355" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="356">
@@ -10385,7 +10385,7 @@
         <v>25.7</v>
       </c>
       <c r="F356" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="357">
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="F357" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="358">
@@ -10441,7 +10441,7 @@
         <v>20.7</v>
       </c>
       <c r="F358" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="359">
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F359" t="n">
         <v>54.1</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="F360" t="n">
-        <v>48.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="361">
@@ -10513,19 +10513,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E361" t="n">
         <v>14</v>
       </c>
       <c r="F361" t="n">
-        <v>51.4</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="362">
@@ -10541,19 +10541,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="F362" t="n">
-        <v>54.3</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="363">
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F363" t="n">
-        <v>52.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="364">
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F364" t="n">
-        <v>45.3</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="365">
@@ -10625,19 +10625,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F365" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="366">
@@ -10653,19 +10653,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F366" t="n">
-        <v>46.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="367">
@@ -10681,19 +10681,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F367" t="n">
-        <v>46.4</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="368">
@@ -10709,19 +10709,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F368" t="n">
-        <v>49.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="369">
@@ -10737,19 +10737,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F369" t="n">
-        <v>47.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="370">
@@ -10765,19 +10765,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E370" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="F370" t="n">
-        <v>49.3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="371">
@@ -10793,19 +10793,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F371" t="n">
-        <v>52.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="372">
@@ -10821,19 +10821,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="F372" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="373">
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="F373" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="374">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="F374" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="375">
@@ -10914,10 +10914,10 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="F375" t="n">
-        <v>50.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="376">
@@ -10933,19 +10933,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E376" t="n">
         <v>6</v>
       </c>
       <c r="F376" t="n">
-        <v>47.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="377">
@@ -10961,19 +10961,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F377" t="n">
-        <v>44.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="378">
@@ -10989,19 +10989,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="F378" t="n">
-        <v>45.3</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="379">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -11029,7 +11029,7 @@
         <v>5.3</v>
       </c>
       <c r="F379" t="n">
-        <v>46.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="380">
@@ -11045,19 +11045,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="F380" t="n">
-        <v>53.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="381">
@@ -11073,19 +11073,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F381" t="n">
-        <v>48.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="382">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -11113,7 +11113,7 @@
         <v>5</v>
       </c>
       <c r="F382" t="n">
-        <v>49.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="383">
@@ -11141,7 +11141,7 @@
         <v>5</v>
       </c>
       <c r="F383" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="384">
@@ -11157,19 +11157,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F384" t="n">
-        <v>47.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="385">
@@ -11185,19 +11185,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F385" t="n">
-        <v>52</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="386">
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F386" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="387">
@@ -11250,10 +11250,10 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F387" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="388">
@@ -11281,7 +11281,7 @@
         <v>3.6</v>
       </c>
       <c r="F388" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="389">
@@ -11309,7 +11309,7 @@
         <v>3.4</v>
       </c>
       <c r="F389" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="390">
@@ -11325,19 +11325,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E390" t="n">
         <v>3.3</v>
       </c>
       <c r="F390" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="391">
@@ -11353,19 +11353,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E391" t="n">
         <v>3.2</v>
       </c>
       <c r="F391" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="392">
@@ -11393,7 +11393,7 @@
         <v>2.9</v>
       </c>
       <c r="F392" t="n">
-        <v>45.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="393">
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F393" t="n">
-        <v>52.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="394">
@@ -11449,7 +11449,7 @@
         <v>2.4</v>
       </c>
       <c r="F394" t="n">
-        <v>46.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="395">
@@ -11474,10 +11474,10 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F395" t="n">
-        <v>43.6</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="396">
@@ -11493,19 +11493,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F396" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="397">
@@ -11521,19 +11521,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E397" t="n">
         <v>2.1</v>
       </c>
       <c r="F397" t="n">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="398">
@@ -11561,7 +11561,7 @@
         <v>1.6</v>
       </c>
       <c r="F398" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="399">
@@ -11577,19 +11577,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E399" t="n">
         <v>1.5</v>
       </c>
       <c r="F399" t="n">
-        <v>41.3</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="400">
@@ -11605,19 +11605,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F400" t="n">
-        <v>48.2</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="401">
@@ -11645,7 +11645,7 @@
         <v>0.9</v>
       </c>
       <c r="F401" t="n">
-        <v>44.7</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="402">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="F454" t="n">
         <v>50.1</v>
@@ -13182,7 +13182,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F456" t="n">
         <v>48</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="F457" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="458">
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="F458" t="n">
         <v>48.8</v>
@@ -13269,7 +13269,7 @@
         <v>14.6</v>
       </c>
       <c r="F459" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="460">
@@ -13325,7 +13325,7 @@
         <v>13.8</v>
       </c>
       <c r="F461" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="462">
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F464" t="n">
         <v>51.1</v>
@@ -13437,7 +13437,7 @@
         <v>12.3</v>
       </c>
       <c r="F465" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="466">
@@ -13521,7 +13521,7 @@
         <v>11.5</v>
       </c>
       <c r="F468" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="469">
@@ -13577,7 +13577,7 @@
         <v>11.3</v>
       </c>
       <c r="F470" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="471">
@@ -13633,7 +13633,7 @@
         <v>10.4</v>
       </c>
       <c r="F472" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="473">
@@ -13661,7 +13661,7 @@
         <v>10.4</v>
       </c>
       <c r="F473" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="474">
@@ -13801,7 +13801,7 @@
         <v>7.7</v>
       </c>
       <c r="F478" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="479">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -13857,7 +13857,7 @@
         <v>6.8</v>
       </c>
       <c r="F480" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="481">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13882,10 +13882,10 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F481" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="482">
@@ -13913,7 +13913,7 @@
         <v>6.2</v>
       </c>
       <c r="F482" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="483">
@@ -13941,7 +13941,7 @@
         <v>6.1</v>
       </c>
       <c r="F483" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="484">
@@ -13997,7 +13997,7 @@
         <v>5.8</v>
       </c>
       <c r="F485" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="486">
@@ -14025,7 +14025,7 @@
         <v>5.4</v>
       </c>
       <c r="F486" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="487">
@@ -14053,7 +14053,7 @@
         <v>5.1</v>
       </c>
       <c r="F487" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="488">
@@ -14109,7 +14109,7 @@
         <v>4.2</v>
       </c>
       <c r="F489" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="490">
@@ -14137,7 +14137,7 @@
         <v>4.1</v>
       </c>
       <c r="F490" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="491">
@@ -14165,7 +14165,7 @@
         <v>4</v>
       </c>
       <c r="F491" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="492">
@@ -14181,19 +14181,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F492" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="493">
@@ -14209,19 +14209,19 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E493" t="n">
         <v>3.7</v>
       </c>
       <c r="F493" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="494">
@@ -14249,7 +14249,7 @@
         <v>3.7</v>
       </c>
       <c r="F494" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="495">
@@ -14277,7 +14277,7 @@
         <v>3.4</v>
       </c>
       <c r="F495" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="496">
@@ -14293,19 +14293,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E496" t="n">
         <v>3.4</v>
       </c>
       <c r="F496" t="n">
-        <v>50.9</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="497">
@@ -14321,19 +14321,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F497" t="n">
-        <v>52.4</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="498">
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F498" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="499">
@@ -14389,7 +14389,7 @@
         <v>3.2</v>
       </c>
       <c r="F499" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="500">
@@ -14417,7 +14417,7 @@
         <v>2.6</v>
       </c>
       <c r="F500" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="501">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -15870,10 +15870,10 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="F552" t="n">
-        <v>46.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="553">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -15901,7 +15901,7 @@
         <v>29</v>
       </c>
       <c r="F553" t="n">
-        <v>47.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="554">
@@ -15954,10 +15954,10 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="F555" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="556">
@@ -16094,10 +16094,10 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="F560" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="561">
@@ -16153,7 +16153,7 @@
         <v>14.5</v>
       </c>
       <c r="F562" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="563">
@@ -16181,7 +16181,7 @@
         <v>13.7</v>
       </c>
       <c r="F563" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="564">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="E564" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F564" t="n">
         <v>52.2</v>
@@ -16290,10 +16290,10 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F567" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="568">
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="E568" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F568" t="n">
         <v>53.7</v>
@@ -16349,7 +16349,7 @@
         <v>10.8</v>
       </c>
       <c r="F569" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="570">
@@ -16374,10 +16374,10 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F570" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="571">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F571" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="572">
@@ -16430,10 +16430,10 @@
         </is>
       </c>
       <c r="E572" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F572" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="573">
@@ -16486,7 +16486,7 @@
         </is>
       </c>
       <c r="E574" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F574" t="n">
         <v>49.3</v>
@@ -16517,7 +16517,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F575" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="576">
@@ -16545,7 +16545,7 @@
         <v>8.1</v>
       </c>
       <c r="F576" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="577">
@@ -16601,7 +16601,7 @@
         <v>7.6</v>
       </c>
       <c r="F578" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="579">
@@ -16629,7 +16629,7 @@
         <v>7.5</v>
       </c>
       <c r="F579" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="580">
@@ -16657,7 +16657,7 @@
         <v>7.4</v>
       </c>
       <c r="F580" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="581">
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F581" t="n">
         <v>51.2</v>
@@ -16769,7 +16769,7 @@
         <v>5.4</v>
       </c>
       <c r="F584" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="585">
@@ -16853,7 +16853,7 @@
         <v>5.3</v>
       </c>
       <c r="F587" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="588">
@@ -16881,7 +16881,7 @@
         <v>5</v>
       </c>
       <c r="F588" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="589">
@@ -16909,7 +16909,7 @@
         <v>4.9</v>
       </c>
       <c r="F589" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="590">
@@ -16925,19 +16925,19 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E590" t="n">
         <v>4.9</v>
       </c>
       <c r="F590" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="591">
@@ -16953,19 +16953,19 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E591" t="n">
         <v>4.8</v>
       </c>
       <c r="F591" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="592">
@@ -16993,7 +16993,7 @@
         <v>4.1</v>
       </c>
       <c r="F592" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="593">
@@ -17077,7 +17077,7 @@
         <v>3.8</v>
       </c>
       <c r="F595" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="596">
@@ -17161,7 +17161,7 @@
         <v>3.4</v>
       </c>
       <c r="F598" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="599">
@@ -17189,7 +17189,7 @@
         <v>3.4</v>
       </c>
       <c r="F599" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="600">
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F600" t="n">
         <v>52.9</v>
@@ -17301,7 +17301,7 @@
         <v>29.3</v>
       </c>
       <c r="F603" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="604">
@@ -17329,7 +17329,7 @@
         <v>22.9</v>
       </c>
       <c r="F604" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="605">
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="F607" t="n">
         <v>52.7</v>
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F608" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="609">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="E609" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="F609" t="n">
         <v>50.4</v>
@@ -17553,7 +17553,7 @@
         <v>13.1</v>
       </c>
       <c r="F612" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="613">
@@ -17606,7 +17606,7 @@
         </is>
       </c>
       <c r="E614" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F614" t="n">
         <v>50.9</v>
@@ -17665,7 +17665,7 @@
         <v>12.1</v>
       </c>
       <c r="F616" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="617">
@@ -17693,7 +17693,7 @@
         <v>11.7</v>
       </c>
       <c r="F617" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="618">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="F618" t="n">
         <v>53.4</v>
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F619" t="n">
         <v>49.8</v>
@@ -17774,10 +17774,10 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F620" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="621">
@@ -17833,7 +17833,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="623">
@@ -17914,7 +17914,7 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F625" t="n">
         <v>49.5</v>
@@ -17945,7 +17945,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F626" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="627">
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F627" t="n">
         <v>51.9</v>
@@ -18029,7 +18029,7 @@
         <v>7.1</v>
       </c>
       <c r="F629" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="630">
@@ -18141,7 +18141,7 @@
         <v>6.9</v>
       </c>
       <c r="F633" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="634">
@@ -18169,7 +18169,7 @@
         <v>6.4</v>
       </c>
       <c r="F634" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="635">
@@ -18197,7 +18197,7 @@
         <v>6.1</v>
       </c>
       <c r="F635" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="636">
@@ -18253,7 +18253,7 @@
         <v>5.5</v>
       </c>
       <c r="F637" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="638">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F638" t="n">
         <v>51.5</v>
@@ -18306,10 +18306,10 @@
         </is>
       </c>
       <c r="E639" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F639" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="640">
@@ -18337,7 +18337,7 @@
         <v>4.6</v>
       </c>
       <c r="F640" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="641">
@@ -18393,7 +18393,7 @@
         <v>4.2</v>
       </c>
       <c r="F642" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="643">
@@ -18421,7 +18421,7 @@
         <v>4.1</v>
       </c>
       <c r="F643" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="644">
@@ -18505,7 +18505,7 @@
         <v>3.8</v>
       </c>
       <c r="F646" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="647">
@@ -18533,7 +18533,7 @@
         <v>3.5</v>
       </c>
       <c r="F647" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="648">
@@ -18561,7 +18561,7 @@
         <v>3.4</v>
       </c>
       <c r="F648" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="649">
@@ -18589,7 +18589,7 @@
         <v>3.3</v>
       </c>
       <c r="F649" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="650">
@@ -21470,10 +21470,10 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="F752" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="753">
@@ -21501,7 +21501,7 @@
         <v>27.3</v>
       </c>
       <c r="F753" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="754">
@@ -21526,7 +21526,7 @@
         </is>
       </c>
       <c r="E754" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="F754" t="n">
         <v>50.8</v>
@@ -21554,10 +21554,10 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="F755" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="756">
@@ -21582,10 +21582,10 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="F756" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="757">
@@ -21641,7 +21641,7 @@
         <v>17.8</v>
       </c>
       <c r="F758" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="759">
@@ -21666,7 +21666,7 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F759" t="n">
         <v>49.8</v>
@@ -21694,10 +21694,10 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="F760" t="n">
-        <v>54.2</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="761">
@@ -21713,19 +21713,19 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E761" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F761" t="n">
-        <v>49.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="762">
@@ -21741,19 +21741,19 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E762" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F762" t="n">
-        <v>51.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="763">
@@ -21778,10 +21778,10 @@
         </is>
       </c>
       <c r="E763" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="F763" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="764">
@@ -21806,10 +21806,10 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F764" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="765">
@@ -21825,19 +21825,19 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E765" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F765" t="n">
-        <v>54.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="766">
@@ -21853,19 +21853,19 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="F766" t="n">
-        <v>48</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="767">
@@ -21893,7 +21893,7 @@
         <v>10.6</v>
       </c>
       <c r="F767" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="768">
@@ -21918,10 +21918,10 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F768" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="769">
@@ -21949,7 +21949,7 @@
         <v>9.6</v>
       </c>
       <c r="F769" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="770">
@@ -21974,10 +21974,10 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F770" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="771">
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="F771" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="772">
@@ -22033,7 +22033,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="773">
@@ -22061,7 +22061,7 @@
         <v>8.4</v>
       </c>
       <c r="F773" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="774">
@@ -22086,10 +22086,10 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F774" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="775">
@@ -22145,7 +22145,7 @@
         <v>7.4</v>
       </c>
       <c r="F776" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="777">
@@ -22173,7 +22173,7 @@
         <v>7.2</v>
       </c>
       <c r="F777" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="778">
@@ -22201,7 +22201,7 @@
         <v>7.2</v>
       </c>
       <c r="F778" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="779">
@@ -22229,7 +22229,7 @@
         <v>7.1</v>
       </c>
       <c r="F779" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="780">
@@ -22245,19 +22245,19 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E780" t="n">
         <v>6.7</v>
       </c>
       <c r="F780" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="781">
@@ -22273,19 +22273,19 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E781" t="n">
         <v>6.7</v>
       </c>
       <c r="F781" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="782">
@@ -22301,19 +22301,19 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E782" t="n">
         <v>6.6</v>
       </c>
       <c r="F782" t="n">
-        <v>49.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="783">
@@ -22338,10 +22338,10 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F783" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="784">
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="F784" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="785">
@@ -22397,7 +22397,7 @@
         <v>6</v>
       </c>
       <c r="F785" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="786">
@@ -22413,19 +22413,19 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E786" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F786" t="n">
-        <v>49.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="787">
@@ -22441,19 +22441,19 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E787" t="n">
         <v>5.7</v>
       </c>
       <c r="F787" t="n">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="788">
@@ -22469,19 +22469,19 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E788" t="n">
         <v>5.1</v>
       </c>
       <c r="F788" t="n">
-        <v>52.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="789">
@@ -22497,19 +22497,19 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E789" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F789" t="n">
-        <v>47.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="790">
@@ -22534,10 +22534,10 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F790" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="791">
@@ -22565,7 +22565,7 @@
         <v>4.3</v>
       </c>
       <c r="F791" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="792">
@@ -22593,7 +22593,7 @@
         <v>4.2</v>
       </c>
       <c r="F792" t="n">
-        <v>52.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="793">
@@ -22621,7 +22621,7 @@
         <v>4</v>
       </c>
       <c r="F793" t="n">
-        <v>52.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="794">
@@ -22637,19 +22637,19 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E794" t="n">
         <v>3.7</v>
       </c>
       <c r="F794" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="795">
@@ -22665,19 +22665,19 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E795" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F795" t="n">
-        <v>48</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="796">
@@ -22705,7 +22705,7 @@
         <v>3.6</v>
       </c>
       <c r="F796" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="797">
@@ -22733,7 +22733,7 @@
         <v>3.5</v>
       </c>
       <c r="F797" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="798">
@@ -22777,19 +22777,19 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E799" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F799" t="n">
-        <v>51.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="800">
@@ -22805,19 +22805,19 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E800" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F800" t="n">
-        <v>47.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="801">
@@ -22845,7 +22845,7 @@
         <v>2.3</v>
       </c>
       <c r="F801" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="802">
@@ -24270,7 +24270,7 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="F852" t="n">
         <v>50.4</v>
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="E853" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="F853" t="n">
         <v>47.4</v>
@@ -24326,7 +24326,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="F854" t="n">
         <v>47.6</v>
@@ -24354,10 +24354,10 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="F855" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="856">
@@ -24382,7 +24382,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F856" t="n">
         <v>48.2</v>
@@ -24413,7 +24413,7 @@
         <v>19.2</v>
       </c>
       <c r="F857" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="858">
@@ -24438,10 +24438,10 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="F858" t="n">
-        <v>53.9</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="859">
@@ -24497,7 +24497,7 @@
         <v>15.1</v>
       </c>
       <c r="F860" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="861">
@@ -24609,7 +24609,7 @@
         <v>12.9</v>
       </c>
       <c r="F864" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="865">
@@ -24690,10 +24690,10 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="F867" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="868">
@@ -24805,7 +24805,7 @@
         <v>11.1</v>
       </c>
       <c r="F871" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="872">
@@ -24945,7 +24945,7 @@
         <v>8.1</v>
       </c>
       <c r="F876" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="877">
@@ -25001,7 +25001,7 @@
         <v>7.3</v>
       </c>
       <c r="F878" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="879">
@@ -25029,7 +25029,7 @@
         <v>7.2</v>
       </c>
       <c r="F879" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="880">
@@ -25057,7 +25057,7 @@
         <v>7.1</v>
       </c>
       <c r="F880" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="881">
@@ -25085,7 +25085,7 @@
         <v>7.1</v>
       </c>
       <c r="F881" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="882">
@@ -25141,7 +25141,7 @@
         <v>6.3</v>
       </c>
       <c r="F883" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="884">
@@ -25169,7 +25169,7 @@
         <v>6</v>
       </c>
       <c r="F884" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="885">
@@ -25185,19 +25185,19 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E885" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F885" t="n">
-        <v>46.1</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="886">
@@ -25213,19 +25213,19 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E886" t="n">
         <v>5.5</v>
       </c>
       <c r="F886" t="n">
-        <v>50.9</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="887">
@@ -25253,7 +25253,7 @@
         <v>5.4</v>
       </c>
       <c r="F887" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="888">
@@ -25281,7 +25281,7 @@
         <v>5.2</v>
       </c>
       <c r="F888" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="889">
@@ -25309,7 +25309,7 @@
         <v>4.2</v>
       </c>
       <c r="F889" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="890">
@@ -25337,7 +25337,7 @@
         <v>3.7</v>
       </c>
       <c r="F890" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="891">
@@ -25365,7 +25365,7 @@
         <v>3.7</v>
       </c>
       <c r="F891" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="892">
@@ -25381,19 +25381,19 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E892" t="n">
         <v>3.6</v>
       </c>
       <c r="F892" t="n">
-        <v>52.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="893">
@@ -25409,19 +25409,19 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E893" t="n">
         <v>3.5</v>
       </c>
       <c r="F893" t="n">
-        <v>50.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="894">
@@ -25449,7 +25449,7 @@
         <v>3.4</v>
       </c>
       <c r="F894" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="895">
@@ -25561,7 +25561,7 @@
         <v>2.9</v>
       </c>
       <c r="F898" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="899">
@@ -25589,7 +25589,7 @@
         <v>2.6</v>
       </c>
       <c r="F899" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="900">
@@ -25701,7 +25701,7 @@
         <v>26.4</v>
       </c>
       <c r="F903" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="904">
@@ -25726,7 +25726,7 @@
         </is>
       </c>
       <c r="E904" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="F904" t="n">
         <v>47.7</v>
@@ -25813,7 +25813,7 @@
         <v>19.4</v>
       </c>
       <c r="F907" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="908">
@@ -25866,7 +25866,7 @@
         </is>
       </c>
       <c r="E909" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="F909" t="n">
         <v>50.3</v>
@@ -25885,19 +25885,19 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E910" t="n">
         <v>14.2</v>
       </c>
       <c r="F910" t="n">
-        <v>46.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="911">
@@ -25913,19 +25913,19 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E911" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F911" t="n">
-        <v>49.1</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="912">
@@ -25953,7 +25953,7 @@
         <v>14</v>
       </c>
       <c r="F912" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="913">
@@ -25981,7 +25981,7 @@
         <v>13.7</v>
       </c>
       <c r="F913" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="914">
@@ -26009,7 +26009,7 @@
         <v>13.3</v>
       </c>
       <c r="F914" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="915">
@@ -26062,10 +26062,10 @@
         </is>
       </c>
       <c r="E916" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F916" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="917">
@@ -26121,7 +26121,7 @@
         <v>12.2</v>
       </c>
       <c r="F918" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="919">
@@ -26289,7 +26289,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F924" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="925">
@@ -26317,7 +26317,7 @@
         <v>8.9</v>
       </c>
       <c r="F925" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="926">
@@ -26342,10 +26342,10 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="927">
@@ -26373,7 +26373,7 @@
         <v>8.4</v>
       </c>
       <c r="F927" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="928">
@@ -26429,7 +26429,7 @@
         <v>7</v>
       </c>
       <c r="F929" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="930">
@@ -26482,10 +26482,10 @@
         </is>
       </c>
       <c r="E931" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F931" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="932">
@@ -26513,7 +26513,7 @@
         <v>6</v>
       </c>
       <c r="F932" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="933">
@@ -26569,7 +26569,7 @@
         <v>5.6</v>
       </c>
       <c r="F934" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="935">
@@ -26597,7 +26597,7 @@
         <v>5.4</v>
       </c>
       <c r="F935" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="936">
@@ -26625,7 +26625,7 @@
         <v>5</v>
       </c>
       <c r="F936" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="937">
@@ -26681,7 +26681,7 @@
         <v>4.6</v>
       </c>
       <c r="F938" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="939">
@@ -26793,7 +26793,7 @@
         <v>4.2</v>
       </c>
       <c r="F942" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="943">
@@ -26905,7 +26905,7 @@
         <v>3.4</v>
       </c>
       <c r="F946" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="947">
@@ -26933,7 +26933,7 @@
         <v>3.3</v>
       </c>
       <c r="F947" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="948">
@@ -27017,7 +27017,7 @@
         <v>2.3</v>
       </c>
       <c r="F950" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="951">
@@ -27045,7 +27045,7 @@
         <v>1.8</v>
       </c>
       <c r="F951" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="952">
@@ -27073,7 +27073,7 @@
         <v>30</v>
       </c>
       <c r="F952" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="953">
@@ -27101,7 +27101,7 @@
         <v>28.2</v>
       </c>
       <c r="F953" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="954">
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="E954" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="F954" t="n">
         <v>47.3</v>
@@ -27210,7 +27210,7 @@
         </is>
       </c>
       <c r="E957" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="F957" t="n">
         <v>52.9</v>
@@ -27238,7 +27238,7 @@
         </is>
       </c>
       <c r="E958" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="F958" t="n">
         <v>47.1</v>
@@ -27269,7 +27269,7 @@
         <v>16.4</v>
       </c>
       <c r="F959" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="960">
@@ -27297,7 +27297,7 @@
         <v>16.1</v>
       </c>
       <c r="F960" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="961">
@@ -27378,10 +27378,10 @@
         </is>
       </c>
       <c r="E963" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="F963" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="964">
@@ -27546,7 +27546,7 @@
         </is>
       </c>
       <c r="E969" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F969" t="n">
         <v>53.4</v>
@@ -27577,7 +27577,7 @@
         <v>10.9</v>
       </c>
       <c r="F970" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="971">
@@ -27593,16 +27593,16 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E971" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F971" t="n">
         <v>50.8</v>
@@ -27621,16 +27621,16 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E972" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F972" t="n">
         <v>50.8</v>
@@ -27658,7 +27658,7 @@
         </is>
       </c>
       <c r="E973" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F973" t="n">
         <v>52.6</v>
@@ -27717,7 +27717,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F975" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="976">
@@ -28025,7 +28025,7 @@
         <v>5</v>
       </c>
       <c r="F986" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="987">
@@ -28081,7 +28081,7 @@
         <v>4.8</v>
       </c>
       <c r="F988" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="989">
@@ -28221,7 +28221,7 @@
         <v>4.2</v>
       </c>
       <c r="F993" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="994">
@@ -28249,7 +28249,7 @@
         <v>4</v>
       </c>
       <c r="F994" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="995">
@@ -28361,7 +28361,7 @@
         <v>3.3</v>
       </c>
       <c r="F998" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="999">
@@ -28386,7 +28386,7 @@
         </is>
       </c>
       <c r="E999" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F999" t="n">
         <v>51.7</v>
@@ -28445,7 +28445,7 @@
         <v>2.2</v>
       </c>
       <c r="F1001" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1002">
@@ -28501,7 +28501,7 @@
         <v>30.5</v>
       </c>
       <c r="F1003" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1004">
@@ -28557,7 +28557,7 @@
         <v>20.4</v>
       </c>
       <c r="F1005" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1006">
@@ -28666,7 +28666,7 @@
         </is>
       </c>
       <c r="E1009" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="F1009" t="n">
         <v>52.3</v>
@@ -28697,7 +28697,7 @@
         <v>16.1</v>
       </c>
       <c r="F1010" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1011">
@@ -28725,7 +28725,7 @@
         <v>14.9</v>
       </c>
       <c r="F1011" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1012">
@@ -28837,7 +28837,7 @@
         <v>12.4</v>
       </c>
       <c r="F1015" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1016">
@@ -28893,7 +28893,7 @@
         <v>11.7</v>
       </c>
       <c r="F1017" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1018">
@@ -28946,7 +28946,7 @@
         </is>
       </c>
       <c r="E1019" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F1019" t="n">
         <v>52.9</v>
@@ -29002,7 +29002,7 @@
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F1021" t="n">
         <v>49.8</v>
@@ -29229,7 +29229,7 @@
         <v>7</v>
       </c>
       <c r="F1029" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1030">
@@ -29425,7 +29425,7 @@
         <v>5.7</v>
       </c>
       <c r="F1036" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1037">
@@ -29453,7 +29453,7 @@
         <v>5.6</v>
       </c>
       <c r="F1037" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1038">
@@ -29478,7 +29478,7 @@
         </is>
       </c>
       <c r="E1038" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F1038" t="n">
         <v>52.1</v>
@@ -29509,7 +29509,7 @@
         <v>4.9</v>
       </c>
       <c r="F1039" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1040">
@@ -29537,7 +29537,7 @@
         <v>4.8</v>
       </c>
       <c r="F1040" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1041">
@@ -29565,7 +29565,7 @@
         <v>4.4</v>
       </c>
       <c r="F1041" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1042">
@@ -29593,7 +29593,7 @@
         <v>4.3</v>
       </c>
       <c r="F1042" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1043">
@@ -29621,7 +29621,7 @@
         <v>4.1</v>
       </c>
       <c r="F1043" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1044">
@@ -29677,7 +29677,7 @@
         <v>4</v>
       </c>
       <c r="F1045" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1046">
@@ -29733,7 +29733,7 @@
         <v>3.4</v>
       </c>
       <c r="F1047" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1048">
@@ -29761,7 +29761,7 @@
         <v>3.3</v>
       </c>
       <c r="F1048" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1049">
@@ -29789,7 +29789,7 @@
         <v>3.2</v>
       </c>
       <c r="F1049" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1050">
@@ -29817,7 +29817,7 @@
         <v>3.2</v>
       </c>
       <c r="F1050" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1051">
@@ -29870,7 +29870,7 @@
         </is>
       </c>
       <c r="E1052" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="F1052" t="n">
         <v>47.7</v>
@@ -29898,7 +29898,7 @@
         </is>
       </c>
       <c r="E1053" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="F1053" t="n">
         <v>46.4</v>
@@ -29954,7 +29954,7 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="F1055" t="n">
         <v>51.2</v>
@@ -29985,7 +29985,7 @@
         <v>18.6</v>
       </c>
       <c r="F1056" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1057">
@@ -30013,7 +30013,7 @@
         <v>18.3</v>
       </c>
       <c r="F1057" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1058">
@@ -30041,7 +30041,7 @@
         <v>16.3</v>
       </c>
       <c r="F1058" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1059">
@@ -30150,7 +30150,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F1062" t="n">
         <v>51.6</v>
@@ -30178,7 +30178,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="F1063" t="n">
         <v>50.7</v>
@@ -30209,7 +30209,7 @@
         <v>12.5</v>
       </c>
       <c r="F1064" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1065">
@@ -30262,10 +30262,10 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F1066" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1067">
@@ -30309,19 +30309,19 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1068" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F1068" t="n">
-        <v>50.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1069">
@@ -30337,19 +30337,19 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F1069" t="n">
-        <v>47.2</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1070">
@@ -30486,7 +30486,7 @@
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F1074" t="n">
         <v>51.9</v>
@@ -30517,7 +30517,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F1075" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1076">
@@ -30545,7 +30545,7 @@
         <v>8</v>
       </c>
       <c r="F1076" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1077">
@@ -30601,7 +30601,7 @@
         <v>7</v>
       </c>
       <c r="F1078" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1079">
@@ -30657,7 +30657,7 @@
         <v>6.6</v>
       </c>
       <c r="F1080" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1081">
@@ -30741,7 +30741,7 @@
         <v>6.4</v>
       </c>
       <c r="F1083" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1084">
@@ -30797,7 +30797,7 @@
         <v>5.8</v>
       </c>
       <c r="F1085" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1086">
@@ -30825,7 +30825,7 @@
         <v>5.7</v>
       </c>
       <c r="F1086" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1087">
@@ -30881,7 +30881,7 @@
         <v>5.2</v>
       </c>
       <c r="F1088" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1089">
@@ -30909,7 +30909,7 @@
         <v>4.9</v>
       </c>
       <c r="F1089" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1090">
@@ -30925,7 +30925,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -30937,7 +30937,7 @@
         <v>4.7</v>
       </c>
       <c r="F1090" t="n">
-        <v>45.4</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1091">
@@ -30953,7 +30953,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
@@ -30962,10 +30962,10 @@
         </is>
       </c>
       <c r="E1091" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F1091" t="n">
-        <v>51.4</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1092">
@@ -31021,7 +31021,7 @@
         <v>4.4</v>
       </c>
       <c r="F1093" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1094">
@@ -31049,7 +31049,7 @@
         <v>4.2</v>
       </c>
       <c r="F1094" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1095">
@@ -31077,7 +31077,7 @@
         <v>4.1</v>
       </c>
       <c r="F1095" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1096">
@@ -31121,19 +31121,19 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1097" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F1097" t="n">
-        <v>46.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1098">
@@ -31149,19 +31149,19 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1098" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1098" t="n">
-        <v>50.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1099">
@@ -31217,7 +31217,7 @@
         <v>2.9</v>
       </c>
       <c r="F1100" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1101">
@@ -31242,10 +31242,10 @@
         </is>
       </c>
       <c r="E1101" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1101" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1102">
@@ -34717,7 +34717,7 @@
         <v>1.7</v>
       </c>
       <c r="F1225" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1226">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="E1228" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1228" t="n">
         <v>50.3</v>
@@ -35025,7 +35025,7 @@
         <v>1.1</v>
       </c>
       <c r="F1236" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1237">
@@ -35193,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="F1242" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1243">
@@ -35221,7 +35221,7 @@
         <v>1</v>
       </c>
       <c r="F1243" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1244">
@@ -35473,7 +35473,7 @@
         <v>5.9</v>
       </c>
       <c r="F1252" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1253">
@@ -35529,7 +35529,7 @@
         <v>4.4</v>
       </c>
       <c r="F1254" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1255">
@@ -35554,7 +35554,7 @@
         </is>
       </c>
       <c r="E1255" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F1255" t="n">
         <v>47.4</v>
@@ -35697,7 +35697,7 @@
         <v>3.1</v>
       </c>
       <c r="F1260" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1261">
@@ -35725,7 +35725,7 @@
         <v>3</v>
       </c>
       <c r="F1261" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1262">
@@ -35825,19 +35825,19 @@
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1265" t="n">
         <v>2.8</v>
       </c>
       <c r="F1265" t="n">
-        <v>51.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1266">
@@ -35853,19 +35853,19 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1266" t="n">
         <v>2.7</v>
       </c>
       <c r="F1266" t="n">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1267">
@@ -36229,7 +36229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1279" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1280">
@@ -36341,7 +36341,7 @@
         <v>1.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1284">
@@ -36509,7 +36509,7 @@
         <v>1</v>
       </c>
       <c r="F1289" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1290">
@@ -36593,7 +36593,7 @@
         <v>0.9</v>
       </c>
       <c r="F1292" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1293">
@@ -36649,7 +36649,7 @@
         <v>0.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1295">
@@ -36677,7 +36677,7 @@
         <v>0.7</v>
       </c>
       <c r="F1295" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1296">
@@ -36733,7 +36733,7 @@
         <v>0.6</v>
       </c>
       <c r="F1297" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1298">
@@ -36817,7 +36817,7 @@
         <v>0.5</v>
       </c>
       <c r="F1300" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="1301">
@@ -37178,7 +37178,7 @@
         </is>
       </c>
       <c r="E1313" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F1313" t="n">
         <v>49.5</v>
@@ -37769,7 +37769,7 @@
         <v>1.2</v>
       </c>
       <c r="F1334" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1335">
@@ -37853,7 +37853,7 @@
         <v>1.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1338">
@@ -37909,7 +37909,7 @@
         <v>1.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1340">
@@ -38245,7 +38245,7 @@
         <v>0.4</v>
       </c>
       <c r="F1351" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1352">
@@ -38469,7 +38469,7 @@
         <v>3.1</v>
       </c>
       <c r="F1359" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1360">
@@ -38550,7 +38550,7 @@
         </is>
       </c>
       <c r="E1362" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F1362" t="n">
         <v>52.4</v>
@@ -38749,7 +38749,7 @@
         <v>2.2</v>
       </c>
       <c r="F1369" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1370">
@@ -38777,7 +38777,7 @@
         <v>2.1</v>
       </c>
       <c r="F1370" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1371">
@@ -38961,7 +38961,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1377" t="inlineStr">
@@ -38973,7 +38973,7 @@
         <v>1.6</v>
       </c>
       <c r="F1377" t="n">
-        <v>49.5</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1378">
@@ -38989,7 +38989,7 @@
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr">
@@ -38998,10 +38998,10 @@
         </is>
       </c>
       <c r="E1378" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1378" t="n">
-        <v>43.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1379">
@@ -39113,7 +39113,7 @@
         <v>1.2</v>
       </c>
       <c r="F1382" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1383">
@@ -39185,19 +39185,19 @@
       </c>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1385" t="n">
         <v>1.1</v>
       </c>
       <c r="F1385" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1386">
@@ -39213,19 +39213,19 @@
       </c>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1386" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1386" t="n">
         <v>1.1</v>
       </c>
       <c r="F1386" t="n">
-        <v>46.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1387">
@@ -39241,19 +39241,19 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1387" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1387" t="n">
         <v>1.1</v>
       </c>
       <c r="F1387" t="n">
-        <v>50.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1388">
@@ -39325,19 +39325,19 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1390" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1390" t="n">
         <v>1.1</v>
       </c>
       <c r="F1390" t="n">
-        <v>50.7</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1391">
@@ -39353,19 +39353,19 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1391" t="n">
         <v>1.1</v>
       </c>
       <c r="F1391" t="n">
-        <v>41.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1392">
@@ -39477,7 +39477,7 @@
         <v>0.9</v>
       </c>
       <c r="F1395" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1396">
@@ -39645,7 +39645,7 @@
         <v>0.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1402">
@@ -39925,7 +39925,7 @@
         <v>2.8</v>
       </c>
       <c r="F1411" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>2.8</v>
       </c>
       <c r="F1412" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>2.7</v>
       </c>
       <c r="F1413" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1414">
@@ -40009,7 +40009,7 @@
         <v>2.4</v>
       </c>
       <c r="F1414" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1415">
@@ -40065,7 +40065,7 @@
         <v>2.3</v>
       </c>
       <c r="F1416" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1417">
@@ -40569,7 +40569,7 @@
         <v>1.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1435">
@@ -40709,7 +40709,7 @@
         <v>1</v>
       </c>
       <c r="F1439" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1440">
@@ -40793,7 +40793,7 @@
         <v>0.9</v>
       </c>
       <c r="F1442" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1443">
@@ -40849,7 +40849,7 @@
         <v>0.8</v>
       </c>
       <c r="F1444" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1445">
@@ -40933,7 +40933,7 @@
         <v>0.8</v>
       </c>
       <c r="F1447" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1448">
@@ -41154,7 +41154,7 @@
         </is>
       </c>
       <c r="E1455" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1455" t="n">
         <v>47.5</v>
@@ -41269,7 +41269,7 @@
         <v>3.2</v>
       </c>
       <c r="F1459" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1460">
@@ -41437,7 +41437,7 @@
         <v>2.4</v>
       </c>
       <c r="F1465" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1466">
@@ -41605,7 +41605,7 @@
         <v>2.1</v>
       </c>
       <c r="F1471" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1472">
@@ -41773,7 +41773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1478">
@@ -41885,7 +41885,7 @@
         <v>1.3</v>
       </c>
       <c r="F1481" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1482">
@@ -41941,7 +41941,7 @@
         <v>1.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1484">
@@ -41957,7 +41957,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -41969,7 +41969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1484" t="n">
-        <v>45.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1485">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -41997,7 +41997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1485" t="n">
-        <v>51.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1486">
@@ -42013,19 +42013,19 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1486" t="n">
         <v>1</v>
       </c>
       <c r="F1486" t="n">
-        <v>43.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1487">
@@ -42041,19 +42041,19 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1487" t="n">
         <v>1</v>
       </c>
       <c r="F1487" t="n">
-        <v>45.9</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1488">
@@ -42081,7 +42081,7 @@
         <v>1</v>
       </c>
       <c r="F1488" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1489">
@@ -42221,7 +42221,7 @@
         <v>0.7</v>
       </c>
       <c r="F1493" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1494">
@@ -42249,7 +42249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1495">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>0.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>0.4</v>
       </c>
       <c r="F1500" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1501">
@@ -42445,7 +42445,7 @@
         <v>0.4</v>
       </c>
       <c r="F1501" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>6.3</v>
       </c>
       <c r="F1502" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1503">
@@ -42501,7 +42501,7 @@
         <v>6</v>
       </c>
       <c r="F1503" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1504">
@@ -42557,7 +42557,7 @@
         <v>4.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1506">
@@ -42585,7 +42585,7 @@
         <v>4.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1507">
@@ -42669,7 +42669,7 @@
         <v>3.8</v>
       </c>
       <c r="F1509" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1510">
@@ -42697,7 +42697,7 @@
         <v>3.7</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1511">
@@ -42725,7 +42725,7 @@
         <v>3.3</v>
       </c>
       <c r="F1511" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1512">
@@ -42753,7 +42753,7 @@
         <v>2.9</v>
       </c>
       <c r="F1512" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1513">
@@ -42781,7 +42781,7 @@
         <v>2.6</v>
       </c>
       <c r="F1513" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1514">
@@ -42837,7 +42837,7 @@
         <v>2.5</v>
       </c>
       <c r="F1515" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1516">
@@ -42865,7 +42865,7 @@
         <v>2.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1517">
@@ -42893,7 +42893,7 @@
         <v>2.4</v>
       </c>
       <c r="F1517" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1518">
@@ -42921,7 +42921,7 @@
         <v>2.3</v>
       </c>
       <c r="F1518" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1519">
@@ -42949,7 +42949,7 @@
         <v>2.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1520">
@@ -42965,19 +42965,19 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1520" t="n">
         <v>2.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1521">
@@ -42993,19 +42993,19 @@
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1521" t="n">
         <v>2.1</v>
       </c>
       <c r="F1521" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1522">
@@ -43033,7 +43033,7 @@
         <v>2</v>
       </c>
       <c r="F1522" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>1.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>53.9</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1524">
@@ -43089,7 +43089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1524" t="n">
-        <v>46.8</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1525">
@@ -43105,19 +43105,19 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1525" t="n">
         <v>1.8</v>
       </c>
       <c r="F1525" t="n">
-        <v>47.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1526">
@@ -43133,19 +43133,19 @@
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1526" t="n">
         <v>1.8</v>
       </c>
       <c r="F1526" t="n">
-        <v>45.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1527">
@@ -43170,10 +43170,10 @@
         </is>
       </c>
       <c r="E1527" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F1527" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1528">
@@ -43189,19 +43189,19 @@
       </c>
       <c r="C1528" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1528" t="n">
         <v>1.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>40.1</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="1529">
@@ -43217,19 +43217,19 @@
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1529" t="n">
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>38.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1531">
@@ -43285,7 +43285,7 @@
         <v>1.4</v>
       </c>
       <c r="F1531" t="n">
-        <v>31.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1532">
@@ -43313,7 +43313,7 @@
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1533">
@@ -43341,7 +43341,7 @@
         <v>1.3</v>
       </c>
       <c r="F1533" t="n">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>1.1</v>
       </c>
       <c r="F1534" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="1535">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>51.3</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>1</v>
       </c>
       <c r="F1536" t="n">
-        <v>53.5</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>0.9</v>
       </c>
       <c r="F1537" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1538">
@@ -43509,7 +43509,7 @@
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1540">
@@ -43534,7 +43534,7 @@
         </is>
       </c>
       <c r="E1540" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1540" t="n">
         <v>39.4</v>
@@ -43565,7 +43565,7 @@
         <v>0.7</v>
       </c>
       <c r="F1541" t="n">
-        <v>39.2</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="1542">
@@ -43593,7 +43593,7 @@
         <v>0.7</v>
       </c>
       <c r="F1542" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1543">
@@ -43621,7 +43621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1543" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1544">
@@ -43637,7 +43637,7 @@
       </c>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
@@ -43649,7 +43649,7 @@
         <v>0.5</v>
       </c>
       <c r="F1544" t="n">
-        <v>42.5</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1545">
@@ -43665,7 +43665,7 @@
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
@@ -43677,7 +43677,7 @@
         <v>0.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>46.6</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1546">
@@ -43705,7 +43705,7 @@
         <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="1547">
@@ -43733,7 +43733,7 @@
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="1548">
@@ -43817,7 +43817,7 @@
         <v>0.3</v>
       </c>
       <c r="F1550" t="n">
-        <v>37.7</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="1551">
@@ -43845,7 +43845,7 @@
         <v>0.3</v>
       </c>
       <c r="F1551" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1552">
@@ -43870,10 +43870,10 @@
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F1552" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1553">
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>10.9</v>
+        <v>9</v>
       </c>
       <c r="F1553" t="n">
         <v>40.5</v>
@@ -43917,19 +43917,19 @@
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F1554" t="n">
-        <v>44.5</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="1555">
@@ -43945,19 +43945,19 @@
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="F1555" t="n">
-        <v>43.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1556">
@@ -43982,10 +43982,10 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F1556" t="n">
-        <v>10.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1557">
@@ -44001,19 +44001,19 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="F1557" t="n">
-        <v>61.3</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="1558">
@@ -44029,19 +44029,19 @@
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="F1558" t="n">
-        <v>86.40000000000001</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="1559">
@@ -44057,19 +44057,19 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1559" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="F1559" t="n">
-        <v>15.6</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="1560">
@@ -44085,19 +44085,19 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1560" t="n">
         <v>3.1</v>
       </c>
       <c r="F1560" t="n">
-        <v>63.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="1561">
@@ -44113,19 +44113,19 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1561" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="F1561" t="n">
-        <v>65.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="1562">
@@ -44141,19 +44141,19 @@
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1562" t="n">
-        <v>26.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="F1563" t="n">
-        <v>44.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1564">
@@ -44197,19 +44197,19 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="F1564" t="n">
-        <v>63.9</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="1565">
@@ -44225,19 +44225,19 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1565" t="n">
-        <v>62.9</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="1566">
@@ -44253,19 +44253,19 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1566" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="F1566" t="n">
-        <v>69.2</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1567">
@@ -44281,19 +44281,19 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="F1567" t="n">
-        <v>56.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="1568">
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1568" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="F1568" t="n">
-        <v>43.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1569">
@@ -44337,19 +44337,19 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1569" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="F1569" t="n">
-        <v>40.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1570">
@@ -44365,19 +44365,19 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1570" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1570" t="n">
-        <v>77.2</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1571" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1571" t="n">
-        <v>39.5</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,19 +44421,19 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1572" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1572" t="n">
-        <v>100</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="1573">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1573" t="n">
         <v>1.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>25.3</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1574" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F1574" t="n">
-        <v>100</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="1575">
@@ -44505,19 +44505,19 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1575" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F1575" t="n">
-        <v>11.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1576">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1576" t="n">
         <v>1.3</v>
       </c>
       <c r="F1576" t="n">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="1577">
@@ -44570,7 +44570,7 @@
         </is>
       </c>
       <c r="E1577" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F1577" t="n">
         <v>57.7</v>
@@ -44589,19 +44589,19 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1578" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F1578" t="n">
-        <v>0</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1579">
@@ -44617,19 +44617,19 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1579" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F1579" t="n">
-        <v>98.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1580">
@@ -44645,19 +44645,19 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1580" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1580" t="n">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="1581">
@@ -44673,19 +44673,19 @@
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1581" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1581" t="n">
-        <v>51.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1582">
@@ -44701,19 +44701,19 @@
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1582" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1582" t="n">
-        <v>68.09999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="1583">
@@ -44729,19 +44729,19 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F1583" t="n">
-        <v>72.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1584">
@@ -44766,7 +44766,7 @@
         </is>
       </c>
       <c r="E1584" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1584" t="n">
         <v>0</v>
@@ -44794,7 +44794,7 @@
         </is>
       </c>
       <c r="E1585" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1585" t="n">
         <v>100</v>
@@ -44822,7 +44822,7 @@
         </is>
       </c>
       <c r="E1586" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1586" t="n">
         <v>100</v>
@@ -44841,7 +44841,7 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -44850,10 +44850,10 @@
         </is>
       </c>
       <c r="E1587" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1587" t="n">
-        <v>41.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1588">
@@ -44869,19 +44869,19 @@
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1588" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F1588" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1589">
@@ -44897,12 +44897,12 @@
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1589" t="n">
@@ -44925,7 +44925,7 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -44937,7 +44937,7 @@
         <v>0.3</v>
       </c>
       <c r="F1590" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1591">
@@ -44953,19 +44953,19 @@
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1591" t="n">
         <v>0.3</v>
       </c>
       <c r="F1591" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1592">
@@ -44981,18 +44981,46 @@
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1592" t="n">
         <v>0.3</v>
       </c>
       <c r="F1592" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>제트팩 캣</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>지원 · 전술가</t>
+        </is>
+      </c>
+      <c r="E1593" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1593" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -1957,7 +1957,7 @@
         <v>20.5</v>
       </c>
       <c r="F55" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="56">
@@ -2013,7 +2013,7 @@
         <v>19.2</v>
       </c>
       <c r="F57" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="58">
@@ -2041,7 +2041,7 @@
         <v>18.9</v>
       </c>
       <c r="F58" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="59">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="F59" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="60">
@@ -2097,7 +2097,7 @@
         <v>16.7</v>
       </c>
       <c r="F60" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="61">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="F61" t="n">
         <v>52.8</v>
@@ -2237,7 +2237,7 @@
         <v>13.5</v>
       </c>
       <c r="F65" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="66">
@@ -2265,7 +2265,7 @@
         <v>12.8</v>
       </c>
       <c r="F66" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="67">
@@ -2349,7 +2349,7 @@
         <v>10.9</v>
       </c>
       <c r="F69" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="70">
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F70" t="n">
         <v>47.5</v>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F71" t="n">
         <v>45.6</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F72" t="n">
         <v>48.1</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F73" t="n">
         <v>48.4</v>
@@ -2517,7 +2517,7 @@
         <v>7.9</v>
       </c>
       <c r="F75" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="76">
@@ -2601,7 +2601,7 @@
         <v>7.4</v>
       </c>
       <c r="F78" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="79">
@@ -2629,7 +2629,7 @@
         <v>6.9</v>
       </c>
       <c r="F79" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="80">
@@ -2657,7 +2657,7 @@
         <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="81">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F81" t="n">
         <v>44.7</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F82" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="83">
@@ -2769,7 +2769,7 @@
         <v>5.6</v>
       </c>
       <c r="F84" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="85">
@@ -2797,7 +2797,7 @@
         <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="86">
@@ -2825,7 +2825,7 @@
         <v>5.2</v>
       </c>
       <c r="F86" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="87">
@@ -2853,7 +2853,7 @@
         <v>5.2</v>
       </c>
       <c r="F87" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="88">
@@ -2881,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="89">
@@ -2909,7 +2909,7 @@
         <v>4.4</v>
       </c>
       <c r="F89" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="90">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F90" t="n">
         <v>54.9</v>
@@ -2965,7 +2965,7 @@
         <v>3.9</v>
       </c>
       <c r="F91" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="92">
@@ -2993,7 +2993,7 @@
         <v>3.6</v>
       </c>
       <c r="F92" t="n">
-        <v>44.1</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="93">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F93" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="94">
@@ -3049,7 +3049,7 @@
         <v>3.2</v>
       </c>
       <c r="F94" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="95">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96">
@@ -3105,7 +3105,7 @@
         <v>2.9</v>
       </c>
       <c r="F96" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="97">
@@ -3133,7 +3133,7 @@
         <v>2.8</v>
       </c>
       <c r="F97" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="98">
@@ -3245,7 +3245,7 @@
         <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="102">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="F102" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="103">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="F103" t="n">
         <v>48.7</v>
@@ -3385,7 +3385,7 @@
         <v>19.8</v>
       </c>
       <c r="F106" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="107">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="F107" t="n">
         <v>52.7</v>
@@ -3497,7 +3497,7 @@
         <v>15.3</v>
       </c>
       <c r="F110" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="111">
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="F111" t="n">
         <v>52.1</v>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F113" t="n">
         <v>46.1</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="F114" t="n">
         <v>47.5</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F115" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="116">
@@ -3709,19 +3709,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>11</v>
       </c>
       <c r="F118" t="n">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="119">
@@ -3737,19 +3737,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F119" t="n">
-        <v>52.3</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="120">
@@ -3833,7 +3833,7 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="123">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F126" t="n">
         <v>48.4</v>
@@ -4001,7 +4001,7 @@
         <v>7.5</v>
       </c>
       <c r="F128" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="129">
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F129" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="130">
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F133" t="n">
         <v>44.8</v>
@@ -4169,7 +4169,7 @@
         <v>6.5</v>
       </c>
       <c r="F134" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="135">
@@ -4269,19 +4269,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F138" t="n">
-        <v>47.1</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="139">
@@ -4297,19 +4297,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E139" t="n">
         <v>4.4</v>
       </c>
       <c r="F139" t="n">
-        <v>51.7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="140">
@@ -4325,19 +4325,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F140" t="n">
-        <v>54.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="141">
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F142" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="143">
@@ -4449,7 +4449,7 @@
         <v>3.7</v>
       </c>
       <c r="F144" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="145">
@@ -4477,7 +4477,7 @@
         <v>3.4</v>
       </c>
       <c r="F145" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="146">
@@ -4533,7 +4533,7 @@
         <v>2.9</v>
       </c>
       <c r="F147" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="148">
@@ -4561,7 +4561,7 @@
         <v>2.6</v>
       </c>
       <c r="F148" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="149">
@@ -4589,7 +4589,7 @@
         <v>2.5</v>
       </c>
       <c r="F149" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="150">
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="F203" t="n">
         <v>47.7</v>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="F207" t="n">
         <v>51.5</v>
@@ -6241,7 +6241,7 @@
         <v>14.8</v>
       </c>
       <c r="F208" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="209">
@@ -6353,7 +6353,7 @@
         <v>13.2</v>
       </c>
       <c r="F212" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="213">
@@ -6381,7 +6381,7 @@
         <v>12.6</v>
       </c>
       <c r="F213" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="214">
@@ -6397,19 +6397,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F214" t="n">
-        <v>50.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="215">
@@ -6425,19 +6425,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F215" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="216">
@@ -6453,19 +6453,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F216" t="n">
-        <v>53.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="217">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F219" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="220">
@@ -6577,7 +6577,7 @@
         <v>8.6</v>
       </c>
       <c r="F220" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="221">
@@ -6661,7 +6661,7 @@
         <v>7.8</v>
       </c>
       <c r="F223" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="224">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="F225" t="n">
         <v>49.5</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F226" t="n">
         <v>53.2</v>
@@ -6773,7 +6773,7 @@
         <v>7.2</v>
       </c>
       <c r="F227" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="228">
@@ -6801,7 +6801,7 @@
         <v>7</v>
       </c>
       <c r="F228" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="229">
@@ -6885,7 +6885,7 @@
         <v>6.9</v>
       </c>
       <c r="F231" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="232">
@@ -6997,7 +6997,7 @@
         <v>4.7</v>
       </c>
       <c r="F235" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="236">
@@ -7041,19 +7041,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E237" t="n">
         <v>4.6</v>
       </c>
       <c r="F237" t="n">
-        <v>47.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="238">
@@ -7069,19 +7069,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F238" t="n">
-        <v>53.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="239">
@@ -7109,7 +7109,7 @@
         <v>4.4</v>
       </c>
       <c r="F239" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="240">
@@ -7137,7 +7137,7 @@
         <v>4.4</v>
       </c>
       <c r="F240" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="241">
@@ -7165,7 +7165,7 @@
         <v>4.4</v>
       </c>
       <c r="F241" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="242">
@@ -7305,7 +7305,7 @@
         <v>3.7</v>
       </c>
       <c r="F246" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="247">
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F247" t="n">
         <v>49.2</v>
@@ -7417,7 +7417,7 @@
         <v>3.2</v>
       </c>
       <c r="F250" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="251">
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="F254" t="n">
         <v>45.9</v>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F257" t="n">
         <v>50.8</v>
@@ -7641,7 +7641,7 @@
         <v>16.4</v>
       </c>
       <c r="F258" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="259">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F260" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="261">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="F261" t="n">
         <v>54.7</v>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F262" t="n">
         <v>50.9</v>
@@ -7781,7 +7781,7 @@
         <v>12.8</v>
       </c>
       <c r="F263" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="264">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F265" t="n">
         <v>49.6</v>
@@ -7865,7 +7865,7 @@
         <v>10.9</v>
       </c>
       <c r="F266" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="267">
@@ -7893,7 +7893,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F267" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="268">
@@ -7977,7 +7977,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F270" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="271">
@@ -8005,7 +8005,7 @@
         <v>8.1</v>
       </c>
       <c r="F271" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="272">
@@ -8033,7 +8033,7 @@
         <v>8</v>
       </c>
       <c r="F272" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="273">
@@ -8117,7 +8117,7 @@
         <v>7.8</v>
       </c>
       <c r="F275" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="276">
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F276" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="277">
@@ -8173,7 +8173,7 @@
         <v>6.7</v>
       </c>
       <c r="F277" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="278">
@@ -8257,7 +8257,7 @@
         <v>5.8</v>
       </c>
       <c r="F280" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="281">
@@ -8282,10 +8282,10 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F281" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="282">
@@ -8313,7 +8313,7 @@
         <v>5.3</v>
       </c>
       <c r="F282" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="283">
@@ -8397,7 +8397,7 @@
         <v>4.7</v>
       </c>
       <c r="F285" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="286">
@@ -8425,7 +8425,7 @@
         <v>4.7</v>
       </c>
       <c r="F286" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="287">
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F292" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="293">
@@ -8621,7 +8621,7 @@
         <v>3.8</v>
       </c>
       <c r="F293" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="294">
@@ -8649,7 +8649,7 @@
         <v>3.6</v>
       </c>
       <c r="F294" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="295">
@@ -8677,7 +8677,7 @@
         <v>3.6</v>
       </c>
       <c r="F295" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="296">
@@ -8705,7 +8705,7 @@
         <v>3.4</v>
       </c>
       <c r="F296" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="297">
@@ -8761,7 +8761,7 @@
         <v>3.3</v>
       </c>
       <c r="F298" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="299">
@@ -8789,7 +8789,7 @@
         <v>3.2</v>
       </c>
       <c r="F299" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="300">
@@ -8845,7 +8845,7 @@
         <v>2.5</v>
       </c>
       <c r="F301" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="302">
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="F403" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="404">
@@ -11745,19 +11745,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E405" t="n">
         <v>19.6</v>
       </c>
       <c r="F405" t="n">
-        <v>53.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="406">
@@ -11773,19 +11773,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="F406" t="n">
-        <v>48.5</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="407">
@@ -11869,7 +11869,7 @@
         <v>17.6</v>
       </c>
       <c r="F409" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="410">
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="F410" t="n">
         <v>50.1</v>
@@ -11981,7 +11981,7 @@
         <v>13.3</v>
       </c>
       <c r="F413" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="414">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -12177,7 +12177,7 @@
         <v>10</v>
       </c>
       <c r="F420" t="n">
-        <v>51</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="421">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F421" t="n">
-        <v>52.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="422">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F425" t="n">
         <v>47.5</v>
@@ -12429,7 +12429,7 @@
         <v>7.7</v>
       </c>
       <c r="F429" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="430">
@@ -12905,7 +12905,7 @@
         <v>3.8</v>
       </c>
       <c r="F446" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="447">
@@ -12933,7 +12933,7 @@
         <v>3.6</v>
       </c>
       <c r="F447" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="448">
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="F452" t="n">
         <v>49.4</v>
@@ -13213,7 +13213,7 @@
         <v>20</v>
       </c>
       <c r="F457" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="458">
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F461" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="462">
@@ -13341,19 +13341,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E462" t="n">
         <v>13.7</v>
       </c>
       <c r="F462" t="n">
-        <v>52.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="463">
@@ -13369,19 +13369,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="F463" t="n">
-        <v>43.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="464">
@@ -13409,7 +13409,7 @@
         <v>12.6</v>
       </c>
       <c r="F464" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="465">
@@ -13605,7 +13605,7 @@
         <v>10.8</v>
       </c>
       <c r="F471" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="472">
@@ -13633,7 +13633,7 @@
         <v>10.4</v>
       </c>
       <c r="F472" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="473">
@@ -13661,7 +13661,7 @@
         <v>10.4</v>
       </c>
       <c r="F473" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="474">
@@ -13689,7 +13689,7 @@
         <v>10.3</v>
       </c>
       <c r="F474" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="475">
@@ -13745,7 +13745,7 @@
         <v>7.9</v>
       </c>
       <c r="F476" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="477">
@@ -13801,7 +13801,7 @@
         <v>7.7</v>
       </c>
       <c r="F478" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="479">
@@ -13829,7 +13829,7 @@
         <v>7.2</v>
       </c>
       <c r="F479" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="480">
@@ -13857,7 +13857,7 @@
         <v>6.8</v>
       </c>
       <c r="F480" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="481">
@@ -13885,7 +13885,7 @@
         <v>6.8</v>
       </c>
       <c r="F481" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="482">
@@ -13941,7 +13941,7 @@
         <v>6.1</v>
       </c>
       <c r="F483" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="484">
@@ -13997,7 +13997,7 @@
         <v>5.8</v>
       </c>
       <c r="F485" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="486">
@@ -14165,7 +14165,7 @@
         <v>4</v>
       </c>
       <c r="F491" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="492">
@@ -14221,7 +14221,7 @@
         <v>3.7</v>
       </c>
       <c r="F493" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="494">
@@ -14246,10 +14246,10 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F494" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="495">
@@ -14277,7 +14277,7 @@
         <v>3.4</v>
       </c>
       <c r="F495" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="496">
@@ -14293,19 +14293,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E496" t="n">
         <v>3.4</v>
       </c>
       <c r="F496" t="n">
-        <v>52.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="497">
@@ -14321,19 +14321,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F497" t="n">
-        <v>50.9</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="498">
@@ -14361,7 +14361,7 @@
         <v>3.2</v>
       </c>
       <c r="F498" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="499">
@@ -14389,7 +14389,7 @@
         <v>3.2</v>
       </c>
       <c r="F499" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="500">
@@ -14417,7 +14417,7 @@
         <v>2.6</v>
       </c>
       <c r="F500" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="501">
@@ -14445,7 +14445,7 @@
         <v>2</v>
       </c>
       <c r="F501" t="n">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="502">
@@ -14501,7 +14501,7 @@
         <v>26.4</v>
       </c>
       <c r="F503" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="504">
@@ -14529,7 +14529,7 @@
         <v>21.4</v>
       </c>
       <c r="F504" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="505">
@@ -14557,7 +14557,7 @@
         <v>20.7</v>
       </c>
       <c r="F505" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="506">
@@ -14613,7 +14613,7 @@
         <v>20.3</v>
       </c>
       <c r="F507" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="508">
@@ -14638,10 +14638,10 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="F508" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="509">
@@ -14669,7 +14669,7 @@
         <v>17.4</v>
       </c>
       <c r="F509" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="510">
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="F511" t="n">
         <v>52.5</v>
@@ -14753,7 +14753,7 @@
         <v>13.9</v>
       </c>
       <c r="F512" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="513">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="F513" t="n">
         <v>44.9</v>
@@ -14921,7 +14921,7 @@
         <v>11.5</v>
       </c>
       <c r="F518" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="519">
@@ -15005,7 +15005,7 @@
         <v>10.7</v>
       </c>
       <c r="F521" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="522">
@@ -15117,7 +15117,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F525" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="526">
@@ -15173,7 +15173,7 @@
         <v>7.9</v>
       </c>
       <c r="F527" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="528">
@@ -15226,7 +15226,7 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F529" t="n">
         <v>52.2</v>
@@ -15257,7 +15257,7 @@
         <v>7</v>
       </c>
       <c r="F530" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="531">
@@ -15273,19 +15273,19 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E531" t="n">
         <v>6.5</v>
       </c>
       <c r="F531" t="n">
-        <v>44.7</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="532">
@@ -15301,19 +15301,19 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F532" t="n">
-        <v>49.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="533">
@@ -15537,7 +15537,7 @@
         <v>4.4</v>
       </c>
       <c r="F540" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="541">
@@ -15565,7 +15565,7 @@
         <v>4.3</v>
       </c>
       <c r="F541" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="542">
@@ -15705,7 +15705,7 @@
         <v>3.6</v>
       </c>
       <c r="F546" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="547">
@@ -15845,7 +15845,7 @@
         <v>1.9</v>
       </c>
       <c r="F551" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="552">
@@ -15954,7 +15954,7 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="F555" t="n">
         <v>53.6</v>
@@ -16013,7 +16013,7 @@
         <v>18.9</v>
       </c>
       <c r="F557" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="558">
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F558" t="n">
         <v>50</v>
@@ -16097,7 +16097,7 @@
         <v>16.6</v>
       </c>
       <c r="F560" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="561">
@@ -16125,7 +16125,7 @@
         <v>15.8</v>
       </c>
       <c r="F561" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="562">
@@ -16433,7 +16433,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="F572" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="573">
@@ -16514,10 +16514,10 @@
         </is>
       </c>
       <c r="E575" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F575" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="576">
@@ -16685,7 +16685,7 @@
         <v>7.2</v>
       </c>
       <c r="F581" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="582">
@@ -16769,7 +16769,7 @@
         <v>5.4</v>
       </c>
       <c r="F584" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="585">
@@ -16825,7 +16825,7 @@
         <v>5.4</v>
       </c>
       <c r="F586" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="587">
@@ -17161,7 +17161,7 @@
         <v>3.4</v>
       </c>
       <c r="F598" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="599">
@@ -17245,7 +17245,7 @@
         <v>2.2</v>
       </c>
       <c r="F601" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="602">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="F603" t="n">
         <v>47.3</v>
@@ -17385,7 +17385,7 @@
         <v>19.7</v>
       </c>
       <c r="F606" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="607">
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="F607" t="n">
         <v>52.7</v>
@@ -17497,7 +17497,7 @@
         <v>17.2</v>
       </c>
       <c r="F610" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="611">
@@ -17550,7 +17550,7 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="F612" t="n">
         <v>49.9</v>
@@ -17662,7 +17662,7 @@
         </is>
       </c>
       <c r="E616" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F616" t="n">
         <v>51.7</v>
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F622" t="n">
         <v>49.9</v>
@@ -17858,7 +17858,7 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F623" t="n">
         <v>51.1</v>
@@ -17917,7 +17917,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F625" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="626">
@@ -17945,7 +17945,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F626" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="627">
@@ -18169,7 +18169,7 @@
         <v>6.4</v>
       </c>
       <c r="F634" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="635">
@@ -18253,7 +18253,7 @@
         <v>5.5</v>
       </c>
       <c r="F637" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="638">
@@ -18337,7 +18337,7 @@
         <v>4.6</v>
       </c>
       <c r="F640" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="641">
@@ -18393,7 +18393,7 @@
         <v>4.2</v>
       </c>
       <c r="F642" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="643">
@@ -18577,19 +18577,19 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F649" t="n">
-        <v>51.4</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="650">
@@ -18605,19 +18605,19 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E650" t="n">
         <v>3.3</v>
       </c>
       <c r="F650" t="n">
-        <v>54</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="651">
@@ -18645,7 +18645,7 @@
         <v>3</v>
       </c>
       <c r="F651" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="652">
@@ -18673,7 +18673,7 @@
         <v>34.9</v>
       </c>
       <c r="F652" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="653">
@@ -18698,10 +18698,10 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="F653" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="654">
@@ -18754,7 +18754,7 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="F655" t="n">
         <v>51.5</v>
@@ -18782,10 +18782,10 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="F656" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="657">
@@ -18813,7 +18813,7 @@
         <v>18</v>
       </c>
       <c r="F657" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="658">
@@ -18829,19 +18829,19 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E658" t="n">
         <v>16.4</v>
       </c>
       <c r="F658" t="n">
-        <v>51.6</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="659">
@@ -18857,19 +18857,19 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F659" t="n">
-        <v>53</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="660">
@@ -18922,7 +18922,7 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="F661" t="n">
         <v>45.7</v>
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="F662" t="n">
         <v>51</v>
@@ -18981,7 +18981,7 @@
         <v>12.7</v>
       </c>
       <c r="F663" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="664">
@@ -19034,10 +19034,10 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F665" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="666">
@@ -19121,7 +19121,7 @@
         <v>10.5</v>
       </c>
       <c r="F668" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="669">
@@ -19149,7 +19149,7 @@
         <v>10.3</v>
       </c>
       <c r="F669" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="670">
@@ -19205,7 +19205,7 @@
         <v>9.5</v>
       </c>
       <c r="F671" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="672">
@@ -19333,19 +19333,19 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E676" t="n">
         <v>7.6</v>
       </c>
       <c r="F676" t="n">
-        <v>50.2</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="677">
@@ -19361,19 +19361,19 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F677" t="n">
-        <v>51.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="678">
@@ -19389,19 +19389,19 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E678" t="n">
         <v>7.5</v>
       </c>
       <c r="F678" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="679">
@@ -19429,7 +19429,7 @@
         <v>7.1</v>
       </c>
       <c r="F679" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="680">
@@ -19457,7 +19457,7 @@
         <v>7</v>
       </c>
       <c r="F680" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="681">
@@ -19513,7 +19513,7 @@
         <v>6.5</v>
       </c>
       <c r="F682" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="683">
@@ -19541,7 +19541,7 @@
         <v>6.3</v>
       </c>
       <c r="F683" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="684">
@@ -19569,7 +19569,7 @@
         <v>5.9</v>
       </c>
       <c r="F684" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="685">
@@ -19597,7 +19597,7 @@
         <v>5.8</v>
       </c>
       <c r="F685" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="686">
@@ -19625,7 +19625,7 @@
         <v>5.6</v>
       </c>
       <c r="F686" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="687">
@@ -19653,7 +19653,7 @@
         <v>5.6</v>
       </c>
       <c r="F687" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="688">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -19681,7 +19681,7 @@
         <v>5.2</v>
       </c>
       <c r="F688" t="n">
-        <v>44.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="689">
@@ -19697,19 +19697,19 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E689" t="n">
         <v>5.2</v>
       </c>
       <c r="F689" t="n">
-        <v>51.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="690">
@@ -19725,19 +19725,19 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="F690" t="n">
-        <v>49.3</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="691">
@@ -19793,7 +19793,7 @@
         <v>4.6</v>
       </c>
       <c r="F692" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="693">
@@ -19837,19 +19837,19 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E694" t="n">
         <v>4.2</v>
       </c>
       <c r="F694" t="n">
-        <v>53.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="695">
@@ -19865,19 +19865,19 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F695" t="n">
-        <v>47.6</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="696">
@@ -19905,7 +19905,7 @@
         <v>4.1</v>
       </c>
       <c r="F696" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="697">
@@ -19933,7 +19933,7 @@
         <v>3.4</v>
       </c>
       <c r="F697" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="698">
@@ -19961,7 +19961,7 @@
         <v>3.4</v>
       </c>
       <c r="F698" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="699">
@@ -19989,7 +19989,7 @@
         <v>3.2</v>
       </c>
       <c r="F699" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="700">
@@ -21473,7 +21473,7 @@
         <v>51.7</v>
       </c>
       <c r="F752" t="n">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="753">
@@ -21526,7 +21526,7 @@
         </is>
       </c>
       <c r="E754" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="F754" t="n">
         <v>50.8</v>
@@ -21554,10 +21554,10 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="F755" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="756">
@@ -21585,7 +21585,7 @@
         <v>23.1</v>
       </c>
       <c r="F756" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="757">
@@ -21610,7 +21610,7 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="F757" t="n">
         <v>47</v>
@@ -21638,7 +21638,7 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="F758" t="n">
         <v>51.5</v>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -21666,10 +21666,10 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="F759" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="760">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -21694,10 +21694,10 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="F760" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="761">
@@ -21725,7 +21725,7 @@
         <v>12.9</v>
       </c>
       <c r="F761" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="762">
@@ -21753,7 +21753,7 @@
         <v>12.8</v>
       </c>
       <c r="F762" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="763">
@@ -21781,7 +21781,7 @@
         <v>11.9</v>
       </c>
       <c r="F763" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="764">
@@ -21809,7 +21809,7 @@
         <v>11.2</v>
       </c>
       <c r="F764" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="765">
@@ -21837,7 +21837,7 @@
         <v>10.8</v>
       </c>
       <c r="F765" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="766">
@@ -21862,10 +21862,10 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F766" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="767">
@@ -21890,10 +21890,10 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F767" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="768">
@@ -21918,10 +21918,10 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F768" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="769">
@@ -21946,10 +21946,10 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F769" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="770">
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F771" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="772">
@@ -22030,7 +22030,7 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F772" t="n">
         <v>50.3</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="F773" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="774">
@@ -22086,10 +22086,10 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F774" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="775">
@@ -22117,7 +22117,7 @@
         <v>7.5</v>
       </c>
       <c r="F775" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="776">
@@ -22145,7 +22145,7 @@
         <v>7.5</v>
       </c>
       <c r="F776" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="777">
@@ -22170,10 +22170,10 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F777" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="778">
@@ -22201,7 +22201,7 @@
         <v>7.2</v>
       </c>
       <c r="F778" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="779">
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="F779" t="n">
         <v>51.7</v>
@@ -22245,19 +22245,19 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E780" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F780" t="n">
-        <v>49.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="781">
@@ -22273,19 +22273,19 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E781" t="n">
         <v>6.7</v>
       </c>
       <c r="F781" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="782">
@@ -22310,10 +22310,10 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="F782" t="n">
-        <v>45.8</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="783">
@@ -22341,7 +22341,7 @@
         <v>6.4</v>
       </c>
       <c r="F783" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="784">
@@ -22369,7 +22369,7 @@
         <v>6.2</v>
       </c>
       <c r="F784" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="785">
@@ -22385,19 +22385,19 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E785" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F785" t="n">
-        <v>48.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="786">
@@ -22413,19 +22413,19 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E786" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F786" t="n">
-        <v>51.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="787">
@@ -22453,7 +22453,7 @@
         <v>5.7</v>
       </c>
       <c r="F787" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="788">
@@ -22481,7 +22481,7 @@
         <v>5</v>
       </c>
       <c r="F788" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="789">
@@ -22509,7 +22509,7 @@
         <v>5</v>
       </c>
       <c r="F789" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="790">
@@ -22537,7 +22537,7 @@
         <v>4.9</v>
       </c>
       <c r="F790" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="791">
@@ -22562,10 +22562,10 @@
         </is>
       </c>
       <c r="E791" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F791" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="792">
@@ -22593,7 +22593,7 @@
         <v>4.2</v>
       </c>
       <c r="F792" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="793">
@@ -22618,10 +22618,10 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F793" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="794">
@@ -22649,7 +22649,7 @@
         <v>3.7</v>
       </c>
       <c r="F794" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="795">
@@ -22677,7 +22677,7 @@
         <v>3.6</v>
       </c>
       <c r="F795" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="796">
@@ -22730,10 +22730,10 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F797" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="798">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F798" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="799">
@@ -22789,7 +22789,7 @@
         <v>2.8</v>
       </c>
       <c r="F799" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="800">
@@ -22817,7 +22817,7 @@
         <v>2.7</v>
       </c>
       <c r="F800" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="801">
@@ -22845,7 +22845,7 @@
         <v>2.3</v>
       </c>
       <c r="F801" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="802">
@@ -22957,7 +22957,7 @@
         <v>21.1</v>
       </c>
       <c r="F805" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="806">
@@ -23010,7 +23010,7 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="F807" t="n">
         <v>52.7</v>
@@ -23038,10 +23038,10 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="F808" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="809">
@@ -23057,19 +23057,19 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E809" t="n">
         <v>16.5</v>
       </c>
       <c r="F809" t="n">
-        <v>50.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="810">
@@ -23085,19 +23085,19 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E810" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="F810" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="811">
@@ -23293,7 +23293,7 @@
         <v>11.9</v>
       </c>
       <c r="F817" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="818">
@@ -23514,7 +23514,7 @@
         </is>
       </c>
       <c r="E825" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F825" t="n">
         <v>51</v>
@@ -23545,7 +23545,7 @@
         <v>7.9</v>
       </c>
       <c r="F826" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="827">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="F827" t="n">
         <v>47.1</v>
@@ -23598,7 +23598,7 @@
         </is>
       </c>
       <c r="E828" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F828" t="n">
         <v>47.2</v>
@@ -23965,7 +23965,7 @@
         <v>5</v>
       </c>
       <c r="F841" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="842">
@@ -24217,7 +24217,7 @@
         <v>2.9</v>
       </c>
       <c r="F850" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="851">
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F852" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="853">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="E853" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="F853" t="n">
         <v>47.4</v>
@@ -24326,10 +24326,10 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="F854" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="855">
@@ -24385,7 +24385,7 @@
         <v>20.4</v>
       </c>
       <c r="F856" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="857">
@@ -24441,7 +24441,7 @@
         <v>18.5</v>
       </c>
       <c r="F858" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="859">
@@ -24466,10 +24466,10 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="F859" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="860">
@@ -24525,7 +24525,7 @@
         <v>14</v>
       </c>
       <c r="F861" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="862">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F862" t="n">
         <v>49.4</v>
@@ -24581,7 +24581,7 @@
         <v>13.4</v>
       </c>
       <c r="F863" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="864">
@@ -24609,7 +24609,7 @@
         <v>12.9</v>
       </c>
       <c r="F864" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="865">
@@ -24637,7 +24637,7 @@
         <v>12.4</v>
       </c>
       <c r="F865" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="866">
@@ -24693,7 +24693,7 @@
         <v>11.9</v>
       </c>
       <c r="F867" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="868">
@@ -24805,7 +24805,7 @@
         <v>11.1</v>
       </c>
       <c r="F871" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="872">
@@ -24861,7 +24861,7 @@
         <v>9.9</v>
       </c>
       <c r="F873" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="874">
@@ -24917,7 +24917,7 @@
         <v>9.6</v>
       </c>
       <c r="F875" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="876">
@@ -24973,7 +24973,7 @@
         <v>7.5</v>
       </c>
       <c r="F877" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="878">
@@ -25001,7 +25001,7 @@
         <v>7.3</v>
       </c>
       <c r="F878" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="879">
@@ -25029,7 +25029,7 @@
         <v>7.2</v>
       </c>
       <c r="F879" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="880">
@@ -25085,7 +25085,7 @@
         <v>7.1</v>
       </c>
       <c r="F881" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="882">
@@ -25113,7 +25113,7 @@
         <v>6.8</v>
       </c>
       <c r="F882" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="883">
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="E883" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="F883" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="884">
@@ -25166,10 +25166,10 @@
         </is>
       </c>
       <c r="E884" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F884" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="885">
@@ -25197,7 +25197,7 @@
         <v>5.5</v>
       </c>
       <c r="F885" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="886">
@@ -25225,7 +25225,7 @@
         <v>5.5</v>
       </c>
       <c r="F886" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="887">
@@ -25253,7 +25253,7 @@
         <v>5.4</v>
       </c>
       <c r="F887" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="888">
@@ -25309,7 +25309,7 @@
         <v>4.2</v>
       </c>
       <c r="F889" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="890">
@@ -25337,7 +25337,7 @@
         <v>3.7</v>
       </c>
       <c r="F890" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="891">
@@ -25353,19 +25353,19 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E891" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F891" t="n">
-        <v>54.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="892">
@@ -25381,19 +25381,19 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E892" t="n">
         <v>3.6</v>
       </c>
       <c r="F892" t="n">
-        <v>50.2</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="893">
@@ -25421,7 +25421,7 @@
         <v>3.5</v>
       </c>
       <c r="F893" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="894">
@@ -25437,19 +25437,19 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E894" t="n">
         <v>3.4</v>
       </c>
       <c r="F894" t="n">
-        <v>49.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="895">
@@ -25465,19 +25465,19 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E895" t="n">
         <v>3.3</v>
       </c>
       <c r="F895" t="n">
-        <v>50.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="896">
@@ -25533,7 +25533,7 @@
         <v>3.1</v>
       </c>
       <c r="F897" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="898">
@@ -25561,7 +25561,7 @@
         <v>2.9</v>
       </c>
       <c r="F898" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="899">
@@ -25589,7 +25589,7 @@
         <v>2.6</v>
       </c>
       <c r="F899" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="900">
@@ -25617,7 +25617,7 @@
         <v>2</v>
       </c>
       <c r="F900" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="901">
@@ -25645,7 +25645,7 @@
         <v>2</v>
       </c>
       <c r="F901" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="902">
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="F952" t="n">
         <v>47.7</v>
@@ -27098,10 +27098,10 @@
         </is>
       </c>
       <c r="E953" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="F953" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="954">
@@ -27213,7 +27213,7 @@
         <v>19.2</v>
       </c>
       <c r="F957" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="958">
@@ -27241,7 +27241,7 @@
         <v>16.9</v>
       </c>
       <c r="F958" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="959">
@@ -27322,7 +27322,7 @@
         </is>
       </c>
       <c r="E961" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="F961" t="n">
         <v>49.4</v>
@@ -27425,19 +27425,19 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E965" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F965" t="n">
-        <v>52</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="966">
@@ -27453,19 +27453,19 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E966" t="n">
         <v>13</v>
       </c>
       <c r="F966" t="n">
-        <v>45.3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="967">
@@ -27521,7 +27521,7 @@
         <v>11.4</v>
       </c>
       <c r="F968" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="969">
@@ -27661,7 +27661,7 @@
         <v>9.5</v>
       </c>
       <c r="F973" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="974">
@@ -27689,7 +27689,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F974" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="975">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="E975" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F975" t="n">
         <v>51.1</v>
@@ -27857,7 +27857,7 @@
         <v>7</v>
       </c>
       <c r="F980" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="981">
@@ -27882,7 +27882,7 @@
         </is>
       </c>
       <c r="E981" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F981" t="n">
         <v>50.8</v>
@@ -27985,19 +27985,19 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E985" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F985" t="n">
-        <v>50.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="986">
@@ -28013,19 +28013,19 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E986" t="n">
         <v>5</v>
       </c>
       <c r="F986" t="n">
-        <v>52.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="987">
@@ -28053,7 +28053,7 @@
         <v>5</v>
       </c>
       <c r="F987" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="988">
@@ -28078,7 +28078,7 @@
         </is>
       </c>
       <c r="E988" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F988" t="n">
         <v>51.6</v>
@@ -28109,7 +28109,7 @@
         <v>4.8</v>
       </c>
       <c r="F989" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="990">
@@ -28125,19 +28125,19 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E990" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F990" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="991">
@@ -28153,19 +28153,19 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E991" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F991" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="992">
@@ -28193,7 +28193,7 @@
         <v>4.4</v>
       </c>
       <c r="F992" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="993">
@@ -28246,7 +28246,7 @@
         </is>
       </c>
       <c r="E994" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F994" t="n">
         <v>53</v>
@@ -29898,7 +29898,7 @@
         </is>
       </c>
       <c r="E1053" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F1053" t="n">
         <v>46.4</v>
@@ -29929,7 +29929,7 @@
         <v>23.5</v>
       </c>
       <c r="F1054" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1055">
@@ -29954,7 +29954,7 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F1055" t="n">
         <v>51.2</v>
@@ -30069,7 +30069,7 @@
         <v>15.6</v>
       </c>
       <c r="F1059" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1060">
@@ -30094,7 +30094,7 @@
         </is>
       </c>
       <c r="E1060" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="F1060" t="n">
         <v>46.2</v>
@@ -30150,10 +30150,10 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="F1062" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1063">
@@ -30181,7 +30181,7 @@
         <v>14.1</v>
       </c>
       <c r="F1063" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1064">
@@ -30237,7 +30237,7 @@
         <v>12.3</v>
       </c>
       <c r="F1065" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1066">
@@ -30262,7 +30262,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F1066" t="n">
         <v>53.6</v>
@@ -30290,7 +30290,7 @@
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F1067" t="n">
         <v>50.3</v>
@@ -30309,19 +30309,19 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1068" t="n">
         <v>10.4</v>
       </c>
       <c r="F1068" t="n">
-        <v>50.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1069">
@@ -30337,19 +30337,19 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F1069" t="n">
-        <v>47.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1070">
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F1070" t="n">
         <v>51.3</v>
@@ -30405,7 +30405,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F1071" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1072">
@@ -30430,10 +30430,10 @@
         </is>
       </c>
       <c r="E1072" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F1072" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1073">
@@ -30461,7 +30461,7 @@
         <v>9</v>
       </c>
       <c r="F1073" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1074">
@@ -30517,7 +30517,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F1075" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1076">
@@ -30570,10 +30570,10 @@
         </is>
       </c>
       <c r="E1077" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F1077" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1078">
@@ -30769,7 +30769,7 @@
         <v>6</v>
       </c>
       <c r="F1084" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1085">
@@ -30825,7 +30825,7 @@
         <v>5.7</v>
       </c>
       <c r="F1086" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1087">
@@ -30853,7 +30853,7 @@
         <v>5.6</v>
       </c>
       <c r="F1087" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1088">
@@ -30881,7 +30881,7 @@
         <v>5.2</v>
       </c>
       <c r="F1088" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1089">
@@ -30934,7 +30934,7 @@
         </is>
       </c>
       <c r="E1090" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F1090" t="n">
         <v>54</v>
@@ -30993,7 +30993,7 @@
         <v>4.6</v>
       </c>
       <c r="F1092" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1093">
@@ -31021,7 +31021,7 @@
         <v>4.5</v>
       </c>
       <c r="F1093" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1094">
@@ -31049,7 +31049,7 @@
         <v>4.2</v>
       </c>
       <c r="F1094" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1095">
@@ -31105,7 +31105,7 @@
         <v>4.1</v>
       </c>
       <c r="F1096" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1097">
@@ -31133,7 +31133,7 @@
         <v>4</v>
       </c>
       <c r="F1097" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1098">
@@ -31189,7 +31189,7 @@
         <v>3.7</v>
       </c>
       <c r="F1099" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1100">
@@ -31245,7 +31245,7 @@
         <v>2.6</v>
       </c>
       <c r="F1101" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1102">
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="F1152" t="n">
         <v>47.2</v>
@@ -32698,10 +32698,10 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="F1153" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1154">
@@ -32726,7 +32726,7 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="F1154" t="n">
         <v>52.3</v>
@@ -32754,7 +32754,7 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="F1155" t="n">
         <v>52.5</v>
@@ -32782,7 +32782,7 @@
         </is>
       </c>
       <c r="E1156" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="F1156" t="n">
         <v>47.1</v>
@@ -32810,10 +32810,10 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="F1157" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1158">
@@ -32838,10 +32838,10 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="F1158" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1159">
@@ -32866,10 +32866,10 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="F1159" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1160">
@@ -32894,10 +32894,10 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="F1160" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1161">
@@ -32922,10 +32922,10 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F1161" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1162">
@@ -32950,10 +32950,10 @@
         </is>
       </c>
       <c r="E1162" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="F1162" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1163">
@@ -32978,7 +32978,7 @@
         </is>
       </c>
       <c r="E1163" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="F1163" t="n">
         <v>50</v>
@@ -32997,19 +32997,19 @@
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1164" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1164" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F1164" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1165">
@@ -33025,19 +33025,19 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1165" t="n">
         <v>11.1</v>
       </c>
       <c r="F1165" t="n">
-        <v>51.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1166">
@@ -33090,10 +33090,10 @@
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F1167" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1168">
@@ -33121,7 +33121,7 @@
         <v>10.3</v>
       </c>
       <c r="F1168" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1169">
@@ -33146,10 +33146,10 @@
         </is>
       </c>
       <c r="E1169" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F1169" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1170">
@@ -33165,19 +33165,19 @@
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1170" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="F1170" t="n">
-        <v>51.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1171">
@@ -33193,19 +33193,19 @@
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1171" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="F1171" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1172">
@@ -33230,10 +33230,10 @@
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F1172" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1173">
@@ -33258,10 +33258,10 @@
         </is>
       </c>
       <c r="E1173" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F1173" t="n">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1174">
@@ -33314,10 +33314,10 @@
         </is>
       </c>
       <c r="E1175" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F1175" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1176">
@@ -33342,7 +33342,7 @@
         </is>
       </c>
       <c r="E1176" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F1176" t="n">
         <v>51.5</v>
@@ -33373,7 +33373,7 @@
         <v>7.4</v>
       </c>
       <c r="F1177" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1178">
@@ -33401,7 +33401,7 @@
         <v>7</v>
       </c>
       <c r="F1178" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1179">
@@ -33426,10 +33426,10 @@
         </is>
       </c>
       <c r="E1179" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F1179" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1180">
@@ -33482,10 +33482,10 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F1181" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1182">
@@ -33510,10 +33510,10 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F1182" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1183">
@@ -33541,7 +33541,7 @@
         <v>6.2</v>
       </c>
       <c r="F1183" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1184">
@@ -33566,10 +33566,10 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F1184" t="n">
-        <v>47.3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1185">
@@ -33625,7 +33625,7 @@
         <v>5</v>
       </c>
       <c r="F1186" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1187">
@@ -33650,7 +33650,7 @@
         </is>
       </c>
       <c r="E1187" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F1187" t="n">
         <v>45.4</v>
@@ -33669,19 +33669,19 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1188" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F1188" t="n">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1189">
@@ -33697,19 +33697,19 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1189" t="n">
         <v>4.5</v>
       </c>
       <c r="F1189" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1190">
@@ -33737,7 +33737,7 @@
         <v>4.4</v>
       </c>
       <c r="F1190" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1191">
@@ -33762,10 +33762,10 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F1191" t="n">
-        <v>53.3</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1192">
@@ -33790,10 +33790,10 @@
         </is>
       </c>
       <c r="E1192" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1192" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1193">
@@ -33818,10 +33818,10 @@
         </is>
       </c>
       <c r="E1193" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1193" t="n">
-        <v>56.1</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="1194">
@@ -33877,7 +33877,7 @@
         <v>3.7</v>
       </c>
       <c r="F1195" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1196">
@@ -33902,10 +33902,10 @@
         </is>
       </c>
       <c r="E1196" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F1196" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1197">
@@ -33961,7 +33961,7 @@
         <v>3.3</v>
       </c>
       <c r="F1198" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1199">
@@ -33989,7 +33989,7 @@
         <v>2.9</v>
       </c>
       <c r="F1199" t="n">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1200">
@@ -34017,7 +34017,7 @@
         <v>2.3</v>
       </c>
       <c r="F1200" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1201">
@@ -34045,7 +34045,7 @@
         <v>2.3</v>
       </c>
       <c r="F1201" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1202">
@@ -34490,7 +34490,7 @@
         </is>
       </c>
       <c r="E1217" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F1217" t="n">
         <v>49.8</v>
@@ -35389,7 +35389,7 @@
         <v>0.6</v>
       </c>
       <c r="F1249" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1250">
@@ -35725,7 +35725,7 @@
         <v>3</v>
       </c>
       <c r="F1261" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1262">
@@ -36033,7 +36033,7 @@
         <v>2</v>
       </c>
       <c r="F1272" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1273">
@@ -36453,7 +36453,7 @@
         <v>1.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1288">
@@ -36537,7 +36537,7 @@
         <v>1</v>
       </c>
       <c r="F1290" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1291">
@@ -36733,7 +36733,7 @@
         <v>0.6</v>
       </c>
       <c r="F1297" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1298">
@@ -36957,7 +36957,7 @@
         <v>4.3</v>
       </c>
       <c r="F1305" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1306">
@@ -37461,7 +37461,7 @@
         <v>1.8</v>
       </c>
       <c r="F1323" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1324">
@@ -37769,7 +37769,7 @@
         <v>1.2</v>
       </c>
       <c r="F1334" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1335">
@@ -37909,7 +37909,7 @@
         <v>1.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1340">
@@ -37993,7 +37993,7 @@
         <v>1</v>
       </c>
       <c r="F1342" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1343">
@@ -38105,7 +38105,7 @@
         <v>0.7</v>
       </c>
       <c r="F1346" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1347">
@@ -38217,7 +38217,7 @@
         <v>0.5</v>
       </c>
       <c r="F1350" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1351">
@@ -38245,7 +38245,7 @@
         <v>0.4</v>
       </c>
       <c r="F1351" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1352">
@@ -38301,7 +38301,7 @@
         <v>5.5</v>
       </c>
       <c r="F1353" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1354">
@@ -38581,7 +38581,7 @@
         <v>2.8</v>
       </c>
       <c r="F1363" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1364">
@@ -38693,7 +38693,7 @@
         <v>2.5</v>
       </c>
       <c r="F1367" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1368">
@@ -39141,7 +39141,7 @@
         <v>1.1</v>
       </c>
       <c r="F1383" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1384">
@@ -39225,7 +39225,7 @@
         <v>1.1</v>
       </c>
       <c r="F1386" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1387">
@@ -39281,7 +39281,7 @@
         <v>1.1</v>
       </c>
       <c r="F1388" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1389">
@@ -39309,7 +39309,7 @@
         <v>1.1</v>
       </c>
       <c r="F1389" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="1390">
@@ -39477,7 +39477,7 @@
         <v>0.9</v>
       </c>
       <c r="F1395" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1396">
@@ -39981,7 +39981,7 @@
         <v>2.7</v>
       </c>
       <c r="F1413" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1414">
@@ -40093,7 +40093,7 @@
         <v>2.2</v>
       </c>
       <c r="F1417" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1418">
@@ -40205,7 +40205,7 @@
         <v>2</v>
       </c>
       <c r="F1421" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1422">
@@ -40389,19 +40389,19 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1428" t="n">
         <v>1.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>52.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1429">
@@ -40417,19 +40417,19 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1429" t="n">
         <v>1.6</v>
       </c>
       <c r="F1429" t="n">
-        <v>49.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1430">
@@ -40653,7 +40653,7 @@
         <v>1.1</v>
       </c>
       <c r="F1437" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="1438">
@@ -40865,19 +40865,19 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1445" t="n">
         <v>0.8</v>
       </c>
       <c r="F1445" t="n">
-        <v>50.9</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1446">
@@ -40893,19 +40893,19 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1446" t="n">
         <v>0.8</v>
       </c>
       <c r="F1446" t="n">
-        <v>49.1</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1447">
@@ -41045,7 +41045,7 @@
         <v>0.6</v>
       </c>
       <c r="F1451" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1452">
@@ -41129,7 +41129,7 @@
         <v>6.5</v>
       </c>
       <c r="F1454" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1455">
@@ -41154,7 +41154,7 @@
         </is>
       </c>
       <c r="E1455" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1455" t="n">
         <v>47.5</v>
@@ -41661,7 +41661,7 @@
         <v>2</v>
       </c>
       <c r="F1473" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1474">
@@ -41717,7 +41717,7 @@
         <v>1.8</v>
       </c>
       <c r="F1475" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1476">
@@ -41773,7 +41773,7 @@
         <v>1.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1478">
@@ -41801,7 +41801,7 @@
         <v>1.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1479">
@@ -41913,7 +41913,7 @@
         <v>1.3</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1483">
@@ -41957,7 +41957,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -41969,7 +41969,7 @@
         <v>1.1</v>
       </c>
       <c r="F1484" t="n">
-        <v>46</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1485">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -41997,7 +41997,7 @@
         <v>1.1</v>
       </c>
       <c r="F1485" t="n">
-        <v>51.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1486">
@@ -42025,7 +42025,7 @@
         <v>1</v>
       </c>
       <c r="F1486" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1487">
@@ -42221,7 +42221,7 @@
         <v>0.7</v>
       </c>
       <c r="F1493" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1494">
@@ -42249,7 +42249,7 @@
         <v>0.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1495">
@@ -42277,7 +42277,7 @@
         <v>0.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1496">
@@ -42361,7 +42361,7 @@
         <v>0.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1499">
@@ -42445,7 +42445,7 @@
         <v>0.4</v>
       </c>
       <c r="F1501" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>6.3</v>
       </c>
       <c r="F1502" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1503">
@@ -42529,7 +42529,7 @@
         <v>5.4</v>
       </c>
       <c r="F1504" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1505">
@@ -42554,10 +42554,10 @@
         </is>
       </c>
       <c r="E1505" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F1505" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1506">
@@ -42585,7 +42585,7 @@
         <v>4.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1507">
@@ -42657,19 +42657,19 @@
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1509" t="n">
         <v>3.8</v>
       </c>
       <c r="F1509" t="n">
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1510">
@@ -42685,19 +42685,19 @@
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1510" t="n">
         <v>3.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>46.6</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="1511">
@@ -42778,7 +42778,7 @@
         </is>
       </c>
       <c r="E1513" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1513" t="n">
         <v>44.8</v>
@@ -42837,7 +42837,7 @@
         <v>2.5</v>
       </c>
       <c r="F1515" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1516">
@@ -42918,10 +42918,10 @@
         </is>
       </c>
       <c r="E1518" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1518" t="n">
-        <v>45.3</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1519">
@@ -42946,7 +42946,7 @@
         </is>
       </c>
       <c r="E1519" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F1519" t="n">
         <v>44.7</v>
@@ -42974,10 +42974,10 @@
         </is>
       </c>
       <c r="E1520" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F1520" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1521">
@@ -43005,7 +43005,7 @@
         <v>2.1</v>
       </c>
       <c r="F1521" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1522">
@@ -43033,7 +43033,7 @@
         <v>1.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1523">
@@ -43089,7 +43089,7 @@
         <v>1.9</v>
       </c>
       <c r="F1524" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1525">
@@ -43105,19 +43105,19 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1525" t="n">
         <v>1.8</v>
       </c>
       <c r="F1525" t="n">
-        <v>45.7</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1526">
@@ -43133,19 +43133,19 @@
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1526" t="n">
         <v>1.8</v>
       </c>
       <c r="F1526" t="n">
-        <v>47.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1527">
@@ -43229,7 +43229,7 @@
         <v>1.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>1.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1531">
@@ -43313,7 +43313,7 @@
         <v>1.3</v>
       </c>
       <c r="F1532" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1533">
@@ -43341,7 +43341,7 @@
         <v>1.3</v>
       </c>
       <c r="F1533" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>1.1</v>
       </c>
       <c r="F1534" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1535">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="F1535" t="n">
-        <v>52.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>1</v>
       </c>
       <c r="F1536" t="n">
-        <v>53.7</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1537">
@@ -43481,7 +43481,7 @@
         <v>0.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1539">
@@ -43509,7 +43509,7 @@
         <v>0.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1540">
@@ -43537,7 +43537,7 @@
         <v>0.7</v>
       </c>
       <c r="F1540" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="1541">
@@ -43593,7 +43593,7 @@
         <v>0.7</v>
       </c>
       <c r="F1542" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1543">
@@ -43621,7 +43621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1543" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="1544">
@@ -43649,7 +43649,7 @@
         <v>0.5</v>
       </c>
       <c r="F1544" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1545">
@@ -43705,7 +43705,7 @@
         <v>0.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="1547">
@@ -43733,7 +43733,7 @@
         <v>0.4</v>
       </c>
       <c r="F1547" t="n">
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1548">
@@ -43761,7 +43761,7 @@
         <v>0.4</v>
       </c>
       <c r="F1548" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="1549">
@@ -43817,7 +43817,7 @@
         <v>0.3</v>
       </c>
       <c r="F1550" t="n">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="1551">
@@ -43870,7 +43870,7 @@
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F1552" t="n">
         <v>48.9</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F1553" t="n">
         <v>40.4</v>
@@ -43926,7 +43926,7 @@
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="F1554" t="n">
         <v>77.2</v>
@@ -43954,7 +43954,7 @@
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="F1555" t="n">
         <v>52.5</v>
@@ -43982,7 +43982,7 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F1556" t="n">
         <v>30.5</v>
@@ -44010,7 +44010,7 @@
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F1557" t="n">
         <v>42.1</v>
@@ -44029,19 +44029,19 @@
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F1558" t="n">
-        <v>61.3</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="1559">
@@ -44057,19 +44057,19 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1559" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1559" t="n">
-        <v>31.3</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="1560">
@@ -44085,19 +44085,19 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="F1560" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="1561">
@@ -44178,7 +44178,7 @@
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1563" t="n">
         <v>63.5</v>
@@ -44206,7 +44206,7 @@
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1564" t="n">
         <v>51.7</v>
@@ -44262,7 +44262,7 @@
         </is>
       </c>
       <c r="E1566" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1566" t="n">
         <v>26.3</v>
@@ -44281,19 +44281,19 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F1567" t="n">
-        <v>44.6</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="1568">
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1568" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F1568" t="n">
-        <v>63.9</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="1569">
@@ -44337,19 +44337,19 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1569" t="n">
         <v>1.7</v>
       </c>
       <c r="F1569" t="n">
-        <v>49.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1570">
@@ -44365,19 +44365,19 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1570" t="n">
         <v>1.7</v>
       </c>
       <c r="F1570" t="n">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1571" t="n">
         <v>1.7</v>
       </c>
       <c r="F1571" t="n">
-        <v>69.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,19 +44421,19 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1572" t="n">
         <v>1.7</v>
       </c>
       <c r="F1572" t="n">
-        <v>56.9</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="1573">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1573" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F1573" t="n">
-        <v>77.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1574" t="n">
         <v>1.5</v>
       </c>
       <c r="F1574" t="n">
-        <v>23.8</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="1575">
@@ -44654,7 +44654,7 @@
         </is>
       </c>
       <c r="E1580" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1580" t="n">
         <v>98.2</v>
@@ -44682,7 +44682,7 @@
         </is>
       </c>
       <c r="E1581" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1581" t="n">
         <v>0</v>
@@ -44710,7 +44710,7 @@
         </is>
       </c>
       <c r="E1582" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1582" t="n">
         <v>72.5</v>
@@ -44738,7 +44738,7 @@
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1583" t="n">
         <v>51.1</v>
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="E1590" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1590" t="n">
         <v>0</v>
@@ -44962,7 +44962,7 @@
         </is>
       </c>
       <c r="E1591" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1591" t="n">
         <v>100</v>
@@ -44990,7 +44990,7 @@
         </is>
       </c>
       <c r="E1592" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1592" t="n">
         <v>0</v>
@@ -45018,7 +45018,7 @@
         </is>
       </c>
       <c r="E1593" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1593" t="n">
         <v>100</v>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -557,7 +557,7 @@
         <v>20.6</v>
       </c>
       <c r="F5" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="F6" t="n">
         <v>48.2</v>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="F7" t="n">
         <v>48.3</v>
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="F11" t="n">
         <v>52.4</v>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="F12" t="n">
         <v>51.6</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="14">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F14" t="n">
         <v>51.1</v>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>50.5</v>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="F16" t="n">
         <v>52</v>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F17" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="18">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F20" t="n">
         <v>49.7</v>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F21" t="n">
         <v>51.2</v>
@@ -1033,7 +1033,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="23">
@@ -1117,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="26">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F26" t="n">
         <v>52.9</v>
@@ -1229,7 +1229,7 @@
         <v>7.3</v>
       </c>
       <c r="F29" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="30">
@@ -1313,7 +1313,7 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="33">
@@ -1385,19 +1385,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>5.8</v>
       </c>
       <c r="F35" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="36">
@@ -1413,19 +1413,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>5.7</v>
       </c>
       <c r="F36" t="n">
-        <v>46.8</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="37">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="38">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F38" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="39">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F39" t="n">
         <v>47.3</v>
@@ -1537,7 +1537,7 @@
         <v>4.2</v>
       </c>
       <c r="F40" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="41">
@@ -1565,7 +1565,7 @@
         <v>4.1</v>
       </c>
       <c r="F41" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="42">
@@ -1649,7 +1649,7 @@
         <v>3.9</v>
       </c>
       <c r="F44" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -1677,7 +1677,7 @@
         <v>3.8</v>
       </c>
       <c r="F45" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="46">
@@ -1733,7 +1733,7 @@
         <v>3.5</v>
       </c>
       <c r="F47" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="48">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F49" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="50">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="51">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F51" t="n">
         <v>50.2</v>
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="F152" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="153">
@@ -4757,7 +4757,7 @@
         <v>20.2</v>
       </c>
       <c r="F155" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="156">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="F156" t="n">
         <v>48.2</v>
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="159">
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F161" t="n">
         <v>50.9</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F162" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="163">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="F163" t="n">
         <v>50.5</v>
@@ -4997,19 +4997,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F164" t="n">
-        <v>52.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="165">
@@ -5025,19 +5025,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E165" t="n">
         <v>12.2</v>
       </c>
       <c r="F165" t="n">
-        <v>46.6</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="166">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F166" t="n">
-        <v>53.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="167">
@@ -5093,7 +5093,7 @@
         <v>11.5</v>
       </c>
       <c r="F167" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="168">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="F169" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="170">
@@ -5193,19 +5193,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>8.6</v>
       </c>
       <c r="F171" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="172">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>8.6</v>
       </c>
       <c r="F172" t="n">
-        <v>46.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="173">
@@ -5249,19 +5249,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E173" t="n">
         <v>8.6</v>
       </c>
       <c r="F173" t="n">
-        <v>48.2</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="174">
@@ -5277,16 +5277,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="F174" t="n">
         <v>48.2</v>
@@ -5317,7 +5317,7 @@
         <v>8.1</v>
       </c>
       <c r="F175" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="176">
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="F177" t="n">
         <v>52.6</v>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F178" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="179">
@@ -5429,7 +5429,7 @@
         <v>7.4</v>
       </c>
       <c r="F179" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="180">
@@ -5457,7 +5457,7 @@
         <v>7.2</v>
       </c>
       <c r="F180" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="181">
@@ -5485,7 +5485,7 @@
         <v>6.8</v>
       </c>
       <c r="F181" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="182">
@@ -5513,7 +5513,7 @@
         <v>6</v>
       </c>
       <c r="F182" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="183">
@@ -5541,7 +5541,7 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="184">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="F184" t="n">
         <v>46.6</v>
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="F185" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="186">
@@ -5625,7 +5625,7 @@
         <v>5.4</v>
       </c>
       <c r="F186" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="187">
@@ -5653,7 +5653,7 @@
         <v>5.3</v>
       </c>
       <c r="F187" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="188">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F188" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="189">
@@ -5709,7 +5709,7 @@
         <v>4.3</v>
       </c>
       <c r="F189" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="190">
@@ -5737,7 +5737,7 @@
         <v>4.2</v>
       </c>
       <c r="F190" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="191">
@@ -5765,7 +5765,7 @@
         <v>4.2</v>
       </c>
       <c r="F191" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="192">
@@ -5793,7 +5793,7 @@
         <v>4</v>
       </c>
       <c r="F192" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="193">
@@ -5821,7 +5821,7 @@
         <v>4</v>
       </c>
       <c r="F193" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="194">
@@ -5849,7 +5849,7 @@
         <v>3.9</v>
       </c>
       <c r="F194" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="195">
@@ -5877,7 +5877,7 @@
         <v>3.9</v>
       </c>
       <c r="F195" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="196">
@@ -5905,7 +5905,7 @@
         <v>3.6</v>
       </c>
       <c r="F196" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="197">
@@ -5933,7 +5933,7 @@
         <v>3.3</v>
       </c>
       <c r="F197" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="198">
@@ -5961,7 +5961,7 @@
         <v>3</v>
       </c>
       <c r="F198" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="199">
@@ -5989,7 +5989,7 @@
         <v>3</v>
       </c>
       <c r="F199" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="200">
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F201" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="202">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="F202" t="n">
         <v>49.8</v>
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="F206" t="n">
         <v>51.5</v>
@@ -6201,19 +6201,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E207" t="n">
         <v>15</v>
       </c>
       <c r="F207" t="n">
-        <v>51.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="208">
@@ -6229,19 +6229,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="F208" t="n">
-        <v>48.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="209">
@@ -6257,19 +6257,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="F209" t="n">
-        <v>52.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="210">
@@ -6285,19 +6285,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E210" t="n">
         <v>14.4</v>
       </c>
       <c r="F210" t="n">
-        <v>45.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="211">
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F211" t="n">
         <v>47.5</v>
@@ -6353,7 +6353,7 @@
         <v>13.2</v>
       </c>
       <c r="F212" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="213">
@@ -6369,19 +6369,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E213" t="n">
         <v>12.6</v>
       </c>
       <c r="F213" t="n">
-        <v>51.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="214">
@@ -6397,19 +6397,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="F214" t="n">
-        <v>53.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="215">
@@ -6425,19 +6425,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F215" t="n">
-        <v>50.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="216">
@@ -6453,19 +6453,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F216" t="n">
-        <v>52</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="217">
@@ -6493,7 +6493,7 @@
         <v>11.4</v>
       </c>
       <c r="F217" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="218">
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F218" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="219">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F219" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="220">
@@ -6565,19 +6565,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E220" t="n">
         <v>8.6</v>
       </c>
       <c r="F220" t="n">
-        <v>51.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="221">
@@ -6621,19 +6621,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="F222" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="223">
@@ -6661,7 +6661,7 @@
         <v>7.8</v>
       </c>
       <c r="F223" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="224">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="F224" t="n">
         <v>45.2</v>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6745,7 +6745,7 @@
         <v>7.2</v>
       </c>
       <c r="F226" t="n">
-        <v>53.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="227">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F227" t="n">
-        <v>48.4</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="228">
@@ -6801,7 +6801,7 @@
         <v>7</v>
       </c>
       <c r="F228" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="229">
@@ -6913,7 +6913,7 @@
         <v>6.2</v>
       </c>
       <c r="F232" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="233">
@@ -6941,7 +6941,7 @@
         <v>6</v>
       </c>
       <c r="F233" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="234">
@@ -6969,7 +6969,7 @@
         <v>5.5</v>
       </c>
       <c r="F234" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="235">
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F235" t="n">
         <v>48.6</v>
@@ -7013,19 +7013,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F236" t="n">
-        <v>45.9</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="237">
@@ -7041,19 +7041,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F237" t="n">
-        <v>53.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="238">
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F238" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="239">
@@ -7109,7 +7109,7 @@
         <v>4.4</v>
       </c>
       <c r="F239" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="240">
@@ -7125,19 +7125,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E240" t="n">
         <v>4.4</v>
       </c>
       <c r="F240" t="n">
-        <v>48.6</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="241">
@@ -7153,19 +7153,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F241" t="n">
-        <v>50.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="242">
@@ -7193,7 +7193,7 @@
         <v>4.1</v>
       </c>
       <c r="F242" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="243">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F243" t="n">
         <v>43.2</v>
@@ -7237,19 +7237,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E244" t="n">
         <v>3.8</v>
       </c>
       <c r="F244" t="n">
-        <v>48.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="245">
@@ -7265,19 +7265,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F245" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="246">
@@ -7293,19 +7293,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E246" t="n">
         <v>3.7</v>
       </c>
       <c r="F246" t="n">
-        <v>46.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="247">
@@ -7321,19 +7321,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F247" t="n">
-        <v>49.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="248">
@@ -7349,19 +7349,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F248" t="n">
-        <v>47.1</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="249">
@@ -7389,7 +7389,7 @@
         <v>3.5</v>
       </c>
       <c r="F249" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="250">
@@ -7414,10 +7414,10 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F250" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="251">
@@ -7445,7 +7445,7 @@
         <v>2.7</v>
       </c>
       <c r="F251" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="252">
@@ -8873,7 +8873,7 @@
         <v>52</v>
       </c>
       <c r="F302" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="303">
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="F303" t="n">
         <v>47.7</v>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="F304" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="305">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="F305" t="n">
         <v>52.2</v>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="F306" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="307">
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="F307" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="308">
@@ -9038,7 +9038,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="F308" t="n">
         <v>52.2</v>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="F309" t="n">
         <v>55.7</v>
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="F310" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="311">
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="F311" t="n">
         <v>49.6</v>
@@ -9153,7 +9153,7 @@
         <v>13.6</v>
       </c>
       <c r="F312" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="313">
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="F313" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="314">
@@ -9197,19 +9197,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E314" t="n">
         <v>10.3</v>
       </c>
       <c r="F314" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="315">
@@ -9225,19 +9225,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F315" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="316">
@@ -9253,19 +9253,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>9.4</v>
       </c>
       <c r="F316" t="n">
-        <v>53.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="317">
@@ -9281,19 +9281,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F317" t="n">
-        <v>45.8</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="318">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="F318" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="319">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="F319" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="320">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F320" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="321">
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="F321" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="322">
@@ -9433,7 +9433,7 @@
         <v>7.4</v>
       </c>
       <c r="F322" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="323">
@@ -9449,19 +9449,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E323" t="n">
         <v>7</v>
       </c>
       <c r="F323" t="n">
-        <v>49.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="324">
@@ -9477,19 +9477,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F324" t="n">
-        <v>45.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="325">
@@ -9505,19 +9505,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="F325" t="n">
-        <v>52.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="326">
@@ -9533,19 +9533,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F326" t="n">
-        <v>46.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="327">
@@ -9561,19 +9561,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="F327" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="328">
@@ -9601,7 +9601,7 @@
         <v>6.1</v>
       </c>
       <c r="F328" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="329">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F329" t="n">
-        <v>47.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="330">
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="F330" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="331">
@@ -9685,7 +9685,7 @@
         <v>5.3</v>
       </c>
       <c r="F331" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="332">
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F332" t="n">
-        <v>54.7</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="333">
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F333" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="334">
@@ -9769,7 +9769,7 @@
         <v>4.8</v>
       </c>
       <c r="F334" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="335">
@@ -9797,7 +9797,7 @@
         <v>4.8</v>
       </c>
       <c r="F335" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="336">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="F336" t="n">
-        <v>42.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="337">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9853,7 +9853,7 @@
         <v>4.5</v>
       </c>
       <c r="F337" t="n">
-        <v>53.8</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="338">
@@ -9881,7 +9881,7 @@
         <v>4.3</v>
       </c>
       <c r="F338" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="339">
@@ -9909,7 +9909,7 @@
         <v>4.2</v>
       </c>
       <c r="F339" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="340">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F340" t="n">
-        <v>47.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="341">
@@ -9953,19 +9953,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F341" t="n">
-        <v>48.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="342">
@@ -9981,19 +9981,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E342" t="n">
         <v>3.7</v>
       </c>
       <c r="F342" t="n">
-        <v>52.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="343">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F343" t="n">
-        <v>51.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="344">
@@ -10077,7 +10077,7 @@
         <v>2.9</v>
       </c>
       <c r="F345" t="n">
-        <v>47.8</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="346">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F346" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="347">
@@ -10133,7 +10133,7 @@
         <v>2.6</v>
       </c>
       <c r="F347" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="348">
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F348" t="n">
-        <v>46.3</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="349">
@@ -10186,10 +10186,10 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F349" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="350">
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F350" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="351">
@@ -10245,7 +10245,7 @@
         <v>1.8</v>
       </c>
       <c r="F351" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="352">
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F502" t="n">
         <v>48.1</v>
@@ -14498,7 +14498,7 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="F503" t="n">
         <v>47.2</v>
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="F504" t="n">
         <v>54</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F505" t="n">
         <v>47.5</v>
@@ -14641,7 +14641,7 @@
         <v>20</v>
       </c>
       <c r="F508" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="509">
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="F509" t="n">
         <v>46.9</v>
@@ -14697,7 +14697,7 @@
         <v>14.7</v>
       </c>
       <c r="F510" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="511">
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="F511" t="n">
         <v>52.5</v>
@@ -14806,10 +14806,10 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="F514" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="515">
@@ -14837,7 +14837,7 @@
         <v>13.2</v>
       </c>
       <c r="F515" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="516">
@@ -14862,7 +14862,7 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F516" t="n">
         <v>52.4</v>
@@ -14909,19 +14909,19 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F518" t="n">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="519">
@@ -14937,19 +14937,19 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="F519" t="n">
-        <v>53.4</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="520">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F520" t="n">
         <v>50.4</v>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F521" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="522">
@@ -15117,7 +15117,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F525" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="526">
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F526" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="527">
@@ -15170,10 +15170,10 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F527" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="528">
@@ -15229,7 +15229,7 @@
         <v>7.4</v>
       </c>
       <c r="F529" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="530">
@@ -15313,7 +15313,7 @@
         <v>6.5</v>
       </c>
       <c r="F532" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="533">
@@ -15369,7 +15369,7 @@
         <v>5.6</v>
       </c>
       <c r="F534" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="535">
@@ -15397,7 +15397,7 @@
         <v>5.6</v>
       </c>
       <c r="F535" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="536">
@@ -15453,7 +15453,7 @@
         <v>4.8</v>
       </c>
       <c r="F537" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="538">
@@ -15481,7 +15481,7 @@
         <v>4.7</v>
       </c>
       <c r="F538" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="539">
@@ -15593,7 +15593,7 @@
         <v>4</v>
       </c>
       <c r="F542" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="543">
@@ -15665,19 +15665,19 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F545" t="n">
-        <v>54.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="546">
@@ -15693,19 +15693,19 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E546" t="n">
         <v>3.6</v>
       </c>
       <c r="F546" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="547">
@@ -15721,19 +15721,19 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E547" t="n">
         <v>3.6</v>
       </c>
       <c r="F547" t="n">
-        <v>49.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="548">
@@ -15789,7 +15789,7 @@
         <v>3.3</v>
       </c>
       <c r="F549" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="550">
@@ -15814,10 +15814,10 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F550" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="551">
@@ -15845,7 +15845,7 @@
         <v>1.9</v>
       </c>
       <c r="F551" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="552">
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="F552" t="n">
         <v>47.3</v>
@@ -15898,7 +15898,7 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="F553" t="n">
         <v>46.5</v>
@@ -15929,7 +15929,7 @@
         <v>23.2</v>
       </c>
       <c r="F554" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="555">
@@ -15945,19 +15945,19 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E555" t="n">
         <v>20.4</v>
       </c>
       <c r="F555" t="n">
-        <v>53.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="556">
@@ -15973,19 +15973,19 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F556" t="n">
-        <v>48.2</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="557">
@@ -16041,7 +16041,7 @@
         <v>18.7</v>
       </c>
       <c r="F558" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="559">
@@ -16097,7 +16097,7 @@
         <v>16.6</v>
       </c>
       <c r="F560" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="561">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="E561" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="F561" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="562">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="E564" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="F564" t="n">
         <v>52.2</v>
@@ -16234,10 +16234,10 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="F565" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="566">
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="E568" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F568" t="n">
         <v>53.7</v>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="E569" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F569" t="n">
         <v>48.9</v>
@@ -16374,10 +16374,10 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F570" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="571">
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F571" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="572">
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="E573" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F573" t="n">
         <v>47.5</v>
@@ -16486,7 +16486,7 @@
         </is>
       </c>
       <c r="E574" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F574" t="n">
         <v>49.3</v>
@@ -16514,7 +16514,7 @@
         </is>
       </c>
       <c r="E575" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F575" t="n">
         <v>52.6</v>
@@ -16542,7 +16542,7 @@
         </is>
       </c>
       <c r="E576" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F576" t="n">
         <v>51.2</v>
@@ -16573,7 +16573,7 @@
         <v>8</v>
       </c>
       <c r="F577" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="578">
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="E578" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="F578" t="n">
         <v>46.9</v>
@@ -16657,7 +16657,7 @@
         <v>7.4</v>
       </c>
       <c r="F580" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="581">
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F581" t="n">
         <v>51.1</v>
@@ -16710,7 +16710,7 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F582" t="n">
         <v>49.2</v>
@@ -16741,7 +16741,7 @@
         <v>5.6</v>
       </c>
       <c r="F583" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="584">
@@ -16757,19 +16757,19 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F584" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="585">
@@ -16785,19 +16785,19 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E585" t="n">
         <v>5.4</v>
       </c>
       <c r="F585" t="n">
-        <v>47.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="586">
@@ -16813,19 +16813,19 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E586" t="n">
         <v>5.4</v>
       </c>
       <c r="F586" t="n">
-        <v>51.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="587">
@@ -16853,7 +16853,7 @@
         <v>5.3</v>
       </c>
       <c r="F587" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="588">
@@ -16937,7 +16937,7 @@
         <v>4.9</v>
       </c>
       <c r="F590" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="591">
@@ -16993,7 +16993,7 @@
         <v>4.1</v>
       </c>
       <c r="F592" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="593">
@@ -17021,7 +17021,7 @@
         <v>4</v>
       </c>
       <c r="F593" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="594">
@@ -17077,7 +17077,7 @@
         <v>3.8</v>
       </c>
       <c r="F595" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="596">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F597" t="n">
-        <v>53.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="598">
@@ -17149,19 +17149,19 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E598" t="n">
         <v>3.4</v>
       </c>
       <c r="F598" t="n">
-        <v>51.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="599">
@@ -17177,19 +17177,19 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E599" t="n">
         <v>3.4</v>
       </c>
       <c r="F599" t="n">
-        <v>48.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="600">
@@ -17245,7 +17245,7 @@
         <v>2.2</v>
       </c>
       <c r="F601" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="602">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="F652" t="n">
         <v>46.1</v>
@@ -18698,10 +18698,10 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="F653" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="654">
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="F654" t="n">
         <v>46</v>
@@ -18754,10 +18754,10 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="F655" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="656">
@@ -18782,7 +18782,7 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="F656" t="n">
         <v>51.8</v>
@@ -18838,10 +18838,10 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F658" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="659">
@@ -18866,7 +18866,7 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="F659" t="n">
         <v>51.6</v>
@@ -18894,10 +18894,10 @@
         </is>
       </c>
       <c r="E660" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="F660" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="661">
@@ -18925,7 +18925,7 @@
         <v>15.4</v>
       </c>
       <c r="F661" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="662">
@@ -18950,10 +18950,10 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="F662" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="663">
@@ -18978,10 +18978,10 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F663" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="664">
@@ -19006,7 +19006,7 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F664" t="n">
         <v>51.9</v>
@@ -19037,7 +19037,7 @@
         <v>11.8</v>
       </c>
       <c r="F665" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="666">
@@ -19065,7 +19065,7 @@
         <v>11</v>
       </c>
       <c r="F666" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="667">
@@ -19093,7 +19093,7 @@
         <v>10.6</v>
       </c>
       <c r="F667" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="668">
@@ -19121,7 +19121,7 @@
         <v>10.5</v>
       </c>
       <c r="F668" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="669">
@@ -19146,7 +19146,7 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F669" t="n">
         <v>50.6</v>
@@ -19230,10 +19230,10 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F672" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="673">
@@ -19261,7 +19261,7 @@
         <v>9</v>
       </c>
       <c r="F673" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="674">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F675" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="676">
@@ -19345,7 +19345,7 @@
         <v>7.6</v>
       </c>
       <c r="F676" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="677">
@@ -19373,7 +19373,7 @@
         <v>7.6</v>
       </c>
       <c r="F677" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="678">
@@ -19398,10 +19398,10 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F678" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="679">
@@ -19417,19 +19417,19 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="F679" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="680">
@@ -19445,19 +19445,19 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E680" t="n">
         <v>7</v>
       </c>
       <c r="F680" t="n">
-        <v>44</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="681">
@@ -19482,7 +19482,7 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F681" t="n">
         <v>48.1</v>
@@ -19510,10 +19510,10 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F682" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="683">
@@ -19541,7 +19541,7 @@
         <v>6.3</v>
       </c>
       <c r="F683" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="684">
@@ -19594,10 +19594,10 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F685" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="686">
@@ -19613,19 +19613,19 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F686" t="n">
-        <v>47.2</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="687">
@@ -19641,19 +19641,19 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E687" t="n">
         <v>5.6</v>
       </c>
       <c r="F687" t="n">
-        <v>52.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="688">
@@ -19681,7 +19681,7 @@
         <v>5.2</v>
       </c>
       <c r="F688" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="689">
@@ -19709,7 +19709,7 @@
         <v>5.2</v>
       </c>
       <c r="F689" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="690">
@@ -19737,7 +19737,7 @@
         <v>5.1</v>
       </c>
       <c r="F690" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="691">
@@ -19753,16 +19753,16 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F691" t="n">
         <v>50.4</v>
@@ -19781,19 +19781,19 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E692" t="n">
         <v>4.6</v>
       </c>
       <c r="F692" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="693">
@@ -19837,19 +19837,19 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F694" t="n">
-        <v>47.7</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="695">
@@ -19865,19 +19865,19 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E695" t="n">
         <v>4.2</v>
       </c>
       <c r="F695" t="n">
-        <v>53.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="696">
@@ -19905,7 +19905,7 @@
         <v>4.1</v>
       </c>
       <c r="F696" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="697">
@@ -19930,10 +19930,10 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F697" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="698">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F698" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="699">
@@ -20045,7 +20045,7 @@
         <v>3.2</v>
       </c>
       <c r="F701" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="702">
@@ -28498,7 +28498,7 @@
         </is>
       </c>
       <c r="E1003" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="F1003" t="n">
         <v>46.2</v>
@@ -28526,7 +28526,7 @@
         </is>
       </c>
       <c r="E1004" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="F1004" t="n">
         <v>47</v>
@@ -28557,7 +28557,7 @@
         <v>20.4</v>
       </c>
       <c r="F1005" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1006">
@@ -28585,7 +28585,7 @@
         <v>20.3</v>
       </c>
       <c r="F1006" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1007">
@@ -28638,7 +28638,7 @@
         </is>
       </c>
       <c r="E1008" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="F1008" t="n">
         <v>50.5</v>
@@ -28666,10 +28666,10 @@
         </is>
       </c>
       <c r="E1009" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="F1009" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1010">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="E1010" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F1010" t="n">
         <v>51.3</v>
@@ -28725,7 +28725,7 @@
         <v>14.8</v>
       </c>
       <c r="F1011" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1012">
@@ -28750,7 +28750,7 @@
         </is>
       </c>
       <c r="E1012" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="F1012" t="n">
         <v>52.1</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="E1015" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F1015" t="n">
         <v>51.3</v>
@@ -28865,7 +28865,7 @@
         <v>12</v>
       </c>
       <c r="F1016" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1017">
@@ -28890,7 +28890,7 @@
         </is>
       </c>
       <c r="E1017" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F1017" t="n">
         <v>53.5</v>
@@ -28974,7 +28974,7 @@
         </is>
       </c>
       <c r="E1020" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F1020" t="n">
         <v>44.8</v>
@@ -29002,10 +29002,10 @@
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F1021" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1022">
@@ -29086,7 +29086,7 @@
         </is>
       </c>
       <c r="E1024" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F1024" t="n">
         <v>51.3</v>
@@ -29114,10 +29114,10 @@
         </is>
       </c>
       <c r="E1025" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F1025" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1026">
@@ -29145,7 +29145,7 @@
         <v>8</v>
       </c>
       <c r="F1026" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1027">
@@ -29161,19 +29161,19 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1027" t="n">
         <v>7.4</v>
       </c>
       <c r="F1027" t="n">
-        <v>51.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1028">
@@ -29189,19 +29189,19 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1028" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F1028" t="n">
-        <v>46.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1029">
@@ -29226,7 +29226,7 @@
         </is>
       </c>
       <c r="E1029" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F1029" t="n">
         <v>47.9</v>
@@ -29257,7 +29257,7 @@
         <v>6.6</v>
       </c>
       <c r="F1030" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1031">
@@ -29369,7 +29369,7 @@
         <v>6</v>
       </c>
       <c r="F1034" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1035">
@@ -29397,7 +29397,7 @@
         <v>5.9</v>
       </c>
       <c r="F1035" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1036">
@@ -29425,7 +29425,7 @@
         <v>5.7</v>
       </c>
       <c r="F1036" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1037">
@@ -29481,7 +29481,7 @@
         <v>5.3</v>
       </c>
       <c r="F1038" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1039">
@@ -29497,19 +29497,19 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1039" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F1039" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1040">
@@ -29525,19 +29525,19 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1040" t="n">
         <v>4.9</v>
       </c>
       <c r="F1040" t="n">
-        <v>51.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1041">
@@ -29562,7 +29562,7 @@
         </is>
       </c>
       <c r="E1041" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F1041" t="n">
         <v>51.4</v>
@@ -29618,7 +29618,7 @@
         </is>
       </c>
       <c r="E1043" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F1043" t="n">
         <v>51.3</v>
@@ -29649,7 +29649,7 @@
         <v>4</v>
       </c>
       <c r="F1044" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1045">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="E1045" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1045" t="n">
         <v>46.6</v>
@@ -29705,7 +29705,7 @@
         <v>3.7</v>
       </c>
       <c r="F1046" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1047">
@@ -29721,19 +29721,19 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F1047" t="n">
-        <v>50.3</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1048">
@@ -29749,19 +29749,19 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1048" t="n">
         <v>3.4</v>
       </c>
       <c r="F1048" t="n">
-        <v>54</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1049">
@@ -29786,7 +29786,7 @@
         </is>
       </c>
       <c r="E1049" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1049" t="n">
         <v>51.3</v>
@@ -29817,7 +29817,7 @@
         <v>3.2</v>
       </c>
       <c r="F1050" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1051">
@@ -29845,7 +29845,7 @@
         <v>2.8</v>
       </c>
       <c r="F1051" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1052">
@@ -31298,10 +31298,10 @@
         </is>
       </c>
       <c r="E1103" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="F1103" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1104">
@@ -31326,10 +31326,10 @@
         </is>
       </c>
       <c r="E1104" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="F1104" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1105">
@@ -31354,7 +31354,7 @@
         </is>
       </c>
       <c r="E1105" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F1105" t="n">
         <v>45.4</v>
@@ -31382,10 +31382,10 @@
         </is>
       </c>
       <c r="E1106" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="F1106" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1107">
@@ -31410,10 +31410,10 @@
         </is>
       </c>
       <c r="E1107" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="F1107" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1108">
@@ -31441,7 +31441,7 @@
         <v>16.5</v>
       </c>
       <c r="F1108" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1109">
@@ -31466,10 +31466,10 @@
         </is>
       </c>
       <c r="E1109" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="F1109" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1110">
@@ -31494,7 +31494,7 @@
         </is>
       </c>
       <c r="E1110" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="F1110" t="n">
         <v>51.5</v>
@@ -31522,7 +31522,7 @@
         </is>
       </c>
       <c r="E1111" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="F1111" t="n">
         <v>49.6</v>
@@ -31550,10 +31550,10 @@
         </is>
       </c>
       <c r="E1112" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F1112" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="1113">
@@ -31578,10 +31578,10 @@
         </is>
       </c>
       <c r="E1113" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F1113" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1114">
@@ -31606,10 +31606,10 @@
         </is>
       </c>
       <c r="E1114" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="F1114" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1115">
@@ -31634,7 +31634,7 @@
         </is>
       </c>
       <c r="E1115" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F1115" t="n">
         <v>51.3</v>
@@ -31662,10 +31662,10 @@
         </is>
       </c>
       <c r="E1116" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F1116" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1117">
@@ -31690,7 +31690,7 @@
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="F1117" t="n">
         <v>49.9</v>
@@ -31718,10 +31718,10 @@
         </is>
       </c>
       <c r="E1118" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F1118" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1119">
@@ -31746,10 +31746,10 @@
         </is>
       </c>
       <c r="E1119" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="F1119" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1120">
@@ -31774,10 +31774,10 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F1120" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1121">
@@ -31886,10 +31886,10 @@
         </is>
       </c>
       <c r="E1124" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F1124" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1125">
@@ -31905,19 +31905,19 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1125" t="n">
         <v>7.4</v>
       </c>
       <c r="F1125" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1126">
@@ -31933,19 +31933,19 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1126" t="n">
         <v>7.3</v>
       </c>
       <c r="F1126" t="n">
-        <v>52.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1127">
@@ -31961,19 +31961,19 @@
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F1127" t="n">
-        <v>48.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1128">
@@ -32001,7 +32001,7 @@
         <v>7.2</v>
       </c>
       <c r="F1128" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1129">
@@ -32054,10 +32054,10 @@
         </is>
       </c>
       <c r="E1130" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="F1130" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="1131">
@@ -32073,19 +32073,19 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1131" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="F1131" t="n">
-        <v>48.9</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1132">
@@ -32101,19 +32101,19 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="F1132" t="n">
-        <v>45.8</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1133">
@@ -32141,7 +32141,7 @@
         <v>6.5</v>
       </c>
       <c r="F1133" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1134">
@@ -32166,7 +32166,7 @@
         </is>
       </c>
       <c r="E1134" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F1134" t="n">
         <v>50.6</v>
@@ -32197,7 +32197,7 @@
         <v>6</v>
       </c>
       <c r="F1135" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1136">
@@ -32225,7 +32225,7 @@
         <v>6</v>
       </c>
       <c r="F1136" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1137">
@@ -32253,7 +32253,7 @@
         <v>5.5</v>
       </c>
       <c r="F1137" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1138">
@@ -32281,7 +32281,7 @@
         <v>5.1</v>
       </c>
       <c r="F1138" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1139">
@@ -32306,7 +32306,7 @@
         </is>
       </c>
       <c r="E1139" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F1139" t="n">
         <v>50.2</v>
@@ -32334,10 +32334,10 @@
         </is>
       </c>
       <c r="E1140" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F1140" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="1141">
@@ -32365,7 +32365,7 @@
         <v>4.4</v>
       </c>
       <c r="F1141" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1142">
@@ -32393,7 +32393,7 @@
         <v>4.3</v>
       </c>
       <c r="F1142" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1143">
@@ -32418,10 +32418,10 @@
         </is>
       </c>
       <c r="E1143" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1143" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1144">
@@ -32449,7 +32449,7 @@
         <v>4</v>
       </c>
       <c r="F1144" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1145">
@@ -32477,7 +32477,7 @@
         <v>3.9</v>
       </c>
       <c r="F1145" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1146">
@@ -32493,19 +32493,19 @@
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1146" t="n">
         <v>3.7</v>
       </c>
       <c r="F1146" t="n">
-        <v>53</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1147">
@@ -32521,19 +32521,19 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1147" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F1147" t="n">
-        <v>46.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1148">
@@ -32561,7 +32561,7 @@
         <v>3.6</v>
       </c>
       <c r="F1148" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1149">
@@ -32586,10 +32586,10 @@
         </is>
       </c>
       <c r="E1149" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1149" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1150">
@@ -32614,7 +32614,7 @@
         </is>
       </c>
       <c r="E1150" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1150" t="n">
         <v>45</v>
@@ -32670,10 +32670,10 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="F1152" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1153">
@@ -32698,10 +32698,10 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="F1153" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1154">
@@ -32726,10 +32726,10 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="F1154" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1155">
@@ -32754,10 +32754,10 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>28.3</v>
+        <v>27.9</v>
       </c>
       <c r="F1155" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1156">
@@ -32782,10 +32782,10 @@
         </is>
       </c>
       <c r="E1156" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="F1156" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1157">
@@ -32810,10 +32810,10 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="F1157" t="n">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1158">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="F1158" t="n">
         <v>45.6</v>
@@ -32866,7 +32866,7 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F1159" t="n">
         <v>51.2</v>
@@ -32894,10 +32894,10 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="F1160" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1161">
@@ -32913,19 +32913,19 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F1161" t="n">
-        <v>50</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1162">
@@ -32941,19 +32941,19 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1162" t="n">
         <v>12.7</v>
       </c>
       <c r="F1162" t="n">
-        <v>48.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1163">
@@ -32969,16 +32969,16 @@
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1163" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1163" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F1163" t="n">
         <v>50</v>
@@ -33006,10 +33006,10 @@
         </is>
       </c>
       <c r="E1164" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F1164" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1165">
@@ -33037,7 +33037,7 @@
         <v>11.1</v>
       </c>
       <c r="F1165" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1166">
@@ -33062,10 +33062,10 @@
         </is>
       </c>
       <c r="E1166" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F1166" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1167">
@@ -33081,19 +33081,19 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F1167" t="n">
-        <v>50.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1168">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1168" t="inlineStr">
@@ -33118,10 +33118,10 @@
         </is>
       </c>
       <c r="E1168" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F1168" t="n">
-        <v>48.5</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1169">
@@ -33137,19 +33137,19 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1169" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="F1169" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1170">
@@ -33174,10 +33174,10 @@
         </is>
       </c>
       <c r="E1170" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="F1170" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1171">
@@ -33202,7 +33202,7 @@
         </is>
       </c>
       <c r="E1171" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="F1171" t="n">
         <v>51.1</v>
@@ -33221,19 +33221,19 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F1172" t="n">
-        <v>48.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="1173">
@@ -33249,19 +33249,19 @@
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1173" t="n">
         <v>8.9</v>
       </c>
       <c r="F1173" t="n">
-        <v>53.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1174">
@@ -33286,10 +33286,10 @@
         </is>
       </c>
       <c r="E1174" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F1174" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1175">
@@ -33314,10 +33314,10 @@
         </is>
       </c>
       <c r="E1175" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F1175" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1176">
@@ -33333,19 +33333,19 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1176" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="F1176" t="n">
-        <v>51.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1177">
@@ -33361,19 +33361,19 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1177" t="n">
         <v>7.4</v>
       </c>
       <c r="F1177" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1178">
@@ -33389,19 +33389,19 @@
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1178" t="n">
         <v>7</v>
       </c>
       <c r="F1178" t="n">
-        <v>51.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1179">
@@ -33417,19 +33417,19 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1179" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="F1179" t="n">
-        <v>49.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1180">
@@ -33445,19 +33445,19 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1180" t="n">
         <v>6.7</v>
       </c>
       <c r="F1180" t="n">
-        <v>51.2</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1181">
@@ -33473,19 +33473,19 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="F1181" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1182">
@@ -33510,10 +33510,10 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F1182" t="n">
-        <v>46.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1183">
@@ -33541,7 +33541,7 @@
         <v>6.2</v>
       </c>
       <c r="F1183" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1184">
@@ -33566,10 +33566,10 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="F1184" t="n">
-        <v>47</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1185">
@@ -33594,10 +33594,10 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F1185" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1186">
@@ -33622,7 +33622,7 @@
         </is>
       </c>
       <c r="E1186" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F1186" t="n">
         <v>44.6</v>
@@ -33653,7 +33653,7 @@
         <v>4.9</v>
       </c>
       <c r="F1187" t="n">
-        <v>45.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1188">
@@ -33669,19 +33669,19 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1188" t="n">
         <v>4.6</v>
       </c>
       <c r="F1188" t="n">
-        <v>49.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1189">
@@ -33697,19 +33697,19 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F1189" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1190">
@@ -33725,19 +33725,19 @@
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1190" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F1190" t="n">
-        <v>51.8</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1191">
@@ -33753,19 +33753,19 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F1191" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1192">
@@ -33781,19 +33781,19 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1192" t="n">
         <v>4</v>
       </c>
       <c r="F1192" t="n">
-        <v>52.6</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="1193">
@@ -33809,19 +33809,19 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1193" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1193" t="n">
-        <v>56.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1194">
@@ -33846,10 +33846,10 @@
         </is>
       </c>
       <c r="E1194" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F1194" t="n">
-        <v>48.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1195">
@@ -33874,10 +33874,10 @@
         </is>
       </c>
       <c r="E1195" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F1195" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1196">
@@ -33905,7 +33905,7 @@
         <v>3.5</v>
       </c>
       <c r="F1196" t="n">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1197">
@@ -33930,10 +33930,10 @@
         </is>
       </c>
       <c r="E1197" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1197" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1198">
@@ -33958,10 +33958,10 @@
         </is>
       </c>
       <c r="E1198" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1198" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1199">
@@ -33989,7 +33989,7 @@
         <v>2.9</v>
       </c>
       <c r="F1199" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1200">
@@ -34005,19 +34005,19 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1200" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1200" t="n">
-        <v>48.4</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1201">
@@ -34033,19 +34033,19 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1201" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1201" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1201" t="n">
-        <v>44.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1202">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>40.2</v>
+        <v>39.9</v>
       </c>
       <c r="F52" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="53">
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="F53" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="F54" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="55">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="F55" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="56">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="57">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="F57" t="n">
-        <v>44.3</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="58">
@@ -2029,19 +2029,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="F58" t="n">
-        <v>49.8</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="59">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="F59" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="60">
@@ -2097,7 +2097,7 @@
         <v>16.7</v>
       </c>
       <c r="F60" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="61">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="F61" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="62">
@@ -2153,7 +2153,7 @@
         <v>14.6</v>
       </c>
       <c r="F62" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="63">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="F63" t="n">
-        <v>48.2</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="64">
@@ -2197,19 +2197,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="F64" t="n">
-        <v>52.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="65">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="F65" t="n">
         <v>52.1</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="F66" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F67" t="n">
         <v>50</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F68" t="n">
         <v>52.5</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F70" t="n">
         <v>47.5</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="F71" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="72">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F72" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="73">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F73" t="n">
         <v>48.4</v>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F74" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="75">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F75" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="76">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="F76" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="77">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>7.6</v>
       </c>
       <c r="F77" t="n">
-        <v>51.4</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="78">
@@ -2589,19 +2589,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="F78" t="n">
-        <v>48.1</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="79">
@@ -2629,7 +2629,7 @@
         <v>6.9</v>
       </c>
       <c r="F79" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="80">
@@ -2657,7 +2657,7 @@
         <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81">
@@ -2685,7 +2685,7 @@
         <v>6.2</v>
       </c>
       <c r="F81" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="82">
@@ -2713,7 +2713,7 @@
         <v>6.1</v>
       </c>
       <c r="F82" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="83">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="F83" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="84">
@@ -2797,7 +2797,7 @@
         <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="86">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F86" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="87">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F87" t="n">
         <v>50.9</v>
@@ -2881,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="89">
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F89" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="90">
@@ -2937,7 +2937,7 @@
         <v>4.2</v>
       </c>
       <c r="F90" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91">
@@ -2965,7 +2965,7 @@
         <v>3.9</v>
       </c>
       <c r="F91" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="92">
@@ -2993,7 +2993,7 @@
         <v>3.6</v>
       </c>
       <c r="F92" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="93">
@@ -3009,19 +3009,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>3.3</v>
       </c>
       <c r="F93" t="n">
-        <v>51.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="94">
@@ -3037,19 +3037,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>3.2</v>
       </c>
       <c r="F94" t="n">
-        <v>49.7</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="95">
@@ -3077,7 +3077,7 @@
         <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="96">
@@ -3105,7 +3105,7 @@
         <v>2.9</v>
       </c>
       <c r="F96" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="97">
@@ -3133,7 +3133,7 @@
         <v>2.8</v>
       </c>
       <c r="F97" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="98">
@@ -3161,7 +3161,7 @@
         <v>2.5</v>
       </c>
       <c r="F98" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99">
@@ -3189,7 +3189,7 @@
         <v>2.3</v>
       </c>
       <c r="F99" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="100">
@@ -3245,7 +3245,7 @@
         <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="102">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="F102" t="n">
         <v>48.5</v>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="F103" t="n">
         <v>48.7</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="F104" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="105">
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="F105" t="n">
         <v>47.9</v>
@@ -3385,7 +3385,7 @@
         <v>19.8</v>
       </c>
       <c r="F106" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="F107" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="108">
@@ -3441,7 +3441,7 @@
         <v>17.2</v>
       </c>
       <c r="F108" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="109">
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="F109" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="110">
@@ -3485,19 +3485,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>15.3</v>
       </c>
       <c r="F110" t="n">
-        <v>52.7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111">
@@ -3513,19 +3513,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="F111" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="112">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="F112" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="113">
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="F113" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="114">
@@ -3597,19 +3597,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="F114" t="n">
-        <v>47.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="115">
@@ -3625,19 +3625,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>12.5</v>
       </c>
       <c r="F115" t="n">
-        <v>52.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="116">
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="F116" t="n">
         <v>50.3</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F117" t="n">
         <v>52.1</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F118" t="n">
         <v>52.3</v>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="F119" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="120">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="F120" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="121">
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F122" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="123">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="124">
@@ -3945,7 +3945,7 @@
         <v>7.9</v>
       </c>
       <c r="F126" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="127">
@@ -3973,7 +3973,7 @@
         <v>7.8</v>
       </c>
       <c r="F127" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="128">
@@ -4029,7 +4029,7 @@
         <v>7.4</v>
       </c>
       <c r="F129" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="130">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F130" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="131">
@@ -4073,19 +4073,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F131" t="n">
-        <v>46.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="132">
@@ -4101,19 +4101,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E132" t="n">
         <v>6.7</v>
       </c>
       <c r="F132" t="n">
-        <v>51.6</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="133">
@@ -4129,19 +4129,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="F133" t="n">
-        <v>44.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="134">
@@ -4169,7 +4169,7 @@
         <v>6.5</v>
       </c>
       <c r="F134" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="135">
@@ -4197,7 +4197,7 @@
         <v>6.2</v>
       </c>
       <c r="F135" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="136">
@@ -4225,7 +4225,7 @@
         <v>4.8</v>
       </c>
       <c r="F136" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="137">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F138" t="n">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="139">
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F139" t="n">
         <v>47.1</v>
@@ -4337,7 +4337,7 @@
         <v>4.3</v>
       </c>
       <c r="F140" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="141">
@@ -4353,19 +4353,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F141" t="n">
-        <v>47.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="142">
@@ -4381,19 +4381,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>45.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="143">
@@ -4421,7 +4421,7 @@
         <v>3.8</v>
       </c>
       <c r="F143" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="144">
@@ -4477,7 +4477,7 @@
         <v>3.4</v>
       </c>
       <c r="F145" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="146">
@@ -4589,7 +4589,7 @@
         <v>2.5</v>
       </c>
       <c r="F149" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="150">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F150" t="n">
-        <v>50.3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F151" t="n">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="152">
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="F252" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="253">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="F253" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="254">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="F254" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="255">
@@ -7557,7 +7557,7 @@
         <v>22.4</v>
       </c>
       <c r="F255" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="256">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="F256" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="257">
@@ -7613,7 +7613,7 @@
         <v>17.1</v>
       </c>
       <c r="F257" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="258">
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="F258" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="259">
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F259" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="260">
@@ -7697,7 +7697,7 @@
         <v>15.7</v>
       </c>
       <c r="F260" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="261">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="F261" t="n">
         <v>54.7</v>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="F262" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="263">
@@ -7781,7 +7781,7 @@
         <v>12.8</v>
       </c>
       <c r="F263" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="264">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="F265" t="n">
         <v>49.6</v>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F266" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="267">
@@ -7881,19 +7881,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F267" t="n">
-        <v>47.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="268">
@@ -7909,19 +7909,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E268" t="n">
         <v>9.1</v>
       </c>
       <c r="F268" t="n">
-        <v>49.6</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="269">
@@ -7937,19 +7937,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E269" t="n">
         <v>9.1</v>
       </c>
       <c r="F269" t="n">
-        <v>50.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="270">
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="F270" t="n">
         <v>47</v>
@@ -7993,19 +7993,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E271" t="n">
         <v>8.1</v>
       </c>
       <c r="F271" t="n">
-        <v>49.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="272">
@@ -8021,19 +8021,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F272" t="n">
-        <v>45.3</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="273">
@@ -8089,7 +8089,7 @@
         <v>7.8</v>
       </c>
       <c r="F274" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="275">
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F275" t="n">
         <v>45.6</v>
@@ -8145,7 +8145,7 @@
         <v>7.5</v>
       </c>
       <c r="F276" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="277">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F277" t="n">
         <v>53.7</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="F278" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="279">
@@ -8229,7 +8229,7 @@
         <v>5.9</v>
       </c>
       <c r="F279" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="280">
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F280" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="281">
@@ -8285,7 +8285,7 @@
         <v>5.6</v>
       </c>
       <c r="F281" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="282">
@@ -8341,7 +8341,7 @@
         <v>5</v>
       </c>
       <c r="F283" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="284">
@@ -8357,19 +8357,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E284" t="n">
         <v>4.8</v>
       </c>
       <c r="F284" t="n">
-        <v>47.4</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="285">
@@ -8385,19 +8385,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E285" t="n">
         <v>4.7</v>
       </c>
       <c r="F285" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="286">
@@ -8413,19 +8413,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E286" t="n">
         <v>4.7</v>
       </c>
       <c r="F286" t="n">
-        <v>49.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="287">
@@ -8441,19 +8441,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F287" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="288">
@@ -8469,19 +8469,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E288" t="n">
         <v>4.5</v>
       </c>
       <c r="F288" t="n">
-        <v>47.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="289">
@@ -8497,19 +8497,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F289" t="n">
-        <v>49.7</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="290">
@@ -8525,19 +8525,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F290" t="n">
-        <v>48</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="291">
@@ -8553,19 +8553,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F291" t="n">
-        <v>51.8</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="292">
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F292" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="293">
@@ -8621,7 +8621,7 @@
         <v>3.8</v>
       </c>
       <c r="F293" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="294">
@@ -8637,19 +8637,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="F294" t="n">
-        <v>50.9</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="295">
@@ -8665,19 +8665,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E295" t="n">
         <v>3.6</v>
       </c>
       <c r="F295" t="n">
-        <v>52.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="296">
@@ -8693,19 +8693,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E296" t="n">
         <v>3.4</v>
       </c>
       <c r="F296" t="n">
-        <v>45.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="297">
@@ -8721,19 +8721,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F297" t="n">
-        <v>48.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="298">
@@ -8749,19 +8749,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E298" t="n">
         <v>3.3</v>
       </c>
       <c r="F298" t="n">
-        <v>40.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="299">
@@ -8845,7 +8845,7 @@
         <v>2.5</v>
       </c>
       <c r="F301" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="302">
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
       <c r="F352" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="353">
@@ -10298,10 +10298,10 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>44.2</v>
+        <v>44.6</v>
       </c>
       <c r="F353" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="354">
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>39.3</v>
+        <v>38.8</v>
       </c>
       <c r="F354" t="n">
-        <v>54.9</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="355">
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="F355" t="n">
         <v>53</v>
@@ -10382,10 +10382,10 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="F356" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="357">
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="F357" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="358">
@@ -10429,19 +10429,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="F358" t="n">
-        <v>52.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="359">
@@ -10457,19 +10457,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="F359" t="n">
-        <v>54.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="360">
@@ -10494,7 +10494,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F360" t="n">
         <v>47.7</v>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F361" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="362">
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="F362" t="n">
-        <v>51</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="363">
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F363" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="364">
@@ -10609,7 +10609,7 @@
         <v>10.3</v>
       </c>
       <c r="F364" t="n">
-        <v>45.6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="365">
@@ -10665,7 +10665,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F366" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="367">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10693,7 +10693,7 @@
         <v>9.1</v>
       </c>
       <c r="F367" t="n">
-        <v>50</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="368">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>47.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="369">
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F369" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="370">
@@ -10777,7 +10777,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F370" t="n">
-        <v>49.6</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="371">
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F371" t="n">
-        <v>48.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="372">
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F372" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="373">
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="F373" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="374">
@@ -10877,19 +10877,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="F374" t="n">
-        <v>47.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="375">
@@ -10905,19 +10905,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="F375" t="n">
-        <v>49.5</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="376">
@@ -10933,19 +10933,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E376" t="n">
         <v>6.4</v>
       </c>
       <c r="F376" t="n">
-        <v>47</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="377">
@@ -10970,10 +10970,10 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="F377" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="378">
@@ -10989,19 +10989,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E378" t="n">
         <v>5.8</v>
       </c>
       <c r="F378" t="n">
-        <v>43.7</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="379">
@@ -11017,19 +11017,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="F379" t="n">
-        <v>45.1</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="380">
@@ -11045,19 +11045,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F380" t="n">
-        <v>53.5</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="381">
@@ -11073,19 +11073,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E381" t="n">
         <v>5.2</v>
       </c>
       <c r="F381" t="n">
-        <v>51.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="382">
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F382" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="383">
@@ -11129,19 +11129,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E383" t="n">
         <v>5</v>
       </c>
       <c r="F383" t="n">
-        <v>46.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="384">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F384" t="n">
-        <v>52.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="385">
@@ -11197,7 +11197,7 @@
         <v>4.9</v>
       </c>
       <c r="F385" t="n">
-        <v>48.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="386">
@@ -11213,19 +11213,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E386" t="n">
         <v>4.4</v>
       </c>
       <c r="F386" t="n">
-        <v>48.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="387">
@@ -11241,19 +11241,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F387" t="n">
-        <v>56.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="388">
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F388" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="389">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="F389" t="n">
-        <v>47.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="390">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F390" t="n">
-        <v>39.4</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="391">
@@ -11365,7 +11365,7 @@
         <v>3.1</v>
       </c>
       <c r="F391" t="n">
-        <v>48.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="392">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F392" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="393">
@@ -11409,19 +11409,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F393" t="n">
-        <v>50.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="394">
@@ -11437,19 +11437,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F394" t="n">
-        <v>47.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="395">
@@ -11477,7 +11477,7 @@
         <v>2.2</v>
       </c>
       <c r="F395" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="396">
@@ -11505,7 +11505,7 @@
         <v>2.2</v>
       </c>
       <c r="F396" t="n">
-        <v>44.3</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="397">
@@ -11533,7 +11533,7 @@
         <v>2.1</v>
       </c>
       <c r="F397" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="398">
@@ -11589,7 +11589,7 @@
         <v>1.6</v>
       </c>
       <c r="F399" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="400">
@@ -11617,7 +11617,7 @@
         <v>1.3</v>
       </c>
       <c r="F400" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="401">
@@ -11645,7 +11645,7 @@
         <v>0.9</v>
       </c>
       <c r="F401" t="n">
-        <v>46.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="402">
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="F452" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="453">
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="F453" t="n">
         <v>47.8</v>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="F454" t="n">
         <v>50.1</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="F457" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="458">
@@ -13241,7 +13241,7 @@
         <v>17.9</v>
       </c>
       <c r="F458" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="459">
@@ -13266,7 +13266,7 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="F459" t="n">
         <v>49.1</v>
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="F460" t="n">
         <v>45.8</v>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="F461" t="n">
         <v>49.5</v>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F464" t="n">
         <v>51.2</v>
@@ -13437,7 +13437,7 @@
         <v>12.3</v>
       </c>
       <c r="F465" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="466">
@@ -13465,7 +13465,7 @@
         <v>12.2</v>
       </c>
       <c r="F466" t="n">
-        <v>53.4</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="467">
@@ -13493,7 +13493,7 @@
         <v>11.7</v>
       </c>
       <c r="F467" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="468">
@@ -13521,7 +13521,7 @@
         <v>11.5</v>
       </c>
       <c r="F468" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="469">
@@ -13549,7 +13549,7 @@
         <v>11.5</v>
       </c>
       <c r="F469" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="470">
@@ -13574,10 +13574,10 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F470" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="471">
@@ -13602,7 +13602,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F471" t="n">
         <v>50</v>
@@ -13621,19 +13621,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F472" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="473">
@@ -13649,19 +13649,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E473" t="n">
         <v>10.4</v>
       </c>
       <c r="F473" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="474">
@@ -13686,10 +13686,10 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F474" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="475">
@@ -13717,7 +13717,7 @@
         <v>10.1</v>
       </c>
       <c r="F475" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="476">
@@ -13745,7 +13745,7 @@
         <v>7.9</v>
       </c>
       <c r="F476" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="477">
@@ -13761,19 +13761,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F477" t="n">
-        <v>49.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="478">
@@ -13789,19 +13789,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E478" t="n">
         <v>7.7</v>
       </c>
       <c r="F478" t="n">
-        <v>47</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="479">
@@ -13829,7 +13829,7 @@
         <v>7.2</v>
       </c>
       <c r="F479" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="480">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -13854,10 +13854,10 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F480" t="n">
-        <v>48.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="481">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13885,7 +13885,7 @@
         <v>6.8</v>
       </c>
       <c r="F481" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="482">
@@ -13913,7 +13913,7 @@
         <v>6.2</v>
       </c>
       <c r="F482" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="483">
@@ -13938,10 +13938,10 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F483" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="484">
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F485" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="486">
@@ -14025,7 +14025,7 @@
         <v>5.4</v>
       </c>
       <c r="F486" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="487">
@@ -14053,7 +14053,7 @@
         <v>5.1</v>
       </c>
       <c r="F487" t="n">
-        <v>45.7</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="488">
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F488" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="489">
@@ -14106,10 +14106,10 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F489" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="490">
@@ -14165,7 +14165,7 @@
         <v>4</v>
       </c>
       <c r="F491" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="492">
@@ -14193,7 +14193,7 @@
         <v>3.8</v>
       </c>
       <c r="F492" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="493">
@@ -14221,7 +14221,7 @@
         <v>3.7</v>
       </c>
       <c r="F493" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="494">
@@ -14249,7 +14249,7 @@
         <v>3.6</v>
       </c>
       <c r="F494" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="495">
@@ -14277,7 +14277,7 @@
         <v>3.4</v>
       </c>
       <c r="F495" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="496">
@@ -14302,10 +14302,10 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F496" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="497">
@@ -14330,7 +14330,7 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F497" t="n">
         <v>52.5</v>
@@ -14349,19 +14349,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F498" t="n">
-        <v>47.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="499">
@@ -14377,19 +14377,19 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E499" t="n">
         <v>3.2</v>
       </c>
       <c r="F499" t="n">
-        <v>48.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="500">
@@ -14442,10 +14442,10 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F501" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="502">
@@ -21470,10 +21470,10 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>51.7</v>
+        <v>51.3</v>
       </c>
       <c r="F752" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="753">
@@ -21501,7 +21501,7 @@
         <v>27.4</v>
       </c>
       <c r="F753" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="754">
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="E754" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="F754" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="755">
@@ -21557,7 +21557,7 @@
         <v>25</v>
       </c>
       <c r="F755" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="756">
@@ -21582,10 +21582,10 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="F756" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="757">
@@ -21610,10 +21610,10 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F757" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="758">
@@ -21638,10 +21638,10 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="F758" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="759">
@@ -21666,10 +21666,10 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="F759" t="n">
-        <v>55</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="760">
@@ -21697,7 +21697,7 @@
         <v>13.9</v>
       </c>
       <c r="F760" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="761">
@@ -21722,10 +21722,10 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F761" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="762">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="F762" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="763">
@@ -21778,10 +21778,10 @@
         </is>
       </c>
       <c r="E763" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="F763" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="764">
@@ -21806,7 +21806,7 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="F764" t="n">
         <v>50.7</v>
@@ -21825,19 +21825,19 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E765" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F765" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="766">
@@ -21853,19 +21853,19 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="F766" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="767">
@@ -21890,10 +21890,10 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F767" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="768">
@@ -21918,10 +21918,10 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="F768" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="769">
@@ -21946,10 +21946,10 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="F769" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="770">
@@ -21977,7 +21977,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F770" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="771">
@@ -21993,19 +21993,19 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E771" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F771" t="n">
-        <v>51.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="772">
@@ -22021,19 +22021,19 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E772" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="F772" t="n">
-        <v>50.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="773">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F773" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="774">
@@ -22086,7 +22086,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F774" t="n">
         <v>50.6</v>
@@ -22114,10 +22114,10 @@
         </is>
       </c>
       <c r="E775" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F775" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="776">
@@ -22133,19 +22133,19 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E776" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F776" t="n">
-        <v>45.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="777">
@@ -22161,19 +22161,19 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E777" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="F777" t="n">
-        <v>49.9</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="778">
@@ -22198,10 +22198,10 @@
         </is>
       </c>
       <c r="E778" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="F778" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="779">
@@ -22229,7 +22229,7 @@
         <v>7</v>
       </c>
       <c r="F779" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="780">
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F780" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="781">
@@ -22282,7 +22282,7 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F781" t="n">
         <v>48.8</v>
@@ -22301,19 +22301,19 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E782" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="F782" t="n">
-        <v>46.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="783">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -22338,10 +22338,10 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="F783" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="784">
@@ -22366,7 +22366,7 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F784" t="n">
         <v>50.5</v>
@@ -22385,19 +22385,19 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E785" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F785" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="786">
@@ -22413,19 +22413,19 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E786" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F786" t="n">
-        <v>48.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="787">
@@ -22450,10 +22450,10 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F787" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="788">
@@ -22469,19 +22469,19 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E788" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F788" t="n">
-        <v>52.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="789">
@@ -22497,19 +22497,19 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E789" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F789" t="n">
-        <v>47.5</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="790">
@@ -22534,10 +22534,10 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F790" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="791">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -22562,10 +22562,10 @@
         </is>
       </c>
       <c r="E791" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F791" t="n">
-        <v>44.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="792">
@@ -22581,19 +22581,19 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E792" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F792" t="n">
-        <v>52.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="793">
@@ -22609,19 +22609,19 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E793" t="n">
         <v>4.1</v>
       </c>
       <c r="F793" t="n">
-        <v>52.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="794">
@@ -22665,19 +22665,19 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E795" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F795" t="n">
-        <v>49.8</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="796">
@@ -22693,19 +22693,19 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E796" t="n">
         <v>3.5</v>
       </c>
       <c r="F796" t="n">
-        <v>47.9</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="797">
@@ -22721,19 +22721,19 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E797" t="n">
         <v>3.4</v>
       </c>
       <c r="F797" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="798">
@@ -22761,7 +22761,7 @@
         <v>3</v>
       </c>
       <c r="F798" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="799">
@@ -22786,10 +22786,10 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F799" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="800">
@@ -22814,10 +22814,10 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="F800" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="801">
@@ -22842,10 +22842,10 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F801" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="802">
@@ -22870,10 +22870,10 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="F802" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="803">
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="F804" t="n">
         <v>47.3</v>
@@ -22957,7 +22957,7 @@
         <v>21.1</v>
       </c>
       <c r="F805" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="806">
@@ -22985,7 +22985,7 @@
         <v>20.4</v>
       </c>
       <c r="F806" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="807">
@@ -23001,19 +23001,19 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E807" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F807" t="n">
-        <v>52.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="808">
@@ -23029,19 +23029,19 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E808" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="F808" t="n">
-        <v>47.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="809">
@@ -23066,7 +23066,7 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="F809" t="n">
         <v>50</v>
@@ -23094,10 +23094,10 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="F810" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="811">
@@ -23141,19 +23141,19 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E812" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="F812" t="n">
-        <v>50.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="813">
@@ -23169,19 +23169,19 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E813" t="n">
         <v>13.7</v>
       </c>
       <c r="F813" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="814">
@@ -23206,7 +23206,7 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="F814" t="n">
         <v>45.4</v>
@@ -23234,7 +23234,7 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F815" t="n">
         <v>51.7</v>
@@ -23265,7 +23265,7 @@
         <v>12.2</v>
       </c>
       <c r="F816" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="817">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="F817" t="n">
         <v>45.3</v>
@@ -23318,7 +23318,7 @@
         </is>
       </c>
       <c r="E818" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F818" t="n">
         <v>53.2</v>
@@ -23349,7 +23349,7 @@
         <v>11.5</v>
       </c>
       <c r="F819" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="820">
@@ -23374,10 +23374,10 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F820" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="821">
@@ -23402,7 +23402,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F821" t="n">
         <v>48.7</v>
@@ -23430,7 +23430,7 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F822" t="n">
         <v>49.2</v>
@@ -23458,7 +23458,7 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F823" t="n">
         <v>50.3</v>
@@ -23486,7 +23486,7 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F824" t="n">
         <v>50.9</v>
@@ -23517,7 +23517,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F825" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="826">
@@ -23573,7 +23573,7 @@
         <v>7.6</v>
       </c>
       <c r="F827" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="828">
@@ -23601,7 +23601,7 @@
         <v>7.5</v>
       </c>
       <c r="F828" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="829">
@@ -23629,7 +23629,7 @@
         <v>7.5</v>
       </c>
       <c r="F829" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="830">
@@ -23685,7 +23685,7 @@
         <v>7.1</v>
       </c>
       <c r="F831" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="832">
@@ -23713,7 +23713,7 @@
         <v>5.9</v>
       </c>
       <c r="F832" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="833">
@@ -23729,19 +23729,19 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E833" t="n">
         <v>5.6</v>
       </c>
       <c r="F833" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="834">
@@ -23757,19 +23757,19 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E834" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F834" t="n">
-        <v>52.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="835">
@@ -23785,19 +23785,19 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E835" t="n">
         <v>5.5</v>
       </c>
       <c r="F835" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="836">
@@ -23825,7 +23825,7 @@
         <v>5.5</v>
       </c>
       <c r="F836" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="837">
@@ -23881,7 +23881,7 @@
         <v>5.4</v>
       </c>
       <c r="F838" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="839">
@@ -23937,7 +23937,7 @@
         <v>5</v>
       </c>
       <c r="F840" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="841">
@@ -23993,7 +23993,7 @@
         <v>4.8</v>
       </c>
       <c r="F842" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="843">
@@ -24018,7 +24018,7 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F843" t="n">
         <v>46.2</v>
@@ -24037,19 +24037,19 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F844" t="n">
-        <v>53.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="845">
@@ -24065,19 +24065,19 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E845" t="n">
         <v>3.8</v>
       </c>
       <c r="F845" t="n">
-        <v>51.3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="846">
@@ -24093,19 +24093,19 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E846" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F846" t="n">
-        <v>47.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="847">
@@ -24133,7 +24133,7 @@
         <v>3.6</v>
       </c>
       <c r="F847" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="848">
@@ -24149,19 +24149,19 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E848" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F848" t="n">
-        <v>50.6</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="849">
@@ -24177,19 +24177,19 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E849" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F849" t="n">
-        <v>53.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="850">
@@ -24217,7 +24217,7 @@
         <v>2.9</v>
       </c>
       <c r="F850" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="851">
@@ -24245,7 +24245,7 @@
         <v>2.9</v>
       </c>
       <c r="F851" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="852">
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="F852" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="853">
@@ -24326,7 +24326,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="F854" t="n">
         <v>47.7</v>
@@ -24357,7 +24357,7 @@
         <v>21.2</v>
       </c>
       <c r="F855" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="856">
@@ -24385,7 +24385,7 @@
         <v>20.4</v>
       </c>
       <c r="F856" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="857">
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="F857" t="n">
         <v>49.2</v>
@@ -24438,10 +24438,10 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="F858" t="n">
-        <v>53.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="859">
@@ -24469,7 +24469,7 @@
         <v>15.6</v>
       </c>
       <c r="F859" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="860">
@@ -24494,10 +24494,10 @@
         </is>
       </c>
       <c r="E860" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="F860" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="861">
@@ -24513,19 +24513,19 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E861" t="n">
         <v>14</v>
       </c>
       <c r="F861" t="n">
-        <v>44.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="862">
@@ -24541,19 +24541,19 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E862" t="n">
         <v>13.9</v>
       </c>
       <c r="F862" t="n">
-        <v>49.4</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="863">
@@ -24578,10 +24578,10 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="F863" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="864">
@@ -24606,7 +24606,7 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F864" t="n">
         <v>47.3</v>
@@ -24634,10 +24634,10 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F865" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="866">
@@ -24665,7 +24665,7 @@
         <v>12.2</v>
       </c>
       <c r="F866" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="867">
@@ -24693,7 +24693,7 @@
         <v>11.9</v>
       </c>
       <c r="F867" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="868">
@@ -24749,7 +24749,7 @@
         <v>11.5</v>
       </c>
       <c r="F869" t="n">
-        <v>53.9</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="870">
@@ -24802,10 +24802,10 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F871" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="872">
@@ -24830,10 +24830,10 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="F872" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="873">
@@ -24861,7 +24861,7 @@
         <v>9.9</v>
       </c>
       <c r="F873" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="874">
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F874" t="n">
         <v>50</v>
@@ -24945,7 +24945,7 @@
         <v>8.1</v>
       </c>
       <c r="F876" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="877">
@@ -24970,10 +24970,10 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F877" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="878">
@@ -24989,19 +24989,19 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E878" t="n">
         <v>7.3</v>
       </c>
       <c r="F878" t="n">
-        <v>49.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="879">
@@ -25017,19 +25017,19 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E879" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="F879" t="n">
-        <v>47.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="880">
@@ -25045,19 +25045,19 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E880" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="F880" t="n">
-        <v>47.3</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="881">
@@ -25073,19 +25073,19 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E881" t="n">
         <v>7.1</v>
       </c>
       <c r="F881" t="n">
-        <v>46.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="882">
@@ -25110,10 +25110,10 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F882" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="883">
@@ -25194,10 +25194,10 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F885" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="886">
@@ -25213,19 +25213,19 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E886" t="n">
         <v>5.5</v>
       </c>
       <c r="F886" t="n">
-        <v>46.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="887">
@@ -25241,19 +25241,19 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E887" t="n">
         <v>5.4</v>
       </c>
       <c r="F887" t="n">
-        <v>45.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="888">
@@ -25278,10 +25278,10 @@
         </is>
       </c>
       <c r="E888" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F888" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="889">
@@ -25306,10 +25306,10 @@
         </is>
       </c>
       <c r="E889" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F889" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="890">
@@ -25337,7 +25337,7 @@
         <v>3.7</v>
       </c>
       <c r="F890" t="n">
-        <v>47.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="891">
@@ -25365,7 +25365,7 @@
         <v>3.6</v>
       </c>
       <c r="F891" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="892">
@@ -25381,19 +25381,19 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E892" t="n">
         <v>3.6</v>
       </c>
       <c r="F892" t="n">
-        <v>54.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="893">
@@ -25409,19 +25409,19 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E893" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F893" t="n">
-        <v>52.7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="894">
@@ -25449,7 +25449,7 @@
         <v>3.4</v>
       </c>
       <c r="F894" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="895">
@@ -25465,19 +25465,19 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E895" t="n">
         <v>3.3</v>
       </c>
       <c r="F895" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="896">
@@ -25493,19 +25493,19 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E896" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F896" t="n">
-        <v>51.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="897">
@@ -25533,7 +25533,7 @@
         <v>3.1</v>
       </c>
       <c r="F897" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="898">
@@ -25561,7 +25561,7 @@
         <v>2.9</v>
       </c>
       <c r="F898" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="899">
@@ -25589,7 +25589,7 @@
         <v>2.6</v>
       </c>
       <c r="F899" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="900">
@@ -25617,7 +25617,7 @@
         <v>2</v>
       </c>
       <c r="F900" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="901">
@@ -25645,7 +25645,7 @@
         <v>2</v>
       </c>
       <c r="F901" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="902">
@@ -25670,7 +25670,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="F902" t="n">
         <v>48.7</v>
@@ -25698,10 +25698,10 @@
         </is>
       </c>
       <c r="E903" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="F903" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="904">
@@ -25754,10 +25754,10 @@
         </is>
       </c>
       <c r="E905" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F905" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="906">
@@ -25782,10 +25782,10 @@
         </is>
       </c>
       <c r="E906" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="F906" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="907">
@@ -25813,7 +25813,7 @@
         <v>19.5</v>
       </c>
       <c r="F907" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="908">
@@ -25841,7 +25841,7 @@
         <v>18.4</v>
       </c>
       <c r="F908" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="909">
@@ -25866,10 +25866,10 @@
         </is>
       </c>
       <c r="E909" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="F909" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="910">
@@ -25894,7 +25894,7 @@
         </is>
       </c>
       <c r="E910" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="F910" t="n">
         <v>49</v>
@@ -25981,7 +25981,7 @@
         <v>13.7</v>
       </c>
       <c r="F913" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="914">
@@ -25997,19 +25997,19 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E914" t="n">
         <v>13.3</v>
       </c>
       <c r="F914" t="n">
-        <v>48.9</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="915">
@@ -26025,19 +26025,19 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E915" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="F915" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="916">
@@ -26062,10 +26062,10 @@
         </is>
       </c>
       <c r="E916" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F916" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="917">
@@ -26118,10 +26118,10 @@
         </is>
       </c>
       <c r="E918" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="F918" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="919">
@@ -26149,7 +26149,7 @@
         <v>11.9</v>
       </c>
       <c r="F919" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="920">
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="E920" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F920" t="n">
         <v>51.9</v>
@@ -26202,10 +26202,10 @@
         </is>
       </c>
       <c r="E921" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F921" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="922">
@@ -26233,7 +26233,7 @@
         <v>9.6</v>
       </c>
       <c r="F922" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="923">
@@ -26317,7 +26317,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F925" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="926">
@@ -26342,7 +26342,7 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F926" t="n">
         <v>52.1</v>
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="E927" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="F927" t="n">
         <v>47.9</v>
@@ -26401,7 +26401,7 @@
         <v>8</v>
       </c>
       <c r="F928" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="929">
@@ -26429,7 +26429,7 @@
         <v>7.1</v>
       </c>
       <c r="F929" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="930">
@@ -26457,7 +26457,7 @@
         <v>6.8</v>
       </c>
       <c r="F930" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="931">
@@ -26485,7 +26485,7 @@
         <v>6.5</v>
       </c>
       <c r="F931" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="932">
@@ -26501,19 +26501,19 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E932" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F932" t="n">
-        <v>45.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="933">
@@ -26529,19 +26529,19 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E933" t="n">
         <v>6</v>
       </c>
       <c r="F933" t="n">
-        <v>51.8</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="934">
@@ -26566,10 +26566,10 @@
         </is>
       </c>
       <c r="E934" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F934" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="935">
@@ -26597,7 +26597,7 @@
         <v>5.4</v>
       </c>
       <c r="F935" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="936">
@@ -26625,7 +26625,7 @@
         <v>5</v>
       </c>
       <c r="F936" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="937">
@@ -26681,7 +26681,7 @@
         <v>4.6</v>
       </c>
       <c r="F938" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="939">
@@ -26709,7 +26709,7 @@
         <v>4.5</v>
       </c>
       <c r="F939" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="940">
@@ -26737,7 +26737,7 @@
         <v>4.2</v>
       </c>
       <c r="F940" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="941">
@@ -26762,10 +26762,10 @@
         </is>
       </c>
       <c r="E941" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F941" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="942">
@@ -26793,7 +26793,7 @@
         <v>4.1</v>
       </c>
       <c r="F942" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="943">
@@ -26821,7 +26821,7 @@
         <v>4</v>
       </c>
       <c r="F943" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="944">
@@ -26849,7 +26849,7 @@
         <v>4</v>
       </c>
       <c r="F944" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="945">
@@ -26877,7 +26877,7 @@
         <v>3.7</v>
       </c>
       <c r="F945" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="946">
@@ -26902,10 +26902,10 @@
         </is>
       </c>
       <c r="E946" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F946" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="947">
@@ -26989,7 +26989,7 @@
         <v>2.8</v>
       </c>
       <c r="F949" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="950">
@@ -27017,7 +27017,7 @@
         <v>2.3</v>
       </c>
       <c r="F950" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="951">
@@ -27045,7 +27045,7 @@
         <v>1.9</v>
       </c>
       <c r="F951" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="952">
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="F952" t="n">
         <v>47.7</v>
@@ -27098,7 +27098,7 @@
         </is>
       </c>
       <c r="E953" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="F953" t="n">
         <v>46.8</v>
@@ -27129,7 +27129,7 @@
         <v>24.7</v>
       </c>
       <c r="F954" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="955">
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="E955" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="F955" t="n">
         <v>49.8</v>
@@ -27185,7 +27185,7 @@
         <v>21.4</v>
       </c>
       <c r="F956" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="957">
@@ -27210,10 +27210,10 @@
         </is>
       </c>
       <c r="E957" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="F957" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="958">
@@ -27294,10 +27294,10 @@
         </is>
       </c>
       <c r="E960" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F960" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="961">
@@ -27322,10 +27322,10 @@
         </is>
       </c>
       <c r="E961" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="F961" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="962">
@@ -27353,7 +27353,7 @@
         <v>14.2</v>
       </c>
       <c r="F962" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="963">
@@ -27381,7 +27381,7 @@
         <v>14.1</v>
       </c>
       <c r="F963" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="964">
@@ -27406,7 +27406,7 @@
         </is>
       </c>
       <c r="E964" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F964" t="n">
         <v>51.1</v>
@@ -27437,7 +27437,7 @@
         <v>13</v>
       </c>
       <c r="F965" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="966">
@@ -27490,7 +27490,7 @@
         </is>
       </c>
       <c r="E967" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F967" t="n">
         <v>52.3</v>
@@ -27521,7 +27521,7 @@
         <v>11.4</v>
       </c>
       <c r="F968" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="969">
@@ -27546,7 +27546,7 @@
         </is>
       </c>
       <c r="E969" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F969" t="n">
         <v>53.4</v>
@@ -27574,7 +27574,7 @@
         </is>
       </c>
       <c r="E970" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F970" t="n">
         <v>48.5</v>
@@ -27605,7 +27605,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F971" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="972">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -27633,7 +27633,7 @@
         <v>9.5</v>
       </c>
       <c r="F972" t="n">
-        <v>50.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="973">
@@ -27649,7 +27649,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -27658,10 +27658,10 @@
         </is>
       </c>
       <c r="E973" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="F973" t="n">
-        <v>52.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="974">
@@ -27686,7 +27686,7 @@
         </is>
       </c>
       <c r="E974" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F974" t="n">
         <v>49</v>
@@ -27717,7 +27717,7 @@
         <v>9.1</v>
       </c>
       <c r="F975" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="976">
@@ -27742,7 +27742,7 @@
         </is>
       </c>
       <c r="E976" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="F976" t="n">
         <v>47.2</v>
@@ -27826,7 +27826,7 @@
         </is>
       </c>
       <c r="E979" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="F979" t="n">
         <v>46.8</v>
@@ -27969,7 +27969,7 @@
         <v>5.4</v>
       </c>
       <c r="F984" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="985">
@@ -28053,7 +28053,7 @@
         <v>5</v>
       </c>
       <c r="F987" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="988">
@@ -28081,7 +28081,7 @@
         <v>4.9</v>
       </c>
       <c r="F988" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="989">
@@ -28109,7 +28109,7 @@
         <v>4.8</v>
       </c>
       <c r="F989" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="990">
@@ -28218,10 +28218,10 @@
         </is>
       </c>
       <c r="E993" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F993" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="994">
@@ -28277,7 +28277,7 @@
         <v>3.7</v>
       </c>
       <c r="F995" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="996">
@@ -28333,7 +28333,7 @@
         <v>3.4</v>
       </c>
       <c r="F997" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="998">
@@ -28361,7 +28361,7 @@
         <v>3.3</v>
       </c>
       <c r="F998" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="999">
@@ -28389,7 +28389,7 @@
         <v>2.9</v>
       </c>
       <c r="F999" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1000">
@@ -28414,7 +28414,7 @@
         </is>
       </c>
       <c r="E1000" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1000" t="n">
         <v>52.9</v>
@@ -28445,7 +28445,7 @@
         <v>2.2</v>
       </c>
       <c r="F1001" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1002">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>33.5</v>
+        <v>30.1</v>
       </c>
       <c r="F452" t="n">
-        <v>49.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="453">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>25.2</v>
+        <v>26.5</v>
       </c>
       <c r="F453" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="454">
@@ -13117,19 +13117,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>24.6</v>
+        <v>12.3</v>
       </c>
       <c r="F454" t="n">
-        <v>50.1</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="455">
@@ -13145,19 +13145,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>23.7</v>
+        <v>17.9</v>
       </c>
       <c r="F455" t="n">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="456">
@@ -13173,19 +13173,19 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>22</v>
+        <v>19.9</v>
       </c>
       <c r="F456" t="n">
-        <v>48</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="457">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>19.9</v>
+        <v>24.6</v>
       </c>
       <c r="F457" t="n">
-        <v>54.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="458">
@@ -13229,19 +13229,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>17.9</v>
+        <v>23.7</v>
       </c>
       <c r="F458" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="459">
@@ -13257,16 +13257,16 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="F459" t="n">
         <v>49.1</v>
@@ -13285,19 +13285,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="F460" t="n">
-        <v>45.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="461">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F461" t="n">
-        <v>49.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="462">
@@ -13341,19 +13341,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>13.7</v>
+        <v>12.2</v>
       </c>
       <c r="F462" t="n">
-        <v>43.9</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="463">
@@ -13397,19 +13397,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="F464" t="n">
-        <v>51.2</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="465">
@@ -13425,19 +13425,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>12.3</v>
+        <v>10.4</v>
       </c>
       <c r="F465" t="n">
-        <v>47.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="466">
@@ -13453,19 +13453,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="F466" t="n">
-        <v>53.6</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="467">
@@ -13481,19 +13481,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="F467" t="n">
-        <v>45.4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="468">
@@ -13509,19 +13509,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>11.5</v>
+        <v>14.3</v>
       </c>
       <c r="F468" t="n">
-        <v>53</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="469">
@@ -13537,19 +13537,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
       <c r="F469" t="n">
-        <v>52.8</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="470">
@@ -13565,19 +13565,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>11.2</v>
+        <v>7.2</v>
       </c>
       <c r="F470" t="n">
-        <v>49.1</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="471">
@@ -13593,19 +13593,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="F471" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="472">
@@ -13621,19 +13621,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="F472" t="n">
-        <v>50.1</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="473">
@@ -13649,19 +13649,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="F473" t="n">
-        <v>49.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="474">
@@ -13677,19 +13677,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="F474" t="n">
-        <v>52.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="475">
@@ -13705,19 +13705,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="F475" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="476">
@@ -13733,19 +13733,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="F476" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="477">
@@ -13761,19 +13761,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="F477" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="478">
@@ -13789,19 +13789,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
       <c r="F478" t="n">
-        <v>49.9</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="479">
@@ -13817,19 +13817,19 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>7.2</v>
+        <v>11.7</v>
       </c>
       <c r="F479" t="n">
-        <v>51.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="480">
@@ -13845,19 +13845,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="F480" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="481">
@@ -13873,19 +13873,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="F481" t="n">
-        <v>48.9</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="482">
@@ -13901,19 +13901,19 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="F482" t="n">
-        <v>51.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="483">
@@ -13929,19 +13929,19 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="F483" t="n">
-        <v>53.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="484">
@@ -13985,19 +13985,19 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="F485" t="n">
-        <v>48.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="486">
@@ -14013,19 +14013,19 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="F486" t="n">
-        <v>45.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="487">
@@ -14041,19 +14041,19 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="F487" t="n">
-        <v>46.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="488">
@@ -14069,19 +14069,19 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="F488" t="n">
-        <v>49.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="489">
@@ -14097,19 +14097,19 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F489" t="n">
-        <v>46.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="490">
@@ -14125,19 +14125,19 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="F490" t="n">
-        <v>50.5</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="491">
@@ -14153,19 +14153,19 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="F491" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="492">
@@ -14181,19 +14181,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="F492" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="493">
@@ -14237,19 +14237,19 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="F494" t="n">
-        <v>54.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="495">
@@ -14265,19 +14265,19 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F495" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="496">
@@ -14293,19 +14293,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="F496" t="n">
-        <v>51.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="497">
@@ -14321,19 +14321,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F497" t="n">
-        <v>52.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="498">
@@ -14349,19 +14349,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="F498" t="n">
-        <v>48.9</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="499">
@@ -14377,19 +14377,19 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="F499" t="n">
-        <v>47.7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="500">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>30.1</v>
+        <v>33.5</v>
       </c>
       <c r="F452" t="n">
-        <v>46.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="453">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>26.5</v>
+        <v>25.2</v>
       </c>
       <c r="F453" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="454">
@@ -13117,19 +13117,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>12.3</v>
+        <v>24.6</v>
       </c>
       <c r="F454" t="n">
-        <v>47.1</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="455">
@@ -13145,19 +13145,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>17.9</v>
+        <v>23.7</v>
       </c>
       <c r="F455" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="456">
@@ -13173,19 +13173,19 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>19.9</v>
+        <v>22</v>
       </c>
       <c r="F456" t="n">
-        <v>54.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="457">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>24.6</v>
+        <v>19.9</v>
       </c>
       <c r="F457" t="n">
-        <v>50.1</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="458">
@@ -13229,19 +13229,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>23.7</v>
+        <v>17.9</v>
       </c>
       <c r="F458" t="n">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="459">
@@ -13257,16 +13257,16 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>11.2</v>
+        <v>14.7</v>
       </c>
       <c r="F459" t="n">
         <v>49.1</v>
@@ -13285,19 +13285,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="F460" t="n">
-        <v>49.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="461">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F461" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="462">
@@ -13341,19 +13341,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>12.2</v>
+        <v>13.7</v>
       </c>
       <c r="F462" t="n">
-        <v>53.6</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="463">
@@ -13397,19 +13397,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="F464" t="n">
-        <v>43.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="465">
@@ -13425,19 +13425,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>10.4</v>
+        <v>12.3</v>
       </c>
       <c r="F465" t="n">
-        <v>49.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="466">
@@ -13453,19 +13453,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="F466" t="n">
-        <v>52.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="467">
@@ -13481,19 +13481,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="F467" t="n">
-        <v>53</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="468">
@@ -13509,19 +13509,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="F468" t="n">
-        <v>45.8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="469">
@@ -13537,19 +13537,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>14.7</v>
+        <v>11.5</v>
       </c>
       <c r="F469" t="n">
-        <v>49.1</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="470">
@@ -13565,19 +13565,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>7.2</v>
+        <v>11.2</v>
       </c>
       <c r="F470" t="n">
-        <v>51.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="471">
@@ -13593,19 +13593,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="F471" t="n">
-        <v>51.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="472">
@@ -13621,19 +13621,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="F472" t="n">
-        <v>51.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="473">
@@ -13649,19 +13649,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="F473" t="n">
-        <v>52.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="474">
@@ -13677,19 +13677,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="F474" t="n">
-        <v>48.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="475">
@@ -13705,19 +13705,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="F475" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="476">
@@ -13733,19 +13733,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="F476" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="477">
@@ -13761,19 +13761,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="F477" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="478">
@@ -13789,19 +13789,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5.4</v>
+        <v>7.7</v>
       </c>
       <c r="F478" t="n">
-        <v>45.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="479">
@@ -13817,19 +13817,19 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>11.7</v>
+        <v>7.2</v>
       </c>
       <c r="F479" t="n">
-        <v>45.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="480">
@@ -13845,19 +13845,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="F480" t="n">
-        <v>49.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="481">
@@ -13873,19 +13873,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="F481" t="n">
-        <v>46.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="482">
@@ -13901,19 +13901,19 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="F482" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="483">
@@ -13929,19 +13929,19 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="F483" t="n">
-        <v>50.5</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="484">
@@ -13985,19 +13985,19 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="F485" t="n">
-        <v>48.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="486">
@@ -14013,19 +14013,19 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="F486" t="n">
-        <v>52.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="487">
@@ -14041,19 +14041,19 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="F487" t="n">
-        <v>48.9</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="488">
@@ -14069,19 +14069,19 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="F488" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="489">
@@ -14097,19 +14097,19 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F489" t="n">
-        <v>48.3</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="490">
@@ -14125,19 +14125,19 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="F490" t="n">
-        <v>53.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="491">
@@ -14153,19 +14153,19 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="F491" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="492">
@@ -14181,19 +14181,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="F492" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="493">
@@ -14237,19 +14237,19 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="F494" t="n">
-        <v>46.9</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="495">
@@ -14265,19 +14265,19 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="F495" t="n">
-        <v>51.4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="496">
@@ -14293,19 +14293,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="F496" t="n">
-        <v>46.1</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="497">
@@ -14321,19 +14321,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F497" t="n">
-        <v>47.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="498">
@@ -14349,19 +14349,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="F498" t="n">
-        <v>54.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="499">
@@ -14377,19 +14377,19 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="F499" t="n">
-        <v>53</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="500">

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1599"/>
+  <dimension ref="A1:F1602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34745,7 +34745,7 @@
         <v>7</v>
       </c>
       <c r="F1226" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1227">
@@ -34773,7 +34773,7 @@
         <v>5.8</v>
       </c>
       <c r="F1227" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1228">
@@ -34801,7 +34801,7 @@
         <v>4.5</v>
       </c>
       <c r="F1228" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1229">
@@ -34826,7 +34826,7 @@
         </is>
       </c>
       <c r="E1229" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1229" t="n">
         <v>48.7</v>
@@ -34845,19 +34845,19 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1230" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F1230" t="n">
-        <v>47.9</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1231">
@@ -34873,19 +34873,19 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1231" t="n">
         <v>3.7</v>
       </c>
       <c r="F1231" t="n">
-        <v>49.9</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1232">
@@ -34913,7 +34913,7 @@
         <v>3.3</v>
       </c>
       <c r="F1232" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1233">
@@ -34941,7 +34941,7 @@
         <v>3.3</v>
       </c>
       <c r="F1233" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1234">
@@ -34997,7 +34997,7 @@
         <v>3</v>
       </c>
       <c r="F1235" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1236">
@@ -35025,7 +35025,7 @@
         <v>2.7</v>
       </c>
       <c r="F1236" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1237">
@@ -35050,10 +35050,10 @@
         </is>
       </c>
       <c r="E1237" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1237" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1238">
@@ -35078,10 +35078,10 @@
         </is>
       </c>
       <c r="E1238" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1238" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1239">
@@ -35106,10 +35106,10 @@
         </is>
       </c>
       <c r="E1239" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1239" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1240">
@@ -35137,7 +35137,7 @@
         <v>2.3</v>
       </c>
       <c r="F1240" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1241">
@@ -35165,7 +35165,7 @@
         <v>2.2</v>
       </c>
       <c r="F1241" t="n">
-        <v>45.3</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1242">
@@ -35193,7 +35193,7 @@
         <v>2.1</v>
       </c>
       <c r="F1242" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1243">
@@ -35221,7 +35221,7 @@
         <v>2.1</v>
       </c>
       <c r="F1243" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1244">
@@ -35249,7 +35249,7 @@
         <v>2.1</v>
       </c>
       <c r="F1244" t="n">
-        <v>52.9</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1245">
@@ -35265,19 +35265,19 @@
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1245" t="n">
         <v>2</v>
       </c>
       <c r="F1245" t="n">
-        <v>45.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1246">
@@ -35293,19 +35293,19 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1246" t="n">
         <v>2</v>
       </c>
       <c r="F1246" t="n">
-        <v>51.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1247">
@@ -35321,19 +35321,19 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1247" t="n">
         <v>1.8</v>
       </c>
       <c r="F1247" t="n">
-        <v>51.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1248">
@@ -35349,19 +35349,19 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1248" t="n">
         <v>1.8</v>
       </c>
       <c r="F1248" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1249">
@@ -35377,19 +35377,19 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1249" t="n">
         <v>1.8</v>
       </c>
       <c r="F1249" t="n">
-        <v>50</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1250">
@@ -35417,7 +35417,7 @@
         <v>1.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>45.6</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1251">
@@ -35442,10 +35442,10 @@
         </is>
       </c>
       <c r="E1251" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1251" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1252">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -35470,10 +35470,10 @@
         </is>
       </c>
       <c r="E1252" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1252" t="n">
-        <v>43.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1253">
@@ -35489,19 +35489,19 @@
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1253" t="n">
         <v>1.4</v>
       </c>
       <c r="F1253" t="n">
-        <v>48.6</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1254">
@@ -35517,19 +35517,19 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1254" t="n">
         <v>1.4</v>
       </c>
       <c r="F1254" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1255">
@@ -35557,7 +35557,7 @@
         <v>1.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1256">
@@ -35582,10 +35582,10 @@
         </is>
       </c>
       <c r="E1256" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1256" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1257">
@@ -35613,7 +35613,7 @@
         <v>1.2</v>
       </c>
       <c r="F1257" t="n">
-        <v>48.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1258">
@@ -35669,7 +35669,7 @@
         <v>1.2</v>
       </c>
       <c r="F1259" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1260">
@@ -35694,10 +35694,10 @@
         </is>
       </c>
       <c r="E1260" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1260" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1261">
@@ -35725,7 +35725,7 @@
         <v>1.1</v>
       </c>
       <c r="F1261" t="n">
-        <v>48.4</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1262">
@@ -35753,7 +35753,7 @@
         <v>1.1</v>
       </c>
       <c r="F1262" t="n">
-        <v>44.2</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1263">
@@ -35781,7 +35781,7 @@
         <v>1</v>
       </c>
       <c r="F1263" t="n">
-        <v>46</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1264">
@@ -35797,19 +35797,19 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1264" t="n">
         <v>1</v>
       </c>
       <c r="F1264" t="n">
-        <v>47</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1265">
@@ -35825,19 +35825,19 @@
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1265" t="n">
         <v>1</v>
       </c>
       <c r="F1265" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1266">
@@ -35865,7 +35865,7 @@
         <v>1</v>
       </c>
       <c r="F1266" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1267">
@@ -35881,19 +35881,19 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1267" t="n">
         <v>0.9</v>
       </c>
       <c r="F1267" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1268">
@@ -35909,19 +35909,19 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1268" t="n">
         <v>0.9</v>
       </c>
       <c r="F1268" t="n">
-        <v>50.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1269">
@@ -35949,7 +35949,7 @@
         <v>0.9</v>
       </c>
       <c r="F1269" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1270">
@@ -36002,10 +36002,10 @@
         </is>
       </c>
       <c r="E1271" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1271" t="n">
-        <v>45</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1272">
@@ -36033,7 +36033,7 @@
         <v>0.7</v>
       </c>
       <c r="F1272" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1273">
@@ -36061,7 +36061,7 @@
         <v>0.7</v>
       </c>
       <c r="F1273" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1274">
@@ -36117,7 +36117,7 @@
         <v>0.5</v>
       </c>
       <c r="F1275" t="n">
-        <v>50.6</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1276">
@@ -36145,7 +36145,7 @@
         <v>0.4</v>
       </c>
       <c r="F1276" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1277">
@@ -36170,10 +36170,10 @@
         </is>
       </c>
       <c r="E1277" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F1277" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1278">
@@ -36201,7 +36201,7 @@
         <v>4.8</v>
       </c>
       <c r="F1278" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1279">
@@ -36226,10 +36226,10 @@
         </is>
       </c>
       <c r="E1279" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F1279" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1280">
@@ -36254,10 +36254,10 @@
         </is>
       </c>
       <c r="E1280" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F1280" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1281">
@@ -36282,10 +36282,10 @@
         </is>
       </c>
       <c r="E1281" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F1281" t="n">
-        <v>48.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1282">
@@ -36310,10 +36310,10 @@
         </is>
       </c>
       <c r="E1282" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F1282" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1283">
@@ -36341,7 +36341,7 @@
         <v>3.3</v>
       </c>
       <c r="F1283" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1284">
@@ -36357,19 +36357,19 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1284" t="n">
         <v>3.2</v>
       </c>
       <c r="F1284" t="n">
-        <v>47.1</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1285">
@@ -36385,19 +36385,19 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1285" t="n">
         <v>3.2</v>
       </c>
       <c r="F1285" t="n">
-        <v>51.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1286">
@@ -36425,7 +36425,7 @@
         <v>3.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1287">
@@ -36450,10 +36450,10 @@
         </is>
       </c>
       <c r="E1287" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1288">
@@ -36469,19 +36469,19 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1288" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F1288" t="n">
-        <v>49.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1289">
@@ -36497,19 +36497,19 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1289" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1289" t="n">
         <v>2.9</v>
       </c>
       <c r="F1289" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1290">
@@ -36537,7 +36537,7 @@
         <v>2.6</v>
       </c>
       <c r="F1290" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1291">
@@ -36565,7 +36565,7 @@
         <v>2.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1292">
@@ -36593,7 +36593,7 @@
         <v>2.3</v>
       </c>
       <c r="F1292" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1293">
@@ -36621,7 +36621,7 @@
         <v>2.3</v>
       </c>
       <c r="F1293" t="n">
-        <v>44.6</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1294">
@@ -36649,7 +36649,7 @@
         <v>2.2</v>
       </c>
       <c r="F1294" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1295">
@@ -36677,7 +36677,7 @@
         <v>2.1</v>
       </c>
       <c r="F1295" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1296">
@@ -36693,19 +36693,19 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1296" t="n">
         <v>2</v>
       </c>
       <c r="F1296" t="n">
-        <v>47.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1297">
@@ -36733,7 +36733,7 @@
         <v>2</v>
       </c>
       <c r="F1297" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1298">
@@ -36749,19 +36749,19 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1298" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1298" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1298" t="n">
-        <v>48.9</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1299">
@@ -36786,10 +36786,10 @@
         </is>
       </c>
       <c r="E1299" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1299" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1300">
@@ -36817,7 +36817,7 @@
         <v>1.7</v>
       </c>
       <c r="F1300" t="n">
-        <v>51.1</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1301">
@@ -36845,7 +36845,7 @@
         <v>1.7</v>
       </c>
       <c r="F1301" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1302">
@@ -36873,7 +36873,7 @@
         <v>1.6</v>
       </c>
       <c r="F1302" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1303">
@@ -36901,7 +36901,7 @@
         <v>1.5</v>
       </c>
       <c r="F1303" t="n">
-        <v>46.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1304">
@@ -36929,7 +36929,7 @@
         <v>1.5</v>
       </c>
       <c r="F1304" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1305">
@@ -36957,7 +36957,7 @@
         <v>1.5</v>
       </c>
       <c r="F1305" t="n">
-        <v>50.4</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1306">
@@ -36985,7 +36985,7 @@
         <v>1.5</v>
       </c>
       <c r="F1306" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1307">
@@ -37010,10 +37010,10 @@
         </is>
       </c>
       <c r="E1307" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F1307" t="n">
-        <v>46.5</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1308">
@@ -37041,7 +37041,7 @@
         <v>1.3</v>
       </c>
       <c r="F1308" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1309">
@@ -37069,7 +37069,7 @@
         <v>1.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1310">
@@ -37085,7 +37085,7 @@
       </c>
       <c r="C1310" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1310" t="inlineStr">
@@ -37097,7 +37097,7 @@
         <v>1.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>50.2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1311">
@@ -37113,7 +37113,7 @@
       </c>
       <c r="C1311" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1311" t="inlineStr">
@@ -37125,7 +37125,7 @@
         <v>1.1</v>
       </c>
       <c r="F1311" t="n">
-        <v>45.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1312">
@@ -37153,7 +37153,7 @@
         <v>1</v>
       </c>
       <c r="F1312" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1313">
@@ -37169,19 +37169,19 @@
       </c>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1313" t="n">
         <v>1</v>
       </c>
       <c r="F1313" t="n">
-        <v>44.5</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1314">
@@ -37197,19 +37197,19 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1314" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1314" t="n">
         <v>0.9</v>
       </c>
       <c r="F1314" t="n">
-        <v>44.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1315">
@@ -37225,19 +37225,19 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1315" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1315" t="n">
         <v>0.9</v>
       </c>
       <c r="F1315" t="n">
-        <v>44.4</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1316">
@@ -37253,19 +37253,19 @@
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1316" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1316" t="n">
         <v>0.9</v>
       </c>
       <c r="F1316" t="n">
-        <v>54.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1317">
@@ -37281,19 +37281,19 @@
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1317" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>48.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1318">
@@ -37321,7 +37321,7 @@
         <v>0.8</v>
       </c>
       <c r="F1318" t="n">
-        <v>49.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1319">
@@ -37337,19 +37337,19 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1319" t="n">
         <v>0.7</v>
       </c>
       <c r="F1319" t="n">
-        <v>48.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1320">
@@ -37365,19 +37365,19 @@
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1320" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1320" t="n">
         <v>0.7</v>
       </c>
       <c r="F1320" t="n">
-        <v>44.7</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1321">
@@ -37393,19 +37393,19 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1321" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F1321" t="n">
-        <v>45.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1322">
@@ -37421,19 +37421,19 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1322" t="n">
         <v>0.6</v>
       </c>
       <c r="F1322" t="n">
-        <v>52.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1323">
@@ -37461,7 +37461,7 @@
         <v>0.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1324">
@@ -37486,10 +37486,10 @@
         </is>
       </c>
       <c r="E1324" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1324" t="n">
-        <v>52.8</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1325">
@@ -37517,7 +37517,7 @@
         <v>0.3</v>
       </c>
       <c r="F1325" t="n">
-        <v>53.8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1326">
@@ -37545,7 +37545,7 @@
         <v>0.3</v>
       </c>
       <c r="F1326" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1327">
@@ -37573,7 +37573,7 @@
         <v>0.3</v>
       </c>
       <c r="F1327" t="n">
-        <v>55.7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1328">
@@ -37598,10 +37598,10 @@
         </is>
       </c>
       <c r="E1328" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F1328" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1329">
@@ -37629,7 +37629,7 @@
         <v>5.2</v>
       </c>
       <c r="F1329" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1330">
@@ -37657,7 +37657,7 @@
         <v>4.4</v>
       </c>
       <c r="F1330" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1331">
@@ -37682,10 +37682,10 @@
         </is>
       </c>
       <c r="E1331" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F1331" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1332">
@@ -37701,19 +37701,19 @@
       </c>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1332" t="n">
         <v>3.8</v>
       </c>
       <c r="F1332" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1333">
@@ -37729,19 +37729,19 @@
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1333" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1333" t="n">
         <v>3.8</v>
       </c>
       <c r="F1333" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1334">
@@ -37769,7 +37769,7 @@
         <v>3.5</v>
       </c>
       <c r="F1334" t="n">
-        <v>52.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1335">
@@ -37797,7 +37797,7 @@
         <v>3.4</v>
       </c>
       <c r="F1335" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1336">
@@ -37825,7 +37825,7 @@
         <v>3.3</v>
       </c>
       <c r="F1336" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1337">
@@ -37850,10 +37850,10 @@
         </is>
       </c>
       <c r="E1337" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1337" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1338">
@@ -37909,7 +37909,7 @@
         <v>2.6</v>
       </c>
       <c r="F1339" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1340">
@@ -37990,10 +37990,10 @@
         </is>
       </c>
       <c r="E1342" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1342" t="n">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1343">
@@ -38021,7 +38021,7 @@
         <v>2.2</v>
       </c>
       <c r="F1343" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1344">
@@ -38049,7 +38049,7 @@
         <v>2.1</v>
       </c>
       <c r="F1344" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1345">
@@ -38065,19 +38065,19 @@
       </c>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1345" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1345" t="n">
         <v>2.1</v>
       </c>
       <c r="F1345" t="n">
-        <v>50.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1346">
@@ -38093,19 +38093,19 @@
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1346" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1346" t="n">
         <v>2.1</v>
       </c>
       <c r="F1346" t="n">
-        <v>53.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1347">
@@ -38121,19 +38121,19 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1347" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1347" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1347" t="n">
-        <v>45.3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1348">
@@ -38186,10 +38186,10 @@
         </is>
       </c>
       <c r="E1349" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1349" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1350">
@@ -38205,19 +38205,19 @@
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1350" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1350" t="n">
         <v>1.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>50.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1351">
@@ -38233,19 +38233,19 @@
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1351" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1351" t="n">
         <v>1.9</v>
       </c>
       <c r="F1351" t="n">
-        <v>52</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1352">
@@ -38273,7 +38273,7 @@
         <v>1.6</v>
       </c>
       <c r="F1352" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1353">
@@ -38301,7 +38301,7 @@
         <v>1.5</v>
       </c>
       <c r="F1353" t="n">
-        <v>46.1</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1354">
@@ -38326,10 +38326,10 @@
         </is>
       </c>
       <c r="E1354" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1354" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1355">
@@ -38354,10 +38354,10 @@
         </is>
       </c>
       <c r="E1355" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1355" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1356">
@@ -38385,7 +38385,7 @@
         <v>1.4</v>
       </c>
       <c r="F1356" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1357">
@@ -38413,7 +38413,7 @@
         <v>1.4</v>
       </c>
       <c r="F1357" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1358">
@@ -38469,7 +38469,7 @@
         <v>1.3</v>
       </c>
       <c r="F1359" t="n">
-        <v>48.2</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1360">
@@ -38497,7 +38497,7 @@
         <v>1.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>44.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1361">
@@ -38525,7 +38525,7 @@
         <v>1.2</v>
       </c>
       <c r="F1361" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1362">
@@ -38553,7 +38553,7 @@
         <v>1.2</v>
       </c>
       <c r="F1362" t="n">
-        <v>51.1</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1363">
@@ -38581,7 +38581,7 @@
         <v>1.1</v>
       </c>
       <c r="F1363" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1364">
@@ -38609,7 +38609,7 @@
         <v>1</v>
       </c>
       <c r="F1364" t="n">
-        <v>49.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1365">
@@ -38625,19 +38625,19 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1365" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1365" t="n">
         <v>1</v>
       </c>
       <c r="F1365" t="n">
-        <v>48.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1366">
@@ -38653,19 +38653,19 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1366" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1366" t="n">
         <v>1</v>
       </c>
       <c r="F1366" t="n">
-        <v>44.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1367">
@@ -38693,7 +38693,7 @@
         <v>0.9</v>
       </c>
       <c r="F1367" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="1368">
@@ -38721,7 +38721,7 @@
         <v>0.9</v>
       </c>
       <c r="F1368" t="n">
-        <v>48.8</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1369">
@@ -38737,19 +38737,19 @@
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1369" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1369" t="n">
-        <v>46</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1370">
@@ -38765,19 +38765,19 @@
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1370" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1370" t="n">
         <v>0.8</v>
       </c>
       <c r="F1370" t="n">
-        <v>49.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1371">
@@ -38805,7 +38805,7 @@
         <v>0.8</v>
       </c>
       <c r="F1371" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1372">
@@ -38833,7 +38833,7 @@
         <v>0.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>54.9</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="1373">
@@ -38861,7 +38861,7 @@
         <v>0.7</v>
       </c>
       <c r="F1373" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1374">
@@ -38889,7 +38889,7 @@
         <v>0.6</v>
       </c>
       <c r="F1374" t="n">
-        <v>46.3</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1375">
@@ -38917,7 +38917,7 @@
         <v>0.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1376">
@@ -38945,7 +38945,7 @@
         <v>0.5</v>
       </c>
       <c r="F1376" t="n">
-        <v>52.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1377">
@@ -38970,10 +38970,10 @@
         </is>
       </c>
       <c r="E1377" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F1377" t="n">
-        <v>52.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1378">
@@ -39001,7 +39001,7 @@
         <v>0.3</v>
       </c>
       <c r="F1378" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1379">
@@ -39026,10 +39026,10 @@
         </is>
       </c>
       <c r="E1379" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F1379" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1380">
@@ -39057,7 +39057,7 @@
         <v>6.2</v>
       </c>
       <c r="F1380" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1381">
@@ -39113,7 +39113,7 @@
         <v>4</v>
       </c>
       <c r="F1382" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1383">
@@ -39138,10 +39138,10 @@
         </is>
       </c>
       <c r="E1383" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F1383" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1384">
@@ -39166,10 +39166,10 @@
         </is>
       </c>
       <c r="E1384" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F1384" t="n">
-        <v>47.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1385">
@@ -39194,10 +39194,10 @@
         </is>
       </c>
       <c r="E1385" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1385" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1386">
@@ -39225,7 +39225,7 @@
         <v>3.3</v>
       </c>
       <c r="F1386" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1387">
@@ -39253,7 +39253,7 @@
         <v>3</v>
       </c>
       <c r="F1387" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1388">
@@ -39281,7 +39281,7 @@
         <v>2.9</v>
       </c>
       <c r="F1388" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1389">
@@ -39309,7 +39309,7 @@
         <v>2.7</v>
       </c>
       <c r="F1389" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1390">
@@ -39337,7 +39337,7 @@
         <v>2.6</v>
       </c>
       <c r="F1390" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1391">
@@ -39365,7 +39365,7 @@
         <v>2.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>46</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1392">
@@ -39390,10 +39390,10 @@
         </is>
       </c>
       <c r="E1392" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1392" t="n">
-        <v>51.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1393">
@@ -39421,7 +39421,7 @@
         <v>2.2</v>
       </c>
       <c r="F1393" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1394">
@@ -39446,10 +39446,10 @@
         </is>
       </c>
       <c r="E1394" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F1394" t="n">
-        <v>45.2</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1395">
@@ -39477,7 +39477,7 @@
         <v>2.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1396">
@@ -39505,7 +39505,7 @@
         <v>2</v>
       </c>
       <c r="F1396" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1397">
@@ -39521,19 +39521,19 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1397" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1397" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1397" t="n">
-        <v>47.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1398">
@@ -39549,19 +39549,19 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1398" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1398" t="n">
         <v>1.9</v>
       </c>
       <c r="F1398" t="n">
-        <v>53</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1399">
@@ -39589,7 +39589,7 @@
         <v>1.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1400">
@@ -39614,10 +39614,10 @@
         </is>
       </c>
       <c r="E1400" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F1400" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1401">
@@ -39633,19 +39633,19 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1401" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1401" t="n">
         <v>1.7</v>
       </c>
       <c r="F1401" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1402">
@@ -39661,19 +39661,19 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1402" t="n">
         <v>1.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>50.2</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1403">
@@ -39729,7 +39729,7 @@
         <v>1.6</v>
       </c>
       <c r="F1404" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1405">
@@ -39785,7 +39785,7 @@
         <v>1.5</v>
       </c>
       <c r="F1406" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1407">
@@ -39813,7 +39813,7 @@
         <v>1.4</v>
       </c>
       <c r="F1407" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1408">
@@ -39841,7 +39841,7 @@
         <v>1.4</v>
       </c>
       <c r="F1408" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1409">
@@ -39857,19 +39857,19 @@
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1409" t="n">
         <v>1.3</v>
       </c>
       <c r="F1409" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1410">
@@ -39885,19 +39885,19 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1410" t="n">
         <v>1.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1411">
@@ -39925,7 +39925,7 @@
         <v>1.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>52.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>1.1</v>
       </c>
       <c r="F1412" t="n">
-        <v>52.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>1.1</v>
       </c>
       <c r="F1413" t="n">
-        <v>48.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1414">
@@ -39997,19 +39997,19 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1414" t="n">
         <v>1.1</v>
       </c>
       <c r="F1414" t="n">
-        <v>48.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="1415">
@@ -40025,19 +40025,19 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1415" t="n">
         <v>1.1</v>
       </c>
       <c r="F1415" t="n">
-        <v>44</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1416">
@@ -40053,19 +40053,19 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1416" t="n">
         <v>1.1</v>
       </c>
       <c r="F1416" t="n">
-        <v>50.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1417">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
@@ -40093,7 +40093,7 @@
         <v>1</v>
       </c>
       <c r="F1417" t="n">
-        <v>46.9</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1418">
@@ -40109,7 +40109,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
@@ -40121,7 +40121,7 @@
         <v>1</v>
       </c>
       <c r="F1418" t="n">
-        <v>52.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1419">
@@ -40149,7 +40149,7 @@
         <v>0.9</v>
       </c>
       <c r="F1419" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1420">
@@ -40177,7 +40177,7 @@
         <v>0.9</v>
       </c>
       <c r="F1420" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1421">
@@ -40205,7 +40205,7 @@
         <v>0.9</v>
       </c>
       <c r="F1421" t="n">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1422">
@@ -40233,7 +40233,7 @@
         <v>0.8</v>
       </c>
       <c r="F1422" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1423">
@@ -40261,7 +40261,7 @@
         <v>0.8</v>
       </c>
       <c r="F1423" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1424">
@@ -40277,19 +40277,19 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1424" t="n">
         <v>0.7</v>
       </c>
       <c r="F1424" t="n">
-        <v>44.7</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1425">
@@ -40305,19 +40305,19 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1425" t="n">
         <v>0.7</v>
       </c>
       <c r="F1425" t="n">
-        <v>51.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1426">
@@ -40345,7 +40345,7 @@
         <v>0.6</v>
       </c>
       <c r="F1426" t="n">
-        <v>48.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1427">
@@ -40373,7 +40373,7 @@
         <v>0.6</v>
       </c>
       <c r="F1427" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1428">
@@ -40401,7 +40401,7 @@
         <v>0.5</v>
       </c>
       <c r="F1428" t="n">
-        <v>50.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1429">
@@ -40429,7 +40429,7 @@
         <v>0.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>50.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1430">
@@ -40445,19 +40445,19 @@
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1430" t="n">
         <v>7.1</v>
       </c>
       <c r="F1430" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1431">
@@ -40473,19 +40473,19 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1431" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F1431" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1432">
@@ -40510,7 +40510,7 @@
         </is>
       </c>
       <c r="E1432" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F1432" t="n">
         <v>47.9</v>
@@ -40541,7 +40541,7 @@
         <v>4.2</v>
       </c>
       <c r="F1433" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1434">
@@ -40566,10 +40566,10 @@
         </is>
       </c>
       <c r="E1434" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1434" t="n">
-        <v>49.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1435">
@@ -40594,10 +40594,10 @@
         </is>
       </c>
       <c r="E1435" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1435" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1436">
@@ -40622,7 +40622,7 @@
         </is>
       </c>
       <c r="E1436" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1436" t="n">
         <v>52.6</v>
@@ -40653,7 +40653,7 @@
         <v>3</v>
       </c>
       <c r="F1437" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1438">
@@ -40681,7 +40681,7 @@
         <v>2.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1439">
@@ -40709,7 +40709,7 @@
         <v>2.6</v>
       </c>
       <c r="F1439" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1440">
@@ -40765,7 +40765,7 @@
         <v>2.5</v>
       </c>
       <c r="F1441" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1442">
@@ -40793,7 +40793,7 @@
         <v>2.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>47.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1443">
@@ -40821,7 +40821,7 @@
         <v>2.4</v>
       </c>
       <c r="F1443" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1444">
@@ -40846,10 +40846,10 @@
         </is>
       </c>
       <c r="E1444" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1444" t="n">
-        <v>50.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1445">
@@ -40865,19 +40865,19 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1445" t="n">
         <v>2.1</v>
       </c>
       <c r="F1445" t="n">
-        <v>50.9</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1446">
@@ -40893,19 +40893,19 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1446" t="n">
         <v>2.1</v>
       </c>
       <c r="F1446" t="n">
-        <v>53.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1447">
@@ -40921,19 +40921,19 @@
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1447" t="n">
         <v>2.1</v>
       </c>
       <c r="F1447" t="n">
-        <v>52.1</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1448">
@@ -40961,7 +40961,7 @@
         <v>2</v>
       </c>
       <c r="F1448" t="n">
-        <v>45.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1449">
@@ -40989,7 +40989,7 @@
         <v>1.9</v>
       </c>
       <c r="F1449" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1450">
@@ -41017,7 +41017,7 @@
         <v>1.8</v>
       </c>
       <c r="F1450" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1451">
@@ -41042,10 +41042,10 @@
         </is>
       </c>
       <c r="E1451" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>47.3</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1452">
@@ -41061,19 +41061,19 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1452" t="n">
         <v>1.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1453">
@@ -41089,19 +41089,19 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1453" t="n">
         <v>1.6</v>
       </c>
       <c r="F1453" t="n">
-        <v>49.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1454">
@@ -41117,19 +41117,19 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1454" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1454" t="n">
-        <v>52.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1455">
@@ -41145,19 +41145,19 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1455" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>48.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1456">
@@ -41185,7 +41185,7 @@
         <v>1.5</v>
       </c>
       <c r="F1456" t="n">
-        <v>41.3</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1457">
@@ -41201,19 +41201,19 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1457" t="n">
         <v>1.4</v>
       </c>
       <c r="F1457" t="n">
-        <v>53.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1458">
@@ -41229,19 +41229,19 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1458" t="n">
         <v>1.4</v>
       </c>
       <c r="F1458" t="n">
-        <v>50.8</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1459">
@@ -41257,19 +41257,19 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1459" t="n">
         <v>1.4</v>
       </c>
       <c r="F1459" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1460">
@@ -41313,19 +41313,19 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1461" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>50.1</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1462">
@@ -41341,7 +41341,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -41350,10 +41350,10 @@
         </is>
       </c>
       <c r="E1462" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1463">
@@ -41369,19 +41369,19 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1463" t="n">
         <v>1.3</v>
       </c>
       <c r="F1463" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1464">
@@ -41397,19 +41397,19 @@
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1464" t="n">
         <v>1.3</v>
       </c>
       <c r="F1464" t="n">
-        <v>50.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1465">
@@ -41425,19 +41425,19 @@
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1465" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>44.9</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1466">
@@ -41453,19 +41453,19 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1466" t="n">
         <v>1.2</v>
       </c>
       <c r="F1466" t="n">
-        <v>53.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1467">
@@ -41493,7 +41493,7 @@
         <v>1.2</v>
       </c>
       <c r="F1467" t="n">
-        <v>51.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1468">
@@ -41521,7 +41521,7 @@
         <v>1.1</v>
       </c>
       <c r="F1468" t="n">
-        <v>51.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1469">
@@ -41537,19 +41537,19 @@
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1469" t="n">
         <v>1</v>
       </c>
       <c r="F1469" t="n">
-        <v>50.3</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1470">
@@ -41565,19 +41565,19 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1470" t="n">
         <v>1</v>
       </c>
       <c r="F1470" t="n">
-        <v>43.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1471">
@@ -41605,7 +41605,7 @@
         <v>0.9</v>
       </c>
       <c r="F1471" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1472">
@@ -41621,19 +41621,19 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1472" t="n">
         <v>0.8</v>
       </c>
       <c r="F1472" t="n">
-        <v>45.9</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1473">
@@ -41649,19 +41649,19 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1473" t="n">
         <v>0.7</v>
       </c>
       <c r="F1473" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1474">
@@ -41677,19 +41677,19 @@
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1474" t="n">
         <v>0.7</v>
       </c>
       <c r="F1474" t="n">
-        <v>49.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1475">
@@ -41717,7 +41717,7 @@
         <v>0.7</v>
       </c>
       <c r="F1475" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1476">
@@ -41745,7 +41745,7 @@
         <v>0.6</v>
       </c>
       <c r="F1476" t="n">
-        <v>44.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1477">
@@ -41773,7 +41773,7 @@
         <v>0.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1478">
@@ -41801,7 +41801,7 @@
         <v>0.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>51.6</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1479">
@@ -41829,7 +41829,7 @@
         <v>0.6</v>
       </c>
       <c r="F1479" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1480">
@@ -41857,7 +41857,7 @@
         <v>0.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>46.2</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1481">
@@ -41882,10 +41882,10 @@
         </is>
       </c>
       <c r="E1481" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="F1481" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1482">
@@ -41910,10 +41910,10 @@
         </is>
       </c>
       <c r="E1482" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1483">
@@ -41938,10 +41938,10 @@
         </is>
       </c>
       <c r="E1483" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F1483" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1484">
@@ -41969,7 +41969,7 @@
         <v>3.9</v>
       </c>
       <c r="F1484" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1485">
@@ -41994,10 +41994,10 @@
         </is>
       </c>
       <c r="E1485" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F1485" t="n">
-        <v>47.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1486">
@@ -42025,7 +42025,7 @@
         <v>3.4</v>
       </c>
       <c r="F1486" t="n">
-        <v>45.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1487">
@@ -42050,10 +42050,10 @@
         </is>
       </c>
       <c r="E1487" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1487" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1488">
@@ -42069,19 +42069,19 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1488" t="n">
         <v>3.1</v>
       </c>
       <c r="F1488" t="n">
-        <v>50.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1489">
@@ -42106,10 +42106,10 @@
         </is>
       </c>
       <c r="E1489" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1490">
@@ -42125,19 +42125,19 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1490" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F1490" t="n">
-        <v>47.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1491">
@@ -42162,10 +42162,10 @@
         </is>
       </c>
       <c r="E1491" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F1491" t="n">
-        <v>52.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1492">
@@ -42190,10 +42190,10 @@
         </is>
       </c>
       <c r="E1492" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1492" t="n">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1493">
@@ -42218,10 +42218,10 @@
         </is>
       </c>
       <c r="E1493" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F1493" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1494">
@@ -42237,19 +42237,19 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1494" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1494" t="n">
-        <v>52.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1495">
@@ -42293,19 +42293,19 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1496" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1496" t="n">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>2.2</v>
       </c>
       <c r="F1497" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1498">
@@ -42358,10 +42358,10 @@
         </is>
       </c>
       <c r="E1498" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F1498" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1499">
@@ -42386,10 +42386,10 @@
         </is>
       </c>
       <c r="E1499" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F1499" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1500">
@@ -42405,19 +42405,19 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1500" t="n">
         <v>1.9</v>
       </c>
       <c r="F1500" t="n">
-        <v>50.7</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="1501">
@@ -42433,19 +42433,19 @@
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1501" t="n">
         <v>1.9</v>
       </c>
       <c r="F1501" t="n">
-        <v>44.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1502">
@@ -42461,19 +42461,19 @@
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1502" t="n">
         <v>1.8</v>
       </c>
       <c r="F1502" t="n">
-        <v>47.8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1503">
@@ -42489,19 +42489,19 @@
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1503" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1503" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1504">
@@ -42517,19 +42517,19 @@
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1504" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1504" t="n">
-        <v>42.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1505">
@@ -42554,10 +42554,10 @@
         </is>
       </c>
       <c r="E1505" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1505" t="n">
-        <v>41.6</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1506">
@@ -42573,19 +42573,19 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1506" t="n">
         <v>1.5</v>
       </c>
       <c r="F1506" t="n">
-        <v>52.1</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1507">
@@ -42610,10 +42610,10 @@
         </is>
       </c>
       <c r="E1507" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1507" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1508">
@@ -42629,19 +42629,19 @@
       </c>
       <c r="C1508" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1508" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1508" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="F1508" t="n">
-        <v>42.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1509">
@@ -42657,19 +42657,19 @@
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1509" t="n">
         <v>1.3</v>
       </c>
       <c r="F1509" t="n">
-        <v>49.8</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1510">
@@ -42685,19 +42685,19 @@
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1510" t="n">
         <v>1.3</v>
       </c>
       <c r="F1510" t="n">
-        <v>48.9</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1511">
@@ -42713,19 +42713,19 @@
       </c>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1511" t="n">
         <v>1.3</v>
       </c>
       <c r="F1511" t="n">
-        <v>48.4</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1512">
@@ -42741,19 +42741,19 @@
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1512" t="n">
         <v>1.3</v>
       </c>
       <c r="F1512" t="n">
-        <v>44.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1513">
@@ -42769,19 +42769,19 @@
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1513" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1513" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1514">
@@ -42809,7 +42809,7 @@
         <v>1.1</v>
       </c>
       <c r="F1514" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1515">
@@ -42825,19 +42825,19 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1515" t="n">
         <v>1.1</v>
       </c>
       <c r="F1515" t="n">
-        <v>42.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1516">
@@ -42853,19 +42853,19 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1516" t="n">
         <v>1.1</v>
       </c>
       <c r="F1516" t="n">
-        <v>51.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1517" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1517" t="n">
-        <v>49.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1518">
@@ -42921,7 +42921,7 @@
         <v>1</v>
       </c>
       <c r="F1518" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>1</v>
       </c>
       <c r="F1519" t="n">
-        <v>52.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>0.9</v>
       </c>
       <c r="F1520" t="n">
-        <v>46.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1521">
@@ -43002,10 +43002,10 @@
         </is>
       </c>
       <c r="E1521" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1521" t="n">
-        <v>52.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1522">
@@ -43030,10 +43030,10 @@
         </is>
       </c>
       <c r="E1522" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1522" t="n">
-        <v>46.1</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1523">
@@ -43049,19 +43049,19 @@
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1523" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1523" t="n">
-        <v>43.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1524">
@@ -43077,19 +43077,19 @@
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1524" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1524" t="n">
-        <v>53.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1525">
@@ -43105,19 +43105,19 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1525" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1525" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1526">
@@ -43133,19 +43133,19 @@
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1526" t="n">
         <v>0.5</v>
       </c>
       <c r="F1526" t="n">
-        <v>51.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1527">
@@ -43161,19 +43161,19 @@
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1527" t="n">
         <v>0.5</v>
       </c>
       <c r="F1527" t="n">
-        <v>45.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1528">
@@ -43201,7 +43201,7 @@
         <v>0.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>40.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1529">
@@ -43229,7 +43229,7 @@
         <v>0.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>40.7</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1530">
@@ -43245,19 +43245,19 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1530" t="n">
         <v>0.3</v>
       </c>
       <c r="F1530" t="n">
-        <v>37.6</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1531">
@@ -43273,19 +43273,19 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1531" t="n">
         <v>0.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>43.8</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="1532">
@@ -43313,7 +43313,7 @@
         <v>6.7</v>
       </c>
       <c r="F1532" t="n">
-        <v>46.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1533">
@@ -43329,19 +43329,19 @@
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1533" t="n">
         <v>6.1</v>
       </c>
       <c r="F1533" t="n">
-        <v>49.3</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1534">
@@ -43357,19 +43357,19 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1534" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="F1534" t="n">
-        <v>43</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1535">
@@ -43385,19 +43385,19 @@
       </c>
       <c r="C1535" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1535" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F1535" t="n">
-        <v>46</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1536">
@@ -43422,10 +43422,10 @@
         </is>
       </c>
       <c r="E1536" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F1536" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1537">
@@ -43441,19 +43441,19 @@
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1537" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F1537" t="n">
-        <v>48.8</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1538">
@@ -43469,19 +43469,19 @@
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1538" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="F1538" t="n">
-        <v>41.9</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="1539">
@@ -43497,19 +43497,19 @@
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1539" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F1539" t="n">
-        <v>76.2</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="1540">
@@ -43525,19 +43525,19 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1540" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="F1540" t="n">
-        <v>55.4</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="1541">
@@ -43562,10 +43562,10 @@
         </is>
       </c>
       <c r="E1541" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="F1541" t="n">
-        <v>42.4</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1542">
@@ -43590,10 +43590,10 @@
         </is>
       </c>
       <c r="E1542" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1542" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1543">
@@ -43609,19 +43609,19 @@
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1543" t="n">
         <v>3</v>
       </c>
       <c r="F1543" t="n">
-        <v>41.6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1544">
@@ -43637,19 +43637,19 @@
       </c>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1544" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F1544" t="n">
-        <v>50.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1545">
@@ -43665,19 +43665,19 @@
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1545" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1545" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1546">
@@ -43693,19 +43693,19 @@
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1546" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1546" t="n">
-        <v>43.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1547">
@@ -43721,19 +43721,19 @@
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1547" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1547" t="n">
-        <v>55.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1548">
@@ -43761,7 +43761,7 @@
         <v>2.2</v>
       </c>
       <c r="F1548" t="n">
-        <v>28.5</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="1549">
@@ -43777,19 +43777,19 @@
       </c>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1549" t="n">
         <v>2.1</v>
       </c>
       <c r="F1549" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1550">
@@ -43814,10 +43814,10 @@
         </is>
       </c>
       <c r="E1550" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F1550" t="n">
-        <v>59.8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1551">
@@ -43833,19 +43833,19 @@
       </c>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1551" t="n">
         <v>1.8</v>
       </c>
       <c r="F1551" t="n">
-        <v>38.5</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="1552">
@@ -43861,19 +43861,19 @@
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1552" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1552" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1553">
@@ -43889,19 +43889,19 @@
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1553" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1553" t="n">
-        <v>32.1</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="1554">
@@ -43926,10 +43926,10 @@
         </is>
       </c>
       <c r="E1554" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1554" t="n">
-        <v>44.4</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1555">
@@ -43945,19 +43945,19 @@
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1555" t="n">
         <v>1.6</v>
       </c>
       <c r="F1555" t="n">
-        <v>41.4</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1556">
@@ -43973,19 +43973,19 @@
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1556" t="n">
-        <v>53.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1557">
@@ -44001,19 +44001,19 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1557" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F1557" t="n">
-        <v>32.7</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="1558">
@@ -44029,19 +44029,19 @@
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1558" t="n">
         <v>1.4</v>
       </c>
       <c r="F1558" t="n">
-        <v>54.7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1559">
@@ -44057,19 +44057,19 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1559" t="n">
         <v>1.4</v>
       </c>
       <c r="F1559" t="n">
-        <v>41.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1560">
@@ -44085,19 +44085,19 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F1560" t="n">
-        <v>49.3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1561">
@@ -44113,19 +44113,19 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1561" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1561" t="n">
-        <v>41.3</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="1562">
@@ -44150,10 +44150,10 @@
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F1562" t="n">
-        <v>41.2</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1563" t="n">
-        <v>47.1</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1564">
@@ -44209,7 +44209,7 @@
         <v>0.9</v>
       </c>
       <c r="F1564" t="n">
-        <v>54.4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1565">
@@ -44225,19 +44225,19 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1565" t="n">
-        <v>62.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1566">
@@ -44253,19 +44253,19 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1566" t="n">
         <v>0.8</v>
       </c>
       <c r="F1566" t="n">
-        <v>17.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1567">
@@ -44281,19 +44281,19 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1567" t="n">
         <v>0.8</v>
       </c>
       <c r="F1567" t="n">
-        <v>37.8</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="1568">
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1568" t="n">
         <v>0.8</v>
       </c>
       <c r="F1568" t="n">
-        <v>62.6</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="1569">
@@ -44337,19 +44337,19 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1569" t="n">
         <v>0.7</v>
       </c>
       <c r="F1569" t="n">
-        <v>82.40000000000001</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="1570">
@@ -44377,7 +44377,7 @@
         <v>0.7</v>
       </c>
       <c r="F1570" t="n">
-        <v>95.7</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1571" t="n">
         <v>0.6</v>
       </c>
       <c r="F1571" t="n">
-        <v>29.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,19 +44421,19 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1572" t="n">
         <v>0.6</v>
       </c>
       <c r="F1572" t="n">
-        <v>43.8</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="1573">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1573" t="n">
         <v>0.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>64.90000000000001</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1574" t="n">
         <v>0.5</v>
       </c>
       <c r="F1574" t="n">
-        <v>25.8</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="1575">
@@ -44514,10 +44514,10 @@
         </is>
       </c>
       <c r="E1575" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1575" t="n">
-        <v>2.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="1576">
@@ -44542,10 +44542,10 @@
         </is>
       </c>
       <c r="E1576" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1576" t="n">
-        <v>35</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="1577">
@@ -44561,19 +44561,19 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1577" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F1577" t="n">
-        <v>19.3</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="1578">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
@@ -44598,10 +44598,10 @@
         </is>
       </c>
       <c r="E1578" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F1578" t="n">
-        <v>46.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1579">
@@ -44617,19 +44617,19 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1579" t="n">
         <v>0.2</v>
       </c>
       <c r="F1579" t="n">
-        <v>65.59999999999999</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1580">
@@ -44645,19 +44645,19 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1580" t="n">
         <v>0.2</v>
       </c>
       <c r="F1580" t="n">
-        <v>51</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="1581">
@@ -44682,7 +44682,7 @@
         </is>
       </c>
       <c r="E1581" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F1581" t="n">
         <v>0</v>
@@ -44696,24 +44696,24 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>GRANDMASTER</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1582" t="n">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="F1582" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1583">
@@ -44729,19 +44729,19 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>18.5</v>
+        <v>21.9</v>
       </c>
       <c r="F1583" t="n">
-        <v>18.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1584">
@@ -44766,10 +44766,10 @@
         </is>
       </c>
       <c r="E1584" t="n">
-        <v>15.1</v>
+        <v>17.9</v>
       </c>
       <c r="F1584" t="n">
-        <v>50</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1585">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
@@ -44794,10 +44794,10 @@
         </is>
       </c>
       <c r="E1585" t="n">
-        <v>9.199999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="F1585" t="n">
-        <v>72.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="1586">
@@ -44813,19 +44813,19 @@
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1586" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="F1586" t="n">
-        <v>85.7</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="1587">
@@ -44850,10 +44850,10 @@
         </is>
       </c>
       <c r="E1587" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="F1587" t="n">
-        <v>60</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="1588">
@@ -44869,19 +44869,19 @@
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1588" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="F1588" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="1589">
@@ -44897,19 +44897,19 @@
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1589" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="F1589" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1590">
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="E1590" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1590" t="n">
         <v>100</v>
@@ -44953,19 +44953,19 @@
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1591" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="F1591" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1592">
@@ -44981,19 +44981,19 @@
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1592" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1592" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1593">
@@ -45009,7 +45009,7 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1593" t="inlineStr">
@@ -45018,10 +45018,10 @@
         </is>
       </c>
       <c r="E1593" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F1593" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1594">
@@ -45037,19 +45037,19 @@
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1594" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F1594" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1595">
@@ -45065,16 +45065,16 @@
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1595" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="F1595" t="n">
         <v>0</v>
@@ -45093,19 +45093,19 @@
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1596" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="F1596" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1597">
@@ -45121,19 +45121,19 @@
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1597" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="F1597" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1598">
@@ -45149,19 +45149,19 @@
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1598" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F1598" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1599">
@@ -45177,18 +45177,102 @@
       </c>
       <c r="C1599" t="inlineStr">
         <is>
+          <t>엠레</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>공격 · 전문가</t>
+        </is>
+      </c>
+      <c r="E1599" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>한조</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1600" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Soldier: 76</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>공격 · 전문가</t>
+        </is>
+      </c>
+      <c r="E1601" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
           <t>소전</t>
         </is>
       </c>
-      <c r="D1599" t="inlineStr">
+      <c r="D1602" t="inlineStr">
         <is>
           <t>공격 · 명사수</t>
         </is>
       </c>
-      <c r="E1599" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F1599" t="n">
+      <c r="E1602" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1602" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1607"/>
+  <dimension ref="A1:F1608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34829,7 +34829,7 @@
         <v>3.8</v>
       </c>
       <c r="F1229" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1230">
@@ -34885,7 +34885,7 @@
         <v>3.6</v>
       </c>
       <c r="F1231" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1232">
@@ -34913,7 +34913,7 @@
         <v>3.2</v>
       </c>
       <c r="F1232" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1233">
@@ -34941,7 +34941,7 @@
         <v>3.2</v>
       </c>
       <c r="F1233" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1234">
@@ -35025,7 +35025,7 @@
         <v>2.7</v>
       </c>
       <c r="F1236" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1237">
@@ -35109,7 +35109,7 @@
         <v>2.3</v>
       </c>
       <c r="F1239" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1240">
@@ -35165,7 +35165,7 @@
         <v>2.2</v>
       </c>
       <c r="F1241" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1242">
@@ -35249,7 +35249,7 @@
         <v>2.1</v>
       </c>
       <c r="F1244" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1245">
@@ -35305,7 +35305,7 @@
         <v>1.9</v>
       </c>
       <c r="F1246" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1247">
@@ -35361,7 +35361,7 @@
         <v>1.9</v>
       </c>
       <c r="F1248" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1249">
@@ -35389,7 +35389,7 @@
         <v>1.7</v>
       </c>
       <c r="F1249" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1250">
@@ -35417,7 +35417,7 @@
         <v>1.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1251">
@@ -35442,7 +35442,7 @@
         </is>
       </c>
       <c r="E1251" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1251" t="n">
         <v>44.8</v>
@@ -35473,7 +35473,7 @@
         <v>1.5</v>
       </c>
       <c r="F1252" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1253">
@@ -35501,7 +35501,7 @@
         <v>1.4</v>
       </c>
       <c r="F1253" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1254">
@@ -35529,7 +35529,7 @@
         <v>1.4</v>
       </c>
       <c r="F1254" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1255">
@@ -35557,7 +35557,7 @@
         <v>1.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1256">
@@ -35585,7 +35585,7 @@
         <v>1.4</v>
       </c>
       <c r="F1256" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1257">
@@ -35601,19 +35601,19 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1257" t="n">
         <v>1.2</v>
       </c>
       <c r="F1257" t="n">
-        <v>48.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1258">
@@ -35629,19 +35629,19 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1258" t="n">
         <v>1.2</v>
       </c>
       <c r="F1258" t="n">
-        <v>52.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1259">
@@ -35657,19 +35657,19 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1259" t="n">
         <v>1.2</v>
       </c>
       <c r="F1259" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1260">
@@ -35697,7 +35697,7 @@
         <v>1.2</v>
       </c>
       <c r="F1260" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1261">
@@ -35722,7 +35722,7 @@
         </is>
       </c>
       <c r="E1261" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1261" t="n">
         <v>49.4</v>
@@ -35781,7 +35781,7 @@
         <v>1.1</v>
       </c>
       <c r="F1263" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1264">
@@ -35809,7 +35809,7 @@
         <v>1</v>
       </c>
       <c r="F1264" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1265">
@@ -35865,7 +35865,7 @@
         <v>1</v>
       </c>
       <c r="F1266" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1267">
@@ -35921,7 +35921,7 @@
         <v>1</v>
       </c>
       <c r="F1268" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1269">
@@ -36033,7 +36033,7 @@
         <v>0.7</v>
       </c>
       <c r="F1272" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1273">
@@ -36061,7 +36061,7 @@
         <v>0.6</v>
       </c>
       <c r="F1273" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1274">
@@ -36114,10 +36114,10 @@
         </is>
       </c>
       <c r="E1275" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1275" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1276">
@@ -36145,7 +36145,7 @@
         <v>0.4</v>
       </c>
       <c r="F1276" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1277">
@@ -36173,7 +36173,7 @@
         <v>7.5</v>
       </c>
       <c r="F1277" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1278">
@@ -36198,10 +36198,10 @@
         </is>
       </c>
       <c r="E1278" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F1278" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1279">
@@ -36226,10 +36226,10 @@
         </is>
       </c>
       <c r="E1279" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F1279" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1280">
@@ -36257,7 +36257,7 @@
         <v>4.3</v>
       </c>
       <c r="F1280" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1281">
@@ -36285,7 +36285,7 @@
         <v>4.2</v>
       </c>
       <c r="F1281" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1282">
@@ -36310,10 +36310,10 @@
         </is>
       </c>
       <c r="E1282" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1282" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1283">
@@ -36341,7 +36341,7 @@
         <v>3.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1284">
@@ -36366,10 +36366,10 @@
         </is>
       </c>
       <c r="E1284" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1284" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1285">
@@ -36385,19 +36385,19 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1285" t="n">
         <v>3.1</v>
       </c>
       <c r="F1285" t="n">
-        <v>51.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1286">
@@ -36413,19 +36413,19 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1286" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1286" t="n">
         <v>3.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>49.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1287">
@@ -36453,7 +36453,7 @@
         <v>3</v>
       </c>
       <c r="F1287" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1288">
@@ -36481,7 +36481,7 @@
         <v>3</v>
       </c>
       <c r="F1288" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1289">
@@ -36506,10 +36506,10 @@
         </is>
       </c>
       <c r="E1289" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F1289" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1290">
@@ -36537,7 +36537,7 @@
         <v>2.6</v>
       </c>
       <c r="F1290" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1291">
@@ -36593,7 +36593,7 @@
         <v>2.3</v>
       </c>
       <c r="F1292" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1293">
@@ -36621,7 +36621,7 @@
         <v>2.3</v>
       </c>
       <c r="F1293" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1294">
@@ -36674,10 +36674,10 @@
         </is>
       </c>
       <c r="E1295" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F1295" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1296">
@@ -36705,7 +36705,7 @@
         <v>2.1</v>
       </c>
       <c r="F1296" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1297">
@@ -36733,7 +36733,7 @@
         <v>2</v>
       </c>
       <c r="F1297" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1298">
@@ -36761,7 +36761,7 @@
         <v>1.9</v>
       </c>
       <c r="F1298" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1299">
@@ -36789,7 +36789,7 @@
         <v>1.8</v>
       </c>
       <c r="F1299" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1300">
@@ -36814,10 +36814,10 @@
         </is>
       </c>
       <c r="E1300" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>46.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1301">
@@ -36873,7 +36873,7 @@
         <v>1.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1303">
@@ -36901,7 +36901,7 @@
         <v>1.6</v>
       </c>
       <c r="F1303" t="n">
-        <v>47.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1304">
@@ -36917,19 +36917,19 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1304" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1304" t="n">
         <v>1.5</v>
       </c>
       <c r="F1304" t="n">
-        <v>47.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1305">
@@ -36945,19 +36945,19 @@
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1305" t="n">
         <v>1.5</v>
       </c>
       <c r="F1305" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1306">
@@ -36985,7 +36985,7 @@
         <v>1.4</v>
       </c>
       <c r="F1306" t="n">
-        <v>47.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1307">
@@ -37013,7 +37013,7 @@
         <v>1.3</v>
       </c>
       <c r="F1307" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1308">
@@ -37041,7 +37041,7 @@
         <v>1.3</v>
       </c>
       <c r="F1308" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1309">
@@ -37069,7 +37069,7 @@
         <v>1.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1310">
@@ -37097,7 +37097,7 @@
         <v>1.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1311">
@@ -37125,7 +37125,7 @@
         <v>1.1</v>
       </c>
       <c r="F1311" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1312">
@@ -37153,7 +37153,7 @@
         <v>1</v>
       </c>
       <c r="F1312" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1313">
@@ -37181,7 +37181,7 @@
         <v>1</v>
       </c>
       <c r="F1313" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1314">
@@ -37209,7 +37209,7 @@
         <v>0.9</v>
       </c>
       <c r="F1314" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1315">
@@ -37237,7 +37237,7 @@
         <v>0.9</v>
       </c>
       <c r="F1315" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1316">
@@ -37265,7 +37265,7 @@
         <v>0.9</v>
       </c>
       <c r="F1316" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1317">
@@ -37293,7 +37293,7 @@
         <v>0.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1318">
@@ -37321,7 +37321,7 @@
         <v>0.9</v>
       </c>
       <c r="F1318" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1319">
@@ -37377,7 +37377,7 @@
         <v>0.7</v>
       </c>
       <c r="F1320" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1321">
@@ -37405,7 +37405,7 @@
         <v>0.7</v>
       </c>
       <c r="F1321" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1322">
@@ -37433,7 +37433,7 @@
         <v>0.6</v>
       </c>
       <c r="F1322" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1323">
@@ -37461,7 +37461,7 @@
         <v>0.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1324">
@@ -37489,7 +37489,7 @@
         <v>0.5</v>
       </c>
       <c r="F1324" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="1325">
@@ -37545,7 +37545,7 @@
         <v>0.3</v>
       </c>
       <c r="F1326" t="n">
-        <v>53.2</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1327">
@@ -37573,7 +37573,7 @@
         <v>0.3</v>
       </c>
       <c r="F1327" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1328">
@@ -37601,7 +37601,7 @@
         <v>7</v>
       </c>
       <c r="F1328" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1329">
@@ -37654,7 +37654,7 @@
         </is>
       </c>
       <c r="E1330" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1330" t="n">
         <v>48</v>
@@ -37685,7 +37685,7 @@
         <v>4.2</v>
       </c>
       <c r="F1331" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1332">
@@ -37710,7 +37710,7 @@
         </is>
       </c>
       <c r="E1332" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F1332" t="n">
         <v>49.1</v>
@@ -37769,7 +37769,7 @@
         <v>3.4</v>
       </c>
       <c r="F1334" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1335">
@@ -37825,7 +37825,7 @@
         <v>3.3</v>
       </c>
       <c r="F1336" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1337">
@@ -37853,7 +37853,7 @@
         <v>3.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1338">
@@ -37881,7 +37881,7 @@
         <v>2.6</v>
       </c>
       <c r="F1338" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1339">
@@ -37909,7 +37909,7 @@
         <v>2.6</v>
       </c>
       <c r="F1339" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1340">
@@ -37965,7 +37965,7 @@
         <v>2.5</v>
       </c>
       <c r="F1341" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1342">
@@ -37993,7 +37993,7 @@
         <v>2.3</v>
       </c>
       <c r="F1342" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1343">
@@ -38049,7 +38049,7 @@
         <v>2.1</v>
       </c>
       <c r="F1344" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1345">
@@ -38105,7 +38105,7 @@
         <v>2.1</v>
       </c>
       <c r="F1346" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1347">
@@ -38133,7 +38133,7 @@
         <v>2.1</v>
       </c>
       <c r="F1347" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1348">
@@ -38189,7 +38189,7 @@
         <v>1.9</v>
       </c>
       <c r="F1349" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1350">
@@ -38273,7 +38273,7 @@
         <v>1.7</v>
       </c>
       <c r="F1352" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1353">
@@ -38301,7 +38301,7 @@
         <v>1.6</v>
       </c>
       <c r="F1353" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1354">
@@ -38329,7 +38329,7 @@
         <v>1.5</v>
       </c>
       <c r="F1354" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1355">
@@ -38354,7 +38354,7 @@
         </is>
       </c>
       <c r="E1355" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1355" t="n">
         <v>45</v>
@@ -38385,7 +38385,7 @@
         <v>1.4</v>
       </c>
       <c r="F1356" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1357">
@@ -38410,10 +38410,10 @@
         </is>
       </c>
       <c r="E1357" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1357" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1358">
@@ -38441,7 +38441,7 @@
         <v>1.3</v>
       </c>
       <c r="F1358" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1359">
@@ -38469,7 +38469,7 @@
         <v>1.3</v>
       </c>
       <c r="F1359" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1360">
@@ -38497,7 +38497,7 @@
         <v>1.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1361">
@@ -38553,7 +38553,7 @@
         <v>1.2</v>
       </c>
       <c r="F1362" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1363">
@@ -38581,7 +38581,7 @@
         <v>1.1</v>
       </c>
       <c r="F1363" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1364">
@@ -38609,7 +38609,7 @@
         <v>1</v>
       </c>
       <c r="F1364" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1365">
@@ -38637,7 +38637,7 @@
         <v>1</v>
       </c>
       <c r="F1365" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1366">
@@ -38665,7 +38665,7 @@
         <v>1</v>
       </c>
       <c r="F1366" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1367">
@@ -38693,7 +38693,7 @@
         <v>0.9</v>
       </c>
       <c r="F1367" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="1368">
@@ -38721,7 +38721,7 @@
         <v>0.9</v>
       </c>
       <c r="F1368" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1369">
@@ -38777,7 +38777,7 @@
         <v>0.8</v>
       </c>
       <c r="F1370" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1371">
@@ -38805,7 +38805,7 @@
         <v>0.8</v>
       </c>
       <c r="F1371" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1372">
@@ -38833,7 +38833,7 @@
         <v>0.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>53.6</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1373">
@@ -38861,7 +38861,7 @@
         <v>0.7</v>
       </c>
       <c r="F1373" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1374">
@@ -38917,7 +38917,7 @@
         <v>0.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1376">
@@ -38973,7 +38973,7 @@
         <v>0.4</v>
       </c>
       <c r="F1377" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1378">
@@ -39001,7 +39001,7 @@
         <v>0.4</v>
       </c>
       <c r="F1378" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1379">
@@ -39054,7 +39054,7 @@
         </is>
       </c>
       <c r="E1380" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F1380" t="n">
         <v>48.9</v>
@@ -39113,7 +39113,7 @@
         <v>3.9</v>
       </c>
       <c r="F1382" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1383">
@@ -39129,19 +39129,19 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1383" t="n">
         <v>3.8</v>
       </c>
       <c r="F1383" t="n">
-        <v>50.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1384">
@@ -39157,19 +39157,19 @@
       </c>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1384" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1384" t="n">
         <v>3.8</v>
       </c>
       <c r="F1384" t="n">
-        <v>48.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1385">
@@ -39253,7 +39253,7 @@
         <v>2.9</v>
       </c>
       <c r="F1387" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1388">
@@ -39309,7 +39309,7 @@
         <v>2.6</v>
       </c>
       <c r="F1389" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1390">
@@ -39365,7 +39365,7 @@
         <v>2.6</v>
       </c>
       <c r="F1391" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1392">
@@ -39393,7 +39393,7 @@
         <v>2.2</v>
       </c>
       <c r="F1392" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1393">
@@ -39421,7 +39421,7 @@
         <v>2.1</v>
       </c>
       <c r="F1393" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1394">
@@ -39449,7 +39449,7 @@
         <v>2.1</v>
       </c>
       <c r="F1394" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1395">
@@ -39477,7 +39477,7 @@
         <v>2.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1396">
@@ -39505,7 +39505,7 @@
         <v>2.1</v>
       </c>
       <c r="F1396" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1397">
@@ -39533,7 +39533,7 @@
         <v>2</v>
       </c>
       <c r="F1397" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1398">
@@ -39549,19 +39549,19 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1398" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1398" t="n">
         <v>1.9</v>
       </c>
       <c r="F1398" t="n">
-        <v>47.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1399">
@@ -39577,19 +39577,19 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1399" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1399" t="n">
         <v>1.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>50.6</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1400">
@@ -39617,7 +39617,7 @@
         <v>1.9</v>
       </c>
       <c r="F1400" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1401">
@@ -39645,7 +39645,7 @@
         <v>1.8</v>
       </c>
       <c r="F1401" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1402">
@@ -39673,7 +39673,7 @@
         <v>1.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1403">
@@ -39701,7 +39701,7 @@
         <v>1.6</v>
       </c>
       <c r="F1403" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1404">
@@ -39729,7 +39729,7 @@
         <v>1.6</v>
       </c>
       <c r="F1404" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1405">
@@ -39757,7 +39757,7 @@
         <v>1.5</v>
       </c>
       <c r="F1405" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1406">
@@ -39785,7 +39785,7 @@
         <v>1.5</v>
       </c>
       <c r="F1406" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1407">
@@ -39841,7 +39841,7 @@
         <v>1.4</v>
       </c>
       <c r="F1408" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1409">
@@ -39869,7 +39869,7 @@
         <v>1.4</v>
       </c>
       <c r="F1409" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1410">
@@ -39897,7 +39897,7 @@
         <v>1.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1411">
@@ -39925,7 +39925,7 @@
         <v>1.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>1.2</v>
       </c>
       <c r="F1412" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>1.1</v>
       </c>
       <c r="F1413" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1414">
@@ -40093,7 +40093,7 @@
         <v>1.1</v>
       </c>
       <c r="F1417" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1418">
@@ -40121,7 +40121,7 @@
         <v>1</v>
       </c>
       <c r="F1418" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1419">
@@ -40177,7 +40177,7 @@
         <v>0.9</v>
       </c>
       <c r="F1420" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1421">
@@ -40205,7 +40205,7 @@
         <v>0.9</v>
       </c>
       <c r="F1421" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1422">
@@ -40230,10 +40230,10 @@
         </is>
       </c>
       <c r="E1422" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1422" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1423">
@@ -40261,7 +40261,7 @@
         <v>0.8</v>
       </c>
       <c r="F1423" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1424">
@@ -40289,7 +40289,7 @@
         <v>0.7</v>
       </c>
       <c r="F1424" t="n">
-        <v>52.6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1425">
@@ -40317,7 +40317,7 @@
         <v>0.7</v>
       </c>
       <c r="F1425" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1426">
@@ -40345,7 +40345,7 @@
         <v>0.6</v>
       </c>
       <c r="F1426" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1427">
@@ -40401,7 +40401,7 @@
         <v>0.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1429">
@@ -40429,7 +40429,7 @@
         <v>0.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1430">
@@ -40485,7 +40485,7 @@
         <v>7.1</v>
       </c>
       <c r="F1431" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1432">
@@ -40541,7 +40541,7 @@
         <v>4.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1434">
@@ -40569,7 +40569,7 @@
         <v>3.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1435">
@@ -40597,7 +40597,7 @@
         <v>3.1</v>
       </c>
       <c r="F1435" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1436">
@@ -40625,7 +40625,7 @@
         <v>3</v>
       </c>
       <c r="F1436" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1437">
@@ -40653,7 +40653,7 @@
         <v>3</v>
       </c>
       <c r="F1437" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1438">
@@ -40681,7 +40681,7 @@
         <v>2.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1439">
@@ -40709,7 +40709,7 @@
         <v>2.6</v>
       </c>
       <c r="F1439" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1440">
@@ -40725,7 +40725,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1440" t="inlineStr">
@@ -40737,7 +40737,7 @@
         <v>2.6</v>
       </c>
       <c r="F1440" t="n">
-        <v>48.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1441">
@@ -40753,7 +40753,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
@@ -40765,7 +40765,7 @@
         <v>2.5</v>
       </c>
       <c r="F1441" t="n">
-        <v>50.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1442">
@@ -40793,7 +40793,7 @@
         <v>2.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1443">
@@ -40821,7 +40821,7 @@
         <v>2.4</v>
       </c>
       <c r="F1443" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1444">
@@ -40849,7 +40849,7 @@
         <v>2.2</v>
       </c>
       <c r="F1444" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1445">
@@ -40877,7 +40877,7 @@
         <v>2.1</v>
       </c>
       <c r="F1445" t="n">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1446">
@@ -40905,7 +40905,7 @@
         <v>2.1</v>
       </c>
       <c r="F1446" t="n">
-        <v>49.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1447">
@@ -40933,7 +40933,7 @@
         <v>2</v>
       </c>
       <c r="F1447" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1448">
@@ -40961,7 +40961,7 @@
         <v>2</v>
       </c>
       <c r="F1448" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1449">
@@ -41017,7 +41017,7 @@
         <v>1.7</v>
       </c>
       <c r="F1450" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1451">
@@ -41045,7 +41045,7 @@
         <v>1.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1452">
@@ -41073,7 +41073,7 @@
         <v>1.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1453">
@@ -41101,7 +41101,7 @@
         <v>1.6</v>
       </c>
       <c r="F1453" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1454">
@@ -41129,7 +41129,7 @@
         <v>1.5</v>
       </c>
       <c r="F1454" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1455">
@@ -41157,7 +41157,7 @@
         <v>1.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1456">
@@ -41185,7 +41185,7 @@
         <v>1.5</v>
       </c>
       <c r="F1456" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1457">
@@ -41201,19 +41201,19 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1457" t="n">
         <v>1.4</v>
       </c>
       <c r="F1457" t="n">
-        <v>40.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="1458">
@@ -41229,19 +41229,19 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1458" t="n">
         <v>1.4</v>
       </c>
       <c r="F1458" t="n">
-        <v>54</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1459">
@@ -41285,19 +41285,19 @@
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1460" t="n">
         <v>1.4</v>
       </c>
       <c r="F1460" t="n">
-        <v>50.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1461">
@@ -41313,19 +41313,19 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1461" t="n">
         <v>1.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1462">
@@ -41341,19 +41341,19 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1462" t="n">
         <v>1.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>53.3</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1463">
@@ -41369,19 +41369,19 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1463" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1463" t="n">
-        <v>53.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1464">
@@ -41397,19 +41397,19 @@
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1464" t="n">
         <v>1.3</v>
       </c>
       <c r="F1464" t="n">
-        <v>49.4</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1465">
@@ -41465,7 +41465,7 @@
         <v>1.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>48.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1467">
@@ -41493,7 +41493,7 @@
         <v>1.3</v>
       </c>
       <c r="F1467" t="n">
-        <v>45</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1468">
@@ -41521,7 +41521,7 @@
         <v>1.1</v>
       </c>
       <c r="F1468" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1469">
@@ -41546,10 +41546,10 @@
         </is>
       </c>
       <c r="E1469" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1469" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1470">
@@ -41577,7 +41577,7 @@
         <v>1</v>
       </c>
       <c r="F1470" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1471">
@@ -41605,7 +41605,7 @@
         <v>0.8</v>
       </c>
       <c r="F1471" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1472">
@@ -41633,7 +41633,7 @@
         <v>0.8</v>
       </c>
       <c r="F1472" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1473">
@@ -41661,7 +41661,7 @@
         <v>0.7</v>
       </c>
       <c r="F1473" t="n">
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1474">
@@ -41689,7 +41689,7 @@
         <v>0.7</v>
       </c>
       <c r="F1474" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1475">
@@ -41717,7 +41717,7 @@
         <v>0.7</v>
       </c>
       <c r="F1475" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1476">
@@ -41745,7 +41745,7 @@
         <v>0.6</v>
       </c>
       <c r="F1476" t="n">
-        <v>44</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1477">
@@ -41773,7 +41773,7 @@
         <v>0.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1478">
@@ -41801,7 +41801,7 @@
         <v>0.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1479">
@@ -41829,7 +41829,7 @@
         <v>0.6</v>
       </c>
       <c r="F1479" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1480">
@@ -41857,7 +41857,7 @@
         <v>0.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>43.6</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1481">
@@ -41910,10 +41910,10 @@
         </is>
       </c>
       <c r="E1482" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F1482" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1483">
@@ -41941,7 +41941,7 @@
         <v>6.3</v>
       </c>
       <c r="F1483" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1484">
@@ -41966,10 +41966,10 @@
         </is>
       </c>
       <c r="E1484" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F1484" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1485">
@@ -41994,7 +41994,7 @@
         </is>
       </c>
       <c r="E1485" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F1485" t="n">
         <v>49.8</v>
@@ -42025,7 +42025,7 @@
         <v>3.4</v>
       </c>
       <c r="F1486" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1487">
@@ -42053,7 +42053,7 @@
         <v>3.3</v>
       </c>
       <c r="F1487" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1488">
@@ -42081,7 +42081,7 @@
         <v>3.3</v>
       </c>
       <c r="F1488" t="n">
-        <v>46.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1489">
@@ -42109,7 +42109,7 @@
         <v>3.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1490">
@@ -42125,19 +42125,19 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1490" t="n">
         <v>2.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>52.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1491">
@@ -42153,19 +42153,19 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1491" t="n">
         <v>2.7</v>
       </c>
       <c r="F1491" t="n">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1492">
@@ -42193,7 +42193,7 @@
         <v>2.5</v>
       </c>
       <c r="F1492" t="n">
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1493">
@@ -42221,7 +42221,7 @@
         <v>2.4</v>
       </c>
       <c r="F1493" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1494">
@@ -42246,10 +42246,10 @@
         </is>
       </c>
       <c r="E1494" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1494" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1495">
@@ -42274,10 +42274,10 @@
         </is>
       </c>
       <c r="E1495" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1495" t="n">
-        <v>47.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1496">
@@ -42305,7 +42305,7 @@
         <v>2.2</v>
       </c>
       <c r="F1496" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1497">
@@ -42333,7 +42333,7 @@
         <v>2.1</v>
       </c>
       <c r="F1497" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>2</v>
       </c>
       <c r="F1498" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1499">
@@ -42389,7 +42389,7 @@
         <v>2</v>
       </c>
       <c r="F1499" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1500">
@@ -42417,7 +42417,7 @@
         <v>1.9</v>
       </c>
       <c r="F1500" t="n">
-        <v>54.9</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="1501">
@@ -42445,7 +42445,7 @@
         <v>1.9</v>
       </c>
       <c r="F1501" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>1.9</v>
       </c>
       <c r="F1502" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1503">
@@ -42501,7 +42501,7 @@
         <v>1.7</v>
       </c>
       <c r="F1503" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1504">
@@ -42529,7 +42529,7 @@
         <v>1.7</v>
       </c>
       <c r="F1504" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1505">
@@ -42545,19 +42545,19 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1505" t="n">
         <v>1.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>42.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1506">
@@ -42573,19 +42573,19 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1506" t="n">
         <v>1.5</v>
       </c>
       <c r="F1506" t="n">
-        <v>50.4</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1507">
@@ -42610,10 +42610,10 @@
         </is>
       </c>
       <c r="E1507" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1507" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1508">
@@ -42638,10 +42638,10 @@
         </is>
       </c>
       <c r="E1508" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F1508" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1509">
@@ -42669,7 +42669,7 @@
         <v>1.3</v>
       </c>
       <c r="F1509" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1510">
@@ -42697,7 +42697,7 @@
         <v>1.3</v>
       </c>
       <c r="F1510" t="n">
-        <v>51</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1511">
@@ -42725,7 +42725,7 @@
         <v>1.2</v>
       </c>
       <c r="F1511" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1512">
@@ -42741,19 +42741,19 @@
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1512" t="n">
         <v>1.2</v>
       </c>
       <c r="F1512" t="n">
-        <v>40.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1513">
@@ -42769,19 +42769,19 @@
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1513" t="n">
         <v>1.2</v>
       </c>
       <c r="F1513" t="n">
-        <v>46.4</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="1514">
@@ -42809,7 +42809,7 @@
         <v>1.1</v>
       </c>
       <c r="F1514" t="n">
-        <v>47</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1515">
@@ -42825,19 +42825,19 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1515" t="n">
         <v>1.1</v>
       </c>
       <c r="F1515" t="n">
-        <v>48.7</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1516">
@@ -42865,7 +42865,7 @@
         <v>1.1</v>
       </c>
       <c r="F1516" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1517" t="n">
         <v>1</v>
       </c>
       <c r="F1517" t="n">
-        <v>51.7</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1518">
@@ -42937,19 +42937,19 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1519" t="n">
         <v>1</v>
       </c>
       <c r="F1519" t="n">
-        <v>43.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>0.9</v>
       </c>
       <c r="F1520" t="n">
-        <v>49.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1521">
@@ -43033,7 +43033,7 @@
         <v>0.8</v>
       </c>
       <c r="F1522" t="n">
-        <v>47.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>0.8</v>
       </c>
       <c r="F1523" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1524">
@@ -43086,10 +43086,10 @@
         </is>
       </c>
       <c r="E1524" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F1524" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1525">
@@ -43117,7 +43117,7 @@
         <v>0.6</v>
       </c>
       <c r="F1525" t="n">
-        <v>45</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1526">
@@ -43145,7 +43145,7 @@
         <v>0.6</v>
       </c>
       <c r="F1526" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1527">
@@ -43173,7 +43173,7 @@
         <v>0.5</v>
       </c>
       <c r="F1527" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1528">
@@ -43189,19 +43189,19 @@
       </c>
       <c r="C1528" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1528" t="n">
         <v>0.4</v>
       </c>
       <c r="F1528" t="n">
-        <v>41.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1529">
@@ -43217,19 +43217,19 @@
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1529" t="n">
         <v>0.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>50.4</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>0.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>44.6</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1531">
@@ -43285,7 +43285,7 @@
         <v>0.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="1532">
@@ -43301,19 +43301,19 @@
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1532" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F1532" t="n">
-        <v>44.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1533">
@@ -43329,19 +43329,19 @@
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1533" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F1533" t="n">
-        <v>48.5</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>5.8</v>
       </c>
       <c r="F1534" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1535">
@@ -43394,10 +43394,10 @@
         </is>
       </c>
       <c r="E1535" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F1535" t="n">
-        <v>49.2</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1536">
@@ -43425,7 +43425,7 @@
         <v>4.5</v>
       </c>
       <c r="F1536" t="n">
-        <v>58</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="1537">
@@ -43453,7 +43453,7 @@
         <v>3.8</v>
       </c>
       <c r="F1537" t="n">
-        <v>41.4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1538">
@@ -43478,10 +43478,10 @@
         </is>
       </c>
       <c r="E1538" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="F1538" t="n">
-        <v>48</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1539">
@@ -43506,10 +43506,10 @@
         </is>
       </c>
       <c r="E1539" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F1539" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1540">
@@ -43534,10 +43534,10 @@
         </is>
       </c>
       <c r="E1540" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F1540" t="n">
-        <v>44.9</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1541">
@@ -43553,19 +43553,19 @@
       </c>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1541" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1541" t="n">
-        <v>49.3</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="1542">
@@ -43581,19 +43581,19 @@
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1542" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="F1542" t="n">
-        <v>40.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1543">
@@ -43618,10 +43618,10 @@
         </is>
       </c>
       <c r="E1543" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F1543" t="n">
-        <v>41.1</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="1544">
@@ -43649,7 +43649,7 @@
         <v>2.6</v>
       </c>
       <c r="F1544" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1545">
@@ -43674,10 +43674,10 @@
         </is>
       </c>
       <c r="E1545" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="1546">
@@ -43693,19 +43693,19 @@
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1546" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1546" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1547">
@@ -43721,19 +43721,19 @@
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1547" t="n">
         <v>2.3</v>
       </c>
       <c r="F1547" t="n">
-        <v>48.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1548">
@@ -43758,10 +43758,10 @@
         </is>
       </c>
       <c r="E1548" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F1548" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1549">
@@ -43786,10 +43786,10 @@
         </is>
       </c>
       <c r="E1549" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F1549" t="n">
-        <v>47.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1550">
@@ -43814,10 +43814,10 @@
         </is>
       </c>
       <c r="E1550" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F1550" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1551">
@@ -43845,7 +43845,7 @@
         <v>1.8</v>
       </c>
       <c r="F1551" t="n">
-        <v>50.3</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1552">
@@ -43861,19 +43861,19 @@
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1552" t="n">
         <v>1.7</v>
       </c>
       <c r="F1552" t="n">
-        <v>25.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1553">
@@ -43889,19 +43889,19 @@
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1553" t="n">
         <v>1.6</v>
       </c>
       <c r="F1553" t="n">
-        <v>48.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1554">
@@ -43917,19 +43917,19 @@
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1554" t="n">
         <v>1.6</v>
       </c>
       <c r="F1554" t="n">
-        <v>44.5</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="1555">
@@ -43945,19 +43945,19 @@
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1555" t="n">
         <v>1.6</v>
       </c>
       <c r="F1555" t="n">
-        <v>54.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1556">
@@ -43982,10 +43982,10 @@
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1556" t="n">
-        <v>50.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1557">
@@ -44001,19 +44001,19 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1557" t="n">
         <v>1.5</v>
       </c>
       <c r="F1557" t="n">
-        <v>33.1</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="1558">
@@ -44038,10 +44038,10 @@
         </is>
       </c>
       <c r="E1558" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1558" t="n">
-        <v>45.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1559">
@@ -44057,19 +44057,19 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1559" t="n">
         <v>1.4</v>
       </c>
       <c r="F1559" t="n">
-        <v>37.4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1560">
@@ -44085,19 +44085,19 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1560" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1560" t="n">
-        <v>38.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1561">
@@ -44113,19 +44113,19 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1561" t="n">
         <v>1.3</v>
       </c>
       <c r="F1561" t="n">
-        <v>47.7</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="1562">
@@ -44141,19 +44141,19 @@
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1562" t="n">
         <v>1.3</v>
       </c>
       <c r="F1562" t="n">
-        <v>46.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1563" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F1563" t="n">
-        <v>45</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1564">
@@ -44197,19 +44197,19 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1564" t="n">
         <v>1.2</v>
       </c>
       <c r="F1564" t="n">
-        <v>56.4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1565">
@@ -44225,19 +44225,19 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1565" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1565" t="n">
-        <v>48.8</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1566">
@@ -44253,19 +44253,19 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1566" t="n">
         <v>1</v>
       </c>
       <c r="F1566" t="n">
-        <v>51.1</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1567">
@@ -44290,10 +44290,10 @@
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1567" t="n">
-        <v>50.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1568">
@@ -44321,7 +44321,7 @@
         <v>0.8</v>
       </c>
       <c r="F1568" t="n">
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="1569">
@@ -44346,10 +44346,10 @@
         </is>
       </c>
       <c r="E1569" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F1569" t="n">
-        <v>64.3</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="1570">
@@ -44377,7 +44377,7 @@
         <v>0.7</v>
       </c>
       <c r="F1570" t="n">
-        <v>59.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1571" t="n">
         <v>0.7</v>
       </c>
       <c r="F1571" t="n">
-        <v>44.1</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="1572">
@@ -44421,19 +44421,19 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1572" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F1572" t="n">
-        <v>60.8</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="1573">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1573" t="n">
         <v>0.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>30.4</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1574" t="n">
         <v>0.5</v>
       </c>
       <c r="F1574" t="n">
-        <v>31.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1575">
@@ -44505,19 +44505,19 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1575" t="n">
         <v>0.5</v>
       </c>
       <c r="F1575" t="n">
-        <v>56.8</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1576">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1576" t="n">
         <v>0.5</v>
       </c>
       <c r="F1576" t="n">
-        <v>72.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1577">
@@ -44561,19 +44561,19 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1577" t="n">
         <v>0.5</v>
       </c>
       <c r="F1577" t="n">
-        <v>39.9</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="1578">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
@@ -44601,7 +44601,7 @@
         <v>0.4</v>
       </c>
       <c r="F1578" t="n">
-        <v>41.8</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1579">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -44629,7 +44629,7 @@
         <v>0.4</v>
       </c>
       <c r="F1579" t="n">
-        <v>46.1</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="1580">
@@ -44654,10 +44654,10 @@
         </is>
       </c>
       <c r="E1580" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F1580" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1581">
@@ -44682,10 +44682,10 @@
         </is>
       </c>
       <c r="E1581" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F1581" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="1582">
@@ -44713,7 +44713,7 @@
         <v>0.2</v>
       </c>
       <c r="F1582" t="n">
-        <v>57.4</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1583">
@@ -44738,7 +44738,7 @@
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="F1583" t="n">
         <v>50.6</v>
@@ -44766,10 +44766,10 @@
         </is>
       </c>
       <c r="E1584" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="F1584" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="1585">
@@ -44794,7 +44794,7 @@
         </is>
       </c>
       <c r="E1585" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="F1585" t="n">
         <v>12.9</v>
@@ -44878,7 +44878,7 @@
         </is>
       </c>
       <c r="E1588" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1588" t="n">
         <v>80</v>
@@ -44990,7 +44990,7 @@
         </is>
       </c>
       <c r="E1592" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1592" t="n">
         <v>50</v>
@@ -45401,18 +45401,46 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1607" t="n">
         <v>0.4</v>
       </c>
       <c r="F1607" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>소전</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1608" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1608" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1608"/>
+  <dimension ref="A1:F1613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34773,7 +34773,7 @@
         <v>5.9</v>
       </c>
       <c r="F1227" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1228">
@@ -34798,10 +34798,10 @@
         </is>
       </c>
       <c r="E1228" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F1228" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1229">
@@ -34817,19 +34817,19 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1229" t="n">
         <v>3.8</v>
       </c>
       <c r="F1229" t="n">
-        <v>49.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1230">
@@ -34845,19 +34845,19 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1230" t="n">
         <v>3.8</v>
       </c>
       <c r="F1230" t="n">
-        <v>48.4</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1231">
@@ -34913,7 +34913,7 @@
         <v>3.2</v>
       </c>
       <c r="F1232" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1233">
@@ -35109,7 +35109,7 @@
         <v>2.3</v>
       </c>
       <c r="F1239" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1240">
@@ -35165,7 +35165,7 @@
         <v>2.2</v>
       </c>
       <c r="F1241" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1242">
@@ -35221,7 +35221,7 @@
         <v>2.1</v>
       </c>
       <c r="F1243" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1244">
@@ -35277,7 +35277,7 @@
         <v>2</v>
       </c>
       <c r="F1245" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1246">
@@ -35389,7 +35389,7 @@
         <v>1.7</v>
       </c>
       <c r="F1249" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1250">
@@ -35417,7 +35417,7 @@
         <v>1.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1251">
@@ -35445,7 +35445,7 @@
         <v>1.5</v>
       </c>
       <c r="F1251" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1252">
@@ -35473,7 +35473,7 @@
         <v>1.5</v>
       </c>
       <c r="F1252" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1253">
@@ -35501,7 +35501,7 @@
         <v>1.4</v>
       </c>
       <c r="F1253" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1254">
@@ -35529,7 +35529,7 @@
         <v>1.4</v>
       </c>
       <c r="F1254" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1255">
@@ -35557,7 +35557,7 @@
         <v>1.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1256">
@@ -35585,7 +35585,7 @@
         <v>1.4</v>
       </c>
       <c r="F1256" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1257">
@@ -35613,7 +35613,7 @@
         <v>1.2</v>
       </c>
       <c r="F1257" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1258">
@@ -35641,7 +35641,7 @@
         <v>1.2</v>
       </c>
       <c r="F1258" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1259">
@@ -35657,19 +35657,19 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1259" t="n">
         <v>1.2</v>
       </c>
       <c r="F1259" t="n">
-        <v>52.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1260">
@@ -35685,19 +35685,19 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1260" t="n">
         <v>1.2</v>
       </c>
       <c r="F1260" t="n">
-        <v>49.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1261">
@@ -35722,10 +35722,10 @@
         </is>
       </c>
       <c r="E1261" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F1261" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1262">
@@ -35753,7 +35753,7 @@
         <v>1.1</v>
       </c>
       <c r="F1262" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1263">
@@ -35781,7 +35781,7 @@
         <v>1.1</v>
       </c>
       <c r="F1263" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1264">
@@ -35809,7 +35809,7 @@
         <v>1</v>
       </c>
       <c r="F1264" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1265">
@@ -35837,7 +35837,7 @@
         <v>1</v>
       </c>
       <c r="F1265" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1266">
@@ -35893,7 +35893,7 @@
         <v>1</v>
       </c>
       <c r="F1267" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1268">
@@ -35921,7 +35921,7 @@
         <v>1</v>
       </c>
       <c r="F1268" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1269">
@@ -35977,7 +35977,7 @@
         <v>0.8</v>
       </c>
       <c r="F1270" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1271">
@@ -36033,7 +36033,7 @@
         <v>0.7</v>
       </c>
       <c r="F1272" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1273">
@@ -36114,10 +36114,10 @@
         </is>
       </c>
       <c r="E1275" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F1275" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1276">
@@ -36170,10 +36170,10 @@
         </is>
       </c>
       <c r="E1277" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F1277" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1278">
@@ -36198,10 +36198,10 @@
         </is>
       </c>
       <c r="E1278" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F1278" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1279">
@@ -36285,7 +36285,7 @@
         <v>4.2</v>
       </c>
       <c r="F1281" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1282">
@@ -36313,7 +36313,7 @@
         <v>3.3</v>
       </c>
       <c r="F1282" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1283">
@@ -36357,19 +36357,19 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1284" t="n">
         <v>3.1</v>
       </c>
       <c r="F1284" t="n">
-        <v>50.3</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1285">
@@ -36385,19 +36385,19 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1285" t="n">
         <v>3.1</v>
       </c>
       <c r="F1285" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1286">
@@ -36425,7 +36425,7 @@
         <v>3.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1287">
@@ -36453,7 +36453,7 @@
         <v>3</v>
       </c>
       <c r="F1287" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1288">
@@ -36481,7 +36481,7 @@
         <v>3</v>
       </c>
       <c r="F1288" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1289">
@@ -36509,7 +36509,7 @@
         <v>2.7</v>
       </c>
       <c r="F1289" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1290">
@@ -36537,7 +36537,7 @@
         <v>2.6</v>
       </c>
       <c r="F1290" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1291">
@@ -36565,7 +36565,7 @@
         <v>2.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1292">
@@ -36593,7 +36593,7 @@
         <v>2.3</v>
       </c>
       <c r="F1292" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="1293">
@@ -36621,7 +36621,7 @@
         <v>2.3</v>
       </c>
       <c r="F1293" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1294">
@@ -36649,7 +36649,7 @@
         <v>2.2</v>
       </c>
       <c r="F1294" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1295">
@@ -36674,10 +36674,10 @@
         </is>
       </c>
       <c r="E1295" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1295" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1296">
@@ -36705,7 +36705,7 @@
         <v>2.1</v>
       </c>
       <c r="F1296" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1297">
@@ -36733,7 +36733,7 @@
         <v>2</v>
       </c>
       <c r="F1297" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1298">
@@ -36761,7 +36761,7 @@
         <v>1.9</v>
       </c>
       <c r="F1298" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1299">
@@ -36789,7 +36789,7 @@
         <v>1.8</v>
       </c>
       <c r="F1299" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1300">
@@ -36817,7 +36817,7 @@
         <v>1.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1301">
@@ -36833,19 +36833,19 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1301" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1301" t="n">
         <v>1.7</v>
       </c>
       <c r="F1301" t="n">
-        <v>49.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1302">
@@ -36861,19 +36861,19 @@
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1302" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1302" t="n">
         <v>1.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1303">
@@ -36901,7 +36901,7 @@
         <v>1.6</v>
       </c>
       <c r="F1303" t="n">
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1304">
@@ -36929,7 +36929,7 @@
         <v>1.5</v>
       </c>
       <c r="F1304" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1305">
@@ -36957,7 +36957,7 @@
         <v>1.5</v>
       </c>
       <c r="F1305" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1306">
@@ -36982,7 +36982,7 @@
         </is>
       </c>
       <c r="E1306" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1306" t="n">
         <v>48</v>
@@ -37041,7 +37041,7 @@
         <v>1.3</v>
       </c>
       <c r="F1308" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1309">
@@ -37069,7 +37069,7 @@
         <v>1.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1310">
@@ -37097,7 +37097,7 @@
         <v>1.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1311">
@@ -37125,7 +37125,7 @@
         <v>1.1</v>
       </c>
       <c r="F1311" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1312">
@@ -37141,19 +37141,19 @@
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1312" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1312" t="n">
         <v>1</v>
       </c>
       <c r="F1312" t="n">
-        <v>46.2</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1313">
@@ -37169,19 +37169,19 @@
       </c>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1313" t="n">
         <v>1</v>
       </c>
       <c r="F1313" t="n">
-        <v>52.9</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1314">
@@ -37209,7 +37209,7 @@
         <v>0.9</v>
       </c>
       <c r="F1314" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1315">
@@ -37265,7 +37265,7 @@
         <v>0.9</v>
       </c>
       <c r="F1316" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1317">
@@ -37321,7 +37321,7 @@
         <v>0.9</v>
       </c>
       <c r="F1318" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1319">
@@ -37346,10 +37346,10 @@
         </is>
       </c>
       <c r="E1319" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F1319" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1320">
@@ -37377,7 +37377,7 @@
         <v>0.7</v>
       </c>
       <c r="F1320" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1321">
@@ -37405,7 +37405,7 @@
         <v>0.7</v>
       </c>
       <c r="F1321" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1322">
@@ -37433,7 +37433,7 @@
         <v>0.6</v>
       </c>
       <c r="F1322" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1323">
@@ -37461,7 +37461,7 @@
         <v>0.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1324">
@@ -37489,7 +37489,7 @@
         <v>0.5</v>
       </c>
       <c r="F1324" t="n">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="1325">
@@ -37517,7 +37517,7 @@
         <v>0.4</v>
       </c>
       <c r="F1325" t="n">
-        <v>55.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="1326">
@@ -37545,7 +37545,7 @@
         <v>0.3</v>
       </c>
       <c r="F1326" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1327">
@@ -37573,7 +37573,7 @@
         <v>0.3</v>
       </c>
       <c r="F1327" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1328">
@@ -37601,7 +37601,7 @@
         <v>7</v>
       </c>
       <c r="F1328" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1329">
@@ -37629,7 +37629,7 @@
         <v>5.2</v>
       </c>
       <c r="F1329" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1330">
@@ -37657,7 +37657,7 @@
         <v>4.2</v>
       </c>
       <c r="F1330" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1331">
@@ -37682,7 +37682,7 @@
         </is>
       </c>
       <c r="E1331" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F1331" t="n">
         <v>50</v>
@@ -37713,7 +37713,7 @@
         <v>3.9</v>
       </c>
       <c r="F1332" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1333">
@@ -37769,7 +37769,7 @@
         <v>3.4</v>
       </c>
       <c r="F1334" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1335">
@@ -37794,7 +37794,7 @@
         </is>
       </c>
       <c r="E1335" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1335" t="n">
         <v>51.9</v>
@@ -37825,7 +37825,7 @@
         <v>3.3</v>
       </c>
       <c r="F1336" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1337">
@@ -37878,10 +37878,10 @@
         </is>
       </c>
       <c r="E1338" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1338" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1339">
@@ -37909,7 +37909,7 @@
         <v>2.6</v>
       </c>
       <c r="F1339" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1340">
@@ -37937,7 +37937,7 @@
         <v>2.6</v>
       </c>
       <c r="F1340" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1341">
@@ -38105,7 +38105,7 @@
         <v>2.1</v>
       </c>
       <c r="F1346" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1347">
@@ -38133,7 +38133,7 @@
         <v>2.1</v>
       </c>
       <c r="F1347" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1348">
@@ -38158,10 +38158,10 @@
         </is>
       </c>
       <c r="E1348" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1348" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1349">
@@ -38177,19 +38177,19 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1349" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1349" t="n">
         <v>1.9</v>
       </c>
       <c r="F1349" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1350">
@@ -38205,19 +38205,19 @@
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1350" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1350" t="n">
         <v>1.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1351">
@@ -38245,7 +38245,7 @@
         <v>1.9</v>
       </c>
       <c r="F1351" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1352">
@@ -38273,7 +38273,7 @@
         <v>1.7</v>
       </c>
       <c r="F1352" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1353">
@@ -38301,7 +38301,7 @@
         <v>1.6</v>
       </c>
       <c r="F1353" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1354">
@@ -38329,7 +38329,7 @@
         <v>1.5</v>
       </c>
       <c r="F1354" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1355">
@@ -38357,7 +38357,7 @@
         <v>1.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1356">
@@ -38410,10 +38410,10 @@
         </is>
       </c>
       <c r="E1357" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F1357" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1358">
@@ -38469,7 +38469,7 @@
         <v>1.3</v>
       </c>
       <c r="F1359" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1360">
@@ -38497,7 +38497,7 @@
         <v>1.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1361">
@@ -38525,7 +38525,7 @@
         <v>1.2</v>
       </c>
       <c r="F1361" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1362">
@@ -38553,7 +38553,7 @@
         <v>1.2</v>
       </c>
       <c r="F1362" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1363">
@@ -38609,7 +38609,7 @@
         <v>1</v>
       </c>
       <c r="F1364" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1365">
@@ -38637,7 +38637,7 @@
         <v>1</v>
       </c>
       <c r="F1365" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1366">
@@ -38665,7 +38665,7 @@
         <v>1</v>
       </c>
       <c r="F1366" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1367">
@@ -38693,7 +38693,7 @@
         <v>0.9</v>
       </c>
       <c r="F1367" t="n">
-        <v>55.5</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="1368">
@@ -38777,7 +38777,7 @@
         <v>0.8</v>
       </c>
       <c r="F1370" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1371">
@@ -38805,7 +38805,7 @@
         <v>0.8</v>
       </c>
       <c r="F1371" t="n">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1372">
@@ -38833,7 +38833,7 @@
         <v>0.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="1373">
@@ -38917,7 +38917,7 @@
         <v>0.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1376">
@@ -38945,7 +38945,7 @@
         <v>0.5</v>
       </c>
       <c r="F1376" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1377">
@@ -38973,7 +38973,7 @@
         <v>0.4</v>
       </c>
       <c r="F1377" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1378">
@@ -38998,10 +38998,10 @@
         </is>
       </c>
       <c r="E1378" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1378" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1379">
@@ -39085,7 +39085,7 @@
         <v>4.8</v>
       </c>
       <c r="F1381" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1382">
@@ -39169,7 +39169,7 @@
         <v>3.8</v>
       </c>
       <c r="F1384" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1385">
@@ -39222,10 +39222,10 @@
         </is>
       </c>
       <c r="E1386" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1386" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1387">
@@ -39393,7 +39393,7 @@
         <v>2.2</v>
       </c>
       <c r="F1392" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1393">
@@ -39418,10 +39418,10 @@
         </is>
       </c>
       <c r="E1393" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F1393" t="n">
-        <v>45.6</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1394">
@@ -39449,7 +39449,7 @@
         <v>2.1</v>
       </c>
       <c r="F1394" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1395">
@@ -39477,7 +39477,7 @@
         <v>2.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1396">
@@ -39533,7 +39533,7 @@
         <v>2</v>
       </c>
       <c r="F1397" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1398">
@@ -39561,7 +39561,7 @@
         <v>1.9</v>
       </c>
       <c r="F1398" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1399">
@@ -39645,7 +39645,7 @@
         <v>1.8</v>
       </c>
       <c r="F1401" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1402">
@@ -39673,7 +39673,7 @@
         <v>1.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1403">
@@ -39701,7 +39701,7 @@
         <v>1.6</v>
       </c>
       <c r="F1403" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1404">
@@ -39757,7 +39757,7 @@
         <v>1.5</v>
       </c>
       <c r="F1405" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="1406">
@@ -39785,7 +39785,7 @@
         <v>1.5</v>
       </c>
       <c r="F1406" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1407">
@@ -39801,19 +39801,19 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1407" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1407" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1408">
@@ -39841,7 +39841,7 @@
         <v>1.4</v>
       </c>
       <c r="F1408" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1409">
@@ -39857,19 +39857,19 @@
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1409" t="n">
         <v>1.4</v>
       </c>
       <c r="F1409" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1410">
@@ -39897,7 +39897,7 @@
         <v>1.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1411">
@@ -39925,7 +39925,7 @@
         <v>1.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1412">
@@ -39953,7 +39953,7 @@
         <v>1.2</v>
       </c>
       <c r="F1412" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1413">
@@ -39981,7 +39981,7 @@
         <v>1.1</v>
       </c>
       <c r="F1413" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1414">
@@ -40025,19 +40025,19 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1415" t="n">
         <v>1.1</v>
       </c>
       <c r="F1415" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1416">
@@ -40053,19 +40053,19 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1416" t="n">
         <v>1.1</v>
       </c>
       <c r="F1416" t="n">
-        <v>51.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1417">
@@ -40093,7 +40093,7 @@
         <v>1.1</v>
       </c>
       <c r="F1417" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1418">
@@ -40121,7 +40121,7 @@
         <v>1</v>
       </c>
       <c r="F1418" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1419">
@@ -40149,7 +40149,7 @@
         <v>1</v>
       </c>
       <c r="F1419" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1420">
@@ -40177,7 +40177,7 @@
         <v>0.9</v>
       </c>
       <c r="F1420" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1421">
@@ -40205,7 +40205,7 @@
         <v>0.9</v>
       </c>
       <c r="F1421" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1422">
@@ -40233,7 +40233,7 @@
         <v>0.9</v>
       </c>
       <c r="F1422" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1423">
@@ -40261,7 +40261,7 @@
         <v>0.8</v>
       </c>
       <c r="F1423" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1424">
@@ -40317,7 +40317,7 @@
         <v>0.7</v>
       </c>
       <c r="F1425" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1426">
@@ -40345,7 +40345,7 @@
         <v>0.6</v>
       </c>
       <c r="F1426" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1427">
@@ -40401,7 +40401,7 @@
         <v>0.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1429">
@@ -40429,7 +40429,7 @@
         <v>0.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1430">
@@ -40510,7 +40510,7 @@
         </is>
       </c>
       <c r="E1432" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F1432" t="n">
         <v>47.4</v>
@@ -40541,7 +40541,7 @@
         <v>4.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1434">
@@ -40566,10 +40566,10 @@
         </is>
       </c>
       <c r="E1434" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1434" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1435">
@@ -40625,7 +40625,7 @@
         <v>3</v>
       </c>
       <c r="F1436" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1437">
@@ -40653,7 +40653,7 @@
         <v>3</v>
       </c>
       <c r="F1437" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1438">
@@ -40681,7 +40681,7 @@
         <v>2.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1439">
@@ -40709,7 +40709,7 @@
         <v>2.6</v>
       </c>
       <c r="F1439" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1440">
@@ -40734,10 +40734,10 @@
         </is>
       </c>
       <c r="E1440" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1440" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1441">
@@ -40765,7 +40765,7 @@
         <v>2.5</v>
       </c>
       <c r="F1441" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1442">
@@ -40793,7 +40793,7 @@
         <v>2.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1443">
@@ -40846,10 +40846,10 @@
         </is>
       </c>
       <c r="E1444" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1444" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1445">
@@ -40877,7 +40877,7 @@
         <v>2.1</v>
       </c>
       <c r="F1445" t="n">
-        <v>53.3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1446">
@@ -40905,7 +40905,7 @@
         <v>2.1</v>
       </c>
       <c r="F1446" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1447">
@@ -40930,10 +40930,10 @@
         </is>
       </c>
       <c r="E1447" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1447" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1448">
@@ -40989,7 +40989,7 @@
         <v>1.9</v>
       </c>
       <c r="F1449" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1450">
@@ -41045,7 +41045,7 @@
         <v>1.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1452">
@@ -41073,7 +41073,7 @@
         <v>1.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1453">
@@ -41117,19 +41117,19 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1454" t="n">
         <v>1.5</v>
       </c>
       <c r="F1454" t="n">
-        <v>51.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1455">
@@ -41145,19 +41145,19 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1455" t="n">
         <v>1.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>48.4</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1456">
@@ -41185,7 +41185,7 @@
         <v>1.5</v>
       </c>
       <c r="F1456" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1457">
@@ -41210,7 +41210,7 @@
         </is>
       </c>
       <c r="E1457" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1457" t="n">
         <v>53.8</v>
@@ -41229,19 +41229,19 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1458" t="n">
         <v>1.4</v>
       </c>
       <c r="F1458" t="n">
-        <v>40.8</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1459">
@@ -41257,19 +41257,19 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1459" t="n">
         <v>1.4</v>
       </c>
       <c r="F1459" t="n">
-        <v>49.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="1460">
@@ -41285,19 +41285,19 @@
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1460" t="n">
         <v>1.4</v>
       </c>
       <c r="F1460" t="n">
-        <v>49.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1461">
@@ -41313,19 +41313,19 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1461" t="n">
         <v>1.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>52.7</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1462">
@@ -41353,7 +41353,7 @@
         <v>1.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1463">
@@ -41409,7 +41409,7 @@
         <v>1.3</v>
       </c>
       <c r="F1464" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1465">
@@ -41437,7 +41437,7 @@
         <v>1.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1466">
@@ -41453,19 +41453,19 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1466" t="n">
         <v>1.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>48.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1467">
@@ -41481,19 +41481,19 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1467" t="n">
         <v>1.3</v>
       </c>
       <c r="F1467" t="n">
-        <v>44.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1468">
@@ -41521,7 +41521,7 @@
         <v>1.1</v>
       </c>
       <c r="F1468" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="1469">
@@ -41549,7 +41549,7 @@
         <v>1.1</v>
       </c>
       <c r="F1469" t="n">
-        <v>49.4</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1470">
@@ -41605,7 +41605,7 @@
         <v>0.8</v>
       </c>
       <c r="F1471" t="n">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1472">
@@ -41661,7 +41661,7 @@
         <v>0.7</v>
       </c>
       <c r="F1473" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1474">
@@ -41689,7 +41689,7 @@
         <v>0.7</v>
       </c>
       <c r="F1474" t="n">
-        <v>47.6</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1475">
@@ -41717,7 +41717,7 @@
         <v>0.7</v>
       </c>
       <c r="F1475" t="n">
-        <v>49.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1476">
@@ -41733,19 +41733,19 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1476" t="n">
         <v>0.6</v>
       </c>
       <c r="F1476" t="n">
-        <v>44.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1477">
@@ -41761,19 +41761,19 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1477" t="n">
         <v>0.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>49.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1478">
@@ -41789,19 +41789,19 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1478" t="n">
         <v>0.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>42.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1479">
@@ -41817,19 +41817,19 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1479" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1479" t="n">
-        <v>50.6</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="1480">
@@ -41857,7 +41857,7 @@
         <v>0.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>44.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1481">
@@ -41885,7 +41885,7 @@
         <v>7.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1482">
@@ -41910,10 +41910,10 @@
         </is>
       </c>
       <c r="E1482" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="F1482" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1483">
@@ -41938,10 +41938,10 @@
         </is>
       </c>
       <c r="E1483" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1484">
@@ -41994,10 +41994,10 @@
         </is>
       </c>
       <c r="E1485" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F1485" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1486">
@@ -42025,7 +42025,7 @@
         <v>3.4</v>
       </c>
       <c r="F1486" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1487">
@@ -42081,7 +42081,7 @@
         <v>3.3</v>
       </c>
       <c r="F1488" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1489">
@@ -42109,7 +42109,7 @@
         <v>3.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1490">
@@ -42137,7 +42137,7 @@
         <v>2.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1491">
@@ -42165,7 +42165,7 @@
         <v>2.7</v>
       </c>
       <c r="F1491" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1492">
@@ -42193,7 +42193,7 @@
         <v>2.5</v>
       </c>
       <c r="F1492" t="n">
-        <v>52.2</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1493">
@@ -42221,7 +42221,7 @@
         <v>2.4</v>
       </c>
       <c r="F1493" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1494">
@@ -42246,10 +42246,10 @@
         </is>
       </c>
       <c r="E1494" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1495">
@@ -42265,19 +42265,19 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1495" t="n">
         <v>2.2</v>
       </c>
       <c r="F1495" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1496">
@@ -42293,19 +42293,19 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1496" t="n">
         <v>2.2</v>
       </c>
       <c r="F1496" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1497">
@@ -42330,10 +42330,10 @@
         </is>
       </c>
       <c r="E1497" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F1497" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1498">
@@ -42361,7 +42361,7 @@
         <v>2</v>
       </c>
       <c r="F1498" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1499">
@@ -42377,19 +42377,19 @@
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1499" t="n">
         <v>2</v>
       </c>
       <c r="F1499" t="n">
-        <v>49.4</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="1500">
@@ -42405,19 +42405,19 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1500" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1500" t="n">
-        <v>54.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1501">
@@ -42445,7 +42445,7 @@
         <v>1.9</v>
       </c>
       <c r="F1501" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1502">
@@ -42473,7 +42473,7 @@
         <v>1.9</v>
       </c>
       <c r="F1502" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1503">
@@ -42501,7 +42501,7 @@
         <v>1.7</v>
       </c>
       <c r="F1503" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1504">
@@ -42529,7 +42529,7 @@
         <v>1.7</v>
       </c>
       <c r="F1504" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1505">
@@ -42545,19 +42545,19 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1505" t="n">
         <v>1.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>49.3</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1506">
@@ -42573,19 +42573,19 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1506" t="n">
         <v>1.5</v>
       </c>
       <c r="F1506" t="n">
-        <v>42.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1507">
@@ -42613,7 +42613,7 @@
         <v>1.5</v>
       </c>
       <c r="F1507" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1508">
@@ -42629,19 +42629,19 @@
       </c>
       <c r="C1508" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1508" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1508" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1508" t="n">
-        <v>49.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1509">
@@ -42657,19 +42657,19 @@
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1509" t="n">
         <v>1.3</v>
       </c>
       <c r="F1509" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1510">
@@ -42697,7 +42697,7 @@
         <v>1.3</v>
       </c>
       <c r="F1510" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1511">
@@ -42722,10 +42722,10 @@
         </is>
       </c>
       <c r="E1511" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1511" t="n">
-        <v>41.2</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1512">
@@ -42753,7 +42753,7 @@
         <v>1.2</v>
       </c>
       <c r="F1512" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1513">
@@ -42778,10 +42778,10 @@
         </is>
       </c>
       <c r="E1513" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F1513" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="1514">
@@ -42809,7 +42809,7 @@
         <v>1.1</v>
       </c>
       <c r="F1514" t="n">
-        <v>48.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1515">
@@ -42837,7 +42837,7 @@
         <v>1.1</v>
       </c>
       <c r="F1515" t="n">
-        <v>50.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1516">
@@ -42853,19 +42853,19 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1516" t="n">
         <v>1.1</v>
       </c>
       <c r="F1516" t="n">
-        <v>47.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="1517">
@@ -42881,19 +42881,19 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1517" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F1517" t="n">
-        <v>43.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1518">
@@ -42909,7 +42909,7 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
@@ -42921,7 +42921,7 @@
         <v>1</v>
       </c>
       <c r="F1518" t="n">
-        <v>52.5</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1519">
@@ -42937,7 +42937,7 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
@@ -42949,7 +42949,7 @@
         <v>1</v>
       </c>
       <c r="F1519" t="n">
-        <v>48.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1520">
@@ -42977,7 +42977,7 @@
         <v>0.9</v>
       </c>
       <c r="F1520" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1521">
@@ -42993,19 +42993,19 @@
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1521" t="n">
         <v>0.8</v>
       </c>
       <c r="F1521" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1522">
@@ -43021,19 +43021,19 @@
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1522" t="n">
         <v>0.8</v>
       </c>
       <c r="F1522" t="n">
-        <v>47</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1523">
@@ -43061,7 +43061,7 @@
         <v>0.8</v>
       </c>
       <c r="F1523" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1524">
@@ -43089,7 +43089,7 @@
         <v>0.7</v>
       </c>
       <c r="F1524" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1525">
@@ -43117,7 +43117,7 @@
         <v>0.6</v>
       </c>
       <c r="F1525" t="n">
-        <v>46.1</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1526">
@@ -43145,7 +43145,7 @@
         <v>0.6</v>
       </c>
       <c r="F1526" t="n">
-        <v>45.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1527">
@@ -43173,7 +43173,7 @@
         <v>0.5</v>
       </c>
       <c r="F1527" t="n">
-        <v>48</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1528">
@@ -43201,7 +43201,7 @@
         <v>0.4</v>
       </c>
       <c r="F1528" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1529">
@@ -43229,7 +43229,7 @@
         <v>0.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="1530">
@@ -43257,7 +43257,7 @@
         <v>0.4</v>
       </c>
       <c r="F1530" t="n">
-        <v>43.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1531">
@@ -43285,7 +43285,7 @@
         <v>0.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>38.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="1532">
@@ -43301,19 +43301,19 @@
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1532" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="F1532" t="n">
-        <v>48.6</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1533">
@@ -43329,19 +43329,19 @@
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1533" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F1533" t="n">
-        <v>43.8</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1534">
@@ -43369,7 +43369,7 @@
         <v>5.8</v>
       </c>
       <c r="F1534" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1535">
@@ -43394,10 +43394,10 @@
         </is>
       </c>
       <c r="E1535" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F1535" t="n">
-        <v>50.2</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1536">
@@ -43422,10 +43422,10 @@
         </is>
       </c>
       <c r="E1536" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F1536" t="n">
-        <v>56.5</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="1537">
@@ -43450,10 +43450,10 @@
         </is>
       </c>
       <c r="E1537" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="F1537" t="n">
-        <v>43</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1538">
@@ -43478,10 +43478,10 @@
         </is>
       </c>
       <c r="E1538" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F1538" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1539">
@@ -43497,7 +43497,7 @@
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
@@ -43506,10 +43506,10 @@
         </is>
       </c>
       <c r="E1539" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F1539" t="n">
-        <v>52.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1540">
@@ -43525,7 +43525,7 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
@@ -43537,7 +43537,7 @@
         <v>3.5</v>
       </c>
       <c r="F1540" t="n">
-        <v>42.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1541">
@@ -43562,10 +43562,10 @@
         </is>
       </c>
       <c r="E1541" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1541" t="n">
-        <v>40.3</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="1542">
@@ -43590,10 +43590,10 @@
         </is>
       </c>
       <c r="E1542" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F1542" t="n">
-        <v>49.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1543">
@@ -43621,7 +43621,7 @@
         <v>3</v>
       </c>
       <c r="F1543" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="1544">
@@ -43646,10 +43646,10 @@
         </is>
       </c>
       <c r="E1544" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1544" t="n">
-        <v>52.5</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1545">
@@ -43674,10 +43674,10 @@
         </is>
       </c>
       <c r="E1545" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1545" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="1546">
@@ -43693,19 +43693,19 @@
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1546" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>47.4</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1547">
@@ -43721,19 +43721,19 @@
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1547" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1547" t="n">
-        <v>43.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1548">
@@ -43758,10 +43758,10 @@
         </is>
       </c>
       <c r="E1548" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1548" t="n">
-        <v>43.3</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1549">
@@ -43789,7 +43789,7 @@
         <v>2</v>
       </c>
       <c r="F1549" t="n">
-        <v>48.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1550">
@@ -43817,7 +43817,7 @@
         <v>1.9</v>
       </c>
       <c r="F1550" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="1551">
@@ -43845,7 +43845,7 @@
         <v>1.8</v>
       </c>
       <c r="F1551" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1552">
@@ -43873,7 +43873,7 @@
         <v>1.7</v>
       </c>
       <c r="F1552" t="n">
-        <v>51.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1553">
@@ -43901,7 +43901,7 @@
         <v>1.6</v>
       </c>
       <c r="F1553" t="n">
-        <v>42</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1554">
@@ -43917,19 +43917,19 @@
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1554" t="n">
         <v>1.6</v>
       </c>
       <c r="F1554" t="n">
-        <v>25.3</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1555">
@@ -43945,19 +43945,19 @@
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1555" t="n">
         <v>1.6</v>
       </c>
       <c r="F1555" t="n">
-        <v>40</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1556">
@@ -43973,19 +43973,19 @@
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1556" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F1556" t="n">
-        <v>49.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1557">
@@ -44001,19 +44001,19 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1557" t="n">
         <v>1.5</v>
       </c>
       <c r="F1557" t="n">
-        <v>55.8</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="1558">
@@ -44041,7 +44041,7 @@
         <v>1.5</v>
       </c>
       <c r="F1558" t="n">
-        <v>47</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1559">
@@ -44057,19 +44057,19 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1559" t="n">
         <v>1.4</v>
       </c>
       <c r="F1559" t="n">
-        <v>34</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1560">
@@ -44085,19 +44085,19 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1560" t="n">
         <v>1.4</v>
       </c>
       <c r="F1560" t="n">
-        <v>48.3</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="1561">
@@ -44113,19 +44113,19 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 명사수</t>
         </is>
       </c>
       <c r="E1561" t="n">
         <v>1.3</v>
       </c>
       <c r="F1561" t="n">
-        <v>54.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1562">
@@ -44141,19 +44141,19 @@
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1562" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F1562" t="n">
-        <v>38.1</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="1563">
@@ -44169,19 +44169,19 @@
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1563" t="n">
         <v>1.2</v>
       </c>
       <c r="F1563" t="n">
-        <v>49.6</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1564">
@@ -44206,10 +44206,10 @@
         </is>
       </c>
       <c r="E1564" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F1564" t="n">
-        <v>46</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1565">
@@ -44237,7 +44237,7 @@
         <v>1.1</v>
       </c>
       <c r="F1565" t="n">
-        <v>45.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1566">
@@ -44265,7 +44265,7 @@
         <v>1</v>
       </c>
       <c r="F1566" t="n">
-        <v>46.9</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1567">
@@ -44290,10 +44290,10 @@
         </is>
       </c>
       <c r="E1567" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1567" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1568">
@@ -44309,19 +44309,19 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1568" t="n">
         <v>0.8</v>
       </c>
       <c r="F1568" t="n">
-        <v>56.4</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="1569">
@@ -44349,7 +44349,7 @@
         <v>0.8</v>
       </c>
       <c r="F1569" t="n">
-        <v>59.3</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="1570">
@@ -44365,19 +44365,19 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1570" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F1570" t="n">
-        <v>58.5</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1571">
@@ -44393,19 +44393,19 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1571" t="n">
         <v>0.7</v>
       </c>
       <c r="F1571" t="n">
-        <v>70.40000000000001</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1572">
@@ -44433,7 +44433,7 @@
         <v>0.7</v>
       </c>
       <c r="F1572" t="n">
-        <v>35.4</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="1573">
@@ -44449,19 +44449,19 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1573" t="n">
         <v>0.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>45.1</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="1574">
@@ -44477,19 +44477,19 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1574" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F1574" t="n">
-        <v>57.5</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="1575">
@@ -44533,19 +44533,19 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1576" t="n">
         <v>0.5</v>
       </c>
       <c r="F1576" t="n">
-        <v>30</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="1577">
@@ -44573,7 +44573,7 @@
         <v>0.5</v>
       </c>
       <c r="F1577" t="n">
-        <v>72.8</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="1578">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
@@ -44601,7 +44601,7 @@
         <v>0.4</v>
       </c>
       <c r="F1578" t="n">
-        <v>44.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1579">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -44629,7 +44629,7 @@
         <v>0.4</v>
       </c>
       <c r="F1579" t="n">
-        <v>40.1</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1580">
@@ -44654,10 +44654,10 @@
         </is>
       </c>
       <c r="E1580" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1580" t="n">
-        <v>45.3</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1581">
@@ -44685,7 +44685,7 @@
         <v>0.3</v>
       </c>
       <c r="F1581" t="n">
-        <v>25.8</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="1582">
@@ -44713,7 +44713,7 @@
         <v>0.2</v>
       </c>
       <c r="F1582" t="n">
-        <v>49.2</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1583">
@@ -44738,10 +44738,10 @@
         </is>
       </c>
       <c r="E1583" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="F1583" t="n">
-        <v>50.6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1584">
@@ -44766,10 +44766,10 @@
         </is>
       </c>
       <c r="E1584" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="F1584" t="n">
-        <v>34.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="1585">
@@ -44794,10 +44794,10 @@
         </is>
       </c>
       <c r="E1585" t="n">
-        <v>13.1</v>
+        <v>14.6</v>
       </c>
       <c r="F1585" t="n">
-        <v>12.9</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1586">
@@ -44813,19 +44813,19 @@
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1586" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="F1586" t="n">
-        <v>75</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="1587">
@@ -44841,19 +44841,19 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>돌격 · 투사</t>
         </is>
       </c>
       <c r="E1587" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="F1587" t="n">
-        <v>100</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="1588">
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="E1588" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="F1588" t="n">
-        <v>80</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="1589">
@@ -44897,19 +44897,19 @@
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1589" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="F1589" t="n">
-        <v>13.3</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="1590">
@@ -44925,19 +44925,19 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1590" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="F1590" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1591">
@@ -44953,19 +44953,19 @@
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>돌격 · 개시자</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1591" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F1591" t="n">
-        <v>71.40000000000001</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1592">
@@ -44981,19 +44981,19 @@
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1592" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F1592" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1593">
@@ -45009,19 +45009,19 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1593" t="inlineStr">
         <is>
-          <t>돌격 · 강건한 자</t>
+          <t>돌격 · 개시자</t>
         </is>
       </c>
       <c r="E1593" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="F1593" t="n">
-        <v>100</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="1594">
@@ -45037,19 +45037,19 @@
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>공격 · 수색가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1594" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="F1594" t="n">
-        <v>100</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="1595">
@@ -45065,19 +45065,19 @@
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>지원 · 생존 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1595" t="n">
         <v>2.1</v>
       </c>
       <c r="F1595" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1596">
@@ -45093,19 +45093,19 @@
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>지원 · 생존 전문가</t>
         </is>
       </c>
       <c r="E1596" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="F1596" t="n">
-        <v>28.1</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="1597">
@@ -45121,19 +45121,19 @@
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>돌격 · 투사</t>
+          <t>돌격 · 강건한 자</t>
         </is>
       </c>
       <c r="E1597" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F1597" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1598">
@@ -45149,16 +45149,16 @@
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>지원 · 의무병</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1598" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="F1598" t="n">
         <v>100</v>
@@ -45177,19 +45177,19 @@
       </c>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1599" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F1599" t="n">
-        <v>66.59999999999999</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="1600">
@@ -45205,16 +45205,16 @@
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>공격 · 측면 공격가</t>
+          <t>지원 · 의무병</t>
         </is>
       </c>
       <c r="E1600" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F1600" t="n">
         <v>100</v>
@@ -45233,19 +45233,19 @@
       </c>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>공격 · 전문가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1601" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F1601" t="n">
-        <v>0</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="1602">
@@ -45261,7 +45261,7 @@
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr">
@@ -45270,10 +45270,10 @@
         </is>
       </c>
       <c r="E1602" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1602" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1603">
@@ -45289,19 +45289,19 @@
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 수색가</t>
         </is>
       </c>
       <c r="E1603" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F1603" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1604">
@@ -45317,7 +45317,7 @@
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
@@ -45326,10 +45326,10 @@
         </is>
       </c>
       <c r="E1604" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F1604" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1605">
@@ -45345,16 +45345,16 @@
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>지원 · 전술가</t>
         </is>
       </c>
       <c r="E1605" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1605" t="n">
         <v>100</v>
@@ -45373,19 +45373,19 @@
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>공격 · 명사수</t>
+          <t>공격 · 전문가</t>
         </is>
       </c>
       <c r="E1606" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1606" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1607">
@@ -45401,19 +45401,19 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>지원 · 전술가</t>
+          <t>공격 · 측면 공격가</t>
         </is>
       </c>
       <c r="E1607" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1607" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1608">
@@ -45429,7 +45429,7 @@
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">
@@ -45438,10 +45438,150 @@
         </is>
       </c>
       <c r="E1608" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F1608" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>위도우메이커</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1609" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>캐서디</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1610" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>자리야</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>돌격 · 투사</t>
+        </is>
+      </c>
+      <c r="E1611" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>소전</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1612" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>애쉬</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>공격 · 명사수</t>
+        </is>
+      </c>
+      <c r="E1613" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1614"/>
+  <dimension ref="A1:F1618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="F2" t="n">
         <v>49.9</v>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="F4" t="n">
         <v>51.9</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F6" t="n">
         <v>49.9</v>
@@ -610,7 +610,7 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="F8" t="n">
         <v>47.9</v>
@@ -637,7 +637,7 @@
         <v>14.6</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="10">
@@ -682,7 +682,7 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F11" t="n">
         <v>51.9</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>46.8</v>
@@ -757,7 +757,7 @@
         <v>11.5</v>
       </c>
       <c r="F14" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F16" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="17">
@@ -826,7 +826,7 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F17" t="n">
         <v>51.4</v>
@@ -850,10 +850,10 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F18" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -874,7 +874,7 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F19" t="n">
         <v>50.6</v>
@@ -973,7 +973,7 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="24">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F25" t="n">
         <v>47</v>
@@ -1042,10 +1042,10 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="F26" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="27">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F28" t="n">
         <v>46.6</v>
@@ -1162,10 +1162,10 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F31" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="32">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F32" t="n">
         <v>48.9</v>
@@ -1205,15 +1205,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="F33" t="n">
-        <v>51.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
         <v>48.7</v>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
         <v>5.8</v>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="36">
@@ -1309,7 +1309,7 @@
         <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -1429,7 +1429,7 @@
         <v>4.3</v>
       </c>
       <c r="F42" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="43">
@@ -1477,7 +1477,7 @@
         <v>3.6</v>
       </c>
       <c r="F44" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="45">
@@ -1525,7 +1525,7 @@
         <v>3.1</v>
       </c>
       <c r="F46" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -1549,7 +1549,7 @@
         <v>2.9</v>
       </c>
       <c r="F47" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="48">
@@ -1573,7 +1573,7 @@
         <v>2.9</v>
       </c>
       <c r="F48" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
@@ -1621,7 +1621,7 @@
         <v>2.7</v>
       </c>
       <c r="F50" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="51">
@@ -1645,7 +1645,7 @@
         <v>2.3</v>
       </c>
       <c r="F51" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="52">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F104" t="n">
         <v>50.1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="F106" t="n">
         <v>52.7</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="F107" t="n">
         <v>48.5</v>
@@ -3037,7 +3037,7 @@
         <v>16.3</v>
       </c>
       <c r="F109" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="110">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F110" t="n">
         <v>46.8</v>
@@ -3085,7 +3085,7 @@
         <v>15</v>
       </c>
       <c r="F111" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="112">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F112" t="n">
         <v>46.6</v>
@@ -3133,7 +3133,7 @@
         <v>13.9</v>
       </c>
       <c r="F113" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="114">
@@ -3157,7 +3157,7 @@
         <v>12.8</v>
       </c>
       <c r="F114" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="115">
@@ -3197,15 +3197,15 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F116" t="n">
-        <v>43.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="117">
@@ -3221,15 +3221,15 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F117" t="n">
-        <v>51.9</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="118">
@@ -3301,7 +3301,7 @@
         <v>10.5</v>
       </c>
       <c r="F120" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="121">
@@ -3325,7 +3325,7 @@
         <v>9.9</v>
       </c>
       <c r="F121" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="122">
@@ -3389,15 +3389,15 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="F124" t="n">
-        <v>45.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="125">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
         <v>9</v>
       </c>
       <c r="F125" t="n">
-        <v>51.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="126">
@@ -3469,7 +3469,7 @@
         <v>8.1</v>
       </c>
       <c r="F127" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="128">
@@ -3565,7 +3565,7 @@
         <v>7.3</v>
       </c>
       <c r="F131" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="132">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F132" t="n">
         <v>51.5</v>
@@ -3637,7 +3637,7 @@
         <v>6.3</v>
       </c>
       <c r="F134" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="135">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
         <v>5.9</v>
       </c>
       <c r="F136" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="137">
@@ -3701,15 +3701,15 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="F137" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="138">
@@ -3733,7 +3733,7 @@
         <v>5.7</v>
       </c>
       <c r="F138" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="139">
@@ -3757,7 +3757,7 @@
         <v>5.5</v>
       </c>
       <c r="F139" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140">
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="F145" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="146">
@@ -3917,15 +3917,15 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F146" t="n">
-        <v>49.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="147">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3949,7 +3949,7 @@
         <v>3.2</v>
       </c>
       <c r="F147" t="n">
-        <v>54</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="148">
@@ -3973,7 +3973,7 @@
         <v>3</v>
       </c>
       <c r="F148" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="149">
@@ -3997,7 +3997,7 @@
         <v>2.7</v>
       </c>
       <c r="F149" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="150">
@@ -4018,10 +4018,10 @@
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F150" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="151">
@@ -4045,7 +4045,7 @@
         <v>2.5</v>
       </c>
       <c r="F151" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="152">
@@ -4069,7 +4069,7 @@
         <v>2.4</v>
       </c>
       <c r="F152" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="153">
@@ -4114,10 +4114,10 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F154" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="155">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F155" t="n">
         <v>49.7</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="F156" t="n">
         <v>49.2</v>
@@ -4186,10 +4186,10 @@
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="F157" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="158">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
         <v>16.6</v>
       </c>
       <c r="F159" t="n">
-        <v>49.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="160">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
         <v>16.6</v>
       </c>
       <c r="F160" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="161">
@@ -4277,15 +4277,15 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="162">
@@ -4333,7 +4333,7 @@
         <v>14</v>
       </c>
       <c r="F163" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="164">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
         <v>12.3</v>
       </c>
       <c r="F165" t="n">
-        <v>52.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="166">
@@ -4397,15 +4397,15 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F166" t="n">
-        <v>46.8</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="167">
@@ -4469,15 +4469,15 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F169" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="170">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4501,7 +4501,7 @@
         <v>10.5</v>
       </c>
       <c r="F170" t="n">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="171">
@@ -4525,7 +4525,7 @@
         <v>10.4</v>
       </c>
       <c r="F171" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="172">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F172" t="n">
         <v>51.6</v>
@@ -4589,15 +4589,15 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F174" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="175">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
         <v>8.5</v>
       </c>
       <c r="F175" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="176">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F177" t="n">
         <v>49.3</v>
@@ -4789,7 +4789,7 @@
         <v>6.4</v>
       </c>
       <c r="F182" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="183">
@@ -4813,7 +4813,7 @@
         <v>6.4</v>
       </c>
       <c r="F183" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="184">
@@ -4837,7 +4837,7 @@
         <v>6.3</v>
       </c>
       <c r="F184" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="185">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -4885,7 +4885,7 @@
         <v>6.1</v>
       </c>
       <c r="F186" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="187">
@@ -4901,15 +4901,15 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F187" t="n">
-        <v>51.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="188">
@@ -4925,15 +4925,15 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F188" t="n">
-        <v>48.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="189">
@@ -4981,7 +4981,7 @@
         <v>5.7</v>
       </c>
       <c r="F190" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="191">
@@ -5005,7 +5005,7 @@
         <v>5.6</v>
       </c>
       <c r="F191" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192">
@@ -5029,7 +5029,7 @@
         <v>4.7</v>
       </c>
       <c r="F192" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="193">
@@ -5053,7 +5053,7 @@
         <v>4.5</v>
       </c>
       <c r="F193" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="194">
@@ -5125,7 +5125,7 @@
         <v>3.6</v>
       </c>
       <c r="F196" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="197">
@@ -5173,7 +5173,7 @@
         <v>3.4</v>
       </c>
       <c r="F198" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="199">
@@ -5197,7 +5197,7 @@
         <v>3.1</v>
       </c>
       <c r="F199" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="200">
@@ -5290,10 +5290,10 @@
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F203" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="204">
@@ -5317,7 +5317,7 @@
         <v>2.5</v>
       </c>
       <c r="F204" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="205">
@@ -5338,10 +5338,10 @@
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F205" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="206">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="F207" t="n">
         <v>49.7</v>
@@ -5410,10 +5410,10 @@
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="F208" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="209">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="F209" t="n">
         <v>45.5</v>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="F211" t="n">
         <v>51.9</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="F212" t="n">
         <v>54.5</v>
@@ -5557,7 +5557,7 @@
         <v>12.5</v>
       </c>
       <c r="F214" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="215">
@@ -5629,7 +5629,7 @@
         <v>11.5</v>
       </c>
       <c r="F217" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="218">
@@ -5701,7 +5701,7 @@
         <v>11.3</v>
       </c>
       <c r="F220" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="221">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F222" t="n">
         <v>46.9</v>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F225" t="n">
         <v>48.5</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="F226" t="n">
         <v>49.7</v>
@@ -5866,10 +5866,10 @@
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F227" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="228">
@@ -5893,7 +5893,7 @@
         <v>7.6</v>
       </c>
       <c r="F228" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="229">
@@ -5914,10 +5914,10 @@
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F229" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="230">
@@ -5941,7 +5941,7 @@
         <v>7.2</v>
       </c>
       <c r="F230" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="231">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -5989,7 +5989,7 @@
         <v>6.5</v>
       </c>
       <c r="F232" t="n">
-        <v>48.1</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="233">
@@ -6005,15 +6005,15 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F233" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="234">
@@ -6029,15 +6029,15 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F234" t="n">
-        <v>42.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="235">
@@ -6053,15 +6053,15 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F235" t="n">
-        <v>48.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="236">
@@ -6077,15 +6077,15 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F236" t="n">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="237">
@@ -6157,7 +6157,7 @@
         <v>5.4</v>
       </c>
       <c r="F239" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="240">
@@ -6181,7 +6181,7 @@
         <v>5.4</v>
       </c>
       <c r="F240" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="241">
@@ -6205,7 +6205,7 @@
         <v>5.3</v>
       </c>
       <c r="F241" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="242">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
         <v>5.3</v>
       </c>
       <c r="F242" t="n">
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="243">
@@ -6245,15 +6245,15 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F243" t="n">
-        <v>46.4</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="244">
@@ -6301,7 +6301,7 @@
         <v>4.9</v>
       </c>
       <c r="F245" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="246">
@@ -6397,7 +6397,7 @@
         <v>3.5</v>
       </c>
       <c r="F249" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="250">
@@ -6493,7 +6493,7 @@
         <v>3</v>
       </c>
       <c r="F253" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="254">
@@ -6517,7 +6517,7 @@
         <v>2.9</v>
       </c>
       <c r="F254" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="255">
@@ -6541,7 +6541,7 @@
         <v>2.3</v>
       </c>
       <c r="F255" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="256">
@@ -6565,7 +6565,7 @@
         <v>2.2</v>
       </c>
       <c r="F256" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="257">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F258" t="n">
         <v>49.9</v>
@@ -6637,7 +6637,7 @@
         <v>26</v>
       </c>
       <c r="F259" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="260">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="F261" t="n">
         <v>49.8</v>
@@ -6706,10 +6706,10 @@
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F262" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="263">
@@ -6754,10 +6754,10 @@
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="F264" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="265">
@@ -6778,10 +6778,10 @@
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="F265" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="266">
@@ -6877,7 +6877,7 @@
         <v>11.4</v>
       </c>
       <c r="F269" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="270">
@@ -6901,7 +6901,7 @@
         <v>11.1</v>
       </c>
       <c r="F270" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="271">
@@ -6922,10 +6922,10 @@
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="F271" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="272">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F274" t="n">
         <v>49.7</v>
@@ -7069,7 +7069,7 @@
         <v>7.4</v>
       </c>
       <c r="F277" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="278">
@@ -7117,7 +7117,7 @@
         <v>7.2</v>
       </c>
       <c r="F279" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="280">
@@ -7189,7 +7189,7 @@
         <v>6.6</v>
       </c>
       <c r="F282" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="283">
@@ -7229,15 +7229,15 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F284" t="n">
-        <v>45.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="285">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -7261,7 +7261,7 @@
         <v>6.2</v>
       </c>
       <c r="F285" t="n">
-        <v>50.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="286">
@@ -7277,15 +7277,15 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="F286" t="n">
-        <v>47</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="287">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F287" t="n">
         <v>43.8</v>
@@ -7333,7 +7333,7 @@
         <v>5.8</v>
       </c>
       <c r="F288" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="289">
@@ -7357,7 +7357,7 @@
         <v>5.5</v>
       </c>
       <c r="F289" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="290">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F291" t="n">
         <v>48</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7429,7 +7429,7 @@
         <v>4.4</v>
       </c>
       <c r="F292" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="293">
@@ -7445,15 +7445,15 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F293" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="294">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F295" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="296">
@@ -7546,10 +7546,10 @@
       </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F297" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="298">
@@ -7565,15 +7565,15 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F298" t="n">
-        <v>46.6</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="299">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
         <v>3.8</v>
       </c>
       <c r="F299" t="n">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="300">
@@ -7642,10 +7642,10 @@
       </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F301" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="302">
@@ -7693,7 +7693,7 @@
         <v>3.1</v>
       </c>
       <c r="F303" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="304">
@@ -7717,7 +7717,7 @@
         <v>2.7</v>
       </c>
       <c r="F304" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="305">
@@ -7765,7 +7765,7 @@
         <v>2</v>
       </c>
       <c r="F306" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="307">
@@ -7789,7 +7789,7 @@
         <v>2</v>
       </c>
       <c r="F307" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="308">
@@ -10282,10 +10282,10 @@
       </c>
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="F411" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="412">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="F415" t="n">
         <v>49.9</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="F417" t="n">
         <v>47</v>
@@ -10525,7 +10525,7 @@
         <v>12.5</v>
       </c>
       <c r="F421" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="422">
@@ -10546,10 +10546,10 @@
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F422" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="423">
@@ -10573,7 +10573,7 @@
         <v>12.2</v>
       </c>
       <c r="F423" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="424">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F428" t="n">
         <v>44.2</v>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -10741,7 +10741,7 @@
         <v>10</v>
       </c>
       <c r="F430" t="n">
-        <v>49.3</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="431">
@@ -10757,15 +10757,15 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="F431" t="n">
-        <v>52.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="432">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -10885,7 +10885,7 @@
         <v>7.3</v>
       </c>
       <c r="F436" t="n">
-        <v>47.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="437">
@@ -10901,15 +10901,15 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="F437" t="n">
-        <v>48.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="438">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D444" t="inlineStr"/>
       <c r="E444" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="F444" t="n">
         <v>51.5</v>
@@ -11125,7 +11125,7 @@
         <v>5.2</v>
       </c>
       <c r="F446" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="447">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -11245,7 +11245,7 @@
         <v>4.4</v>
       </c>
       <c r="F451" t="n">
-        <v>49.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="452">
@@ -11261,15 +11261,15 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F452" t="n">
-        <v>50.8</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="453">
@@ -11461,7 +11461,7 @@
         <v>2.1</v>
       </c>
       <c r="F460" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="461">
@@ -11506,10 +11506,10 @@
       </c>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="n">
-        <v>31.1</v>
+        <v>30.7</v>
       </c>
       <c r="F462" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="463">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="F463" t="n">
         <v>48.9</v>
@@ -11557,7 +11557,7 @@
         <v>24</v>
       </c>
       <c r="F464" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="465">
@@ -11602,10 +11602,10 @@
       </c>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="F466" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="467">
@@ -11674,10 +11674,10 @@
       </c>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="F469" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="470">
@@ -11701,7 +11701,7 @@
         <v>12.7</v>
       </c>
       <c r="F470" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="471">
@@ -11725,7 +11725,7 @@
         <v>12.5</v>
       </c>
       <c r="F471" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="472">
@@ -11749,7 +11749,7 @@
         <v>12.5</v>
       </c>
       <c r="F472" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="473">
@@ -11765,15 +11765,15 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F473" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="474">
@@ -11789,15 +11789,15 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F474" t="n">
-        <v>52.6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="475">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F475" t="n">
         <v>49.4</v>
@@ -11845,7 +11845,7 @@
         <v>11.4</v>
       </c>
       <c r="F476" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="477">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
@@ -11869,7 +11869,7 @@
         <v>11.3</v>
       </c>
       <c r="F477" t="n">
-        <v>48.6</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="478">
@@ -11885,15 +11885,15 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F478" t="n">
-        <v>46.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="479">
@@ -11914,10 +11914,10 @@
       </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F479" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="480">
@@ -11941,7 +11941,7 @@
         <v>10.9</v>
       </c>
       <c r="F480" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="481">
@@ -11965,7 +11965,7 @@
         <v>10.7</v>
       </c>
       <c r="F481" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="482">
@@ -12013,7 +12013,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F483" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="484">
@@ -12061,7 +12061,7 @@
         <v>8.5</v>
       </c>
       <c r="F485" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="486">
@@ -12109,7 +12109,7 @@
         <v>7.8</v>
       </c>
       <c r="F487" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="488">
@@ -12133,7 +12133,7 @@
         <v>7.1</v>
       </c>
       <c r="F488" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="489">
@@ -12178,10 +12178,10 @@
       </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F490" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="491">
@@ -12205,7 +12205,7 @@
         <v>6.2</v>
       </c>
       <c r="F491" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="492">
@@ -12250,10 +12250,10 @@
       </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F493" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="494">
@@ -12301,7 +12301,7 @@
         <v>5</v>
       </c>
       <c r="F495" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="496">
@@ -12325,7 +12325,7 @@
         <v>4.9</v>
       </c>
       <c r="F496" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="497">
@@ -12349,7 +12349,7 @@
         <v>4.4</v>
       </c>
       <c r="F497" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="498">
@@ -12373,7 +12373,7 @@
         <v>4.1</v>
       </c>
       <c r="F498" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="499">
@@ -12397,7 +12397,7 @@
         <v>4.1</v>
       </c>
       <c r="F499" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="500">
@@ -12413,15 +12413,15 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F500" t="n">
-        <v>48</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="501">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D501" t="inlineStr"/>
@@ -12445,7 +12445,7 @@
         <v>4</v>
       </c>
       <c r="F501" t="n">
-        <v>45</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="502">
@@ -12493,7 +12493,7 @@
         <v>3.3</v>
       </c>
       <c r="F503" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="504">
@@ -12509,15 +12509,15 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F504" t="n">
-        <v>51.6</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="505">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
@@ -12541,7 +12541,7 @@
         <v>3.1</v>
       </c>
       <c r="F505" t="n">
-        <v>54.7</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="506">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D506" t="inlineStr"/>
@@ -12565,7 +12565,7 @@
         <v>3.1</v>
       </c>
       <c r="F506" t="n">
-        <v>48.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="507">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D507" t="inlineStr"/>
@@ -12589,7 +12589,7 @@
         <v>3.1</v>
       </c>
       <c r="F507" t="n">
-        <v>52.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="508">
@@ -12613,7 +12613,7 @@
         <v>2.9</v>
       </c>
       <c r="F508" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="509">
@@ -12634,10 +12634,10 @@
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F509" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="510">
@@ -12661,7 +12661,7 @@
         <v>2.5</v>
       </c>
       <c r="F510" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="511">
@@ -12685,7 +12685,7 @@
         <v>2.2</v>
       </c>
       <c r="F511" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="512">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="F563" t="n">
         <v>48.1</v>
@@ -13954,10 +13954,10 @@
       </c>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
       <c r="F564" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="565">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="F568" t="n">
         <v>49.8</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="F570" t="n">
         <v>51.4</v>
@@ -14122,10 +14122,10 @@
       </c>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="F571" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="572">
@@ -14149,7 +14149,7 @@
         <v>13.6</v>
       </c>
       <c r="F572" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="573">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
@@ -14173,7 +14173,7 @@
         <v>13.3</v>
       </c>
       <c r="F573" t="n">
-        <v>51.6</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="574">
@@ -14189,15 +14189,15 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="F574" t="n">
-        <v>50.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="575">
@@ -14269,7 +14269,7 @@
         <v>12.3</v>
       </c>
       <c r="F577" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="578">
@@ -14458,10 +14458,10 @@
       </c>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F585" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="586">
@@ -14557,7 +14557,7 @@
         <v>7.2</v>
       </c>
       <c r="F589" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="590">
@@ -14581,7 +14581,7 @@
         <v>7</v>
       </c>
       <c r="F590" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="591">
@@ -14653,7 +14653,7 @@
         <v>6.3</v>
       </c>
       <c r="F593" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="594">
@@ -14818,10 +14818,10 @@
       </c>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F600" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="601">
@@ -14845,7 +14845,7 @@
         <v>4.5</v>
       </c>
       <c r="F601" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="602">
@@ -14893,7 +14893,7 @@
         <v>4.4</v>
       </c>
       <c r="F603" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="604">
@@ -14965,7 +14965,7 @@
         <v>3.8</v>
       </c>
       <c r="F606" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="607">
@@ -15109,7 +15109,7 @@
         <v>2.4</v>
       </c>
       <c r="F612" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="613">
@@ -15133,7 +15133,7 @@
         <v>2.2</v>
       </c>
       <c r="F613" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="614">
@@ -15154,10 +15154,10 @@
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="F614" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="615">
@@ -15173,15 +15173,15 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>아나</t>
         </is>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="F615" t="n">
-        <v>52.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="616">
@@ -15197,15 +15197,15 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>아나</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="F616" t="n">
-        <v>47.2</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="617">
@@ -15245,15 +15245,15 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="F618" t="n">
-        <v>50.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="619">
@@ -15269,15 +15269,15 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F619" t="n">
-        <v>46.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="620">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F620" t="n">
         <v>48.3</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F621" t="n">
         <v>51.2</v>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="F622" t="n">
         <v>49</v>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="F623" t="n">
         <v>50.5</v>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D624" t="inlineStr"/>
@@ -15397,7 +15397,7 @@
         <v>12.8</v>
       </c>
       <c r="F624" t="n">
-        <v>52.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="625">
@@ -15413,15 +15413,15 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D625" t="inlineStr"/>
       <c r="E625" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F625" t="n">
-        <v>50.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="626">
@@ -15445,7 +15445,7 @@
         <v>12.6</v>
       </c>
       <c r="F626" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="627">
@@ -15541,7 +15541,7 @@
         <v>10.6</v>
       </c>
       <c r="F630" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="631">
@@ -15565,7 +15565,7 @@
         <v>10.3</v>
       </c>
       <c r="F631" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="632">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D632" t="inlineStr"/>
       <c r="E632" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F632" t="n">
         <v>44.4</v>
@@ -15637,7 +15637,7 @@
         <v>9.6</v>
       </c>
       <c r="F634" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="635">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F636" t="n">
         <v>48.3</v>
@@ -15773,15 +15773,15 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F640" t="n">
-        <v>50.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="641">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D641" t="inlineStr"/>
@@ -15805,7 +15805,7 @@
         <v>6.9</v>
       </c>
       <c r="F641" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="642">
@@ -15853,7 +15853,7 @@
         <v>6.8</v>
       </c>
       <c r="F643" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="644">
@@ -15949,7 +15949,7 @@
         <v>6.3</v>
       </c>
       <c r="F647" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="648">
@@ -16013,15 +16013,15 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F650" t="n">
-        <v>51.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="651">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D651" t="inlineStr"/>
@@ -16045,7 +16045,7 @@
         <v>5.2</v>
       </c>
       <c r="F651" t="n">
-        <v>53.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="652">
@@ -16069,7 +16069,7 @@
         <v>4.9</v>
       </c>
       <c r="F652" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="653">
@@ -16117,7 +16117,7 @@
         <v>4.5</v>
       </c>
       <c r="F654" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="655">
@@ -16141,7 +16141,7 @@
         <v>4.3</v>
       </c>
       <c r="F655" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="656">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F656" t="n">
         <v>53.7</v>
@@ -16189,7 +16189,7 @@
         <v>3.8</v>
       </c>
       <c r="F657" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="658">
@@ -16205,15 +16205,15 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F658" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="659">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D659" t="inlineStr"/>
@@ -16237,7 +16237,7 @@
         <v>3.4</v>
       </c>
       <c r="F659" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="660">
@@ -16285,7 +16285,7 @@
         <v>3</v>
       </c>
       <c r="F661" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="662">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F664" t="n">
         <v>47.3</v>
@@ -21277,7 +21277,7 @@
         <v>34.1</v>
       </c>
       <c r="F869" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="870">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="D870" t="inlineStr"/>
       <c r="E870" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="F870" t="n">
         <v>52.7</v>
@@ -21322,10 +21322,10 @@
       </c>
       <c r="D871" t="inlineStr"/>
       <c r="E871" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="F871" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="872">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="D872" t="inlineStr"/>
       <c r="E872" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="F872" t="n">
         <v>47</v>
@@ -21373,7 +21373,7 @@
         <v>21.1</v>
       </c>
       <c r="F873" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="874">
@@ -21394,10 +21394,10 @@
       </c>
       <c r="D874" t="inlineStr"/>
       <c r="E874" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F874" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="875">
@@ -21421,7 +21421,7 @@
         <v>16.9</v>
       </c>
       <c r="F875" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="876">
@@ -21442,10 +21442,10 @@
       </c>
       <c r="D876" t="inlineStr"/>
       <c r="E876" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="F876" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="877">
@@ -21466,10 +21466,10 @@
       </c>
       <c r="D877" t="inlineStr"/>
       <c r="E877" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F877" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="878">
@@ -21493,7 +21493,7 @@
         <v>13</v>
       </c>
       <c r="F878" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="879">
@@ -21541,7 +21541,7 @@
         <v>12.4</v>
       </c>
       <c r="F880" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="881">
@@ -21565,7 +21565,7 @@
         <v>11.5</v>
       </c>
       <c r="F881" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="882">
@@ -21613,7 +21613,7 @@
         <v>11.3</v>
       </c>
       <c r="F883" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="884">
@@ -21637,7 +21637,7 @@
         <v>11.2</v>
       </c>
       <c r="F884" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="885">
@@ -21658,10 +21658,10 @@
       </c>
       <c r="D885" t="inlineStr"/>
       <c r="E885" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="F885" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="886">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="D886" t="inlineStr"/>
       <c r="E886" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F886" t="n">
         <v>51.6</v>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="D887" t="inlineStr"/>
       <c r="E887" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F887" t="n">
         <v>49.4</v>
@@ -21730,7 +21730,7 @@
       </c>
       <c r="D888" t="inlineStr"/>
       <c r="E888" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F888" t="n">
         <v>44</v>
@@ -21781,7 +21781,7 @@
         <v>10.1</v>
       </c>
       <c r="F890" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="891">
@@ -21805,7 +21805,7 @@
         <v>9.9</v>
       </c>
       <c r="F891" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="892">
@@ -21853,7 +21853,7 @@
         <v>9</v>
       </c>
       <c r="F893" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="894">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="D894" t="inlineStr"/>
       <c r="E894" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F894" t="n">
         <v>49.5</v>
@@ -21901,7 +21901,7 @@
         <v>7.9</v>
       </c>
       <c r="F895" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="896">
@@ -21949,7 +21949,7 @@
         <v>7.2</v>
       </c>
       <c r="F897" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="898">
@@ -21973,7 +21973,7 @@
         <v>6.5</v>
       </c>
       <c r="F898" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="899">
@@ -21997,7 +21997,7 @@
         <v>6.3</v>
       </c>
       <c r="F899" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="900">
@@ -22045,7 +22045,7 @@
         <v>5.9</v>
       </c>
       <c r="F901" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="902">
@@ -22093,7 +22093,7 @@
         <v>4.8</v>
       </c>
       <c r="F903" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="904">
@@ -22117,7 +22117,7 @@
         <v>4.8</v>
       </c>
       <c r="F904" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="905">
@@ -22189,7 +22189,7 @@
         <v>3.8</v>
       </c>
       <c r="F907" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="908">
@@ -22213,7 +22213,7 @@
         <v>3.8</v>
       </c>
       <c r="F908" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="909">
@@ -22261,7 +22261,7 @@
         <v>3.4</v>
       </c>
       <c r="F910" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="911">
@@ -22309,7 +22309,7 @@
         <v>3.3</v>
       </c>
       <c r="F912" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="913">
@@ -22333,7 +22333,7 @@
         <v>3.2</v>
       </c>
       <c r="F913" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="914">
@@ -22357,7 +22357,7 @@
         <v>2.9</v>
       </c>
       <c r="F914" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="915">
@@ -22381,7 +22381,7 @@
         <v>2.5</v>
       </c>
       <c r="F915" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="916">
@@ -22405,7 +22405,7 @@
         <v>2.5</v>
       </c>
       <c r="F916" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="917">
@@ -22429,7 +22429,7 @@
         <v>2.4</v>
       </c>
       <c r="F917" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="918">
@@ -22453,7 +22453,7 @@
         <v>2.1</v>
       </c>
       <c r="F918" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="919">
@@ -22498,10 +22498,10 @@
       </c>
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="F920" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="921">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="F921" t="n">
         <v>48.8</v>
@@ -22546,10 +22546,10 @@
       </c>
       <c r="D922" t="inlineStr"/>
       <c r="E922" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="F922" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="923">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="F923" t="n">
         <v>48.1</v>
@@ -22642,7 +22642,7 @@
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="F926" t="n">
         <v>49.9</v>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="F927" t="n">
         <v>51.8</v>
@@ -22690,7 +22690,7 @@
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="F928" t="n">
         <v>46.9</v>
@@ -22717,7 +22717,7 @@
         <v>14.3</v>
       </c>
       <c r="F929" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="930">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F930" t="n">
         <v>51</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D931" t="inlineStr"/>
@@ -22765,7 +22765,7 @@
         <v>12.4</v>
       </c>
       <c r="F931" t="n">
-        <v>52.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="932">
@@ -22781,15 +22781,15 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F932" t="n">
-        <v>50.1</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="933">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="D936" t="inlineStr"/>
       <c r="E936" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F936" t="n">
         <v>48.4</v>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D937" t="inlineStr"/>
@@ -22909,7 +22909,7 @@
         <v>11</v>
       </c>
       <c r="F937" t="n">
-        <v>49.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="938">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D938" t="inlineStr"/>
@@ -22933,7 +22933,7 @@
         <v>10.9</v>
       </c>
       <c r="F938" t="n">
-        <v>53.1</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="939">
@@ -22973,15 +22973,15 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D940" t="inlineStr"/>
       <c r="E940" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F940" t="n">
-        <v>49.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="941">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D941" t="inlineStr"/>
@@ -23005,7 +23005,7 @@
         <v>10.4</v>
       </c>
       <c r="F941" t="n">
-        <v>51.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="942">
@@ -23069,7 +23069,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D944" t="inlineStr"/>
@@ -23077,7 +23077,7 @@
         <v>8.1</v>
       </c>
       <c r="F944" t="n">
-        <v>46.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="945">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D945" t="inlineStr"/>
@@ -23101,7 +23101,7 @@
         <v>8.1</v>
       </c>
       <c r="F945" t="n">
-        <v>51.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="946">
@@ -23117,15 +23117,15 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F946" t="n">
-        <v>49.7</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="947">
@@ -23149,7 +23149,7 @@
         <v>7.3</v>
       </c>
       <c r="F947" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="948">
@@ -23173,7 +23173,7 @@
         <v>7.1</v>
       </c>
       <c r="F948" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="949">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F951" t="n">
         <v>50.6</v>
@@ -23269,7 +23269,7 @@
         <v>5.6</v>
       </c>
       <c r="F952" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="953">
@@ -23365,7 +23365,7 @@
         <v>4.3</v>
       </c>
       <c r="F956" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="957">
@@ -23389,7 +23389,7 @@
         <v>4.2</v>
       </c>
       <c r="F957" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="958">
@@ -23413,7 +23413,7 @@
         <v>4</v>
       </c>
       <c r="F958" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="959">
@@ -23509,7 +23509,7 @@
         <v>3.5</v>
       </c>
       <c r="F962" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="963">
@@ -23533,7 +23533,7 @@
         <v>3.3</v>
       </c>
       <c r="F963" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="964">
@@ -23557,7 +23557,7 @@
         <v>3.1</v>
       </c>
       <c r="F964" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="965">
@@ -23581,7 +23581,7 @@
         <v>3.1</v>
       </c>
       <c r="F965" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="966">
@@ -23605,7 +23605,7 @@
         <v>3.1</v>
       </c>
       <c r="F966" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="967">
@@ -23629,7 +23629,7 @@
         <v>2.6</v>
       </c>
       <c r="F967" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="968">
@@ -23653,7 +23653,7 @@
         <v>2.4</v>
       </c>
       <c r="F968" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="969">
@@ -23677,7 +23677,7 @@
         <v>2.2</v>
       </c>
       <c r="F969" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="970">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F971" t="n">
         <v>48.4</v>
@@ -23746,10 +23746,10 @@
       </c>
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="n">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="F972" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="973">
@@ -23770,7 +23770,7 @@
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="F973" t="n">
         <v>47.9</v>
@@ -23794,10 +23794,10 @@
       </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="F974" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="975">
@@ -23818,10 +23818,10 @@
       </c>
       <c r="D975" t="inlineStr"/>
       <c r="E975" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="F975" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="976">
@@ -23869,7 +23869,7 @@
         <v>15.9</v>
       </c>
       <c r="F977" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="978">
@@ -23890,10 +23890,10 @@
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="F978" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="979">
@@ -23914,7 +23914,7 @@
       </c>
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="F979" t="n">
         <v>47.5</v>
@@ -23938,10 +23938,10 @@
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F980" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="981">
@@ -24037,7 +24037,7 @@
         <v>12.7</v>
       </c>
       <c r="F984" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="985">
@@ -24061,7 +24061,7 @@
         <v>12.3</v>
       </c>
       <c r="F985" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="986">
@@ -24109,7 +24109,7 @@
         <v>11.5</v>
       </c>
       <c r="F987" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="988">
@@ -24133,7 +24133,7 @@
         <v>11.2</v>
       </c>
       <c r="F988" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="989">
@@ -24149,15 +24149,15 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="F989" t="n">
-        <v>53</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="990">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D990" t="inlineStr"/>
@@ -24181,7 +24181,7 @@
         <v>10.6</v>
       </c>
       <c r="F990" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="991">
@@ -24205,7 +24205,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="992">
@@ -24253,7 +24253,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F993" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="994">
@@ -24325,7 +24325,7 @@
         <v>8</v>
       </c>
       <c r="F996" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="997">
@@ -24421,7 +24421,7 @@
         <v>6.5</v>
       </c>
       <c r="F1000" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1001">
@@ -24469,7 +24469,7 @@
         <v>6.2</v>
       </c>
       <c r="F1002" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1003">
@@ -24541,7 +24541,7 @@
         <v>5</v>
       </c>
       <c r="F1005" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1006">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F1009" t="n">
         <v>50.7</v>
@@ -24733,7 +24733,7 @@
         <v>3.9</v>
       </c>
       <c r="F1013" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1014">
@@ -24925,7 +24925,7 @@
         <v>2.2</v>
       </c>
       <c r="F1021" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1022">
@@ -28618,7 +28618,7 @@
       </c>
       <c r="D1175" t="inlineStr"/>
       <c r="E1175" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="F1175" t="n">
         <v>49.7</v>
@@ -28642,7 +28642,7 @@
       </c>
       <c r="D1176" t="inlineStr"/>
       <c r="E1176" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="F1176" t="n">
         <v>46.9</v>
@@ -28666,10 +28666,10 @@
       </c>
       <c r="D1177" t="inlineStr"/>
       <c r="E1177" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="F1177" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1178">
@@ -28690,10 +28690,10 @@
       </c>
       <c r="D1178" t="inlineStr"/>
       <c r="E1178" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="F1178" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1179">
@@ -28714,10 +28714,10 @@
       </c>
       <c r="D1179" t="inlineStr"/>
       <c r="E1179" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="F1179" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1180">
@@ -28733,15 +28733,15 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr"/>
       <c r="E1180" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="F1180" t="n">
-        <v>46.3</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="1181">
@@ -28757,15 +28757,15 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr"/>
       <c r="E1181" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="F1181" t="n">
-        <v>54</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1182">
@@ -28789,7 +28789,7 @@
         <v>16.6</v>
       </c>
       <c r="F1182" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1183">
@@ -28837,7 +28837,7 @@
         <v>13.1</v>
       </c>
       <c r="F1184" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1185">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="D1185" t="inlineStr"/>
       <c r="E1185" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F1185" t="n">
         <v>52.1</v>
@@ -28885,7 +28885,7 @@
         <v>12.9</v>
       </c>
       <c r="F1186" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1187">
@@ -28906,10 +28906,10 @@
       </c>
       <c r="D1187" t="inlineStr"/>
       <c r="E1187" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F1187" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1188">
@@ -28933,7 +28933,7 @@
         <v>11</v>
       </c>
       <c r="F1188" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1189">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="D1189" t="inlineStr"/>
       <c r="E1189" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F1189" t="n">
         <v>53.7</v>
@@ -28978,10 +28978,10 @@
       </c>
       <c r="D1190" t="inlineStr"/>
       <c r="E1190" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="F1190" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1191">
@@ -29005,7 +29005,7 @@
         <v>9.9</v>
       </c>
       <c r="F1191" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1192">
@@ -29021,15 +29021,15 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr"/>
       <c r="E1192" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F1192" t="n">
-        <v>49.7</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="1193">
@@ -29045,15 +29045,15 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr"/>
       <c r="E1193" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>56.4</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1194">
@@ -29069,15 +29069,15 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr"/>
       <c r="E1194" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F1194" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1195">
@@ -29093,15 +29093,15 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr"/>
       <c r="E1195" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="F1195" t="n">
-        <v>50.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1196">
@@ -29122,7 +29122,7 @@
       </c>
       <c r="D1196" t="inlineStr"/>
       <c r="E1196" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F1196" t="n">
         <v>49</v>
@@ -29146,10 +29146,10 @@
       </c>
       <c r="D1197" t="inlineStr"/>
       <c r="E1197" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F1197" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1198">
@@ -29173,7 +29173,7 @@
         <v>7.8</v>
       </c>
       <c r="F1198" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1199">
@@ -29194,7 +29194,7 @@
       </c>
       <c r="D1199" t="inlineStr"/>
       <c r="E1199" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="F1199" t="n">
         <v>52.1</v>
@@ -29221,7 +29221,7 @@
         <v>7.3</v>
       </c>
       <c r="F1200" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1201">
@@ -29245,7 +29245,7 @@
         <v>7.1</v>
       </c>
       <c r="F1201" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1202">
@@ -29261,7 +29261,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr"/>
@@ -29269,7 +29269,7 @@
         <v>7</v>
       </c>
       <c r="F1202" t="n">
-        <v>48.1</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1203">
@@ -29285,7 +29285,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr"/>
@@ -29293,7 +29293,7 @@
         <v>7</v>
       </c>
       <c r="F1203" t="n">
-        <v>45.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1204">
@@ -29309,15 +29309,15 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr"/>
       <c r="E1204" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="F1204" t="n">
-        <v>53.4</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1205">
@@ -29333,15 +29333,15 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1205" t="inlineStr"/>
       <c r="E1205" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F1205" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1206">
@@ -29365,7 +29365,7 @@
         <v>6.4</v>
       </c>
       <c r="F1206" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1207">
@@ -29386,10 +29386,10 @@
       </c>
       <c r="D1207" t="inlineStr"/>
       <c r="E1207" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F1207" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1208">
@@ -29437,7 +29437,7 @@
         <v>5.4</v>
       </c>
       <c r="F1209" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1210">
@@ -29485,7 +29485,7 @@
         <v>5.1</v>
       </c>
       <c r="F1211" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1212">
@@ -29509,7 +29509,7 @@
         <v>4.6</v>
       </c>
       <c r="F1212" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1213">
@@ -29533,7 +29533,7 @@
         <v>4.2</v>
       </c>
       <c r="F1213" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1214">
@@ -29578,10 +29578,10 @@
       </c>
       <c r="D1215" t="inlineStr"/>
       <c r="E1215" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F1215" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1216">
@@ -29602,10 +29602,10 @@
       </c>
       <c r="D1216" t="inlineStr"/>
       <c r="E1216" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1216" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1217">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="D1217" t="inlineStr"/>
       <c r="E1217" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1217" t="n">
         <v>51.9</v>
@@ -29653,7 +29653,7 @@
         <v>3.1</v>
       </c>
       <c r="F1218" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1219">
@@ -29674,10 +29674,10 @@
       </c>
       <c r="D1219" t="inlineStr"/>
       <c r="E1219" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1219" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1220">
@@ -29693,7 +29693,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
         <v>2.8</v>
       </c>
       <c r="F1220" t="n">
-        <v>46.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1221">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr"/>
@@ -29725,7 +29725,7 @@
         <v>2.7</v>
       </c>
       <c r="F1221" t="n">
-        <v>51.3</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1222">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr"/>
@@ -29749,7 +29749,7 @@
         <v>2.7</v>
       </c>
       <c r="F1222" t="n">
-        <v>54</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1223">
@@ -29794,10 +29794,10 @@
       </c>
       <c r="D1224" t="inlineStr"/>
       <c r="E1224" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1224" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1225">
@@ -29821,7 +29821,7 @@
         <v>1.2</v>
       </c>
       <c r="F1225" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="1226">
@@ -29845,7 +29845,7 @@
         <v>7.2</v>
       </c>
       <c r="F1226" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1227">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="D1229" t="inlineStr"/>
       <c r="E1229" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F1229" t="n">
         <v>48.2</v>
@@ -29933,7 +29933,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr"/>
@@ -29941,7 +29941,7 @@
         <v>3.6</v>
       </c>
       <c r="F1230" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1231">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr"/>
@@ -29965,7 +29965,7 @@
         <v>3.6</v>
       </c>
       <c r="F1231" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1232">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="D1237" t="inlineStr"/>
       <c r="E1237" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1237" t="n">
         <v>49</v>
@@ -30181,7 +30181,7 @@
         <v>2.3</v>
       </c>
       <c r="F1240" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1241">
@@ -30205,7 +30205,7 @@
         <v>2.2</v>
       </c>
       <c r="F1241" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1242">
@@ -30277,7 +30277,7 @@
         <v>2.1</v>
       </c>
       <c r="F1244" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1245">
@@ -30301,7 +30301,7 @@
         <v>2</v>
       </c>
       <c r="F1245" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1246">
@@ -30413,7 +30413,7 @@
       </c>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr"/>
@@ -30421,7 +30421,7 @@
         <v>1.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>49.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1251">
@@ -30437,7 +30437,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr"/>
@@ -30445,7 +30445,7 @@
         <v>1.6</v>
       </c>
       <c r="F1251" t="n">
-        <v>51.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1252">
@@ -30517,7 +30517,7 @@
         <v>1.5</v>
       </c>
       <c r="F1254" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1255">
@@ -30541,7 +30541,7 @@
         <v>1.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1256">
@@ -30565,7 +30565,7 @@
         <v>1.4</v>
       </c>
       <c r="F1256" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1257">
@@ -30589,7 +30589,7 @@
         <v>1.3</v>
       </c>
       <c r="F1257" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1258">
@@ -30610,10 +30610,10 @@
       </c>
       <c r="D1258" t="inlineStr"/>
       <c r="E1258" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F1258" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1259">
@@ -30706,7 +30706,7 @@
       </c>
       <c r="D1262" t="inlineStr"/>
       <c r="E1262" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1262" t="n">
         <v>52.4</v>
@@ -30757,7 +30757,7 @@
         <v>1</v>
       </c>
       <c r="F1264" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1265">
@@ -30781,7 +30781,7 @@
         <v>1</v>
       </c>
       <c r="F1265" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1266">
@@ -30805,7 +30805,7 @@
         <v>1</v>
       </c>
       <c r="F1266" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1267">
@@ -30829,7 +30829,7 @@
         <v>1</v>
       </c>
       <c r="F1267" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1268">
@@ -30853,7 +30853,7 @@
         <v>1</v>
       </c>
       <c r="F1268" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1269">
@@ -30877,7 +30877,7 @@
         <v>0.9</v>
       </c>
       <c r="F1269" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1270">
@@ -30901,7 +30901,7 @@
         <v>0.8</v>
       </c>
       <c r="F1270" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="1271">
@@ -30925,7 +30925,7 @@
         <v>0.7</v>
       </c>
       <c r="F1271" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1272">
@@ -30973,7 +30973,7 @@
         <v>0.6</v>
       </c>
       <c r="F1273" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1274">
@@ -31045,7 +31045,7 @@
         <v>0.4</v>
       </c>
       <c r="F1276" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1277">
@@ -31093,7 +31093,7 @@
         <v>4.6</v>
       </c>
       <c r="F1278" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1279">
@@ -31117,7 +31117,7 @@
         <v>4.2</v>
       </c>
       <c r="F1279" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1280">
@@ -31141,7 +31141,7 @@
         <v>4.2</v>
       </c>
       <c r="F1280" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1281">
@@ -31162,10 +31162,10 @@
       </c>
       <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="F1281" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1282">
@@ -31186,10 +31186,10 @@
       </c>
       <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1282" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1283">
@@ -31237,7 +31237,7 @@
         <v>3.1</v>
       </c>
       <c r="F1284" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1285">
@@ -31306,10 +31306,10 @@
       </c>
       <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F1287" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1288">
@@ -31333,7 +31333,7 @@
         <v>3</v>
       </c>
       <c r="F1288" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1289">
@@ -31381,7 +31381,7 @@
         <v>2.6</v>
       </c>
       <c r="F1290" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1291">
@@ -31426,10 +31426,10 @@
       </c>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1292" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1293">
@@ -31477,7 +31477,7 @@
         <v>2.2</v>
       </c>
       <c r="F1294" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1295">
@@ -31501,7 +31501,7 @@
         <v>2.2</v>
       </c>
       <c r="F1295" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1296">
@@ -31525,7 +31525,7 @@
         <v>2.1</v>
       </c>
       <c r="F1296" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1297">
@@ -31549,7 +31549,7 @@
         <v>2</v>
       </c>
       <c r="F1297" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1298">
@@ -31573,7 +31573,7 @@
         <v>1.9</v>
       </c>
       <c r="F1298" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1299">
@@ -31597,7 +31597,7 @@
         <v>1.8</v>
       </c>
       <c r="F1299" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1300">
@@ -31621,7 +31621,7 @@
         <v>1.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1301">
@@ -31645,7 +31645,7 @@
         <v>1.8</v>
       </c>
       <c r="F1301" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1302">
@@ -31669,7 +31669,7 @@
         <v>1.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1303">
@@ -31717,7 +31717,7 @@
         <v>1.5</v>
       </c>
       <c r="F1304" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1305">
@@ -31741,7 +31741,7 @@
         <v>1.5</v>
       </c>
       <c r="F1305" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1306">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1307" t="inlineStr"/>
@@ -31789,7 +31789,7 @@
         <v>1.3</v>
       </c>
       <c r="F1307" t="n">
-        <v>43.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1308">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1308" t="inlineStr"/>
@@ -31813,7 +31813,7 @@
         <v>1.3</v>
       </c>
       <c r="F1308" t="n">
-        <v>45.9</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1309">
@@ -31837,7 +31837,7 @@
         <v>1.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1310">
@@ -31861,7 +31861,7 @@
         <v>1.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>45.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1311">
@@ -31909,7 +31909,7 @@
         <v>1</v>
       </c>
       <c r="F1312" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1313">
@@ -31933,7 +31933,7 @@
         <v>1</v>
       </c>
       <c r="F1313" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1314">
@@ -31957,7 +31957,7 @@
         <v>0.9</v>
       </c>
       <c r="F1314" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1315">
@@ -32029,7 +32029,7 @@
         <v>0.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1318">
@@ -32053,7 +32053,7 @@
         <v>0.9</v>
       </c>
       <c r="F1318" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1319">
@@ -32101,7 +32101,7 @@
         <v>0.7</v>
       </c>
       <c r="F1320" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="1321">
@@ -32125,7 +32125,7 @@
         <v>0.7</v>
       </c>
       <c r="F1321" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1322">
@@ -32146,10 +32146,10 @@
       </c>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F1322" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1323">
@@ -32173,7 +32173,7 @@
         <v>0.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1324">
@@ -32197,7 +32197,7 @@
         <v>0.5</v>
       </c>
       <c r="F1324" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="1325">
@@ -32221,7 +32221,7 @@
         <v>0.4</v>
       </c>
       <c r="F1325" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1326">
@@ -32245,7 +32245,7 @@
         <v>0.4</v>
       </c>
       <c r="F1326" t="n">
-        <v>55.3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1327">
@@ -32269,7 +32269,7 @@
         <v>0.3</v>
       </c>
       <c r="F1327" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1328">
@@ -32341,7 +32341,7 @@
         <v>4.2</v>
       </c>
       <c r="F1330" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1331">
@@ -32533,7 +32533,7 @@
         <v>2.7</v>
       </c>
       <c r="F1338" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1339">
@@ -32549,7 +32549,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1339" t="inlineStr"/>
@@ -32557,7 +32557,7 @@
         <v>2.6</v>
       </c>
       <c r="F1339" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1340">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr"/>
@@ -32581,7 +32581,7 @@
         <v>2.6</v>
       </c>
       <c r="F1340" t="n">
-        <v>49.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1341">
@@ -32605,7 +32605,7 @@
         <v>2.5</v>
       </c>
       <c r="F1341" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1342">
@@ -32621,7 +32621,7 @@
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
         <v>2.2</v>
       </c>
       <c r="F1342" t="n">
-        <v>50.3</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1343">
@@ -32645,7 +32645,7 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1343" t="inlineStr"/>
@@ -32653,7 +32653,7 @@
         <v>2.2</v>
       </c>
       <c r="F1343" t="n">
-        <v>45.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1344">
@@ -32677,7 +32677,7 @@
         <v>2.2</v>
       </c>
       <c r="F1344" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1345">
@@ -32725,7 +32725,7 @@
         <v>2.1</v>
       </c>
       <c r="F1346" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1347">
@@ -32794,10 +32794,10 @@
       </c>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1349" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1350">
@@ -32821,7 +32821,7 @@
         <v>1.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1351">
@@ -32842,10 +32842,10 @@
       </c>
       <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1351" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1352">
@@ -32890,10 +32890,10 @@
       </c>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1353" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1354">
@@ -32941,7 +32941,7 @@
         <v>1.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1356">
@@ -32965,7 +32965,7 @@
         <v>1.4</v>
       </c>
       <c r="F1356" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1357">
@@ -32989,7 +32989,7 @@
         <v>1.3</v>
       </c>
       <c r="F1357" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1358">
@@ -33037,7 +33037,7 @@
         <v>1.3</v>
       </c>
       <c r="F1359" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1360">
@@ -33061,7 +33061,7 @@
         <v>1.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1361">
@@ -33133,7 +33133,7 @@
         <v>1.1</v>
       </c>
       <c r="F1363" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1364">
@@ -33181,7 +33181,7 @@
         <v>1.1</v>
       </c>
       <c r="F1365" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1366">
@@ -33277,7 +33277,7 @@
         <v>0.9</v>
       </c>
       <c r="F1369" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1370">
@@ -33301,7 +33301,7 @@
         <v>0.9</v>
       </c>
       <c r="F1370" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1371">
@@ -33349,7 +33349,7 @@
         <v>0.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1373">
@@ -33397,7 +33397,7 @@
         <v>0.6</v>
       </c>
       <c r="F1374" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1375">
@@ -33445,7 +33445,7 @@
         <v>0.5</v>
       </c>
       <c r="F1376" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1377">
@@ -33469,7 +33469,7 @@
         <v>0.4</v>
       </c>
       <c r="F1377" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1378">
@@ -33493,7 +33493,7 @@
         <v>0.3</v>
       </c>
       <c r="F1378" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1379">
@@ -33565,7 +33565,7 @@
         <v>4.9</v>
       </c>
       <c r="F1381" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1382">
@@ -33613,7 +33613,7 @@
         <v>3.8</v>
       </c>
       <c r="F1383" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1384">
@@ -33637,7 +33637,7 @@
         <v>3.6</v>
       </c>
       <c r="F1384" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1385">
@@ -33653,7 +33653,7 @@
       </c>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr"/>
@@ -33661,7 +33661,7 @@
         <v>3.2</v>
       </c>
       <c r="F1385" t="n">
-        <v>52.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1386">
@@ -33677,7 +33677,7 @@
       </c>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1386" t="inlineStr"/>
@@ -33685,7 +33685,7 @@
         <v>3.2</v>
       </c>
       <c r="F1386" t="n">
-        <v>50.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="1387">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F1389" t="n">
         <v>49.6</v>
@@ -33805,7 +33805,7 @@
         <v>2.6</v>
       </c>
       <c r="F1391" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1392">
@@ -33829,7 +33829,7 @@
         <v>2.2</v>
       </c>
       <c r="F1392" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1393">
@@ -33853,7 +33853,7 @@
         <v>2.1</v>
       </c>
       <c r="F1393" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1394">
@@ -33877,7 +33877,7 @@
         <v>2.1</v>
       </c>
       <c r="F1394" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1395">
@@ -33901,7 +33901,7 @@
         <v>2.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1396">
@@ -33949,7 +33949,7 @@
         <v>2</v>
       </c>
       <c r="F1397" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1398">
@@ -33997,7 +33997,7 @@
         <v>1.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1400">
@@ -34021,7 +34021,7 @@
         <v>1.9</v>
       </c>
       <c r="F1400" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1401">
@@ -34093,7 +34093,7 @@
         <v>1.6</v>
       </c>
       <c r="F1403" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1404">
@@ -34117,7 +34117,7 @@
         <v>1.6</v>
       </c>
       <c r="F1404" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1405">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr"/>
@@ -34165,7 +34165,7 @@
         <v>1.5</v>
       </c>
       <c r="F1406" t="n">
-        <v>42.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1407">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr"/>
@@ -34189,7 +34189,7 @@
         <v>1.5</v>
       </c>
       <c r="F1407" t="n">
-        <v>48.3</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1408">
@@ -34213,7 +34213,7 @@
         <v>1.5</v>
       </c>
       <c r="F1408" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1409">
@@ -34237,7 +34237,7 @@
         <v>1.4</v>
       </c>
       <c r="F1409" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1410">
@@ -34261,7 +34261,7 @@
         <v>1.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1411">
@@ -34285,7 +34285,7 @@
         <v>1.3</v>
       </c>
       <c r="F1411" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1412">
@@ -34333,7 +34333,7 @@
         <v>1.2</v>
       </c>
       <c r="F1413" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1414">
@@ -34354,10 +34354,10 @@
       </c>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1414" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1415">
@@ -34378,7 +34378,7 @@
       </c>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1415" t="n">
         <v>43.3</v>
@@ -34405,7 +34405,7 @@
         <v>1.1</v>
       </c>
       <c r="F1416" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1417">
@@ -34453,7 +34453,7 @@
         <v>1</v>
       </c>
       <c r="F1418" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1419">
@@ -34501,7 +34501,7 @@
         <v>0.9</v>
       </c>
       <c r="F1420" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1421">
@@ -34525,7 +34525,7 @@
         <v>0.9</v>
       </c>
       <c r="F1421" t="n">
-        <v>47.1</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1422">
@@ -34549,7 +34549,7 @@
         <v>0.9</v>
       </c>
       <c r="F1422" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1423">
@@ -34597,7 +34597,7 @@
         <v>0.7</v>
       </c>
       <c r="F1424" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="1425">
@@ -34621,7 +34621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1425" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1426">
@@ -34645,7 +34645,7 @@
         <v>0.6</v>
       </c>
       <c r="F1426" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1427">
@@ -34669,7 +34669,7 @@
         <v>0.6</v>
       </c>
       <c r="F1427" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1428">
@@ -34693,7 +34693,7 @@
         <v>0.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1429">
@@ -34717,7 +34717,7 @@
         <v>0.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1430">
@@ -34789,7 +34789,7 @@
         <v>5.8</v>
       </c>
       <c r="F1432" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1433">
@@ -34829,7 +34829,7 @@
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr"/>
@@ -34837,7 +34837,7 @@
         <v>3.1</v>
       </c>
       <c r="F1434" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1435">
@@ -34853,7 +34853,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr"/>
@@ -34861,7 +34861,7 @@
         <v>3.1</v>
       </c>
       <c r="F1435" t="n">
-        <v>50.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1436">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr"/>
@@ -34885,7 +34885,7 @@
         <v>3</v>
       </c>
       <c r="F1436" t="n">
-        <v>48.7</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1437">
@@ -34901,7 +34901,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
         <v>3</v>
       </c>
       <c r="F1437" t="n">
-        <v>51.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1438">
@@ -34954,7 +34954,7 @@
       </c>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F1439" t="n">
         <v>47.8</v>
@@ -35005,7 +35005,7 @@
         <v>2.5</v>
       </c>
       <c r="F1441" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1442">
@@ -35029,7 +35029,7 @@
         <v>2.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1443">
@@ -35053,7 +35053,7 @@
         <v>2.4</v>
       </c>
       <c r="F1443" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1444">
@@ -35101,7 +35101,7 @@
         <v>2.1</v>
       </c>
       <c r="F1445" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1446">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr"/>
@@ -35125,7 +35125,7 @@
         <v>2.1</v>
       </c>
       <c r="F1446" t="n">
-        <v>49.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1447">
@@ -35141,7 +35141,7 @@
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr"/>
@@ -35149,7 +35149,7 @@
         <v>2.1</v>
       </c>
       <c r="F1447" t="n">
-        <v>52.4</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1448">
@@ -35173,7 +35173,7 @@
         <v>2</v>
       </c>
       <c r="F1448" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1449">
@@ -35213,7 +35213,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr"/>
@@ -35221,7 +35221,7 @@
         <v>1.7</v>
       </c>
       <c r="F1450" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1451">
@@ -35237,7 +35237,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr"/>
@@ -35245,7 +35245,7 @@
         <v>1.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1452">
@@ -35269,7 +35269,7 @@
         <v>1.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1453">
@@ -35293,7 +35293,7 @@
         <v>1.6</v>
       </c>
       <c r="F1453" t="n">
-        <v>53.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1454">
@@ -35317,7 +35317,7 @@
         <v>1.6</v>
       </c>
       <c r="F1454" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1455">
@@ -35365,7 +35365,7 @@
         <v>1.5</v>
       </c>
       <c r="F1456" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1457">
@@ -35381,7 +35381,7 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr"/>
@@ -35389,7 +35389,7 @@
         <v>1.5</v>
       </c>
       <c r="F1457" t="n">
-        <v>48.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1458">
@@ -35405,7 +35405,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr"/>
@@ -35413,7 +35413,7 @@
         <v>1.5</v>
       </c>
       <c r="F1458" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1459">
@@ -35434,10 +35434,10 @@
       </c>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1459" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="1460">
@@ -35461,7 +35461,7 @@
         <v>1.4</v>
       </c>
       <c r="F1460" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1461">
@@ -35477,7 +35477,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr"/>
@@ -35485,7 +35485,7 @@
         <v>1.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1462">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr"/>
@@ -35509,7 +35509,7 @@
         <v>1.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1463">
@@ -35533,7 +35533,7 @@
         <v>1.3</v>
       </c>
       <c r="F1463" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1464">
@@ -35557,7 +35557,7 @@
         <v>1.3</v>
       </c>
       <c r="F1464" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1465">
@@ -35581,7 +35581,7 @@
         <v>1.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1466">
@@ -35605,7 +35605,7 @@
         <v>1.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1467">
@@ -35626,10 +35626,10 @@
       </c>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F1467" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1468">
@@ -35653,7 +35653,7 @@
         <v>1.1</v>
       </c>
       <c r="F1468" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1469">
@@ -35701,7 +35701,7 @@
         <v>1</v>
       </c>
       <c r="F1470" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1471">
@@ -35749,7 +35749,7 @@
         <v>0.8</v>
       </c>
       <c r="F1472" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1473">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr"/>
@@ -35773,7 +35773,7 @@
         <v>0.7</v>
       </c>
       <c r="F1473" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1474">
@@ -35789,7 +35789,7 @@
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr"/>
@@ -35797,7 +35797,7 @@
         <v>0.7</v>
       </c>
       <c r="F1474" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1475">
@@ -35845,7 +35845,7 @@
         <v>0.6</v>
       </c>
       <c r="F1476" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1477">
@@ -35869,7 +35869,7 @@
         <v>0.6</v>
       </c>
       <c r="F1477" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1478">
@@ -35893,7 +35893,7 @@
         <v>0.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1479">
@@ -35941,7 +35941,7 @@
         <v>0.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="1481">
@@ -35965,7 +35965,7 @@
         <v>7.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1482">
@@ -36013,7 +36013,7 @@
         <v>6.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1484">
@@ -36029,7 +36029,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr"/>
@@ -36037,7 +36037,7 @@
         <v>3.9</v>
       </c>
       <c r="F1484" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1485">
@@ -36053,7 +36053,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr"/>
@@ -36061,7 +36061,7 @@
         <v>3.9</v>
       </c>
       <c r="F1485" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1486">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
         <v>3.4</v>
       </c>
       <c r="F1486" t="n">
-        <v>50.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1487">
@@ -36101,7 +36101,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr"/>
@@ -36109,7 +36109,7 @@
         <v>3.4</v>
       </c>
       <c r="F1487" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1488">
@@ -36133,7 +36133,7 @@
         <v>3.3</v>
       </c>
       <c r="F1488" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1489">
@@ -36157,7 +36157,7 @@
         <v>3.2</v>
       </c>
       <c r="F1489" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1490">
@@ -36253,7 +36253,7 @@
         <v>2.3</v>
       </c>
       <c r="F1493" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1494">
@@ -36274,10 +36274,10 @@
       </c>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1495">
@@ -36293,7 +36293,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr"/>
@@ -36301,7 +36301,7 @@
         <v>2.1</v>
       </c>
       <c r="F1495" t="n">
-        <v>47.2</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="1496">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr"/>
@@ -36325,7 +36325,7 @@
         <v>2.1</v>
       </c>
       <c r="F1496" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1497">
@@ -36341,7 +36341,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr"/>
@@ -36349,7 +36349,7 @@
         <v>2.1</v>
       </c>
       <c r="F1497" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1498">
@@ -36365,7 +36365,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr"/>
@@ -36373,7 +36373,7 @@
         <v>2.1</v>
       </c>
       <c r="F1498" t="n">
-        <v>52.2</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1499">
@@ -36397,7 +36397,7 @@
         <v>2</v>
       </c>
       <c r="F1499" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1500">
@@ -36466,10 +36466,10 @@
       </c>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1502" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1503">
@@ -36493,7 +36493,7 @@
         <v>1.7</v>
       </c>
       <c r="F1503" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1504">
@@ -36514,10 +36514,10 @@
       </c>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F1504" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1505">
@@ -36533,7 +36533,7 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
         <v>1.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>43.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1506">
@@ -36557,7 +36557,7 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr"/>
@@ -36565,7 +36565,7 @@
         <v>1.5</v>
       </c>
       <c r="F1506" t="n">
-        <v>49.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="1507">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1507" t="n">
         <v>49.8</v>
@@ -36613,7 +36613,7 @@
         <v>1.4</v>
       </c>
       <c r="F1508" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1509">
@@ -36637,7 +36637,7 @@
         <v>1.4</v>
       </c>
       <c r="F1509" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="1510">
@@ -36661,7 +36661,7 @@
         <v>1.4</v>
       </c>
       <c r="F1510" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1511">
@@ -36709,7 +36709,7 @@
         <v>1.2</v>
       </c>
       <c r="F1512" t="n">
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1513">
@@ -36730,10 +36730,10 @@
       </c>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1513" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1514">
@@ -36754,10 +36754,10 @@
       </c>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1514" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="1515">
@@ -36781,7 +36781,7 @@
         <v>1.1</v>
       </c>
       <c r="F1515" t="n">
-        <v>47.9</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1516">
@@ -36805,7 +36805,7 @@
         <v>1.1</v>
       </c>
       <c r="F1516" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1517">
@@ -36829,7 +36829,7 @@
         <v>1</v>
       </c>
       <c r="F1517" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1518">
@@ -36853,7 +36853,7 @@
         <v>1</v>
       </c>
       <c r="F1518" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1519">
@@ -36877,7 +36877,7 @@
         <v>0.9</v>
       </c>
       <c r="F1519" t="n">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1520">
@@ -36898,10 +36898,10 @@
       </c>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1520" t="n">
-        <v>49.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1521">
@@ -36925,7 +36925,7 @@
         <v>0.8</v>
       </c>
       <c r="F1521" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1522">
@@ -36941,7 +36941,7 @@
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr"/>
@@ -36949,7 +36949,7 @@
         <v>0.8</v>
       </c>
       <c r="F1522" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1523">
@@ -36965,7 +36965,7 @@
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr"/>
@@ -36973,7 +36973,7 @@
         <v>0.8</v>
       </c>
       <c r="F1523" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1524">
@@ -36997,7 +36997,7 @@
         <v>0.7</v>
       </c>
       <c r="F1524" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1525">
@@ -37021,7 +37021,7 @@
         <v>0.6</v>
       </c>
       <c r="F1525" t="n">
-        <v>44.9</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1526">
@@ -37045,7 +37045,7 @@
         <v>0.6</v>
       </c>
       <c r="F1526" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1527">
@@ -37069,7 +37069,7 @@
         <v>0.5</v>
       </c>
       <c r="F1527" t="n">
-        <v>48.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1528">
@@ -37093,7 +37093,7 @@
         <v>0.4</v>
       </c>
       <c r="F1528" t="n">
-        <v>52.9</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="1529">
@@ -37117,7 +37117,7 @@
         <v>0.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1530">
@@ -37141,7 +37141,7 @@
         <v>0.3</v>
       </c>
       <c r="F1530" t="n">
-        <v>41.6</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1531">
@@ -37165,7 +37165,7 @@
         <v>0.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>40.8</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="1532">
@@ -37186,7 +37186,7 @@
       </c>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F1532" t="n">
         <v>46</v>
@@ -37213,7 +37213,7 @@
         <v>6.7</v>
       </c>
       <c r="F1533" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="1534">
@@ -37234,10 +37234,10 @@
       </c>
       <c r="D1534" t="inlineStr"/>
       <c r="E1534" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F1534" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1535">
@@ -37258,10 +37258,10 @@
       </c>
       <c r="D1535" t="inlineStr"/>
       <c r="E1535" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F1535" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1536">
@@ -37285,7 +37285,7 @@
         <v>4.3</v>
       </c>
       <c r="F1536" t="n">
-        <v>45.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1537">
@@ -37306,10 +37306,10 @@
       </c>
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F1537" t="n">
-        <v>53.5</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="1538">
@@ -37333,7 +37333,7 @@
         <v>4.2</v>
       </c>
       <c r="F1538" t="n">
-        <v>44.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1539">
@@ -37349,7 +37349,7 @@
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr"/>
@@ -37357,7 +37357,7 @@
         <v>3.6</v>
       </c>
       <c r="F1539" t="n">
-        <v>46.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1540">
@@ -37373,7 +37373,7 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr"/>
@@ -37381,7 +37381,7 @@
         <v>3.6</v>
       </c>
       <c r="F1540" t="n">
-        <v>49.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1541">
@@ -37405,7 +37405,7 @@
         <v>3.1</v>
       </c>
       <c r="F1541" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1542">
@@ -37421,15 +37421,15 @@
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1542" t="n">
-        <v>46.7</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="1543">
@@ -37445,15 +37445,15 @@
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F1543" t="n">
-        <v>37</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1544">
@@ -37477,7 +37477,7 @@
         <v>2.9</v>
       </c>
       <c r="F1544" t="n">
-        <v>40.2</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="1545">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="D1545" t="inlineStr"/>
       <c r="E1545" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1545" t="n">
         <v>39.7</v>
@@ -37522,10 +37522,10 @@
       </c>
       <c r="D1546" t="inlineStr"/>
       <c r="E1546" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>46.2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1547">
@@ -37541,15 +37541,15 @@
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr"/>
       <c r="E1547" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1547" t="n">
-        <v>46.5</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1548">
@@ -37565,7 +37565,7 @@
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr"/>
@@ -37573,7 +37573,7 @@
         <v>2</v>
       </c>
       <c r="F1548" t="n">
-        <v>53.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1549">
@@ -37597,7 +37597,7 @@
         <v>1.9</v>
       </c>
       <c r="F1549" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1550">
@@ -37621,7 +37621,7 @@
         <v>1.9</v>
       </c>
       <c r="F1550" t="n">
-        <v>45.1</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="1551">
@@ -37637,15 +37637,15 @@
       </c>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr"/>
       <c r="E1551" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1551" t="n">
-        <v>41.2</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1552">
@@ -37661,15 +37661,15 @@
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr"/>
       <c r="E1552" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1552" t="n">
-        <v>49</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="1553">
@@ -37690,10 +37690,10 @@
       </c>
       <c r="D1553" t="inlineStr"/>
       <c r="E1553" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F1553" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1554">
@@ -37709,15 +37709,15 @@
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr"/>
       <c r="E1554" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F1554" t="n">
-        <v>50</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1555">
@@ -37733,7 +37733,7 @@
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr"/>
@@ -37741,7 +37741,7 @@
         <v>1.6</v>
       </c>
       <c r="F1555" t="n">
-        <v>46.1</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="1556">
@@ -37757,15 +37757,15 @@
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1556" t="n">
-        <v>55.1</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1557">
@@ -37789,7 +37789,7 @@
         <v>1.5</v>
       </c>
       <c r="F1557" t="n">
-        <v>41.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="1558">
@@ -37810,10 +37810,10 @@
       </c>
       <c r="D1558" t="inlineStr"/>
       <c r="E1558" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F1558" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="1559">
@@ -37837,7 +37837,7 @@
         <v>1.3</v>
       </c>
       <c r="F1559" t="n">
-        <v>50.9</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1560">
@@ -37861,7 +37861,7 @@
         <v>1.3</v>
       </c>
       <c r="F1560" t="n">
-        <v>36</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="1561">
@@ -37885,7 +37885,7 @@
         <v>1.3</v>
       </c>
       <c r="F1561" t="n">
-        <v>47</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1562">
@@ -37909,7 +37909,7 @@
         <v>1.3</v>
       </c>
       <c r="F1562" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1563">
@@ -37933,7 +37933,7 @@
         <v>1.1</v>
       </c>
       <c r="F1563" t="n">
-        <v>40</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="1564">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr"/>
@@ -37981,7 +37981,7 @@
         <v>1</v>
       </c>
       <c r="F1565" t="n">
-        <v>45.8</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1566">
@@ -37997,7 +37997,7 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr"/>
@@ -38005,7 +38005,7 @@
         <v>1</v>
       </c>
       <c r="F1566" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1567">
@@ -38029,7 +38029,7 @@
         <v>0.9</v>
       </c>
       <c r="F1567" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1568">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr"/>
@@ -38053,7 +38053,7 @@
         <v>0.9</v>
       </c>
       <c r="F1568" t="n">
-        <v>51.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1569">
@@ -38069,15 +38069,15 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr"/>
       <c r="E1569" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F1569" t="n">
-        <v>49.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1570">
@@ -38101,7 +38101,7 @@
         <v>0.8</v>
       </c>
       <c r="F1570" t="n">
-        <v>58.6</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="1571">
@@ -38125,7 +38125,7 @@
         <v>0.8</v>
       </c>
       <c r="F1571" t="n">
-        <v>56.7</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="1572">
@@ -38146,10 +38146,10 @@
       </c>
       <c r="D1572" t="inlineStr"/>
       <c r="E1572" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F1572" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="1573">
@@ -38165,7 +38165,7 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr"/>
@@ -38173,7 +38173,7 @@
         <v>0.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>74.90000000000001</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="1574">
@@ -38189,7 +38189,7 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr"/>
@@ -38197,7 +38197,7 @@
         <v>0.6</v>
       </c>
       <c r="F1574" t="n">
-        <v>36</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="1575">
@@ -38221,7 +38221,7 @@
         <v>0.5</v>
       </c>
       <c r="F1575" t="n">
-        <v>56.3</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="1576">
@@ -38237,7 +38237,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr"/>
@@ -38245,7 +38245,7 @@
         <v>0.5</v>
       </c>
       <c r="F1576" t="n">
-        <v>39.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="1577">
@@ -38261,7 +38261,7 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr"/>
@@ -38269,7 +38269,7 @@
         <v>0.5</v>
       </c>
       <c r="F1577" t="n">
-        <v>51.5</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="1578">
@@ -38285,15 +38285,15 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr"/>
       <c r="E1578" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1578" t="n">
-        <v>52.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="1579">
@@ -38309,7 +38309,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr"/>
@@ -38317,7 +38317,7 @@
         <v>0.4</v>
       </c>
       <c r="F1579" t="n">
-        <v>50.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1580">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr"/>
@@ -38341,7 +38341,7 @@
         <v>0.4</v>
       </c>
       <c r="F1580" t="n">
-        <v>51.2</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1581">
@@ -38410,7 +38410,7 @@
       </c>
       <c r="D1583" t="inlineStr"/>
       <c r="E1583" t="n">
-        <v>19.6</v>
+        <v>17.1</v>
       </c>
       <c r="F1583" t="n">
         <v>47.3</v>
@@ -38434,7 +38434,7 @@
       </c>
       <c r="D1584" t="inlineStr"/>
       <c r="E1584" t="n">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
       <c r="F1584" t="n">
         <v>39.1</v>
@@ -38458,10 +38458,10 @@
       </c>
       <c r="D1585" t="inlineStr"/>
       <c r="E1585" t="n">
-        <v>14.1</v>
+        <v>12.8</v>
       </c>
       <c r="F1585" t="n">
-        <v>19.3</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="1586">
@@ -38482,10 +38482,10 @@
       </c>
       <c r="D1586" t="inlineStr"/>
       <c r="E1586" t="n">
-        <v>7.1</v>
+        <v>10.4</v>
       </c>
       <c r="F1586" t="n">
-        <v>88.3</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="1587">
@@ -38501,15 +38501,15 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr"/>
       <c r="E1587" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F1587" t="n">
-        <v>82.3</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="1588">
@@ -38525,15 +38525,15 @@
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr"/>
       <c r="E1588" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="F1588" t="n">
-        <v>26.3</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="1589">
@@ -38549,15 +38549,15 @@
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr"/>
       <c r="E1589" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F1589" t="n">
-        <v>12.5</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="1590">
@@ -38573,15 +38573,15 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr"/>
       <c r="E1590" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="F1590" t="n">
-        <v>84.59999999999999</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="1591">
@@ -38597,15 +38597,15 @@
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr"/>
       <c r="E1591" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F1591" t="n">
-        <v>49.4</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="1592">
@@ -38621,15 +38621,15 @@
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr"/>
       <c r="E1592" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1592" t="n">
-        <v>87.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="1593">
@@ -38645,15 +38645,15 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D1593" t="inlineStr"/>
       <c r="E1593" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1593" t="n">
-        <v>73</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="1594">
@@ -38669,15 +38669,15 @@
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr"/>
       <c r="E1594" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1594" t="n">
-        <v>13.3</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="1595">
@@ -38693,15 +38693,15 @@
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr"/>
       <c r="E1595" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1595" t="n">
-        <v>69.90000000000001</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="1596">
@@ -38717,15 +38717,15 @@
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr"/>
       <c r="E1596" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F1596" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1597">
@@ -38746,7 +38746,7 @@
       </c>
       <c r="D1597" t="inlineStr"/>
       <c r="E1597" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F1597" t="n">
         <v>42.9</v>
@@ -38770,7 +38770,7 @@
       </c>
       <c r="D1598" t="inlineStr"/>
       <c r="E1598" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F1598" t="n">
         <v>100</v>
@@ -38789,15 +38789,15 @@
       </c>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr"/>
       <c r="E1599" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F1599" t="n">
-        <v>100</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="1600">
@@ -38813,15 +38813,15 @@
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr"/>
       <c r="E1600" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F1600" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1601">
@@ -38837,15 +38837,15 @@
       </c>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr"/>
       <c r="E1601" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F1601" t="n">
-        <v>28.1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1602">
@@ -38861,15 +38861,15 @@
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr"/>
       <c r="E1602" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1602" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="1603">
@@ -38885,15 +38885,15 @@
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>바스티온</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr"/>
       <c r="E1603" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F1603" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1604">
@@ -38909,15 +38909,15 @@
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr"/>
       <c r="E1604" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F1604" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="1605">
@@ -38933,15 +38933,15 @@
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr"/>
       <c r="E1605" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F1605" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="1606">
@@ -38957,15 +38957,15 @@
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr"/>
       <c r="E1606" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F1606" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1607">
@@ -38981,15 +38981,15 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr"/>
       <c r="E1607" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F1607" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1608">
@@ -39005,15 +39005,15 @@
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>바스티온</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr"/>
       <c r="E1608" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F1608" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1609">
@@ -39029,15 +39029,15 @@
       </c>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr"/>
       <c r="E1609" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F1609" t="n">
-        <v>100</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="1610">
@@ -39053,15 +39053,15 @@
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr"/>
       <c r="E1610" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F1610" t="n">
-        <v>0</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="1611">
@@ -39077,12 +39077,12 @@
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr"/>
       <c r="E1611" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F1611" t="n">
         <v>100</v>
@@ -39101,12 +39101,12 @@
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1612" t="inlineStr"/>
       <c r="E1612" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1612" t="n">
         <v>0</v>
@@ -39125,15 +39125,15 @@
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1613" t="inlineStr"/>
       <c r="E1613" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1613" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1614">
@@ -39149,14 +39149,110 @@
       </c>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr"/>
       <c r="E1614" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1614" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>한조</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr"/>
+      <c r="E1615" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>벤데타</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr"/>
+      <c r="E1616" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>엠레</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr"/>
+      <c r="E1617" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>GRANDMASTER</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>제트팩 캣</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr"/>
+      <c r="E1618" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1618" t="n">
         <v>100</v>
       </c>
     </row>

--- a/ow_hero_stats_v6.xlsx
+++ b/ow_hero_stats_v6.xlsx
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F104" t="n">
         <v>50.1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="F106" t="n">
         <v>52.7</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="F108" t="n">
         <v>47.7</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="F109" t="n">
         <v>49.2</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="F111" t="n">
         <v>51.9</v>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
         <v>14</v>
       </c>
       <c r="F112" t="n">
-        <v>46.6</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="113">
@@ -3125,15 +3125,15 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F113" t="n">
-        <v>53.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="114">
@@ -3157,7 +3157,7 @@
         <v>12.8</v>
       </c>
       <c r="F114" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="115">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F115" t="n">
         <v>51.1</v>
@@ -3202,10 +3202,10 @@
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="F116" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="117">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F117" t="n">
         <v>43.4</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
         <v>10.6</v>
       </c>
       <c r="F119" t="n">
-        <v>48.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="120">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3301,7 +3301,7 @@
         <v>10.5</v>
       </c>
       <c r="F120" t="n">
-        <v>51.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="121">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="F121" t="n">
         <v>51.5</v>
@@ -3346,10 +3346,10 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="123">
@@ -3370,10 +3370,10 @@
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F123" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="124">
@@ -3389,15 +3389,15 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="F124" t="n">
-        <v>45.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
         <v>8.9</v>
       </c>
       <c r="F125" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="126">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F126" t="n">
         <v>50</v>
@@ -3469,7 +3469,7 @@
         <v>8.1</v>
       </c>
       <c r="F127" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="128">
@@ -3493,7 +3493,7 @@
         <v>7.8</v>
       </c>
       <c r="F128" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="129">
@@ -3541,7 +3541,7 @@
         <v>7.7</v>
       </c>
       <c r="F130" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="131">
@@ -3586,10 +3586,10 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="F132" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="133">
@@ -3605,15 +3605,15 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="F133" t="n">
-        <v>53.6</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="134">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
         <v>6.4</v>
       </c>
       <c r="F134" t="n">
-        <v>49.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="135">
@@ -3653,15 +3653,15 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="F135" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="136">
@@ -3685,7 +3685,7 @@
         <v>6</v>
       </c>
       <c r="F136" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="137">
@@ -3709,7 +3709,7 @@
         <v>5.9</v>
       </c>
       <c r="F137" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="138">
@@ -3733,7 +3733,7 @@
         <v>5.7</v>
       </c>
       <c r="F138" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="139">
@@ -3757,7 +3757,7 @@
         <v>5.5</v>
       </c>
       <c r="F139" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140">
@@ -3805,7 +3805,7 @@
         <v>4.9</v>
       </c>
       <c r="F141" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="142">
@@ -3829,7 +3829,7 @@
         <v>3.6</v>
       </c>
       <c r="F142" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="143">
@@ -3845,15 +3845,15 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F143" t="n">
-        <v>50.3</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="144">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3877,7 +3877,7 @@
         <v>3.5</v>
       </c>
       <c r="F144" t="n">
-        <v>51.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="145">
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="F145" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="146">
@@ -3949,7 +3949,7 @@
         <v>3.2</v>
       </c>
       <c r="F147" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="148">
@@ -3970,10 +3970,10 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F148" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="149">
@@ -3997,7 +3997,7 @@
         <v>2.7</v>
       </c>
       <c r="F149" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="150">
@@ -4021,7 +4021,7 @@
         <v>2.7</v>
       </c>
       <c r="F150" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="151">
@@ -4045,7 +4045,7 @@
         <v>2.5</v>
       </c>
       <c r="F151" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="152">
@@ -4069,7 +4069,7 @@
         <v>2.4</v>
       </c>
       <c r="F152" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="153">
@@ -4093,7 +4093,7 @@
         <v>2.2</v>
       </c>
       <c r="F153" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="154">
@@ -9034,10 +9034,10 @@
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="n">
-        <v>54.1</v>
+        <v>53.8</v>
       </c>
       <c r="F359" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="360">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="F360" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="361">
@@ -9082,10 +9082,10 @@
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="F361" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="362">
@@ -9106,10 +9106,10 @@
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="F362" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="363">
@@ -9130,10 +9130,10 @@
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="F363" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="364">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="F364" t="n">
         <v>56.7</v>
@@ -9178,10 +9178,10 @@
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="F365" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="366">
@@ -9202,10 +9202,10 @@
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="F366" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="367">
@@ -9226,10 +9226,10 @@
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F367" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="368">
@@ -9253,7 +9253,7 @@
         <v>14.5</v>
       </c>
       <c r="F368" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="369">
@@ -9274,10 +9274,10 @@
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="F369" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="370">
@@ -9298,10 +9298,10 @@
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F370" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="371">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="F372" t="n">
         <v>50</v>
@@ -9370,10 +9370,10 @@
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F373" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="374">
@@ -9421,7 +9421,7 @@
         <v>8.6</v>
       </c>
       <c r="F375" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="376">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F376" t="n">
         <v>56.7</v>
@@ -9466,10 +9466,10 @@
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F377" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="378">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F378" t="n">
         <v>47.2</v>
@@ -9509,15 +9509,15 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="F379" t="n">
-        <v>45.2</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="380">
@@ -9533,15 +9533,15 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="F380" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="381">
@@ -9557,15 +9557,15 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="F381" t="n">
-        <v>45.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="382">
@@ -9581,15 +9581,15 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="F382" t="n">
-        <v>46.7</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="383">
@@ -9610,10 +9610,10 @@
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F383" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="384">
@@ -9634,10 +9634,10 @@
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F384" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="385">
@@ -9653,15 +9653,15 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F385" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="386">
@@ -9677,15 +9677,15 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F386" t="n">
-        <v>50.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="387">
@@ -9701,15 +9701,15 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F387" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="388">
@@ -9730,10 +9730,10 @@
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F388" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="389">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
         <v>4.4</v>
       </c>
       <c r="F389" t="n">
-        <v>45.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="390">
@@ -9773,15 +9773,15 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>시메트라</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F390" t="n">
-        <v>53.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="391">
@@ -9797,15 +9797,15 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>시메트라</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="F391" t="n">
-        <v>41.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="392">
@@ -9821,15 +9821,15 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F392" t="n">
-        <v>44.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="393">
@@ -9850,10 +9850,10 @@
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F393" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="394">
@@ -9877,7 +9877,7 @@
         <v>3.8</v>
       </c>
       <c r="F394" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="395">
@@ -9901,7 +9901,7 @@
         <v>3.3</v>
       </c>
       <c r="F395" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="396">
@@ -9925,7 +9925,7 @@
         <v>3.1</v>
       </c>
       <c r="F396" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="397">
@@ -9946,10 +9946,10 @@
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F397" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="398">
@@ -9973,7 +9973,7 @@
         <v>2.9</v>
       </c>
       <c r="F398" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="399">
@@ -10021,7 +10021,7 @@
         <v>2.9</v>
       </c>
       <c r="F400" t="n">
-        <v>45.7</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="401">
@@ -10045,7 +10045,7 @@
         <v>2.9</v>
       </c>
       <c r="F401" t="n">
-        <v>39</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="402">
@@ -10093,7 +10093,7 @@
         <v>2.7</v>
       </c>
       <c r="F403" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="404">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10117,7 +10117,7 @@
         <v>2.6</v>
       </c>
       <c r="F404" t="n">
-        <v>50.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="405">
@@ -10133,15 +10133,15 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F405" t="n">
-        <v>48.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="406">
@@ -10162,10 +10162,10 @@
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F406" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="407">
@@ -10186,10 +10186,10 @@
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F407" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="408">
@@ -10213,7 +10213,7 @@
         <v>1.3</v>
       </c>
       <c r="F408" t="n">
-        <v>42</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="409">
@@ -10237,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="F409" t="n">
-        <v>48.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="410">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="F411" t="n">
         <v>52.5</v>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="F413" t="n">
         <v>47</v>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="F414" t="n">
         <v>50.4</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F415" t="n">
         <v>49.9</v>
@@ -10426,10 +10426,10 @@
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="F417" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="418">
@@ -10450,10 +10450,10 @@
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="F418" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="419">
@@ -10498,10 +10498,10 @@
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F420" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="421">
@@ -10517,15 +10517,15 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="F421" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="422">
@@ -10541,15 +10541,15 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F422" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="423">
@@ -10573,7 +10573,7 @@
         <v>12.1</v>
       </c>
       <c r="F423" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="424">
@@ -10594,10 +10594,10 @@
       </c>
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F424" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="425">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="F428" t="n">
         <v>44.2</v>
@@ -10741,7 +10741,7 @@
         <v>10</v>
       </c>
       <c r="F430" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="431">
@@ -10765,7 +10765,7 @@
         <v>10</v>
       </c>
       <c r="F431" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="432">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F432" t="n">
         <v>49.9</v>
@@ -10885,7 +10885,7 @@
         <v>7.3</v>
       </c>
       <c r="F436" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="437">
@@ -10906,10 +10906,10 @@
       </c>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F437" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="438">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D438" t="inlineStr"/>
       <c r="E438" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F438" t="n">
         <v>50.8</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="D439" t="inlineStr"/>
       <c r="E439" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F439" t="n">
         <v>44.6</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D440" t="inlineStr"/>
       <c r="E440" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F440" t="n">
         <v>50.3</v>
@@ -11021,15 +11021,15 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
       <c r="E442" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F442" t="n">
-        <v>49.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="443">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -11053,7 +11053,7 @@
         <v>6.3</v>
       </c>
       <c r="F443" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="444">
@@ -11077,7 +11077,7 @@
         <v>5.4</v>
       </c>
       <c r="F444" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="445">
@@ -11101,7 +11101,7 @@
         <v>5.4</v>
       </c>
       <c r="F445" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="446">
@@ -11117,15 +11117,15 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="F446" t="n">
-        <v>47.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="447">
@@ -11141,15 +11141,15 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F447" t="n">
-        <v>51</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="448">
@@ -11170,10 +11170,10 @@
       </c>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F448" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="449">
@@ -11221,7 +11221,7 @@
         <v>4.6</v>
       </c>
       <c r="F450" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="451">
@@ -11341,7 +11341,7 @@
         <v>3.1</v>
       </c>
       <c r="F455" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="456">
@@ -11413,7 +11413,7 @@
         <v>2.9</v>
       </c>
       <c r="F458" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="459">
@@ -11437,7 +11437,7 @@
         <v>2.6</v>
       </c>
       <c r="F459" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="460">
@@ -11461,7 +11461,7 @@
         <v>2.1</v>
       </c>
       <c r="F460" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="461">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="F615" t="n">
         <v>47.2</v>
@@ -15202,10 +15202,10 @@
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="n">
-        <v>28.1</v>
+        <v>27.4</v>
       </c>
       <c r="F616" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="617">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="F618" t="n">
         <v>46.5</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="F619" t="n">
         <v>50.7</v>
@@ -15301,7 +15301,7 @@
         <v>17</v>
       </c>
       <c r="F620" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="621">
@@ -15322,10 +15322,10 @@
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="F621" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="622">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="F622" t="n">
         <v>49</v>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="D623" t="inlineStr"/>
       <c r="E623" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F623" t="n">
         <v>50.5</v>
@@ -15394,10 +15394,10 @@
       </c>
       <c r="D624" t="inlineStr"/>
       <c r="E624" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F624" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="625">
@@ -15421,7 +15421,7 @@
         <v>12.7</v>
       </c>
       <c r="F625" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="626">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="D627" t="inlineStr"/>
       <c r="E627" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F627" t="n">
         <v>50.8</v>
@@ -15541,7 +15541,7 @@
         <v>10.7</v>
       </c>
       <c r="F630" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="631">
@@ -15562,10 +15562,10 @@
       </c>
       <c r="D631" t="inlineStr"/>
       <c r="E631" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F631" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="632">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D632" t="inlineStr"/>
       <c r="E632" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F632" t="n">
         <v>44.4</v>
@@ -15634,10 +15634,10 @@
       </c>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F634" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="635">
@@ -15661,7 +15661,7 @@
         <v>9.4</v>
       </c>
       <c r="F635" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="636">
@@ -15709,7 +15709,7 @@
         <v>8.1</v>
       </c>
       <c r="F637" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="638">
@@ -15754,10 +15754,10 @@
       </c>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F639" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="640">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F640" t="n">
         <v>50.8</v>
@@ -15877,7 +15877,7 @@
         <v>6.6</v>
       </c>
       <c r="F644" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="645">
@@ -15901,7 +15901,7 @@
         <v>6.5</v>
       </c>
       <c r="F645" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="646">
@@ -15946,10 +15946,10 @@
       </c>
       <c r="D647" t="inlineStr"/>
       <c r="E647" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F647" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="648">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D648" t="inlineStr"/>
@@ -15973,7 +15973,7 @@
         <v>5.8</v>
       </c>
       <c r="F648" t="n">
-        <v>46.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="649">
@@ -15989,15 +15989,15 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D649" t="inlineStr"/>
       <c r="E649" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F649" t="n">
-        <v>49.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="650">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F652" t="n">
         <v>50.5</v>
@@ -16093,7 +16093,7 @@
         <v>4.6</v>
       </c>
       <c r="F653" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="654">
@@ -16117,7 +16117,7 @@
         <v>4.5</v>
       </c>
       <c r="F654" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="655">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F655" t="n">
         <v>50.8</v>
@@ -16162,10 +16162,10 @@
       </c>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F656" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="657">
@@ -16189,7 +16189,7 @@
         <v>3.8</v>
       </c>
       <c r="F657" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="658">
@@ -16237,7 +16237,7 @@
         <v>3.4</v>
       </c>
       <c r="F659" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="660">
@@ -16285,7 +16285,7 @@
         <v>3</v>
       </c>
       <c r="F661" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="662">
@@ -16309,7 +16309,7 @@
         <v>2.7</v>
       </c>
       <c r="F662" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="663">
@@ -16333,7 +16333,7 @@
         <v>2.6</v>
       </c>
       <c r="F663" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="664">
@@ -16357,7 +16357,7 @@
         <v>2</v>
       </c>
       <c r="F664" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="665">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="D667" t="inlineStr"/>
       <c r="E667" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="F667" t="n">
         <v>51</v>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="D669" t="inlineStr"/>
       <c r="E669" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="F669" t="n">
         <v>50.8</v>
@@ -16498,7 +16498,7 @@
       </c>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="F670" t="n">
         <v>50.1</v>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="D671" t="inlineStr"/>
       <c r="E671" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F671" t="n">
         <v>51.8</v>
@@ -16549,7 +16549,7 @@
         <v>16</v>
       </c>
       <c r="F672" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="673">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F675" t="n">
         <v>45.4</v>
@@ -16642,10 +16642,10 @@
       </c>
       <c r="D676" t="inlineStr"/>
       <c r="E676" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="F676" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="677">
@@ -16669,7 +16669,7 @@
         <v>11.6</v>
       </c>
       <c r="F677" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="678">
@@ -16690,10 +16690,10 @@
       </c>
       <c r="D678" t="inlineStr"/>
       <c r="E678" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F678" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="679">
@@ -16733,15 +16733,15 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F680" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="681">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D681" t="inlineStr"/>
@@ -16765,7 +16765,7 @@
         <v>10.8</v>
       </c>
       <c r="F681" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="682">
@@ -16786,10 +16786,10 @@
       </c>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F682" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="683">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F685" t="n">
         <v>50.3</v>
@@ -16882,10 +16882,10 @@
       </c>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="F686" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="687">
@@ -16930,10 +16930,10 @@
       </c>
       <c r="D688" t="inlineStr"/>
       <c r="E688" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F688" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="689">
@@ -16957,7 +16957,7 @@
         <v>8</v>
       </c>
       <c r="F689" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="690">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F690" t="n">
         <v>44.8</v>
@@ -16997,15 +16997,15 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D691" t="inlineStr"/>
       <c r="E691" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F691" t="n">
-        <v>51.3</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="692">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D692" t="inlineStr"/>
@@ -17029,7 +17029,7 @@
         <v>7.7</v>
       </c>
       <c r="F692" t="n">
-        <v>44.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="693">
@@ -17053,7 +17053,7 @@
         <v>7.2</v>
       </c>
       <c r="F693" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="694">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="D694" t="inlineStr"/>
       <c r="E694" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F694" t="n">
         <v>53.7</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="D696" t="inlineStr"/>
       <c r="E696" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="F696" t="n">
         <v>50.8</v>
@@ -17146,10 +17146,10 @@
       </c>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="F697" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="698">
@@ -17173,7 +17173,7 @@
         <v>6</v>
       </c>
       <c r="F698" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="699">
@@ -17197,7 +17197,7 @@
         <v>5.9</v>
       </c>
       <c r="F699" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="700">
@@ -17218,10 +17218,10 @@
       </c>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="F700" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="701">
@@ -17245,7 +17245,7 @@
         <v>5.2</v>
       </c>
       <c r="F701" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="702">
@@ -17269,7 +17269,7 @@
         <v>5.2</v>
       </c>
       <c r="F702" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="703">
@@ -17317,7 +17317,7 @@
         <v>4.9</v>
       </c>
       <c r="F704" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="705">
@@ -17365,7 +17365,7 @@
         <v>4.7</v>
       </c>
       <c r="F706" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="707">
@@ -17410,10 +17410,10 @@
       </c>
       <c r="D708" t="inlineStr"/>
       <c r="E708" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F708" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="709">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="D709" t="inlineStr"/>
       <c r="E709" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F709" t="n">
         <v>52</v>
@@ -17461,7 +17461,7 @@
         <v>3.3</v>
       </c>
       <c r="F710" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="711">
@@ -17509,7 +17509,7 @@
         <v>2.6</v>
       </c>
       <c r="F712" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="713">
@@ -17557,7 +17557,7 @@
         <v>2.3</v>
       </c>
       <c r="F714" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="715">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="F716" t="n">
         <v>48.6</v>
@@ -17626,7 +17626,7 @@
       </c>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F717" t="n">
         <v>47.1</v>
@@ -17650,10 +17650,10 @@
       </c>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="F718" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="719">
@@ -17674,10 +17674,10 @@
       </c>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="F719" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="720">
@@ -17698,10 +17698,10 @@
       </c>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="F720" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="721">
@@ -17725,7 +17725,7 @@
         <v>18</v>
       </c>
       <c r="F721" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="722">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="F722" t="n">
         <v>50.4</v>
@@ -17770,10 +17770,10 @@
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="F723" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="724">
@@ -17794,10 +17794,10 @@
       </c>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="F724" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="725">
@@ -17821,7 +17821,7 @@
         <v>14.9</v>
       </c>
       <c r="F725" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="726">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="F726" t="n">
         <v>52.1</v>
@@ -17866,10 +17866,10 @@
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="F727" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="728">
@@ -17890,10 +17890,10 @@
       </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="F728" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="729">
@@ -17914,10 +17914,10 @@
       </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="F729" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="730">
@@ -17941,7 +17941,7 @@
         <v>10.4</v>
       </c>
       <c r="F730" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="731">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="F731" t="n">
         <v>50.8</v>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D732" t="inlineStr"/>
@@ -17989,7 +17989,7 @@
         <v>9.9</v>
       </c>
       <c r="F732" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="733">
@@ -18005,15 +18005,15 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F733" t="n">
-        <v>51.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="734">
@@ -18037,7 +18037,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F734" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="735">
@@ -18058,10 +18058,10 @@
       </c>
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F735" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="736">
@@ -18082,10 +18082,10 @@
       </c>
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F736" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="737">
@@ -18109,7 +18109,7 @@
         <v>9</v>
       </c>
       <c r="F737" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="738">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D738" t="inlineStr"/>
@@ -18133,7 +18133,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F738" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="739">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D739" t="inlineStr"/>
@@ -18157,7 +18157,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F739" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="740">
@@ -18178,10 +18178,10 @@
       </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="F740" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="741">
@@ -18202,10 +18202,10 @@
       </c>
       <c r="D741" t="inlineStr"/>
       <c r="E741" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F741" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="742">
@@ -18245,15 +18245,15 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D743" t="inlineStr"/>
       <c r="E743" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F743" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="744">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D744" t="inlineStr"/>
@@ -18277,7 +18277,7 @@
         <v>7</v>
       </c>
       <c r="F744" t="n">
-        <v>51.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="745">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D745" t="inlineStr"/>
@@ -18301,7 +18301,7 @@
         <v>6.9</v>
       </c>
       <c r="F745" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="746">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D746" t="inlineStr"/>
@@ -18325,7 +18325,7 @@
         <v>6.8</v>
       </c>
       <c r="F746" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="747">
@@ -18341,15 +18341,15 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F747" t="n">
-        <v>47.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="748">
@@ -18365,15 +18365,15 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F748" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="749">
@@ -18389,15 +18389,15 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F749" t="n">
-        <v>52.3</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="750">
@@ -18418,10 +18418,10 @@
       </c>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F750" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="751">
@@ -18466,7 +18466,7 @@
       </c>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F752" t="n">
         <v>56.1</v>
@@ -18493,7 +18493,7 @@
         <v>5.2</v>
       </c>
       <c r="F753" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="754">
@@ -18517,7 +18517,7 @@
         <v>5</v>
       </c>
       <c r="F754" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="755">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D755" t="inlineStr"/>
@@ -18541,7 +18541,7 @@
         <v>4.5</v>
       </c>
       <c r="F755" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="756">
@@ -18557,15 +18557,15 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F756" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="757">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F757" t="n">
         <v>51.2</v>
@@ -18613,7 +18613,7 @@
         <v>4.1</v>
       </c>
       <c r="F758" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="759">
@@ -18637,7 +18637,7 @@
         <v>3.8</v>
       </c>
       <c r="F759" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="760">
@@ -18661,7 +18661,7 @@
         <v>3.4</v>
       </c>
       <c r="F760" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="761">
@@ -18685,7 +18685,7 @@
         <v>3.4</v>
       </c>
       <c r="F761" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="762">
@@ -18709,7 +18709,7 @@
         <v>3.2</v>
       </c>
       <c r="F762" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="763">
@@ -18754,10 +18754,10 @@
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F764" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="765">
@@ -18781,7 +18781,7 @@
         <v>2</v>
       </c>
       <c r="F765" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="766">
@@ -18805,7 +18805,7 @@
         <v>1.3</v>
       </c>
       <c r="F766" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="767">
@@ -18826,10 +18826,10 @@
       </c>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="F767" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="768">
@@ -18850,10 +18850,10 @@
       </c>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="F768" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="769">
@@ -18874,10 +18874,10 @@
       </c>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="F769" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="770">
@@ -18898,10 +18898,10 @@
       </c>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="F770" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="771">
@@ -18925,7 +18925,7 @@
         <v>20.9</v>
       </c>
       <c r="F771" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="772">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="D772" t="inlineStr"/>
       <c r="E772" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="F772" t="n">
         <v>47.3</v>
@@ -18970,10 +18970,10 @@
       </c>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="F773" t="n">
-        <v>55.2</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="774">
@@ -18994,10 +18994,10 @@
       </c>
       <c r="D774" t="inlineStr"/>
       <c r="E774" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F774" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="775">
@@ -19018,10 +19018,10 @@
       </c>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="F775" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="776">
@@ -19042,10 +19042,10 @@
       </c>
       <c r="D776" t="inlineStr"/>
       <c r="E776" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F776" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="777">
@@ -19066,10 +19066,10 @@
       </c>
       <c r="D777" t="inlineStr"/>
       <c r="E777" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F777" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="778">
@@ -19090,10 +19090,10 @@
       </c>
       <c r="D778" t="inlineStr"/>
       <c r="E778" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="F778" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="779">
@@ -19109,15 +19109,15 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D779" t="inlineStr"/>
       <c r="E779" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="F779" t="n">
-        <v>50.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="780">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D780" t="inlineStr"/>
@@ -19141,7 +19141,7 @@
         <v>11.6</v>
       </c>
       <c r="F780" t="n">
-        <v>49.4</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="781">
@@ -19165,7 +19165,7 @@
         <v>10.6</v>
       </c>
       <c r="F781" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="782">
@@ -19189,7 +19189,7 @@
         <v>10.5</v>
       </c>
       <c r="F782" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="783">
@@ -19213,7 +19213,7 @@
         <v>9.9</v>
       </c>
       <c r="F783" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="784">
@@ -19237,7 +19237,7 @@
         <v>8.9</v>
       </c>
       <c r="F784" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="785">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="F785" t="n">
         <v>45.7</v>
@@ -19285,7 +19285,7 @@
         <v>8.4</v>
       </c>
       <c r="F786" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="787">
@@ -19309,7 +19309,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="F787" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="788">
@@ -19349,15 +19349,15 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D789" t="inlineStr"/>
       <c r="E789" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F789" t="n">
-        <v>56.4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="790">
@@ -19373,15 +19373,15 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D790" t="inlineStr"/>
       <c r="E790" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F790" t="n">
-        <v>47.4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="791">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D791" t="inlineStr"/>
@@ -19405,7 +19405,7 @@
         <v>7.8</v>
       </c>
       <c r="F791" t="n">
-        <v>51.6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="792">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D792" t="inlineStr"/>
@@ -19429,7 +19429,7 @@
         <v>7.5</v>
       </c>
       <c r="F792" t="n">
-        <v>44.7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="793">
@@ -19445,15 +19445,15 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="F793" t="n">
-        <v>51.6</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="794">
@@ -19474,10 +19474,10 @@
       </c>
       <c r="D794" t="inlineStr"/>
       <c r="E794" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F794" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="795">
@@ -19498,10 +19498,10 @@
       </c>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F795" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="796">
@@ -19525,7 +19525,7 @@
         <v>6.3</v>
       </c>
       <c r="F796" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="797">
@@ -19573,7 +19573,7 @@
         <v>6.2</v>
       </c>
       <c r="F798" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="799">
@@ -19594,10 +19594,10 @@
       </c>
       <c r="D799" t="inlineStr"/>
       <c r="E799" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="F799" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="800">
@@ -19618,10 +19618,10 @@
       </c>
       <c r="D800" t="inlineStr"/>
       <c r="E800" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F800" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="801">
@@ -19642,10 +19642,10 @@
       </c>
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F801" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="802">
@@ -19669,7 +19669,7 @@
         <v>5.4</v>
       </c>
       <c r="F802" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="803">
@@ -19693,7 +19693,7 @@
         <v>5.3</v>
       </c>
       <c r="F803" t="n">
-        <v>48.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="804">
@@ -19714,10 +19714,10 @@
       </c>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F804" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="805">
@@ -19741,7 +19741,7 @@
         <v>4.8</v>
       </c>
       <c r="F805" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="806">
@@ -19765,7 +19765,7 @@
         <v>4.5</v>
       </c>
       <c r="F806" t="n">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="807">
@@ -19789,7 +19789,7 @@
         <v>4.4</v>
       </c>
       <c r="F807" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="808">
@@ -19810,10 +19810,10 @@
       </c>
       <c r="D808" t="inlineStr"/>
       <c r="E808" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F808" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="809">
@@ -19837,7 +19837,7 @@
         <v>4</v>
       </c>
       <c r="F809" t="n">
-        <v>51.3</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="810">
@@ -19858,10 +19858,10 @@
       </c>
       <c r="D810" t="inlineStr"/>
       <c r="E810" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F810" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="811">
@@ -19882,10 +19882,10 @@
       </c>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F811" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="812">
@@ -19909,7 +19909,7 @@
         <v>2.9</v>
       </c>
       <c r="F812" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="813">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="D813" t="inlineStr"/>
       <c r="E813" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="F813" t="n">
         <v>51.9</v>
@@ -19954,10 +19954,10 @@
       </c>
       <c r="D814" t="inlineStr"/>
       <c r="E814" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="F814" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="815">
@@ -19978,10 +19978,10 @@
       </c>
       <c r="D815" t="inlineStr"/>
       <c r="E815" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F815" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="816">
@@ -20002,10 +20002,10 @@
       </c>
       <c r="D816" t="inlineStr"/>
       <c r="E816" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F816" t="n">
-        <v>44.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="817">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="D819" t="inlineStr"/>
       <c r="E819" t="n">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
       <c r="F819" t="n">
         <v>51.7</v>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="D820" t="inlineStr"/>
       <c r="E820" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F820" t="n">
         <v>47.2</v>
@@ -20146,10 +20146,10 @@
       </c>
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="F822" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="823">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="D824" t="inlineStr"/>
       <c r="E824" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="F824" t="n">
         <v>50.2</v>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="D825" t="inlineStr"/>
       <c r="E825" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F825" t="n">
         <v>47.2</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="D826" t="inlineStr"/>
       <c r="E826" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F826" t="n">
         <v>49.1</v>
@@ -20266,10 +20266,10 @@
       </c>
       <c r="D827" t="inlineStr"/>
       <c r="E827" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="F827" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="828">
@@ -20290,10 +20290,10 @@
       </c>
       <c r="D828" t="inlineStr"/>
       <c r="E828" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="F828" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="829">
@@ -20314,10 +20314,10 @@
       </c>
       <c r="D829" t="inlineStr"/>
       <c r="E829" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F829" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="830">
@@ -20338,10 +20338,10 @@
       </c>
       <c r="D830" t="inlineStr"/>
       <c r="E830" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="F830" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="831">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="D832" t="inlineStr"/>
       <c r="E832" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F832" t="n">
         <v>52.4</v>
@@ -20413,7 +20413,7 @@
         <v>11.5</v>
       </c>
       <c r="F833" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="834">
@@ -20509,7 +20509,7 @@
         <v>11.1</v>
       </c>
       <c r="F837" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="838">
@@ -20530,10 +20530,10 @@
       </c>
       <c r="D838" t="inlineStr"/>
       <c r="E838" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F838" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="839">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="D840" t="inlineStr"/>
       <c r="E840" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F840" t="n">
         <v>48.9</v>
@@ -20626,10 +20626,10 @@
       </c>
       <c r="D842" t="inlineStr"/>
       <c r="E842" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F842" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="843">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="D843" t="inlineStr"/>
       <c r="E843" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="F843" t="n">
         <v>49.6</v>
@@ -20677,7 +20677,7 @@
         <v>7.2</v>
       </c>
       <c r="F844" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="845">
@@ -20794,10 +20794,10 @@
       </c>
       <c r="D849" t="inlineStr"/>
       <c r="E849" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F849" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="850">
@@ -20818,10 +20818,10 @@
       </c>
       <c r="D850" t="inlineStr"/>
       <c r="E850" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F850" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="851">
@@ -20869,7 +20869,7 @@
         <v>5.5</v>
       </c>
       <c r="F852" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="853">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="D857" t="inlineStr"/>
       <c r="E857" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F857" t="n">
         <v>49.9</v>
@@ -21010,10 +21010,10 @@
       </c>
       <c r="D858" t="inlineStr"/>
       <c r="E858" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F858" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="859">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D859" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
         <v>4.3</v>
       </c>
       <c r="F859" t="n">
-        <v>49.4</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="860">
@@ -21053,15 +21053,15 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D860" t="inlineStr"/>
       <c r="E860" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F860" t="n">
-        <v>51.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="861">
@@ -21109,7 +21109,7 @@
         <v>3.5</v>
       </c>
       <c r="F862" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="863">
@@ -21133,7 +21133,7 @@
         <v>3.4</v>
       </c>
       <c r="F863" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="864">
@@ -21157,7 +21157,7 @@
         <v>3.2</v>
       </c>
       <c r="F864" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="865">
@@ -21205,7 +21205,7 @@
         <v>2.5</v>
       </c>
       <c r="F866" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="867">
@@ -21229,7 +21229,7 @@
         <v>2.2</v>
       </c>
       <c r="F867" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="868">
@@ -21253,7 +21253,7 @@
         <v>2.1</v>
       </c>
       <c r="F868" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="869">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="D869" t="inlineStr"/>
       <c r="E869" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="F869" t="n">
         <v>49.9</v>
@@ -21293,15 +21293,15 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>키리코</t>
         </is>
       </c>
       <c r="D870" t="inlineStr"/>
       <c r="E870" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="F870" t="n">
-        <v>52.8</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="871">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>키리코</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D871" t="inlineStr"/>
@@ -21325,7 +21325,7 @@
         <v>28.7</v>
       </c>
       <c r="F871" t="n">
-        <v>49.1</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="872">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="D872" t="inlineStr"/>
       <c r="E872" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="F872" t="n">
         <v>47</v>
@@ -21370,10 +21370,10 @@
       </c>
       <c r="D873" t="inlineStr"/>
       <c r="E873" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="F873" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="874">
@@ -21394,10 +21394,10 @@
       </c>
       <c r="D874" t="inlineStr"/>
       <c r="E874" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F874" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="875">
@@ -21421,7 +21421,7 @@
         <v>16.9</v>
       </c>
       <c r="F875" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="876">
@@ -21442,10 +21442,10 @@
       </c>
       <c r="D876" t="inlineStr"/>
       <c r="E876" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="F876" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="877">
@@ -21469,7 +21469,7 @@
         <v>15.7</v>
       </c>
       <c r="F877" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="878">
@@ -21493,7 +21493,7 @@
         <v>13</v>
       </c>
       <c r="F878" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="879">
@@ -21517,7 +21517,7 @@
         <v>12.7</v>
       </c>
       <c r="F879" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="880">
@@ -21541,7 +21541,7 @@
         <v>12.4</v>
       </c>
       <c r="F880" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="881">
@@ -21589,7 +21589,7 @@
         <v>11.3</v>
       </c>
       <c r="F882" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="883">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F883" t="n">
         <v>45.6</v>
@@ -21629,7 +21629,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D884" t="inlineStr"/>
@@ -21637,7 +21637,7 @@
         <v>11.1</v>
       </c>
       <c r="F884" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="885">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D885" t="inlineStr"/>
@@ -21661,7 +21661,7 @@
         <v>11.1</v>
       </c>
       <c r="F885" t="n">
-        <v>52.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="886">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D886" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
         <v>11.1</v>
       </c>
       <c r="F886" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="887">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D887" t="inlineStr"/>
       <c r="E887" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="F887" t="n">
-        <v>49.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="888">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="D888" t="inlineStr"/>
       <c r="E888" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F888" t="n">
         <v>44.1</v>
@@ -21757,7 +21757,7 @@
         <v>10.4</v>
       </c>
       <c r="F889" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="890">
@@ -21781,7 +21781,7 @@
         <v>10.2</v>
       </c>
       <c r="F890" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="891">
@@ -21805,7 +21805,7 @@
         <v>9.9</v>
       </c>
       <c r="F891" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="892">
@@ -21826,10 +21826,10 @@
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F892" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="893">
@@ -21850,10 +21850,10 @@
       </c>
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F893" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="894">
@@ -21877,7 +21877,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F894" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="895">
@@ -21901,7 +21901,7 @@
         <v>8</v>
       </c>
       <c r="F895" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="896">
@@ -21922,7 +21922,7 @@
       </c>
       <c r="D896" t="inlineStr"/>
       <c r="E896" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F896" t="n">
         <v>49</v>
@@ -21949,7 +21949,7 @@
         <v>7.2</v>
       </c>
       <c r="F897" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="898">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="D898" t="inlineStr"/>
       <c r="E898" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F898" t="n">
         <v>46.2</v>
@@ -21997,7 +21997,7 @@
         <v>6.3</v>
       </c>
       <c r="F899" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="900">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="D900" t="inlineStr"/>
       <c r="E900" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F900" t="n">
         <v>50.2</v>
@@ -22045,7 +22045,7 @@
         <v>5.9</v>
       </c>
       <c r="F901" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="902">
@@ -22069,7 +22069,7 @@
         <v>5</v>
       </c>
       <c r="F902" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="903">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>에코</t>
         </is>
       </c>
       <c r="D903" t="inlineStr"/>
@@ -22093,7 +22093,7 @@
         <v>4.8</v>
       </c>
       <c r="F903" t="n">
-        <v>45.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="904">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>에코</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D904" t="inlineStr"/>
@@ -22117,7 +22117,7 @@
         <v>4.8</v>
       </c>
       <c r="F904" t="n">
-        <v>47</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="905">
@@ -22133,15 +22133,15 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D905" t="inlineStr"/>
       <c r="E905" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F905" t="n">
-        <v>50.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="906">
@@ -22165,7 +22165,7 @@
         <v>4.1</v>
       </c>
       <c r="F906" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="907">
@@ -22181,15 +22181,15 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D907" t="inlineStr"/>
       <c r="E907" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F907" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="908">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D908" t="inlineStr"/>
@@ -22213,7 +22213,7 @@
         <v>3.8</v>
       </c>
       <c r="F908" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="909">
@@ -22237,7 +22237,7 @@
         <v>3.8</v>
       </c>
       <c r="F909" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="910">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D910" t="inlineStr"/>
       <c r="E910" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F910" t="n">
-        <v>52.2</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="911">
@@ -22277,7 +22277,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D911" t="inlineStr"/>
@@ -22285,7 +22285,7 @@
         <v>3.4</v>
       </c>
       <c r="F911" t="n">
-        <v>53.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="912">
@@ -22330,10 +22330,10 @@
       </c>
       <c r="D913" t="inlineStr"/>
       <c r="E913" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F913" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="914">
@@ -22354,10 +22354,10 @@
       </c>
       <c r="D914" t="inlineStr"/>
       <c r="E914" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F914" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="915">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>해저드</t>
+          <t>벤데타</t>
         </is>
       </c>
       <c r="D915" t="inlineStr"/>
@@ -22381,7 +22381,7 @@
         <v>2.6</v>
       </c>
       <c r="F915" t="n">
-        <v>52.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="916">
@@ -22397,15 +22397,15 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>벤데타</t>
+          <t>해저드</t>
         </is>
       </c>
       <c r="D916" t="inlineStr"/>
       <c r="E916" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F916" t="n">
-        <v>48.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="917">
@@ -22429,7 +22429,7 @@
         <v>2.4</v>
       </c>
       <c r="F917" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="918">
@@ -22453,7 +22453,7 @@
         <v>2.1</v>
       </c>
       <c r="F918" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="919">
@@ -22477,7 +22477,7 @@
         <v>1.9</v>
       </c>
       <c r="F919" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="920">
@@ -22501,7 +22501,7 @@
         <v>33.3</v>
       </c>
       <c r="F920" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="921">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="F921" t="n">
         <v>48.8</v>
@@ -22546,7 +22546,7 @@
       </c>
       <c r="D922" t="inlineStr"/>
       <c r="E922" t="n">
-        <v>29.7</v>
+        <v>29</v>
       </c>
       <c r="F922" t="n">
         <v>52.4</v>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="F923" t="n">
         <v>48.1</v>
@@ -22618,7 +22618,7 @@
       </c>
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="F925" t="n">
         <v>46.8</v>
@@ -22642,7 +22642,7 @@
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F926" t="n">
         <v>50</v>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="F927" t="n">
         <v>51.8</v>
@@ -22690,7 +22690,7 @@
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="F928" t="n">
         <v>46.8</v>
@@ -22717,7 +22717,7 @@
         <v>14.3</v>
       </c>
       <c r="F929" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="930">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D930" t="inlineStr"/>
@@ -22741,7 +22741,7 @@
         <v>12.8</v>
       </c>
       <c r="F930" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="931">
@@ -22757,15 +22757,15 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="F931" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="932">
@@ -22789,7 +22789,7 @@
         <v>12.4</v>
       </c>
       <c r="F932" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="933">
@@ -22837,7 +22837,7 @@
         <v>11.7</v>
       </c>
       <c r="F934" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="935">
@@ -22853,15 +22853,15 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>정크랫</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D935" t="inlineStr"/>
       <c r="E935" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F935" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="936">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>정크랫</t>
         </is>
       </c>
       <c r="D936" t="inlineStr"/>
@@ -22885,7 +22885,7 @@
         <v>11.5</v>
       </c>
       <c r="F936" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="937">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>안란</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D940" t="inlineStr"/>
@@ -22981,7 +22981,7 @@
         <v>10.5</v>
       </c>
       <c r="F940" t="n">
-        <v>51.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="941">
@@ -22997,15 +22997,15 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>안란</t>
         </is>
       </c>
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F941" t="n">
-        <v>49.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="942">
@@ -23050,10 +23050,10 @@
       </c>
       <c r="D943" t="inlineStr"/>
       <c r="E943" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F943" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="944">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F944" t="n">
         <v>49.7</v>
@@ -23093,7 +23093,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D945" t="inlineStr"/>
@@ -23101,7 +23101,7 @@
         <v>8.1</v>
       </c>
       <c r="F945" t="n">
-        <v>46.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="946">
@@ -23117,15 +23117,15 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F946" t="n">
-        <v>51.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="947">
@@ -23146,10 +23146,10 @@
       </c>
       <c r="D947" t="inlineStr"/>
       <c r="E947" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F947" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="948">
@@ -23194,7 +23194,7 @@
       </c>
       <c r="D949" t="inlineStr"/>
       <c r="E949" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F949" t="n">
         <v>50.7</v>
@@ -23221,7 +23221,7 @@
         <v>6.4</v>
       </c>
       <c r="F950" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="951">
@@ -23245,7 +23245,7 @@
         <v>5.9</v>
       </c>
       <c r="F951" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="952">
@@ -23269,7 +23269,7 @@
         <v>5.6</v>
       </c>
       <c r="F952" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="953">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F953" t="n">
         <v>52</v>
@@ -23309,15 +23309,15 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>윈스턴</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F954" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="955">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>윈스턴</t>
         </is>
       </c>
       <c r="D955" t="inlineStr"/>
@@ -23341,7 +23341,7 @@
         <v>4.6</v>
       </c>
       <c r="F955" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="956">
@@ -23365,7 +23365,7 @@
         <v>4.2</v>
       </c>
       <c r="F956" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="957">
@@ -23389,7 +23389,7 @@
         <v>4.2</v>
       </c>
       <c r="F957" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="958">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F958" t="n">
         <v>48.6</v>
@@ -23434,10 +23434,10 @@
       </c>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F959" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="960">
@@ -23461,7 +23461,7 @@
         <v>3.9</v>
       </c>
       <c r="F960" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="961">
@@ -23506,10 +23506,10 @@
       </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F962" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="963">
@@ -23533,7 +23533,7 @@
         <v>3.3</v>
       </c>
       <c r="F963" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="964">
@@ -23557,7 +23557,7 @@
         <v>3.1</v>
       </c>
       <c r="F964" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="965">
@@ -23581,7 +23581,7 @@
         <v>3.1</v>
       </c>
       <c r="F965" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="966">
@@ -23605,7 +23605,7 @@
         <v>3.1</v>
       </c>
       <c r="F966" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="967">
@@ -23629,7 +23629,7 @@
         <v>2.6</v>
       </c>
       <c r="F967" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="968">
@@ -23650,10 +23650,10 @@
       </c>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F968" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="969">
@@ -23677,7 +23677,7 @@
         <v>2.2</v>
       </c>
       <c r="F969" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="970">
@@ -27394,10 +27394,10 @@
       </c>
       <c r="D1124" t="inlineStr"/>
       <c r="E1124" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="F1124" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1125">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="D1125" t="inlineStr"/>
       <c r="E1125" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="F1125" t="n">
         <v>47.3</v>
@@ -27485,15 +27485,15 @@
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>겐지</t>
+          <t>소전</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="F1128" t="n">
-        <v>50.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1129">
@@ -27509,7 +27509,7 @@
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>겐지</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr"/>
@@ -27517,7 +27517,7 @@
         <v>16.4</v>
       </c>
       <c r="F1129" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1130">
@@ -27533,15 +27533,15 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr"/>
       <c r="E1130" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="F1130" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1131">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>소전</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr"/>
@@ -27565,7 +27565,7 @@
         <v>16.2</v>
       </c>
       <c r="F1131" t="n">
-        <v>45.7</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1132">
@@ -27581,15 +27581,15 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr"/>
       <c r="E1132" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="F1132" t="n">
-        <v>52.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1133">
@@ -27610,7 +27610,7 @@
       </c>
       <c r="D1133" t="inlineStr"/>
       <c r="E1133" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="F1133" t="n">
         <v>48.7</v>
@@ -27629,7 +27629,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>일리아리</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr"/>
@@ -27637,7 +27637,7 @@
         <v>14.6</v>
       </c>
       <c r="F1134" t="n">
-        <v>49.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1135">
@@ -27653,15 +27653,15 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>일리아리</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr"/>
       <c r="E1135" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F1135" t="n">
-        <v>54.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1136">
@@ -27682,10 +27682,10 @@
       </c>
       <c r="D1136" t="inlineStr"/>
       <c r="E1136" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F1136" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1137">
@@ -27709,7 +27709,7 @@
         <v>10.4</v>
       </c>
       <c r="F1137" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1138">
@@ -27730,10 +27730,10 @@
       </c>
       <c r="D1138" t="inlineStr"/>
       <c r="E1138" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F1138" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1139">
@@ -27754,10 +27754,10 @@
       </c>
       <c r="D1139" t="inlineStr"/>
       <c r="E1139" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="F1139" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="1140">
@@ -27826,10 +27826,10 @@
       </c>
       <c r="D1142" t="inlineStr"/>
       <c r="E1142" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F1142" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1143">
@@ -27853,7 +27853,7 @@
         <v>9</v>
       </c>
       <c r="F1143" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1144">
@@ -27877,7 +27877,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1145">
@@ -27898,10 +27898,10 @@
       </c>
       <c r="D1145" t="inlineStr"/>
       <c r="E1145" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F1145" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1146">
@@ -27922,10 +27922,10 @@
       </c>
       <c r="D1146" t="inlineStr"/>
       <c r="E1146" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F1146" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1147">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>우양</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr"/>
@@ -27949,7 +27949,7 @@
         <v>8</v>
       </c>
       <c r="F1147" t="n">
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="1148">
@@ -27965,7 +27965,7 @@
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr"/>
@@ -27973,7 +27973,7 @@
         <v>7.9</v>
       </c>
       <c r="F1148" t="n">
-        <v>52.2</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1149">
@@ -27989,15 +27989,15 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>우양</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr"/>
       <c r="E1149" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="F1149" t="n">
-        <v>49.1</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1150">
@@ -28013,7 +28013,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr"/>
@@ -28021,7 +28021,7 @@
         <v>7.7</v>
       </c>
       <c r="F1150" t="n">
-        <v>46.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1151">
@@ -28045,7 +28045,7 @@
         <v>7.6</v>
       </c>
       <c r="F1151" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1152">
@@ -28066,10 +28066,10 @@
       </c>
       <c r="D1152" t="inlineStr"/>
       <c r="E1152" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F1152" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1153">
@@ -28093,7 +28093,7 @@
         <v>7.3</v>
       </c>
       <c r="F1153" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1154">
@@ -28117,7 +28117,7 @@
         <v>7.3</v>
       </c>
       <c r="F1154" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1155">
@@ -28141,7 +28141,7 @@
         <v>7</v>
       </c>
       <c r="F1155" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1156">
@@ -28165,7 +28165,7 @@
         <v>6.9</v>
       </c>
       <c r="F1156" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1157">
@@ -28186,10 +28186,10 @@
       </c>
       <c r="D1157" t="inlineStr"/>
       <c r="E1157" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F1157" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="1158">
@@ -28213,7 +28213,7 @@
         <v>6.3</v>
       </c>
       <c r="F1158" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1159">
@@ -28282,10 +28282,10 @@
       </c>
       <c r="D1161" t="inlineStr"/>
       <c r="E1161" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F1161" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1162">
@@ -28306,10 +28306,10 @@
       </c>
       <c r="D1162" t="inlineStr"/>
       <c r="E1162" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F1162" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1163">
@@ -28333,7 +28333,7 @@
         <v>5</v>
       </c>
       <c r="F1163" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1164">
@@ -28357,7 +28357,7 @@
         <v>4</v>
       </c>
       <c r="F1164" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1165">
@@ -28381,7 +28381,7 @@
         <v>4</v>
       </c>
       <c r="F1165" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1166">
@@ -28402,10 +28402,10 @@
       </c>
       <c r="D1166" t="inlineStr"/>
       <c r="E1166" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F1166" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1167">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="D1167" t="inlineStr"/>
       <c r="E1167" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F1167" t="n">
         <v>49.6</v>
@@ -28453,7 +28453,7 @@
         <v>3.3</v>
       </c>
       <c r="F1168" t="n">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1169">
@@ -28477,7 +28477,7 @@
         <v>3</v>
       </c>
       <c r="F1169" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1170">
@@ -28501,7 +28501,7 @@
         <v>3</v>
       </c>
       <c r="F1170" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="1171">
@@ -28525,7 +28525,7 @@
         <v>2.8</v>
       </c>
       <c r="F1171" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1172">
@@ -28546,10 +28546,10 @@
       </c>
       <c r="D1172" t="inlineStr"/>
       <c r="E1172" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1172" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="1173">
@@ -28597,7 +28597,7 @@
         <v>1.5</v>
       </c>
       <c r="F1174" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1175">
@@ -29869,7 +29869,7 @@
         <v>6</v>
       </c>
       <c r="F1227" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1228">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="D1228" t="inlineStr"/>
       <c r="E1228" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F1228" t="n">
         <v>48.1</v>
@@ -29941,7 +29941,7 @@
         <v>3.6</v>
       </c>
       <c r="F1230" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1231">
@@ -29989,7 +29989,7 @@
         <v>3.2</v>
       </c>
       <c r="F1232" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1233">
@@ -30037,7 +30037,7 @@
         <v>3.1</v>
       </c>
       <c r="F1234" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1235">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>미즈키</t>
+          <t>엠레</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr"/>
@@ -30061,7 +30061,7 @@
         <v>2.8</v>
       </c>
       <c r="F1235" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="1236">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>엠레</t>
+          <t>미즈키</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr"/>
@@ -30085,7 +30085,7 @@
         <v>2.8</v>
       </c>
       <c r="F1236" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1237">
@@ -30229,7 +30229,7 @@
         <v>2.1</v>
       </c>
       <c r="F1242" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1243">
@@ -30277,7 +30277,7 @@
         <v>2</v>
       </c>
       <c r="F1244" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1245">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr"/>
@@ -30325,7 +30325,7 @@
         <v>1.9</v>
       </c>
       <c r="F1246" t="n">
-        <v>45.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1247">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
         <v>1.9</v>
       </c>
       <c r="F1247" t="n">
-        <v>50.1</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1248">
@@ -30485,7 +30485,7 @@
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>마우가</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr"/>
@@ -30493,7 +30493,7 @@
         <v>1.5</v>
       </c>
       <c r="F1253" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1254">
@@ -30509,7 +30509,7 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>마우가</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr"/>
@@ -30517,7 +30517,7 @@
         <v>1.5</v>
       </c>
       <c r="F1254" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1255">
@@ -30541,7 +30541,7 @@
         <v>1.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1256">
@@ -30565,7 +30565,7 @@
         <v>1.4</v>
       </c>
       <c r="F1256" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="1257">
@@ -30613,7 +30613,7 @@
         <v>1.3</v>
       </c>
       <c r="F1258" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1259">
@@ -30637,7 +30637,7 @@
         <v>1.2</v>
       </c>
       <c r="F1259" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1260">
@@ -30661,7 +30661,7 @@
         <v>1.2</v>
       </c>
       <c r="F1260" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1261">
@@ -30733,7 +30733,7 @@
         <v>1.2</v>
       </c>
       <c r="F1263" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1264">
@@ -30757,7 +30757,7 @@
         <v>1</v>
       </c>
       <c r="F1264" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1265">
@@ -30853,7 +30853,7 @@
         <v>1</v>
       </c>
       <c r="F1268" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1269">
@@ -30925,7 +30925,7 @@
         <v>0.7</v>
       </c>
       <c r="F1271" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1272">
@@ -30949,7 +30949,7 @@
         <v>0.7</v>
       </c>
       <c r="F1272" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1273">
@@ -30973,7 +30973,7 @@
         <v>0.6</v>
       </c>
       <c r="F1273" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="1274">
@@ -30997,7 +30997,7 @@
         <v>0.6</v>
       </c>
       <c r="F1274" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1275">
@@ -31069,7 +31069,7 @@
         <v>7.6</v>
       </c>
       <c r="F1277" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="1278">
@@ -31093,7 +31093,7 @@
         <v>4.5</v>
       </c>
       <c r="F1278" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1279">
@@ -31117,7 +31117,7 @@
         <v>4.3</v>
       </c>
       <c r="F1279" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1280">
@@ -31165,7 +31165,7 @@
         <v>3.9</v>
       </c>
       <c r="F1281" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1282">
@@ -31189,7 +31189,7 @@
         <v>3.2</v>
       </c>
       <c r="F1282" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1283">
@@ -31213,7 +31213,7 @@
         <v>3.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1284">
@@ -31237,7 +31237,7 @@
         <v>3.1</v>
       </c>
       <c r="F1284" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1285">
@@ -31309,7 +31309,7 @@
         <v>3.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1288">
@@ -31357,7 +31357,7 @@
         <v>2.7</v>
       </c>
       <c r="F1289" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1290">
@@ -31381,7 +31381,7 @@
         <v>2.6</v>
       </c>
       <c r="F1290" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1291">
@@ -31405,7 +31405,7 @@
         <v>2.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="1292">
@@ -31429,7 +31429,7 @@
         <v>2.4</v>
       </c>
       <c r="F1292" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1293">
@@ -31450,7 +31450,7 @@
       </c>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F1293" t="n">
         <v>44.2</v>
@@ -31477,7 +31477,7 @@
         <v>2.2</v>
       </c>
       <c r="F1294" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1295">
@@ -31525,7 +31525,7 @@
         <v>2.2</v>
       </c>
       <c r="F1296" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1297">
@@ -31549,7 +31549,7 @@
         <v>2</v>
       </c>
       <c r="F1297" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="1298">
@@ -31573,7 +31573,7 @@
         <v>1.9</v>
       </c>
       <c r="F1298" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1299">
@@ -31594,10 +31594,10 @@
       </c>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F1299" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1300">
@@ -31621,7 +31621,7 @@
         <v>1.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1301">
@@ -31645,7 +31645,7 @@
         <v>1.7</v>
       </c>
       <c r="F1301" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1302">
@@ -31669,7 +31669,7 @@
         <v>1.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1303">
@@ -31693,7 +31693,7 @@
         <v>1.6</v>
       </c>
       <c r="F1303" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="1304">
@@ -31765,7 +31765,7 @@
         <v>1.5</v>
       </c>
       <c r="F1306" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1307">
@@ -31786,10 +31786,10 @@
       </c>
       <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F1307" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="1308">
@@ -31813,7 +31813,7 @@
         <v>1.3</v>
       </c>
       <c r="F1308" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1309">
@@ -31837,7 +31837,7 @@
         <v>1.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="1310">
@@ -31909,7 +31909,7 @@
         <v>1</v>
       </c>
       <c r="F1312" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1313">
@@ -31933,7 +31933,7 @@
         <v>1</v>
       </c>
       <c r="F1313" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="1314">
@@ -31957,7 +31957,7 @@
         <v>1</v>
       </c>
       <c r="F1314" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="1315">
@@ -31981,7 +31981,7 @@
         <v>0.9</v>
       </c>
       <c r="F1315" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1316">
@@ -32005,7 +32005,7 @@
         <v>0.9</v>
       </c>
       <c r="F1316" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1317">
@@ -32029,7 +32029,7 @@
         <v>0.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1318">
@@ -32053,7 +32053,7 @@
         <v>0.9</v>
       </c>
       <c r="F1318" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1319">
@@ -32077,7 +32077,7 @@
         <v>0.8</v>
       </c>
       <c r="F1319" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1320">
@@ -32101,7 +32101,7 @@
         <v>0.8</v>
       </c>
       <c r="F1320" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="1321">
@@ -32125,7 +32125,7 @@
         <v>0.7</v>
       </c>
       <c r="F1321" t="n">
-        <v>47.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1322">
@@ -32149,7 +32149,7 @@
         <v>0.7</v>
       </c>
       <c r="F1322" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1323">
@@ -32173,7 +32173,7 @@
         <v>0.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1324">
@@ -32269,7 +32269,7 @@
         <v>0.3</v>
       </c>
       <c r="F1327" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1328">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F1330" t="n">
         <v>47.9</v>
@@ -32365,7 +32365,7 @@
         <v>4</v>
       </c>
       <c r="F1331" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1332">
@@ -32386,7 +32386,7 @@
       </c>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F1332" t="n">
         <v>50.3</v>
@@ -32410,10 +32410,10 @@
       </c>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F1333" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1334">
@@ -32509,7 +32509,7 @@
         <v>3</v>
       </c>
       <c r="F1337" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1338">
@@ -32533,7 +32533,7 @@
         <v>2.7</v>
       </c>
       <c r="F1338" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1339">
@@ -32549,7 +32549,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>라마트라</t>
+          <t>젠야타</t>
         </is>
       </c>
       <c r="D1339" t="inlineStr"/>
@@ -32557,7 +32557,7 @@
         <v>2.6</v>
       </c>
       <c r="F1339" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1340">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>젠야타</t>
+          <t>라마트라</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr"/>
@@ -32581,7 +32581,7 @@
         <v>2.6</v>
       </c>
       <c r="F1340" t="n">
-        <v>49.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1341">
@@ -32602,10 +32602,10 @@
       </c>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F1341" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1342">
@@ -32629,7 +32629,7 @@
         <v>2.2</v>
       </c>
       <c r="F1342" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1343">
@@ -32677,7 +32677,7 @@
         <v>2.2</v>
       </c>
       <c r="F1344" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1345">
@@ -32701,7 +32701,7 @@
         <v>2.2</v>
       </c>
       <c r="F1345" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1346">
@@ -32749,7 +32749,7 @@
         <v>2.1</v>
       </c>
       <c r="F1347" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1348">
@@ -32818,10 +32818,10 @@
       </c>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1351">
@@ -32869,7 +32869,7 @@
         <v>1.7</v>
       </c>
       <c r="F1352" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1353">
@@ -32893,7 +32893,7 @@
         <v>1.7</v>
       </c>
       <c r="F1353" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1354">
@@ -32917,7 +32917,7 @@
         <v>1.5</v>
       </c>
       <c r="F1354" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1355">
@@ -32933,7 +32933,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>바티스트</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1355" t="inlineStr"/>
@@ -32941,7 +32941,7 @@
         <v>1.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>44.6</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="1356">
@@ -32957,7 +32957,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>바티스트</t>
         </is>
       </c>
       <c r="D1356" t="inlineStr"/>
@@ -32965,7 +32965,7 @@
         <v>1.4</v>
       </c>
       <c r="F1356" t="n">
-        <v>48.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="1357">
@@ -33013,7 +33013,7 @@
         <v>1.3</v>
       </c>
       <c r="F1358" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="1359">
@@ -33037,7 +33037,7 @@
         <v>1.3</v>
       </c>
       <c r="F1359" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1360">
@@ -33061,7 +33061,7 @@
         <v>1.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1361">
@@ -33085,7 +33085,7 @@
         <v>1.2</v>
       </c>
       <c r="F1361" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1362">
@@ -33109,7 +33109,7 @@
         <v>1.2</v>
       </c>
       <c r="F1362" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1363">
@@ -33149,7 +33149,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1364" t="inlineStr"/>
@@ -33157,7 +33157,7 @@
         <v>1.1</v>
       </c>
       <c r="F1364" t="n">
-        <v>44.8</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1365">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1365" t="inlineStr"/>
@@ -33181,7 +33181,7 @@
         <v>1.1</v>
       </c>
       <c r="F1365" t="n">
-        <v>49.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1366">
@@ -33205,7 +33205,7 @@
         <v>1</v>
       </c>
       <c r="F1366" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1367">
@@ -33229,7 +33229,7 @@
         <v>1</v>
       </c>
       <c r="F1367" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1368">
@@ -33250,7 +33250,7 @@
       </c>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F1368" t="n">
         <v>55.4</v>
@@ -33277,7 +33277,7 @@
         <v>0.9</v>
       </c>
       <c r="F1369" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1370">
@@ -33301,7 +33301,7 @@
         <v>0.9</v>
       </c>
       <c r="F1370" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1371">
@@ -33349,7 +33349,7 @@
         <v>0.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1373">
@@ -33373,7 +33373,7 @@
         <v>0.7</v>
       </c>
       <c r="F1373" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1374">
@@ -33397,7 +33397,7 @@
         <v>0.6</v>
       </c>
       <c r="F1374" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="1375">
@@ -33421,7 +33421,7 @@
         <v>0.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1376">
@@ -33445,7 +33445,7 @@
         <v>0.5</v>
       </c>
       <c r="F1376" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1377">
@@ -33469,7 +33469,7 @@
         <v>0.4</v>
       </c>
       <c r="F1377" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1378">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F1381" t="n">
         <v>47.7</v>
@@ -33586,10 +33586,10 @@
       </c>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F1382" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1383">
@@ -33658,10 +33658,10 @@
       </c>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F1385" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="1386">
@@ -33685,7 +33685,7 @@
         <v>3.2</v>
       </c>
       <c r="F1386" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="1387">
@@ -33805,7 +33805,7 @@
         <v>2.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1392">
@@ -33829,7 +33829,7 @@
         <v>2.2</v>
       </c>
       <c r="F1392" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1393">
@@ -33877,7 +33877,7 @@
         <v>2.1</v>
       </c>
       <c r="F1394" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="1395">
@@ -33925,7 +33925,7 @@
         <v>2.1</v>
       </c>
       <c r="F1396" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="1397">
@@ -33973,7 +33973,7 @@
         <v>2</v>
       </c>
       <c r="F1398" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1399">
@@ -33997,7 +33997,7 @@
         <v>1.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1400">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr"/>
@@ -34069,7 +34069,7 @@
         <v>1.6</v>
       </c>
       <c r="F1402" t="n">
-        <v>51.9</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="1403">
@@ -34085,7 +34085,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr"/>
@@ -34093,7 +34093,7 @@
         <v>1.6</v>
       </c>
       <c r="F1403" t="n">
-        <v>50.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1404">
@@ -34117,7 +34117,7 @@
         <v>1.6</v>
       </c>
       <c r="F1404" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="1405">
@@ -34141,7 +34141,7 @@
         <v>1.6</v>
       </c>
       <c r="F1405" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="1406">
@@ -34165,7 +34165,7 @@
         <v>1.5</v>
       </c>
       <c r="F1406" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="1407">
@@ -34189,7 +34189,7 @@
         <v>1.5</v>
       </c>
       <c r="F1407" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="1408">
@@ -34213,7 +34213,7 @@
         <v>1.5</v>
       </c>
       <c r="F1408" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1409">
@@ -34237,7 +34237,7 @@
         <v>1.4</v>
       </c>
       <c r="F1409" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="1410">
@@ -34261,7 +34261,7 @@
         <v>1.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="1411">
@@ -34309,7 +34309,7 @@
         <v>1.2</v>
       </c>
       <c r="F1412" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1413">
@@ -34333,7 +34333,7 @@
         <v>1.2</v>
       </c>
       <c r="F1413" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1414">
@@ -34349,7 +34349,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>브리기테</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr"/>
@@ -34357,7 +34357,7 @@
         <v>1.2</v>
       </c>
       <c r="F1414" t="n">
-        <v>49.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1415">
@@ -34373,7 +34373,7 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>브리기테</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr"/>
@@ -34381,7 +34381,7 @@
         <v>1.2</v>
       </c>
       <c r="F1415" t="n">
-        <v>43.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1416">
@@ -34405,7 +34405,7 @@
         <v>1.1</v>
       </c>
       <c r="F1416" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1417">
@@ -34477,7 +34477,7 @@
         <v>1</v>
       </c>
       <c r="F1419" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1420">
@@ -34501,7 +34501,7 @@
         <v>0.9</v>
       </c>
       <c r="F1420" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1421">
@@ -34525,7 +34525,7 @@
         <v>0.9</v>
       </c>
       <c r="F1421" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1422">
@@ -34549,7 +34549,7 @@
         <v>0.9</v>
       </c>
       <c r="F1422" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1423">
@@ -34573,7 +34573,7 @@
         <v>0.7</v>
       </c>
       <c r="F1423" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="1424">
@@ -34621,7 +34621,7 @@
         <v>0.6</v>
       </c>
       <c r="F1425" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1426">
@@ -34693,7 +34693,7 @@
         <v>0.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1429">
@@ -34717,7 +34717,7 @@
         <v>0.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1430">
@@ -34741,7 +34741,7 @@
         <v>7.3</v>
       </c>
       <c r="F1430" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1431">
@@ -34765,7 +34765,7 @@
         <v>7.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1432">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F1434" t="n">
         <v>50.5</v>
@@ -34861,7 +34861,7 @@
         <v>3</v>
       </c>
       <c r="F1435" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="1436">
@@ -34885,7 +34885,7 @@
         <v>3</v>
       </c>
       <c r="F1436" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1437">
@@ -34981,7 +34981,7 @@
         <v>2.5</v>
       </c>
       <c r="F1440" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="1441">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F1442" t="n">
         <v>48.7</v>
@@ -35053,7 +35053,7 @@
         <v>2.4</v>
       </c>
       <c r="F1443" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1444">
@@ -35125,7 +35125,7 @@
         <v>2.1</v>
       </c>
       <c r="F1446" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1447">
@@ -35197,7 +35197,7 @@
         <v>2</v>
       </c>
       <c r="F1449" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="1450">
@@ -35221,7 +35221,7 @@
         <v>1.7</v>
       </c>
       <c r="F1450" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="1451">
@@ -35245,7 +35245,7 @@
         <v>1.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1452">
@@ -35269,7 +35269,7 @@
         <v>1.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1453">
@@ -35293,7 +35293,7 @@
         <v>1.6</v>
       </c>
       <c r="F1453" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="1454">
@@ -35309,15 +35309,15 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>한조</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F1454" t="n">
-        <v>47.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1455">
@@ -35333,7 +35333,7 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>한조</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr"/>
@@ -35341,7 +35341,7 @@
         <v>1.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>48.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1456">
@@ -35357,7 +35357,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>라이프위버</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
         <v>1.5</v>
       </c>
       <c r="F1456" t="n">
-        <v>48.9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1457">
@@ -35381,7 +35381,7 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>라이프위버</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr"/>
@@ -35389,7 +35389,7 @@
         <v>1.5</v>
       </c>
       <c r="F1457" t="n">
-        <v>53</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="1458">
@@ -35485,7 +35485,7 @@
         <v>1.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1462">
@@ -35509,7 +35509,7 @@
         <v>1.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1463">
@@ -35525,7 +35525,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>벤처</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr"/>
@@ -35533,7 +35533,7 @@
         <v>1.3</v>
       </c>
       <c r="F1463" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1464">
@@ -35549,7 +35549,7 @@
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>벤처</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr"/>
@@ -35557,7 +35557,7 @@
         <v>1.3</v>
       </c>
       <c r="F1464" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1465">
@@ -35581,7 +35581,7 @@
         <v>1.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="1466">
@@ -35653,7 +35653,7 @@
         <v>1.1</v>
       </c>
       <c r="F1468" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1469">
@@ -35677,7 +35677,7 @@
         <v>1.1</v>
       </c>
       <c r="F1469" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="1470">
@@ -35725,7 +35725,7 @@
         <v>0.9</v>
       </c>
       <c r="F1471" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1472">
@@ -35773,7 +35773,7 @@
         <v>0.7</v>
       </c>
       <c r="F1473" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1474">
@@ -35797,7 +35797,7 @@
         <v>0.7</v>
       </c>
       <c r="F1474" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="1475">
@@ -35821,7 +35821,7 @@
         <v>0.6</v>
       </c>
       <c r="F1475" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1476">
@@ -35914,10 +35914,10 @@
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F1479" t="n">
-        <v>44.2</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="1480">
@@ -35941,7 +35941,7 @@
         <v>0.5</v>
       </c>
       <c r="F1480" t="n">
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1481">
@@ -35962,7 +35962,7 @@
       </c>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F1481" t="n">
         <v>48.9</v>
@@ -35989,7 +35989,7 @@
         <v>7.3</v>
       </c>
       <c r="F1482" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="1483">
@@ -36013,7 +36013,7 @@
         <v>6.2</v>
       </c>
       <c r="F1483" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1484">
@@ -36037,7 +36037,7 @@
         <v>3.9</v>
       </c>
       <c r="F1484" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1485">
@@ -36061,7 +36061,7 @@
         <v>3.9</v>
       </c>
       <c r="F1485" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="1486">
@@ -36085,7 +36085,7 @@
         <v>3.4</v>
       </c>
       <c r="F1486" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="1487">
@@ -36133,7 +36133,7 @@
         <v>3.3</v>
       </c>
       <c r="F1488" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1489">
@@ -36154,7 +36154,7 @@
       </c>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1489" t="n">
         <v>47.7</v>
@@ -36181,7 +36181,7 @@
         <v>2.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1491">
@@ -36205,7 +36205,7 @@
         <v>2.7</v>
       </c>
       <c r="F1491" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="1492">
@@ -36229,7 +36229,7 @@
         <v>2.5</v>
       </c>
       <c r="F1492" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1493">
@@ -36253,7 +36253,7 @@
         <v>2.3</v>
       </c>
       <c r="F1493" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1494">
@@ -36277,7 +36277,7 @@
         <v>2.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1495">
@@ -36301,7 +36301,7 @@
         <v>2.1</v>
       </c>
       <c r="F1495" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1496">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Soldier: 76</t>
+          <t>둠피스트</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr"/>
@@ -36325,7 +36325,7 @@
         <v>2.1</v>
       </c>
       <c r="F1496" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1497">
@@ -36349,7 +36349,7 @@
         <v>2.1</v>
       </c>
       <c r="F1497" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="1498">
@@ -36365,7 +36365,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>메르시</t>
+          <t>Soldier: 76</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr"/>
@@ -36373,7 +36373,7 @@
         <v>2.1</v>
       </c>
       <c r="F1498" t="n">
-        <v>51.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1499">
@@ -36389,7 +36389,7 @@
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>둠피스트</t>
+          <t>메르시</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr"/>
@@ -36397,7 +36397,7 @@
         <v>2.1</v>
       </c>
       <c r="F1499" t="n">
-        <v>48.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="1500">
@@ -36421,7 +36421,7 @@
         <v>2</v>
       </c>
       <c r="F1500" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1501">
@@ -36442,7 +36442,7 @@
       </c>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F1501" t="n">
         <v>50</v>
@@ -36469,7 +36469,7 @@
         <v>1.8</v>
       </c>
       <c r="F1502" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="1503">
@@ -36493,7 +36493,7 @@
         <v>1.6</v>
       </c>
       <c r="F1503" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="1504">
@@ -36541,7 +36541,7 @@
         <v>1.5</v>
       </c>
       <c r="F1505" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1506">
@@ -36565,7 +36565,7 @@
         <v>1.5</v>
       </c>
       <c r="F1506" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1507">
@@ -36589,7 +36589,7 @@
         <v>1.5</v>
       </c>
       <c r="F1507" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="1508">
@@ -36613,7 +36613,7 @@
         <v>1.4</v>
       </c>
       <c r="F1508" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1509">
@@ -36661,7 +36661,7 @@
         <v>1.4</v>
       </c>
       <c r="F1510" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="1511">
@@ -36685,7 +36685,7 @@
         <v>1.3</v>
       </c>
       <c r="F1511" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1512">
@@ -36701,7 +36701,7 @@
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>루시우</t>
+          <t>주노</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr"/>
@@ -36709,7 +36709,7 @@
         <v>1.2</v>
       </c>
       <c r="F1512" t="n">
-        <v>45.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1513">
@@ -36725,7 +36725,7 @@
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>주노</t>
+          <t>루시우</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
         <v>1.2</v>
       </c>
       <c r="F1513" t="n">
-        <v>49.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="1514">
@@ -36805,7 +36805,7 @@
         <v>1.1</v>
       </c>
       <c r="F1516" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1517">
@@ -36829,7 +36829,7 @@
         <v>1</v>
       </c>
       <c r="F1517" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1518">
@@ -36845,7 +36845,7 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>디바</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr"/>
@@ -36853,7 +36853,7 @@
         <v>0.9</v>
       </c>
       <c r="F1518" t="n">
-        <v>49</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="1519">
@@ -36869,7 +36869,7 @@
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>디바</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr"/>
@@ -36877,7 +36877,7 @@
         <v>0.9</v>
       </c>
       <c r="F1519" t="n">
-        <v>51.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1520">
@@ -36901,7 +36901,7 @@
         <v>0.9</v>
       </c>
       <c r="F1520" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="1521">
@@ -36925,7 +36925,7 @@
         <v>0.8</v>
       </c>
       <c r="F1521" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="1522">
@@ -36949,7 +36949,7 @@
         <v>0.8</v>
       </c>
       <c r="F1522" t="n">
-        <v>45.9</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="1523">
@@ -36973,7 +36973,7 @@
         <v>0.8</v>
       </c>
       <c r="F1523" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="1524">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr"/>
@@ -37021,7 +37021,7 @@
         <v>0.6</v>
       </c>
       <c r="F1525" t="n">
-        <v>43.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1526">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr"/>
@@ -37045,7 +37045,7 @@
         <v>0.6</v>
       </c>
       <c r="F1526" t="n">
-        <v>47.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1527">
@@ -37069,7 +37069,7 @@
         <v>0.5</v>
       </c>
       <c r="F1527" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="1528">
@@ -37093,7 +37093,7 @@
         <v>0.4</v>
       </c>
       <c r="F1528" t="n">
-        <v>53.5</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="1529">
@@ -37117,7 +37117,7 @@
         <v>0.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>43.6</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1530">
@@ -37141,7 +37141,7 @@
         <v>0.3</v>
       </c>
       <c r="F1530" t="n">
-        <v>44.1</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1531">
@@ -37165,7 +37165,7 @@
         <v>0.3</v>
       </c>
       <c r="F1531" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="1532">
@@ -37189,7 +37189,7 @@
         <v>7</v>
       </c>
       <c r="F1532" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="1533">
@@ -37210,10 +37210,10 @@
       </c>
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F1533" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1534">
@@ -37237,7 +37237,7 @@
         <v>5.8</v>
       </c>
       <c r="F1534" t="n">
-        <v>47</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="1535">
@@ -37301,15 +37301,15 @@
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>시그마</t>
+          <t>트레이서</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F1537" t="n">
-        <v>47.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="1538">
@@ -37325,7 +37325,7 @@
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>트레이서</t>
+          <t>시그마</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr"/>
@@ -37333,7 +37333,7 @@
         <v>4.2</v>
       </c>
       <c r="F1538" t="n">
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1539">
@@ -37354,10 +37354,10 @@
       </c>
       <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F1539" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="1540">
@@ -37378,7 +37378,7 @@
       </c>
       <c r="D1540" t="inlineStr"/>
       <c r="E1540" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F1540" t="n">
         <v>45.9</v>
@@ -37405,7 +37405,7 @@
         <v>3.2</v>
       </c>
       <c r="F1541" t="n">
-        <v>36.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="1542">
@@ -37426,10 +37426,10 @@
       </c>
       <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F1542" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="1543">
@@ -37453,7 +37453,7 @@
         <v>3</v>
       </c>
       <c r="F1543" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="1544">
@@ -37477,7 +37477,7 @@
         <v>2.9</v>
       </c>
       <c r="F1544" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1545">
@@ -37501,7 +37501,7 @@
         <v>2.5</v>
       </c>
       <c r="F1545" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="1546">
@@ -37525,7 +37525,7 @@
         <v>2.4</v>
       </c>
       <c r="F1546" t="n">
-        <v>40.3</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="1547">
@@ -37549,7 +37549,7 @@
         <v>2.1</v>
       </c>
       <c r="F1547" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="1548">
@@ -37570,10 +37570,10 @@
       </c>
       <c r="D1548" t="inlineStr"/>
       <c r="E1548" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F1548" t="n">
-        <v>46.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1549">
@@ -37597,7 +37597,7 @@
         <v>1.9</v>
       </c>
       <c r="F1549" t="n">
-        <v>47.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="1550">
@@ -37618,10 +37618,10 @@
       </c>
       <c r="D1550" t="inlineStr"/>
       <c r="E1550" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F1550" t="n">
-        <v>44.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1551">
@@ -37645,7 +37645,7 @@
         <v>1.8</v>
       </c>
       <c r="F1551" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="1552">
@@ -37669,7 +37669,7 @@
         <v>1.7</v>
       </c>
       <c r="F1552" t="n">
-        <v>40</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="1553">
@@ -37685,15 +37685,15 @@
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>시에라</t>
+          <t>오리사</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr"/>
       <c r="E1553" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F1553" t="n">
-        <v>42.4</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="1554">
@@ -37709,7 +37709,7 @@
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>자리야</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr"/>
@@ -37717,7 +37717,7 @@
         <v>1.6</v>
       </c>
       <c r="F1554" t="n">
-        <v>49.6</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="1555">
@@ -37733,7 +37733,7 @@
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>자리야</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr"/>
@@ -37741,7 +37741,7 @@
         <v>1.6</v>
       </c>
       <c r="F1555" t="n">
-        <v>56.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="1556">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>오리사</t>
+          <t>시에라</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr"/>
@@ -37765,7 +37765,7 @@
         <v>1.6</v>
       </c>
       <c r="F1556" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="1557">
@@ -37786,10 +37786,10 @@
       </c>
       <c r="D1557" t="inlineStr"/>
       <c r="E1557" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F1557" t="n">
-        <v>39.9</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="1558">
@@ -37813,7 +37813,7 @@
         <v>1.4</v>
       </c>
       <c r="F1558" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1559">
@@ -37829,7 +37829,7 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>프레야</t>
+          <t>파라</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr"/>
@@ -37837,7 +37837,7 @@
         <v>1.3</v>
       </c>
       <c r="F1559" t="n">
-        <v>39.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1560">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>파라</t>
+          <t>프레야</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr"/>
@@ -37861,7 +37861,7 @@
         <v>1.3</v>
       </c>
       <c r="F1560" t="n">
-        <v>51</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="1561">
@@ -37885,7 +37885,7 @@
         <v>1.2</v>
       </c>
       <c r="F1561" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="1562">
@@ -37909,7 +37909,7 @@
         <v>1.2</v>
       </c>
       <c r="F1562" t="n">
-        <v>45</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="1563">
@@ -37933,7 +37933,7 @@
         <v>1.1</v>
       </c>
       <c r="F1563" t="n">
-        <v>43.8</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="1564">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>레킹볼</t>
+          <t>로드호그</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr"/>
@@ -37957,7 +37957,7 @@
         <v>1</v>
       </c>
       <c r="F1564" t="n">
-        <v>37.3</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="1565">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>로드호그</t>
+          <t>레킹볼</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr"/>
@@ -37981,7 +37981,7 @@
         <v>1</v>
       </c>
       <c r="F1565" t="n">
-        <v>43.1</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="1566">
@@ -38005,7 +38005,7 @@
         <v>0.9</v>
       </c>
       <c r="F1566" t="n">
-        <v>42.7</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="1567">
@@ -38029,7 +38029,7 @@
         <v>0.9</v>
       </c>
       <c r="F1567" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="1568">
@@ -38053,7 +38053,7 @@
         <v>0.9</v>
       </c>
       <c r="F1568" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="1569">
@@ -38077,7 +38077,7 @@
         <v>0.8</v>
       </c>
       <c r="F1569" t="n">
-        <v>51.9</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="1570">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>제트팩 캣</t>
+          <t>도미나</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
         <v>0.8</v>
       </c>
       <c r="F1570" t="n">
-        <v>56</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="1571">
@@ -38117,7 +38117,7 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>도미나</t>
+          <t>제트팩 캣</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr"/>
@@ -38125,7 +38125,7 @@
         <v>0.8</v>
       </c>
       <c r="F1571" t="n">
-        <v>52.3</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="1572">
@@ -38149,7 +38149,7 @@
         <v>0.7</v>
       </c>
       <c r="F1572" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="1573">
@@ -38170,10 +38170,10 @@
       </c>
       <c r="D1573" t="inlineStr"/>
       <c r="E1573" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F1573" t="n">
-        <v>36.5</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="1574">
@@ -38197,7 +38197,7 @@
         <v>0.5</v>
       </c>
       <c r="F1574" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="1575">
@@ -38221,7 +38221,7 @@
         <v>0.5</v>
       </c>
       <c r="F1575" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="1576">
@@ -38237,7 +38237,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>정커퀸</t>
+          <t>모이라</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr"/>
@@ -38245,7 +38245,7 @@
         <v>0.5</v>
       </c>
       <c r="F1576" t="n">
-        <v>52.7</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="1577">
@@ -38261,7 +38261,7 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>모이라</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr"/>
@@ -38269,7 +38269,7 @@
         <v>0.5</v>
       </c>
       <c r="F1577" t="n">
-        <v>49.3</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="1578">
@@ -38285,7 +38285,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>토르비욘</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr"/>
@@ -38293,7 +38293,7 @@
         <v>0.5</v>
       </c>
       <c r="F1578" t="n">
-        <v>53.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="1579">
@@ -38314,10 +38314,10 @@
       </c>
       <c r="D1579" t="inlineStr"/>
       <c r="E1579" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1579" t="n">
-        <v>53.9</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="1580">
@@ -38333,15 +38333,15 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>토르비욘</t>
+          <t>정커퀸</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr"/>
       <c r="E1580" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F1580" t="n">
-        <v>44.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="1581">
@@ -38362,7 +38362,7 @@
       </c>
       <c r="D1581" t="inlineStr"/>
       <c r="E1581" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F1581" t="n">
         <v>39.9</v>
@@ -38389,7 +38389,7 @@
         <v>0.2</v>
       </c>
       <c r="F1582" t="n">
-        <v>55.3</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="1583">
@@ -38410,7 +38410,7 @@
       </c>
       <c r="D1583" t="inlineStr"/>
       <c r="E1583" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="F1583" t="n">
         <v>47.8</v>
@@ -38458,7 +38458,7 @@
       </c>
       <c r="D1585" t="inlineStr"/>
       <c r="E1585" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="F1585" t="n">
         <v>20.3</v>
@@ -38482,7 +38482,7 @@
       </c>
       <c r="D1586" t="inlineStr"/>
       <c r="E1586" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="F1586" t="n">
         <v>67.90000000000001</v>
@@ -38602,7 +38602,7 @@
       </c>
       <c r="D1591" t="inlineStr"/>
       <c r="E1591" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F1591" t="n">
         <v>85.7</v>
@@ -38626,7 +38626,7 @@
       </c>
       <c r="D1592" t="inlineStr"/>
       <c r="E1592" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F1592" t="n">
         <v>8.699999999999999</v>
@@ -38650,7 +38650,7 @@
       </c>
       <c r="D1593" t="inlineStr"/>
       <c r="E1593" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1593" t="n">
         <v>64.3</v>
@@ -38674,7 +38674,7 @@
       </c>
       <c r="D1594" t="inlineStr"/>
       <c r="E1594" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F1594" t="n">
         <v>83.09999999999999</v>
@@ -38957,7 +38957,7 @@
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>리퍼</t>
+          <t>라인하르트</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr"/>
@@ -38965,7 +38965,7 @@
         <v>1</v>
       </c>
       <c r="F1606" t="n">
-        <v>80</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="1607">
@@ -38981,15 +38981,15 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>애쉬</t>
+          <t>리퍼</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr"/>
       <c r="E1607" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F1607" t="n">
-        <v>99.7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1608">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>솜브라</t>
+          <t>애쉬</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
         <v>0.6</v>
       </c>
       <c r="F1608" t="n">
-        <v>0</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="1609">
@@ -39029,7 +39029,7 @@
       </c>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>캐서디</t>
+          <t>솜브라</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr"/>
@@ -39037,7 +39037,7 @@
         <v>0.6</v>
       </c>
       <c r="F1609" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1610">
@@ -39053,7 +39053,7 @@
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>위도우메이커</t>
+          <t>캐서디</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr"/>
@@ -39061,7 +39061,7 @@
         <v>0.6</v>
       </c>
       <c r="F1610" t="n">
-        <v>79.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1611">
@@ -39077,7 +39077,7 @@
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>라인하르트</t>
+          <t>위도우메이커</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr"/>
@@ -39085,7 +39085,7 @@
         <v>0.6</v>
       </c>
       <c r="F1611" t="n">
-        <v>78.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="1612">
